--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="129">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -447,6 +447,9 @@
   </si>
   <si>
     <t>5x1</t>
+  </si>
+  <si>
+    <t>0x0</t>
   </si>
 </sst>
 </file>
@@ -1469,6 +1472,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1479,51 +1527,6 @@
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2584,7 +2587,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="102"/>
+      <c r="F1" s="98"/>
       <c r="G1" s="86" t="s">
         <v>3</v>
       </c>
@@ -2673,7 +2676,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="103"/>
+      <c r="F2" s="99"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2763,7 +2766,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="104"/>
+      <c r="F3" s="100"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2855,7 +2858,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="103"/>
+      <c r="F4" s="99"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2946,7 +2949,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="104"/>
+      <c r="F5" s="100"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3022,7 +3025,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="109">
+      <c r="A6" s="105">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3039,7 +3042,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="103"/>
+      <c r="F6" s="99"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3115,7 +3118,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="110"/>
+      <c r="A7" s="106"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3130,7 +3133,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="105"/>
+      <c r="F7" s="101"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3206,7 +3209,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="111"/>
+      <c r="A8" s="107"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3221,7 +3224,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="106"/>
+      <c r="F8" s="102"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3297,7 +3300,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="112"/>
+      <c r="A9" s="108"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3312,7 +3315,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="107"/>
+      <c r="F9" s="103"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3388,7 +3391,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="94">
+      <c r="A10" s="109">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3405,7 +3408,7 @@
       <c r="E10" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="F10" s="103"/>
+      <c r="F10" s="99"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3479,7 +3482,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="95"/>
+      <c r="A11" s="110"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3494,7 +3497,7 @@
       <c r="E11" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="F11" s="105"/>
+      <c r="F11" s="101"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3570,7 +3573,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A12" s="96"/>
+      <c r="A12" s="111"/>
       <c r="B12" s="29" t="s">
         <v>61</v>
       </c>
@@ -3585,7 +3588,7 @@
       <c r="E12" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="F12" s="106"/>
+      <c r="F12" s="102"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3661,7 +3664,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="97"/>
+      <c r="A13" s="112"/>
       <c r="B13" s="30" t="s">
         <v>62</v>
       </c>
@@ -3676,7 +3679,7 @@
       <c r="E13" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="F13" s="107"/>
+      <c r="F13" s="103"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3752,7 +3755,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="109">
+      <c r="A14" s="105">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3769,7 +3772,7 @@
       <c r="E14" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="103"/>
+      <c r="F14" s="99"/>
       <c r="G14" s="60"/>
       <c r="H14" s="61"/>
       <c r="I14" s="61"/>
@@ -3805,7 +3808,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="110"/>
+      <c r="A15" s="106"/>
       <c r="B15" s="25" t="s">
         <v>64</v>
       </c>
@@ -3820,7 +3823,7 @@
       <c r="E15" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="105"/>
+      <c r="F15" s="101"/>
       <c r="G15" s="63"/>
       <c r="H15" s="71"/>
       <c r="I15" s="71"/>
@@ -3856,7 +3859,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A16" s="111"/>
+      <c r="A16" s="107"/>
       <c r="B16" s="26" t="s">
         <v>65</v>
       </c>
@@ -3869,45 +3872,85 @@
         <v>Cabo Verde</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="106"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="66"/>
-      <c r="K16" s="66"/>
-      <c r="L16" s="66"/>
-      <c r="M16" s="66"/>
-      <c r="N16" s="66"/>
-      <c r="O16" s="66"/>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="66"/>
-      <c r="U16" s="67"/>
-      <c r="V16" s="67"/>
-      <c r="W16" s="67"/>
-      <c r="X16" s="67"/>
-      <c r="Y16" s="67"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="84" t="str">
+        <v>128</v>
+      </c>
+      <c r="F16" s="102"/>
+      <c r="G16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="K16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="M16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="R16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="S16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="T16" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="U16" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="V16" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W16" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="X16" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y16" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" s="81" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA16" s="84">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB16" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="93">
         <f t="shared" si="3"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC16" s="88" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A17" s="112"/>
+      <c r="A17" s="108"/>
       <c r="B17" s="27" t="s">
         <v>66</v>
       </c>
@@ -3922,7 +3965,7 @@
       <c r="E17" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="107"/>
+      <c r="F17" s="103"/>
       <c r="G17" s="68"/>
       <c r="H17" s="69"/>
       <c r="I17" s="69"/>
@@ -3958,7 +4001,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A18" s="94">
+      <c r="A18" s="109">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -3975,7 +4018,7 @@
       <c r="E18" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="103"/>
+      <c r="F18" s="99"/>
       <c r="G18" s="72"/>
       <c r="H18" s="55"/>
       <c r="I18" s="55"/>
@@ -4011,7 +4054,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A19" s="95"/>
+      <c r="A19" s="110"/>
       <c r="B19" s="28" t="s">
         <v>68</v>
       </c>
@@ -4026,7 +4069,7 @@
       <c r="E19" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="105"/>
+      <c r="F19" s="101"/>
       <c r="G19" s="63"/>
       <c r="H19" s="71"/>
       <c r="I19" s="71"/>
@@ -4062,7 +4105,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A20" s="96"/>
+      <c r="A20" s="111"/>
       <c r="B20" s="29" t="s">
         <v>69</v>
       </c>
@@ -4077,7 +4120,7 @@
       <c r="E20" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="106"/>
+      <c r="F20" s="102"/>
       <c r="G20" s="65"/>
       <c r="H20" s="66"/>
       <c r="I20" s="66"/>
@@ -4113,7 +4156,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A21" s="97"/>
+      <c r="A21" s="112"/>
       <c r="B21" s="30" t="s">
         <v>70</v>
       </c>
@@ -4128,7 +4171,7 @@
       <c r="E21" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="107"/>
+      <c r="F21" s="103"/>
       <c r="G21" s="74"/>
       <c r="H21" s="75"/>
       <c r="I21" s="75"/>
@@ -4164,7 +4207,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A22" s="109">
+      <c r="A22" s="105">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4181,7 +4224,7 @@
       <c r="E22" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F22" s="103"/>
+      <c r="F22" s="99"/>
       <c r="G22" s="63"/>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -4217,7 +4260,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A23" s="110"/>
+      <c r="A23" s="106"/>
       <c r="B23" s="25" t="s">
         <v>72</v>
       </c>
@@ -4232,7 +4275,7 @@
       <c r="E23" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="105"/>
+      <c r="F23" s="101"/>
       <c r="G23" s="63"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -4268,7 +4311,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A24" s="111"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="26" t="s">
         <v>73</v>
       </c>
@@ -4283,7 +4326,7 @@
       <c r="E24" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="106"/>
+      <c r="F24" s="102"/>
       <c r="G24" s="65"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
@@ -4319,7 +4362,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A25" s="112"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="27" t="s">
         <v>74</v>
       </c>
@@ -4334,7 +4377,7 @@
       <c r="E25" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="107"/>
+      <c r="F25" s="103"/>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -4370,7 +4413,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A26" s="94">
+      <c r="A26" s="109">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4387,7 +4430,7 @@
       <c r="E26" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F26" s="103"/>
+      <c r="F26" s="99"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4423,7 +4466,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A27" s="95"/>
+      <c r="A27" s="110"/>
       <c r="B27" s="28" t="s">
         <v>76</v>
       </c>
@@ -4438,7 +4481,7 @@
       <c r="E27" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="105"/>
+      <c r="F27" s="101"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4474,7 +4517,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A28" s="96"/>
+      <c r="A28" s="111"/>
       <c r="B28" s="29" t="s">
         <v>77</v>
       </c>
@@ -4489,7 +4532,7 @@
       <c r="E28" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="106"/>
+      <c r="F28" s="102"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4525,7 +4568,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A29" s="97"/>
+      <c r="A29" s="112"/>
       <c r="B29" s="30" t="s">
         <v>78</v>
       </c>
@@ -4540,7 +4583,7 @@
       <c r="E29" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="F29" s="107"/>
+      <c r="F29" s="103"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4576,7 +4619,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A30" s="109">
+      <c r="A30" s="105">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -4593,7 +4636,7 @@
       <c r="E30" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="103"/>
+      <c r="F30" s="99"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4629,7 +4672,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A31" s="110"/>
+      <c r="A31" s="106"/>
       <c r="B31" s="25" t="s">
         <v>80</v>
       </c>
@@ -4644,7 +4687,7 @@
       <c r="E31" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="F31" s="105"/>
+      <c r="F31" s="101"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4680,7 +4723,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A32" s="111"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="26" t="s">
         <v>81</v>
       </c>
@@ -4695,7 +4738,7 @@
       <c r="E32" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F32" s="106"/>
+      <c r="F32" s="102"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -4731,7 +4774,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A33" s="112"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="27" t="s">
         <v>82</v>
       </c>
@@ -4746,7 +4789,7 @@
       <c r="E33" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="107"/>
+      <c r="F33" s="103"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -4782,7 +4825,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A34" s="94">
+      <c r="A34" s="109">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -4799,7 +4842,7 @@
       <c r="E34" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="103"/>
+      <c r="F34" s="99"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -4835,7 +4878,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A35" s="95"/>
+      <c r="A35" s="110"/>
       <c r="B35" s="28" t="s">
         <v>84</v>
       </c>
@@ -4850,7 +4893,7 @@
       <c r="E35" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F35" s="105"/>
+      <c r="F35" s="101"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -4886,7 +4929,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A36" s="96"/>
+      <c r="A36" s="111"/>
       <c r="B36" s="29" t="s">
         <v>85</v>
       </c>
@@ -4901,7 +4944,7 @@
       <c r="E36" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="106"/>
+      <c r="F36" s="102"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -4937,7 +4980,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A37" s="97"/>
+      <c r="A37" s="112"/>
       <c r="B37" s="30" t="s">
         <v>86</v>
       </c>
@@ -4952,7 +4995,7 @@
       <c r="E37" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="F37" s="107"/>
+      <c r="F37" s="103"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -4988,7 +5031,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A38" s="109">
+      <c r="A38" s="105">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5005,7 +5048,7 @@
       <c r="E38" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F38" s="103"/>
+      <c r="F38" s="99"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5041,7 +5084,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A39" s="110"/>
+      <c r="A39" s="106"/>
       <c r="B39" s="25" t="s">
         <v>88</v>
       </c>
@@ -5056,7 +5099,7 @@
       <c r="E39" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="105"/>
+      <c r="F39" s="101"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5092,7 +5135,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A40" s="111"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="26" t="s">
         <v>89</v>
       </c>
@@ -5107,7 +5150,7 @@
       <c r="E40" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F40" s="106"/>
+      <c r="F40" s="102"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5143,7 +5186,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A41" s="112"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="27" t="s">
         <v>90</v>
       </c>
@@ -5158,7 +5201,7 @@
       <c r="E41" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="F41" s="107"/>
+      <c r="F41" s="103"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5194,7 +5237,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A42" s="94">
+      <c r="A42" s="109">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5211,7 +5254,7 @@
       <c r="E42" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="103"/>
+      <c r="F42" s="99"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5247,7 +5290,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A43" s="95"/>
+      <c r="A43" s="110"/>
       <c r="B43" s="28" t="s">
         <v>92</v>
       </c>
@@ -5262,7 +5305,7 @@
       <c r="E43" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F43" s="105"/>
+      <c r="F43" s="101"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5298,7 +5341,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A44" s="96"/>
+      <c r="A44" s="111"/>
       <c r="B44" s="29" t="s">
         <v>93</v>
       </c>
@@ -5313,7 +5356,7 @@
       <c r="E44" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F44" s="106"/>
+      <c r="F44" s="102"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5349,7 +5392,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A45" s="97"/>
+      <c r="A45" s="112"/>
       <c r="B45" s="30" t="s">
         <v>94</v>
       </c>
@@ -5364,7 +5407,7 @@
       <c r="E45" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="107"/>
+      <c r="F45" s="103"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5400,7 +5443,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A46" s="109">
+      <c r="A46" s="105">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5417,7 +5460,7 @@
       <c r="E46" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F46" s="103"/>
+      <c r="F46" s="99"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5453,7 +5496,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A47" s="110"/>
+      <c r="A47" s="106"/>
       <c r="B47" s="25" t="s">
         <v>96</v>
       </c>
@@ -5468,7 +5511,7 @@
       <c r="E47" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="105"/>
+      <c r="F47" s="101"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5504,7 +5547,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A48" s="111"/>
+      <c r="A48" s="107"/>
       <c r="B48" s="26" t="s">
         <v>97</v>
       </c>
@@ -5519,7 +5562,7 @@
       <c r="E48" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="106"/>
+      <c r="F48" s="102"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5555,7 +5598,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A49" s="112"/>
+      <c r="A49" s="108"/>
       <c r="B49" s="27" t="s">
         <v>98</v>
       </c>
@@ -5570,7 +5613,7 @@
       <c r="E49" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="F49" s="107"/>
+      <c r="F49" s="103"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5606,7 +5649,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A50" s="94">
+      <c r="A50" s="109">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -5623,7 +5666,7 @@
       <c r="E50" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F50" s="103"/>
+      <c r="F50" s="99"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5659,7 +5702,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A51" s="95"/>
+      <c r="A51" s="110"/>
       <c r="B51" s="28" t="s">
         <v>100</v>
       </c>
@@ -5674,7 +5717,7 @@
       <c r="E51" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F51" s="105"/>
+      <c r="F51" s="101"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -5710,7 +5753,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A52" s="96"/>
+      <c r="A52" s="111"/>
       <c r="B52" s="29" t="s">
         <v>101</v>
       </c>
@@ -5725,7 +5768,7 @@
       <c r="E52" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F52" s="106"/>
+      <c r="F52" s="102"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -5761,7 +5804,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A53" s="96"/>
+      <c r="A53" s="111"/>
       <c r="B53" s="29" t="s">
         <v>102</v>
       </c>
@@ -5776,7 +5819,7 @@
       <c r="E53" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F53" s="106"/>
+      <c r="F53" s="102"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -5812,7 +5855,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A54" s="96"/>
+      <c r="A54" s="111"/>
       <c r="B54" s="29" t="s">
         <v>103</v>
       </c>
@@ -5827,7 +5870,7 @@
       <c r="E54" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F54" s="106"/>
+      <c r="F54" s="102"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -5863,7 +5906,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A55" s="97"/>
+      <c r="A55" s="112"/>
       <c r="B55" s="30" t="s">
         <v>104</v>
       </c>
@@ -5878,7 +5921,7 @@
       <c r="E55" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="F55" s="107"/>
+      <c r="F55" s="103"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -5914,7 +5957,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A56" s="109">
+      <c r="A56" s="105">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -5931,7 +5974,7 @@
       <c r="E56" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F56" s="103"/>
+      <c r="F56" s="99"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -5967,7 +6010,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A57" s="110"/>
+      <c r="A57" s="106"/>
       <c r="B57" s="25" t="s">
         <v>106</v>
       </c>
@@ -5982,7 +6025,7 @@
       <c r="E57" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="105"/>
+      <c r="F57" s="101"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6018,7 +6061,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A58" s="111"/>
+      <c r="A58" s="107"/>
       <c r="B58" s="26" t="s">
         <v>107</v>
       </c>
@@ -6033,7 +6076,7 @@
       <c r="E58" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F58" s="106"/>
+      <c r="F58" s="102"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6069,7 +6112,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A59" s="111"/>
+      <c r="A59" s="107"/>
       <c r="B59" s="26" t="s">
         <v>108</v>
       </c>
@@ -6084,7 +6127,7 @@
       <c r="E59" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F59" s="106"/>
+      <c r="F59" s="102"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6120,7 +6163,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A60" s="111"/>
+      <c r="A60" s="107"/>
       <c r="B60" s="26" t="s">
         <v>109</v>
       </c>
@@ -6135,7 +6178,7 @@
       <c r="E60" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F60" s="106"/>
+      <c r="F60" s="102"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6171,7 +6214,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A61" s="112"/>
+      <c r="A61" s="108"/>
       <c r="B61" s="27" t="s">
         <v>110</v>
       </c>
@@ -6186,7 +6229,7 @@
       <c r="E61" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="F61" s="107"/>
+      <c r="F61" s="103"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6222,7 +6265,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A62" s="94">
+      <c r="A62" s="109">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6239,7 +6282,7 @@
       <c r="E62" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F62" s="103"/>
+      <c r="F62" s="99"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6275,7 +6318,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A63" s="95"/>
+      <c r="A63" s="110"/>
       <c r="B63" s="28" t="s">
         <v>112</v>
       </c>
@@ -6290,7 +6333,7 @@
       <c r="E63" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="105"/>
+      <c r="F63" s="101"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6326,7 +6369,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A64" s="96"/>
+      <c r="A64" s="111"/>
       <c r="B64" s="29" t="s">
         <v>113</v>
       </c>
@@ -6341,7 +6384,7 @@
       <c r="E64" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F64" s="106"/>
+      <c r="F64" s="102"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6377,7 +6420,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A65" s="96"/>
+      <c r="A65" s="111"/>
       <c r="B65" s="29" t="s">
         <v>114</v>
       </c>
@@ -6392,7 +6435,7 @@
       <c r="E65" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F65" s="106"/>
+      <c r="F65" s="102"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6428,7 +6471,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A66" s="96"/>
+      <c r="A66" s="111"/>
       <c r="B66" s="29" t="s">
         <v>115</v>
       </c>
@@ -6443,7 +6486,7 @@
       <c r="E66" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F66" s="106"/>
+      <c r="F66" s="102"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6479,7 +6522,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A67" s="97"/>
+      <c r="A67" s="112"/>
       <c r="B67" s="30" t="s">
         <v>116</v>
       </c>
@@ -6494,7 +6537,7 @@
       <c r="E67" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="F67" s="107"/>
+      <c r="F67" s="103"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6530,7 +6573,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A68" s="98">
+      <c r="A68" s="94">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -6547,7 +6590,7 @@
       <c r="E68" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F68" s="103"/>
+      <c r="F68" s="99"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6583,7 +6626,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A69" s="99"/>
+      <c r="A69" s="95"/>
       <c r="B69" s="25" t="s">
         <v>118</v>
       </c>
@@ -6598,7 +6641,7 @@
       <c r="E69" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="F69" s="105"/>
+      <c r="F69" s="101"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6634,7 +6677,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A70" s="100"/>
+      <c r="A70" s="96"/>
       <c r="B70" s="26" t="s">
         <v>119</v>
       </c>
@@ -6649,7 +6692,7 @@
       <c r="E70" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F70" s="106"/>
+      <c r="F70" s="102"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -6685,7 +6728,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A71" s="100"/>
+      <c r="A71" s="96"/>
       <c r="B71" s="26" t="s">
         <v>120</v>
       </c>
@@ -6700,7 +6743,7 @@
       <c r="E71" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F71" s="106"/>
+      <c r="F71" s="102"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -6736,7 +6779,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A72" s="100"/>
+      <c r="A72" s="96"/>
       <c r="B72" s="26" t="s">
         <v>121</v>
       </c>
@@ -6751,7 +6794,7 @@
       <c r="E72" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F72" s="106"/>
+      <c r="F72" s="102"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -6787,7 +6830,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A73" s="101"/>
+      <c r="A73" s="97"/>
       <c r="B73" s="31" t="s">
         <v>122</v>
       </c>
@@ -6802,7 +6845,7 @@
       <c r="E73" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="F73" s="108"/>
+      <c r="F73" s="104"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -6924,7 +6967,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
@@ -6942,6 +6984,7 @@
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10605"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/CA21BB4BE959536C/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B0C2E18-616C-C444-935C-494F4F498835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C964C5ED-7439-44F2-ABAD-3002D98892DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="129">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -242,27 +242,42 @@
     <t>Alemanha x Curaçao</t>
   </si>
   <si>
+    <t>7x1</t>
+  </si>
+  <si>
+    <t>Costa do Marfim x Equador</t>
+  </si>
+  <si>
+    <t>1x0</t>
+  </si>
+  <si>
+    <t>Países Baixos x Japão</t>
+  </si>
+  <si>
+    <t>2x2</t>
+  </si>
+  <si>
+    <t>Suécia x Tunísia</t>
+  </si>
+  <si>
+    <t>5x1</t>
+  </si>
+  <si>
+    <t>Bélgica x Egito</t>
+  </si>
+  <si>
     <t>#x#</t>
   </si>
   <si>
-    <t>Costa do Marfim x Equador</t>
-  </si>
-  <si>
-    <t>Países Baixos x Japão</t>
-  </si>
-  <si>
-    <t>Suécia x Tunísia</t>
-  </si>
-  <si>
-    <t>Bélgica x Egito</t>
-  </si>
-  <si>
     <t>Irã x Nova Zelândia</t>
   </si>
   <si>
     <t>Espanha x Cabo Verde</t>
   </si>
   <si>
+    <t>0x0</t>
+  </si>
+  <si>
     <t>Arábia Saudita x Uruguai</t>
   </si>
   <si>
@@ -435,28 +450,13 @@
   </si>
   <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>7x1</t>
-  </si>
-  <si>
-    <t>2x2</t>
-  </si>
-  <si>
-    <t>1x0</t>
-  </si>
-  <si>
-    <t>5x1</t>
-  </si>
-  <si>
-    <t>0x0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1472,6 +1472,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1504,30 +1528,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1590,19 +1590,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF009C3B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
@@ -1624,6 +1611,19 @@
       </fill>
       <alignment horizontal="center"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF009C3B"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1644,11 +1644,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A4:B20" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1999,13 +1999,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.75" customWidth="1"/>
-    <col min="2" max="3" width="14.2578125" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="3" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="21">
       <c r="A1" s="117" t="s">
         <v>0</v>
       </c>
@@ -2017,7 +2017,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="117"/>
       <c r="B2" s="117"/>
       <c r="C2" s="13"/>
@@ -2027,7 +2027,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="117"/>
       <c r="B3" s="117"/>
       <c r="C3" s="13"/>
@@ -2037,7 +2037,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="26.1" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2178,7 +2178,7 @@
     <mergeCell ref="A1:B3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B20">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Ok">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Ok">
       <formula>NOT(ISERROR(SEARCH("Ok",B5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2197,16 +2197,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.6484375" customWidth="1"/>
-    <col min="2" max="2" width="20.984375" customWidth="1"/>
-    <col min="3" max="7" width="12.10546875" customWidth="1"/>
-    <col min="9" max="9" width="22.8671875" customWidth="1"/>
-    <col min="10" max="10" width="9.55078125" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="7" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="118" t="s">
         <v>20</v>
       </c>
@@ -2217,7 +2217,7 @@
       <c r="F1" s="119"/>
       <c r="G1" s="119"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2265,7 +2265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2308,7 +2308,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2332,7 +2332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2356,7 +2356,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2377,7 +2377,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2398,7 +2398,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2419,7 +2419,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2440,7 +2440,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2461,7 +2461,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2482,7 +2482,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2503,7 +2503,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2524,7 +2524,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2561,17 +2561,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.8359375" customWidth="1"/>
-    <col min="2" max="2" width="32.41796875" customWidth="1"/>
-    <col min="3" max="4" width="20.58203125" customWidth="1"/>
-    <col min="5" max="5" width="12.5078125" customWidth="1"/>
-    <col min="6" max="6" width="6.05078125" customWidth="1"/>
-    <col min="7" max="29" width="16.41015625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="29" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2587,7 +2587,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="98"/>
+      <c r="F1" s="106"/>
       <c r="G1" s="86" t="s">
         <v>3</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30">
       <c r="A2" s="113">
         <v>46184</v>
       </c>
@@ -2676,7 +2676,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="99"/>
+      <c r="F2" s="107"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1">
       <c r="A3" s="114"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2766,7 +2766,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="108"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30">
       <c r="A4" s="115">
         <v>46185</v>
       </c>
@@ -2858,7 +2858,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="99"/>
+      <c r="F4" s="107"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30">
       <c r="A5" s="116"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -2949,7 +2949,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="100"/>
+      <c r="F5" s="108"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3024,8 +3024,8 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="105">
+    <row r="6" spans="1:30">
+      <c r="A6" s="98">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3042,7 +3042,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="99"/>
+      <c r="F6" s="107"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3117,8 +3117,8 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="106"/>
+    <row r="7" spans="1:30">
+      <c r="A7" s="99"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="101"/>
+      <c r="F7" s="109"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3208,8 +3208,8 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="107"/>
+    <row r="8" spans="1:30">
+      <c r="A8" s="100"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3224,7 +3224,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="102"/>
+      <c r="F8" s="110"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3299,8 +3299,8 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="108"/>
+    <row r="9" spans="1:30">
+      <c r="A9" s="101"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3315,7 +3315,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="103"/>
+      <c r="F9" s="111"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3390,8 +3390,8 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="109">
+    <row r="10" spans="1:30">
+      <c r="A10" s="94">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3406,9 +3406,9 @@
         <v>Curaçao</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="99"/>
+        <v>59</v>
+      </c>
+      <c r="F10" s="107"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3481,8 +3481,8 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="110"/>
+    <row r="11" spans="1:30">
+      <c r="A11" s="95"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3495,9 +3495,9 @@
         <v>Equador</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="F11" s="101"/>
+        <v>61</v>
+      </c>
+      <c r="F11" s="109"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3572,10 +3572,10 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A12" s="111"/>
+    <row r="12" spans="1:30">
+      <c r="A12" s="96"/>
       <c r="B12" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="41" t="str">
         <f t="shared" si="0"/>
@@ -3586,9 +3586,9 @@
         <v>Japão</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="102"/>
+        <v>63</v>
+      </c>
+      <c r="F12" s="110"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3663,10 +3663,10 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="112"/>
+    <row r="13" spans="1:30">
+      <c r="A13" s="97"/>
       <c r="B13" s="30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C13" s="42" t="str">
         <f t="shared" si="0"/>
@@ -3677,9 +3677,9 @@
         <v>Tunísia</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F13" s="103"/>
+        <v>65</v>
+      </c>
+      <c r="F13" s="111"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="105">
+    <row r="14" spans="1:30">
+      <c r="A14" s="98">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C14" s="36" t="str">
         <f t="shared" si="0"/>
@@ -3770,29 +3770,69 @@
         <v>Egito</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="99"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="61"/>
-      <c r="N14" s="61"/>
-      <c r="O14" s="61"/>
-      <c r="P14" s="61"/>
-      <c r="Q14" s="61"/>
-      <c r="R14" s="61"/>
-      <c r="S14" s="61"/>
-      <c r="T14" s="61"/>
-      <c r="U14" s="62"/>
-      <c r="V14" s="62"/>
-      <c r="W14" s="62"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
-      <c r="Z14" s="79"/>
+        <v>67</v>
+      </c>
+      <c r="F14" s="107"/>
+      <c r="G14" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="O14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="R14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="S14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="T14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="U14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="V14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="W14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="X14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" s="61" t="s">
+        <v>44</v>
+      </c>
       <c r="AA14" s="84" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3807,10 +3847,10 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="106"/>
+    <row r="15" spans="1:30">
+      <c r="A15" s="99"/>
       <c r="B15" s="25" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C15" s="37" t="str">
         <f t="shared" si="0"/>
@@ -3821,29 +3861,69 @@
         <v>Nova Zelândia</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="101"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-      <c r="T15" s="71"/>
-      <c r="U15" s="56"/>
-      <c r="V15" s="56"/>
-      <c r="W15" s="56"/>
-      <c r="X15" s="56"/>
-      <c r="Y15" s="56"/>
-      <c r="Z15" s="83"/>
+        <v>67</v>
+      </c>
+      <c r="F15" s="109"/>
+      <c r="G15" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="L15" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="R15" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="S15" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="T15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="U15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="V15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="W15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="X15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y15" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z15" s="83" t="s">
+        <v>44</v>
+      </c>
       <c r="AA15" s="84" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3858,10 +3938,10 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A16" s="107"/>
+    <row r="16" spans="1:30">
+      <c r="A16" s="100"/>
       <c r="B16" s="26" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C16" s="38" t="str">
         <f t="shared" si="0"/>
@@ -3872,67 +3952,67 @@
         <v>Cabo Verde</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="102"/>
+        <v>70</v>
+      </c>
+      <c r="F16" s="110"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="K16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="L16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="M16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="N16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="O16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="P16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="R16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="S16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="T16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="U16" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="V16" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="W16" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="X16" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y16" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z16" s="81" t="s">
+      <c r="H16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="K16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="O16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="R16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="S16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="T16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="U16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="V16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="W16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="X16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" s="65" t="s">
         <v>44</v>
       </c>
       <c r="AA16" s="84">
@@ -3949,10 +4029,10 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A17" s="108"/>
+    <row r="17" spans="1:30">
+      <c r="A17" s="101"/>
       <c r="B17" s="27" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C17" s="39" t="str">
         <f t="shared" si="0"/>
@@ -3963,29 +4043,69 @@
         <v>Uruguai</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="103"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="69"/>
-      <c r="P17" s="69"/>
-      <c r="Q17" s="69"/>
-      <c r="R17" s="69"/>
-      <c r="S17" s="69"/>
-      <c r="T17" s="69"/>
-      <c r="U17" s="70"/>
-      <c r="V17" s="70"/>
-      <c r="W17" s="70"/>
-      <c r="X17" s="70"/>
-      <c r="Y17" s="70"/>
-      <c r="Z17" s="82"/>
+        <v>67</v>
+      </c>
+      <c r="F17" s="111"/>
+      <c r="G17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="M17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="N17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="O17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="P17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q17" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="R17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="S17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="T17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="U17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="V17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="W17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="X17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z17" s="69" t="s">
+        <v>45</v>
+      </c>
       <c r="AA17" s="84" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4000,25 +4120,25 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A18" s="109">
+    <row r="18" spans="1:30">
+      <c r="A18" s="94">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>França</v>
+      </c>
+      <c r="D18" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v>Senegal</v>
+      </c>
+      <c r="E18" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>França</v>
-      </c>
-      <c r="D18" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Senegal</v>
-      </c>
-      <c r="E18" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="99"/>
+      <c r="F18" s="107"/>
       <c r="G18" s="72"/>
       <c r="H18" s="55"/>
       <c r="I18" s="55"/>
@@ -4053,10 +4173,10 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A19" s="110"/>
+    <row r="19" spans="1:30">
+      <c r="A19" s="95"/>
       <c r="B19" s="28" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C19" s="40" t="str">
         <f t="shared" si="0"/>
@@ -4067,9 +4187,9 @@
         <v>Noruega</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F19" s="109"/>
       <c r="G19" s="63"/>
       <c r="H19" s="71"/>
       <c r="I19" s="71"/>
@@ -4104,10 +4224,10 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A20" s="111"/>
+    <row r="20" spans="1:30">
+      <c r="A20" s="96"/>
       <c r="B20" s="29" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C20" s="41" t="str">
         <f t="shared" si="0"/>
@@ -4118,9 +4238,9 @@
         <v>Argélia</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F20" s="110"/>
       <c r="G20" s="65"/>
       <c r="H20" s="66"/>
       <c r="I20" s="66"/>
@@ -4155,10 +4275,10 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A21" s="112"/>
+    <row r="21" spans="1:30">
+      <c r="A21" s="97"/>
       <c r="B21" s="30" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C21" s="42" t="str">
         <f t="shared" si="0"/>
@@ -4169,9 +4289,9 @@
         <v>Jordânia</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F21" s="111"/>
       <c r="G21" s="74"/>
       <c r="H21" s="75"/>
       <c r="I21" s="75"/>
@@ -4206,12 +4326,12 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A22" s="105">
+    <row r="22" spans="1:30">
+      <c r="A22" s="98">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C22" s="36" t="str">
         <f t="shared" si="0"/>
@@ -4222,9 +4342,9 @@
         <v>Rep. Dem. Congo</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F22" s="107"/>
       <c r="G22" s="63"/>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -4259,10 +4379,10 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A23" s="106"/>
+    <row r="23" spans="1:30">
+      <c r="A23" s="99"/>
       <c r="B23" s="25" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C23" s="37" t="str">
         <f t="shared" si="0"/>
@@ -4273,9 +4393,9 @@
         <v>Colômbia</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F23" s="109"/>
       <c r="G23" s="63"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -4310,10 +4430,10 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A24" s="107"/>
+    <row r="24" spans="1:30">
+      <c r="A24" s="100"/>
       <c r="B24" s="26" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C24" s="38" t="str">
         <f t="shared" si="0"/>
@@ -4324,9 +4444,9 @@
         <v>Croácia</v>
       </c>
       <c r="E24" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F24" s="110"/>
       <c r="G24" s="65"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
@@ -4361,10 +4481,10 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A25" s="108"/>
+    <row r="25" spans="1:30">
+      <c r="A25" s="101"/>
       <c r="B25" s="27" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C25" s="39" t="str">
         <f t="shared" si="0"/>
@@ -4375,9 +4495,9 @@
         <v>Panamá</v>
       </c>
       <c r="E25" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F25" s="111"/>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -4412,12 +4532,12 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A26" s="109">
+    <row r="26" spans="1:30">
+      <c r="A26" s="94">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C26" s="34" t="str">
         <f t="shared" si="0"/>
@@ -4428,9 +4548,9 @@
         <v>África do Sul</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F26" s="107"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4465,10 +4585,10 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A27" s="110"/>
+    <row r="27" spans="1:30">
+      <c r="A27" s="95"/>
       <c r="B27" s="28" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C27" s="40" t="str">
         <f t="shared" si="0"/>
@@ -4479,9 +4599,9 @@
         <v>Coreia do Sul</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F27" s="109"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4516,10 +4636,10 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A28" s="111"/>
+    <row r="28" spans="1:30">
+      <c r="A28" s="96"/>
       <c r="B28" s="29" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C28" s="41" t="str">
         <f t="shared" si="0"/>
@@ -4530,9 +4650,9 @@
         <v>Bósnia e Herzeg.</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F28" s="110"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4567,10 +4687,10 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A29" s="112"/>
+    <row r="29" spans="1:30">
+      <c r="A29" s="97"/>
       <c r="B29" s="30" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C29" s="42" t="str">
         <f t="shared" si="0"/>
@@ -4581,9 +4701,9 @@
         <v>Catar</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F29" s="111"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4618,12 +4738,12 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A30" s="105">
+    <row r="30" spans="1:30">
+      <c r="A30" s="98">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C30" s="36" t="str">
         <f t="shared" si="0"/>
@@ -4634,9 +4754,9 @@
         <v>Marrocos</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F30" s="107"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4671,10 +4791,10 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A31" s="106"/>
+    <row r="31" spans="1:30">
+      <c r="A31" s="99"/>
       <c r="B31" s="25" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C31" s="37" t="str">
         <f t="shared" si="0"/>
@@ -4685,9 +4805,9 @@
         <v>Haiti</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F31" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F31" s="109"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4722,10 +4842,10 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A32" s="107"/>
+    <row r="32" spans="1:30">
+      <c r="A32" s="100"/>
       <c r="B32" s="26" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C32" s="38" t="str">
         <f t="shared" si="0"/>
@@ -4736,9 +4856,9 @@
         <v>Austrália</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F32" s="110"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -4773,10 +4893,10 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A33" s="108"/>
+    <row r="33" spans="1:30">
+      <c r="A33" s="101"/>
       <c r="B33" s="27" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C33" s="39" t="str">
         <f t="shared" si="0"/>
@@ -4787,9 +4907,9 @@
         <v>Paraguai</v>
       </c>
       <c r="E33" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F33" s="111"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -4824,12 +4944,12 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A34" s="109">
+    <row r="34" spans="1:30">
+      <c r="A34" s="94">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C34" s="34" t="str">
         <f t="shared" si="0"/>
@@ -4840,9 +4960,9 @@
         <v>Costa do Marfim</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F34" s="107"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -4877,10 +4997,10 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A35" s="110"/>
+    <row r="35" spans="1:30">
+      <c r="A35" s="95"/>
       <c r="B35" s="28" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C35" s="40" t="str">
         <f t="shared" si="0"/>
@@ -4891,9 +5011,9 @@
         <v>Curaçao</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F35" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F35" s="109"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -4928,10 +5048,10 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A36" s="111"/>
+    <row r="36" spans="1:30">
+      <c r="A36" s="96"/>
       <c r="B36" s="29" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C36" s="41" t="str">
         <f t="shared" si="0"/>
@@ -4942,9 +5062,9 @@
         <v>Suécia</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F36" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F36" s="110"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -4979,10 +5099,10 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A37" s="112"/>
+    <row r="37" spans="1:30">
+      <c r="A37" s="97"/>
       <c r="B37" s="30" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C37" s="42" t="str">
         <f t="shared" si="0"/>
@@ -4993,9 +5113,9 @@
         <v>Japão</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F37" s="111"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5030,12 +5150,12 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A38" s="105">
+    <row r="38" spans="1:30">
+      <c r="A38" s="98">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C38" s="36" t="str">
         <f t="shared" si="0"/>
@@ -5046,9 +5166,9 @@
         <v>Irã</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F38" s="107"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5083,10 +5203,10 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A39" s="106"/>
+    <row r="39" spans="1:30">
+      <c r="A39" s="99"/>
       <c r="B39" s="25" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C39" s="37" t="str">
         <f t="shared" si="0"/>
@@ -5097,9 +5217,9 @@
         <v>Egito</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F39" s="109"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5134,10 +5254,10 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A40" s="107"/>
+    <row r="40" spans="1:30">
+      <c r="A40" s="100"/>
       <c r="B40" s="26" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C40" s="38" t="str">
         <f t="shared" si="0"/>
@@ -5148,9 +5268,9 @@
         <v>Arábia Saudita</v>
       </c>
       <c r="E40" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F40" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F40" s="110"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5185,10 +5305,10 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A41" s="108"/>
+    <row r="41" spans="1:30">
+      <c r="A41" s="101"/>
       <c r="B41" s="27" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C41" s="39" t="str">
         <f t="shared" si="0"/>
@@ -5199,9 +5319,9 @@
         <v>Cabo Verde</v>
       </c>
       <c r="E41" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F41" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F41" s="111"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5236,12 +5356,12 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A42" s="109">
+    <row r="42" spans="1:30">
+      <c r="A42" s="94">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C42" s="34" t="str">
         <f t="shared" si="0"/>
@@ -5252,9 +5372,9 @@
         <v>Iraque</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F42" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F42" s="107"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5289,10 +5409,10 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A43" s="110"/>
+    <row r="43" spans="1:30">
+      <c r="A43" s="95"/>
       <c r="B43" s="28" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C43" s="40" t="str">
         <f t="shared" si="0"/>
@@ -5303,9 +5423,9 @@
         <v>Senegal</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F43" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F43" s="109"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5340,10 +5460,10 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A44" s="111"/>
+    <row r="44" spans="1:30">
+      <c r="A44" s="96"/>
       <c r="B44" s="29" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C44" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5354,9 +5474,9 @@
         <v>Áustria</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F44" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F44" s="110"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5391,10 +5511,10 @@
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A45" s="112"/>
+    <row r="45" spans="1:30">
+      <c r="A45" s="97"/>
       <c r="B45" s="30" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C45" s="42" t="str">
         <f t="shared" si="0"/>
@@ -5405,9 +5525,9 @@
         <v>Argélia</v>
       </c>
       <c r="E45" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F45" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F45" s="111"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5442,12 +5562,12 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A46" s="105">
+    <row r="46" spans="1:30">
+      <c r="A46" s="98">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C46" s="36" t="str">
         <f t="shared" si="0"/>
@@ -5458,9 +5578,9 @@
         <v>Uzbequistão</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F46" s="107"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5495,10 +5615,10 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A47" s="106"/>
+    <row r="47" spans="1:30">
+      <c r="A47" s="99"/>
       <c r="B47" s="25" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C47" s="37" t="str">
         <f t="shared" si="0"/>
@@ -5509,9 +5629,9 @@
         <v>Rep. Dem. Congo</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F47" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F47" s="109"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5546,10 +5666,10 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A48" s="107"/>
+    <row r="48" spans="1:30">
+      <c r="A48" s="100"/>
       <c r="B48" s="26" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C48" s="38" t="str">
         <f t="shared" si="0"/>
@@ -5560,9 +5680,9 @@
         <v>Gana</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F48" s="110"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5597,10 +5717,10 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A49" s="108"/>
+    <row r="49" spans="1:30">
+      <c r="A49" s="101"/>
       <c r="B49" s="27" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C49" s="39" t="str">
         <f t="shared" si="0"/>
@@ -5611,9 +5731,9 @@
         <v>Croácia</v>
       </c>
       <c r="E49" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F49" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F49" s="111"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5648,12 +5768,12 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A50" s="109">
+    <row r="50" spans="1:30">
+      <c r="A50" s="94">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C50" s="34" t="str">
         <f t="shared" si="0"/>
@@ -5664,9 +5784,9 @@
         <v>Coreia do Sul</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F50" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F50" s="107"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5701,10 +5821,10 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A51" s="110"/>
+    <row r="51" spans="1:30">
+      <c r="A51" s="95"/>
       <c r="B51" s="28" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C51" s="40" t="str">
         <f t="shared" si="0"/>
@@ -5715,9 +5835,9 @@
         <v>México</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F51" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F51" s="109"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -5752,10 +5872,10 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A52" s="111"/>
+    <row r="52" spans="1:30">
+      <c r="A52" s="96"/>
       <c r="B52" s="29" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C52" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5766,9 +5886,9 @@
         <v>Canadá</v>
       </c>
       <c r="E52" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F52" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F52" s="110"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -5803,10 +5923,10 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A53" s="111"/>
+    <row r="53" spans="1:30">
+      <c r="A53" s="96"/>
       <c r="B53" s="29" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C53" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5817,9 +5937,9 @@
         <v>Catar</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F53" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F53" s="110"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -5854,10 +5974,10 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A54" s="111"/>
+    <row r="54" spans="1:30">
+      <c r="A54" s="96"/>
       <c r="B54" s="29" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C54" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5868,9 +5988,9 @@
         <v>Haiti</v>
       </c>
       <c r="E54" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F54" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F54" s="110"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -5905,10 +6025,10 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A55" s="112"/>
+    <row r="55" spans="1:30">
+      <c r="A55" s="97"/>
       <c r="B55" s="30" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C55" s="42" t="str">
         <f t="shared" si="0"/>
@@ -5919,9 +6039,9 @@
         <v>Brasil</v>
       </c>
       <c r="E55" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F55" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F55" s="111"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -5956,12 +6076,12 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A56" s="105">
+    <row r="56" spans="1:30">
+      <c r="A56" s="98">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C56" s="36" t="str">
         <f t="shared" si="0"/>
@@ -5972,9 +6092,9 @@
         <v>Estados Unidos</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F56" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F56" s="107"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6009,10 +6129,10 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A57" s="106"/>
+    <row r="57" spans="1:30">
+      <c r="A57" s="99"/>
       <c r="B57" s="25" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C57" s="37" t="str">
         <f t="shared" si="0"/>
@@ -6023,9 +6143,9 @@
         <v>Austrália</v>
       </c>
       <c r="E57" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F57" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F57" s="109"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6060,10 +6180,10 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A58" s="107"/>
+    <row r="58" spans="1:30">
+      <c r="A58" s="100"/>
       <c r="B58" s="26" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C58" s="38" t="str">
         <f t="shared" si="0"/>
@@ -6074,9 +6194,9 @@
         <v>Costa do Marfim</v>
       </c>
       <c r="E58" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F58" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F58" s="110"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6111,10 +6231,10 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A59" s="107"/>
+    <row r="59" spans="1:30">
+      <c r="A59" s="100"/>
       <c r="B59" s="26" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C59" s="38" t="str">
         <f t="shared" si="0"/>
@@ -6125,9 +6245,9 @@
         <v>Alemanha</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F59" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F59" s="110"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6162,10 +6282,10 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A60" s="107"/>
+    <row r="60" spans="1:30">
+      <c r="A60" s="100"/>
       <c r="B60" s="26" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C60" s="38" t="str">
         <f t="shared" si="0"/>
@@ -6176,9 +6296,9 @@
         <v>Países Baixos</v>
       </c>
       <c r="E60" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F60" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F60" s="110"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6213,10 +6333,10 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A61" s="108"/>
+    <row r="61" spans="1:30">
+      <c r="A61" s="101"/>
       <c r="B61" s="27" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C61" s="39" t="str">
         <f t="shared" si="0"/>
@@ -6227,9 +6347,9 @@
         <v>Suécia</v>
       </c>
       <c r="E61" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F61" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F61" s="111"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6264,12 +6384,12 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A62" s="109">
+    <row r="62" spans="1:30">
+      <c r="A62" s="94">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C62" s="34" t="str">
         <f t="shared" si="0"/>
@@ -6280,9 +6400,9 @@
         <v>Bélgica</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F62" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F62" s="107"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6317,10 +6437,10 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A63" s="110"/>
+    <row r="63" spans="1:30">
+      <c r="A63" s="95"/>
       <c r="B63" s="28" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C63" s="40" t="str">
         <f t="shared" si="0"/>
@@ -6331,9 +6451,9 @@
         <v>Irã</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F63" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F63" s="109"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6368,10 +6488,10 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A64" s="111"/>
+    <row r="64" spans="1:30">
+      <c r="A64" s="96"/>
       <c r="B64" s="29" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C64" s="41" t="str">
         <f t="shared" si="0"/>
@@ -6382,9 +6502,9 @@
         <v>Arábia Saudita</v>
       </c>
       <c r="E64" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F64" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F64" s="110"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6419,10 +6539,10 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A65" s="111"/>
+    <row r="65" spans="1:30">
+      <c r="A65" s="96"/>
       <c r="B65" s="29" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C65" s="41" t="str">
         <f t="shared" si="0"/>
@@ -6433,9 +6553,9 @@
         <v>Espanha</v>
       </c>
       <c r="E65" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F65" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F65" s="110"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6470,10 +6590,10 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A66" s="111"/>
+    <row r="66" spans="1:30">
+      <c r="A66" s="96"/>
       <c r="B66" s="29" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C66" s="41" t="str">
         <f t="shared" si="0"/>
@@ -6484,9 +6604,9 @@
         <v>França</v>
       </c>
       <c r="E66" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F66" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F66" s="110"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6521,10 +6641,10 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A67" s="112"/>
+    <row r="67" spans="1:30">
+      <c r="A67" s="97"/>
       <c r="B67" s="30" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C67" s="42" t="str">
         <f t="shared" ref="C67:C73" si="7">TRIM(LEFT(B67,FIND(" x ",B67)-1))</f>
@@ -6535,9 +6655,9 @@
         <v>Iraque</v>
       </c>
       <c r="E67" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F67" s="103"/>
+        <v>67</v>
+      </c>
+      <c r="F67" s="111"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6572,12 +6692,12 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A68" s="94">
+    <row r="68" spans="1:30">
+      <c r="A68" s="102">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C68" s="36" t="str">
         <f t="shared" si="7"/>
@@ -6588,9 +6708,9 @@
         <v>Áustria</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F68" s="99"/>
+        <v>67</v>
+      </c>
+      <c r="F68" s="107"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6625,10 +6745,10 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A69" s="95"/>
+    <row r="69" spans="1:30">
+      <c r="A69" s="103"/>
       <c r="B69" s="25" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C69" s="37" t="str">
         <f t="shared" si="7"/>
@@ -6639,9 +6759,9 @@
         <v>Argentina</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F69" s="101"/>
+        <v>67</v>
+      </c>
+      <c r="F69" s="109"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6676,10 +6796,10 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A70" s="96"/>
+    <row r="70" spans="1:30">
+      <c r="A70" s="104"/>
       <c r="B70" s="26" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C70" s="38" t="str">
         <f t="shared" si="7"/>
@@ -6690,9 +6810,9 @@
         <v>Portugal</v>
       </c>
       <c r="E70" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F70" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F70" s="110"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -6727,10 +6847,10 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A71" s="96"/>
+    <row r="71" spans="1:30">
+      <c r="A71" s="104"/>
       <c r="B71" s="26" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C71" s="38" t="str">
         <f t="shared" si="7"/>
@@ -6741,9 +6861,9 @@
         <v>Uzbequistão</v>
       </c>
       <c r="E71" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F71" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F71" s="110"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -6778,10 +6898,10 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A72" s="96"/>
+    <row r="72" spans="1:30">
+      <c r="A72" s="104"/>
       <c r="B72" s="26" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C72" s="38" t="str">
         <f t="shared" si="7"/>
@@ -6792,9 +6912,9 @@
         <v>Inglaterra</v>
       </c>
       <c r="E72" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F72" s="102"/>
+        <v>67</v>
+      </c>
+      <c r="F72" s="110"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -6829,10 +6949,10 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A73" s="97"/>
+    <row r="73" spans="1:30">
+      <c r="A73" s="105"/>
       <c r="B73" s="31" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C73" s="43" t="str">
         <f t="shared" si="7"/>
@@ -6843,9 +6963,9 @@
         <v>Gana</v>
       </c>
       <c r="E73" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="F73" s="104"/>
+        <v>67</v>
+      </c>
+      <c r="F73" s="112"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -6880,9 +7000,9 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1">
       <c r="F74" s="19" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G74" s="77" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -6967,8 +7087,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -6985,6 +7103,8 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10605"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/CA21BB4BE959536C/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C964C5ED-7439-44F2-ABAD-3002D98892DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72749073-11A9-7A4E-B559-CE4932D8174A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -456,7 +456,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1472,6 +1472,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1483,51 +1528,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1590,6 +1590,19 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF009C3B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
@@ -1611,19 +1624,6 @@
       </fill>
       <alignment horizontal="center"/>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF009C3B"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1644,11 +1644,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A4:B20" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1999,13 +1999,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="3" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.75" customWidth="1"/>
+    <col min="2" max="3" width="14.2578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="117" t="s">
         <v>0</v>
       </c>
@@ -2017,7 +2017,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="117"/>
       <c r="B2" s="117"/>
       <c r="C2" s="13"/>
@@ -2027,7 +2027,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="117"/>
       <c r="B3" s="117"/>
       <c r="C3" s="13"/>
@@ -2037,7 +2037,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:8" ht="26.1" customHeight="1">
+    <row r="4" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2178,7 +2178,7 @@
     <mergeCell ref="A1:B3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B20">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Ok">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Ok">
       <formula>NOT(ISERROR(SEARCH("Ok",B5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2197,16 +2197,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="7" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="22.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.6484375" customWidth="1"/>
+    <col min="2" max="2" width="20.984375" customWidth="1"/>
+    <col min="3" max="7" width="12.10546875" customWidth="1"/>
+    <col min="9" max="9" width="22.8671875" customWidth="1"/>
+    <col min="10" max="10" width="9.55078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="118" t="s">
         <v>20</v>
       </c>
@@ -2217,7 +2217,7 @@
       <c r="F1" s="119"/>
       <c r="G1" s="119"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1">
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2265,7 +2265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2308,7 +2308,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2332,7 +2332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2356,7 +2356,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2377,7 +2377,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2398,7 +2398,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2419,7 +2419,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2440,7 +2440,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2461,7 +2461,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2482,7 +2482,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2503,7 +2503,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2524,7 +2524,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2561,17 +2561,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="29" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.8359375" customWidth="1"/>
+    <col min="2" max="2" width="32.41796875" customWidth="1"/>
+    <col min="3" max="4" width="20.58203125" customWidth="1"/>
+    <col min="5" max="5" width="12.5078125" customWidth="1"/>
+    <col min="6" max="6" width="6.05078125" customWidth="1"/>
+    <col min="7" max="29" width="16.41015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2587,7 +2587,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="106"/>
+      <c r="F1" s="98"/>
       <c r="G1" s="86" t="s">
         <v>3</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="113">
         <v>46184</v>
       </c>
@@ -2676,7 +2676,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="107"/>
+      <c r="F2" s="99"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="114"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2766,7 +2766,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="108"/>
+      <c r="F3" s="100"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="115">
         <v>46185</v>
       </c>
@@ -2858,7 +2858,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="107"/>
+      <c r="F4" s="99"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="116"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -2949,7 +2949,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="108"/>
+      <c r="F5" s="100"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3024,8 +3024,8 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30">
-      <c r="A6" s="98">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A6" s="105">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3042,7 +3042,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="107"/>
+      <c r="F6" s="99"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3117,8 +3117,8 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30">
-      <c r="A7" s="99"/>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A7" s="106"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="109"/>
+      <c r="F7" s="101"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3208,8 +3208,8 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30">
-      <c r="A8" s="100"/>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A8" s="107"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3224,7 +3224,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="110"/>
+      <c r="F8" s="102"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3299,8 +3299,8 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30">
-      <c r="A9" s="101"/>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A9" s="108"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3315,7 +3315,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="111"/>
+      <c r="F9" s="103"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3390,8 +3390,8 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30">
-      <c r="A10" s="94">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A10" s="109">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3408,7 +3408,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="107"/>
+      <c r="F10" s="99"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3481,8 +3481,8 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30">
-      <c r="A11" s="95"/>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A11" s="110"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3497,7 +3497,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="109"/>
+      <c r="F11" s="101"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3572,8 +3572,8 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30">
-      <c r="A12" s="96"/>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A12" s="111"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3588,7 +3588,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="110"/>
+      <c r="F12" s="102"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3663,8 +3663,8 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30">
-      <c r="A13" s="97"/>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A13" s="112"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3679,7 +3679,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="111"/>
+      <c r="F13" s="103"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3754,8 +3754,8 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30">
-      <c r="A14" s="98">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A14" s="105">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3770,9 +3770,9 @@
         <v>Egito</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="107"/>
+        <v>50</v>
+      </c>
+      <c r="F14" s="99"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3833,22 +3833,22 @@
       <c r="Z14" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="AA14" s="84" t="str">
+      <c r="AA14" s="84">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB14" s="93" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="93">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC14" s="88" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30">
-      <c r="A15" s="99"/>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A15" s="106"/>
       <c r="B15" s="25" t="s">
         <v>68</v>
       </c>
@@ -3863,7 +3863,7 @@
       <c r="E15" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="109"/>
+      <c r="F15" s="101"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -3938,8 +3938,8 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30">
-      <c r="A16" s="100"/>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A16" s="107"/>
       <c r="B16" s="26" t="s">
         <v>69</v>
       </c>
@@ -3954,7 +3954,7 @@
       <c r="E16" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="110"/>
+      <c r="F16" s="102"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4029,8 +4029,8 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30">
-      <c r="A17" s="101"/>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A17" s="108"/>
       <c r="B17" s="27" t="s">
         <v>71</v>
       </c>
@@ -4045,7 +4045,7 @@
       <c r="E17" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="111"/>
+      <c r="F17" s="103"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4120,8 +4120,8 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30">
-      <c r="A18" s="94">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A18" s="109">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4138,7 +4138,7 @@
       <c r="E18" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="107"/>
+      <c r="F18" s="99"/>
       <c r="G18" s="72"/>
       <c r="H18" s="55"/>
       <c r="I18" s="55"/>
@@ -4173,8 +4173,8 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30">
-      <c r="A19" s="95"/>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A19" s="110"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4189,7 +4189,7 @@
       <c r="E19" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="109"/>
+      <c r="F19" s="101"/>
       <c r="G19" s="63"/>
       <c r="H19" s="71"/>
       <c r="I19" s="71"/>
@@ -4224,8 +4224,8 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30">
-      <c r="A20" s="96"/>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A20" s="111"/>
       <c r="B20" s="29" t="s">
         <v>74</v>
       </c>
@@ -4240,7 +4240,7 @@
       <c r="E20" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="110"/>
+      <c r="F20" s="102"/>
       <c r="G20" s="65"/>
       <c r="H20" s="66"/>
       <c r="I20" s="66"/>
@@ -4275,8 +4275,8 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30">
-      <c r="A21" s="97"/>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A21" s="112"/>
       <c r="B21" s="30" t="s">
         <v>75</v>
       </c>
@@ -4291,7 +4291,7 @@
       <c r="E21" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="111"/>
+      <c r="F21" s="103"/>
       <c r="G21" s="74"/>
       <c r="H21" s="75"/>
       <c r="I21" s="75"/>
@@ -4326,8 +4326,8 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30">
-      <c r="A22" s="98">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A22" s="105">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4344,7 +4344,7 @@
       <c r="E22" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="107"/>
+      <c r="F22" s="99"/>
       <c r="G22" s="63"/>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -4379,8 +4379,8 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30">
-      <c r="A23" s="99"/>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A23" s="106"/>
       <c r="B23" s="25" t="s">
         <v>77</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="E23" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="109"/>
+      <c r="F23" s="101"/>
       <c r="G23" s="63"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -4430,8 +4430,8 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30">
-      <c r="A24" s="100"/>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A24" s="107"/>
       <c r="B24" s="26" t="s">
         <v>78</v>
       </c>
@@ -4446,7 +4446,7 @@
       <c r="E24" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="110"/>
+      <c r="F24" s="102"/>
       <c r="G24" s="65"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
@@ -4481,8 +4481,8 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30">
-      <c r="A25" s="101"/>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A25" s="108"/>
       <c r="B25" s="27" t="s">
         <v>79</v>
       </c>
@@ -4497,7 +4497,7 @@
       <c r="E25" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="111"/>
+      <c r="F25" s="103"/>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -4532,8 +4532,8 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30">
-      <c r="A26" s="94">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A26" s="109">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4550,7 +4550,7 @@
       <c r="E26" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="107"/>
+      <c r="F26" s="99"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4585,8 +4585,8 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30">
-      <c r="A27" s="95"/>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A27" s="110"/>
       <c r="B27" s="28" t="s">
         <v>81</v>
       </c>
@@ -4601,7 +4601,7 @@
       <c r="E27" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="109"/>
+      <c r="F27" s="101"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4636,8 +4636,8 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30">
-      <c r="A28" s="96"/>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A28" s="111"/>
       <c r="B28" s="29" t="s">
         <v>82</v>
       </c>
@@ -4652,7 +4652,7 @@
       <c r="E28" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="110"/>
+      <c r="F28" s="102"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4687,8 +4687,8 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30">
-      <c r="A29" s="97"/>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A29" s="112"/>
       <c r="B29" s="30" t="s">
         <v>83</v>
       </c>
@@ -4703,7 +4703,7 @@
       <c r="E29" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="111"/>
+      <c r="F29" s="103"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4738,8 +4738,8 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30">
-      <c r="A30" s="98">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A30" s="105">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -4756,7 +4756,7 @@
       <c r="E30" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="107"/>
+      <c r="F30" s="99"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4791,8 +4791,8 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30">
-      <c r="A31" s="99"/>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A31" s="106"/>
       <c r="B31" s="25" t="s">
         <v>85</v>
       </c>
@@ -4807,7 +4807,7 @@
       <c r="E31" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F31" s="109"/>
+      <c r="F31" s="101"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4842,8 +4842,8 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30">
-      <c r="A32" s="100"/>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A32" s="107"/>
       <c r="B32" s="26" t="s">
         <v>86</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="E32" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="110"/>
+      <c r="F32" s="102"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -4893,8 +4893,8 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30">
-      <c r="A33" s="101"/>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A33" s="108"/>
       <c r="B33" s="27" t="s">
         <v>87</v>
       </c>
@@ -4909,7 +4909,7 @@
       <c r="E33" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F33" s="111"/>
+      <c r="F33" s="103"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -4944,8 +4944,8 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30">
-      <c r="A34" s="94">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A34" s="109">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -4962,7 +4962,7 @@
       <c r="E34" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F34" s="107"/>
+      <c r="F34" s="99"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -4997,8 +4997,8 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30">
-      <c r="A35" s="95"/>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A35" s="110"/>
       <c r="B35" s="28" t="s">
         <v>89</v>
       </c>
@@ -5013,7 +5013,7 @@
       <c r="E35" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="109"/>
+      <c r="F35" s="101"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5048,8 +5048,8 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30">
-      <c r="A36" s="96"/>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A36" s="111"/>
       <c r="B36" s="29" t="s">
         <v>90</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="E36" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="110"/>
+      <c r="F36" s="102"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5099,8 +5099,8 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30">
-      <c r="A37" s="97"/>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A37" s="112"/>
       <c r="B37" s="30" t="s">
         <v>91</v>
       </c>
@@ -5115,7 +5115,7 @@
       <c r="E37" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="111"/>
+      <c r="F37" s="103"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5150,8 +5150,8 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30">
-      <c r="A38" s="98">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A38" s="105">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5168,7 +5168,7 @@
       <c r="E38" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="107"/>
+      <c r="F38" s="99"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5203,8 +5203,8 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30">
-      <c r="A39" s="99"/>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A39" s="106"/>
       <c r="B39" s="25" t="s">
         <v>93</v>
       </c>
@@ -5219,7 +5219,7 @@
       <c r="E39" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="109"/>
+      <c r="F39" s="101"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5254,8 +5254,8 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30">
-      <c r="A40" s="100"/>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A40" s="107"/>
       <c r="B40" s="26" t="s">
         <v>94</v>
       </c>
@@ -5270,7 +5270,7 @@
       <c r="E40" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F40" s="110"/>
+      <c r="F40" s="102"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5305,8 +5305,8 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30">
-      <c r="A41" s="101"/>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A41" s="108"/>
       <c r="B41" s="27" t="s">
         <v>95</v>
       </c>
@@ -5321,7 +5321,7 @@
       <c r="E41" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F41" s="111"/>
+      <c r="F41" s="103"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5356,8 +5356,8 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30">
-      <c r="A42" s="94">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A42" s="109">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5374,7 +5374,7 @@
       <c r="E42" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F42" s="107"/>
+      <c r="F42" s="99"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5409,8 +5409,8 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30">
-      <c r="A43" s="95"/>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A43" s="110"/>
       <c r="B43" s="28" t="s">
         <v>97</v>
       </c>
@@ -5425,7 +5425,7 @@
       <c r="E43" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="109"/>
+      <c r="F43" s="101"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5460,8 +5460,8 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30">
-      <c r="A44" s="96"/>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A44" s="111"/>
       <c r="B44" s="29" t="s">
         <v>98</v>
       </c>
@@ -5476,7 +5476,7 @@
       <c r="E44" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="110"/>
+      <c r="F44" s="102"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5511,8 +5511,8 @@
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30">
-      <c r="A45" s="97"/>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A45" s="112"/>
       <c r="B45" s="30" t="s">
         <v>99</v>
       </c>
@@ -5527,7 +5527,7 @@
       <c r="E45" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F45" s="111"/>
+      <c r="F45" s="103"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5562,8 +5562,8 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30">
-      <c r="A46" s="98">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A46" s="105">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5580,7 +5580,7 @@
       <c r="E46" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="107"/>
+      <c r="F46" s="99"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5615,8 +5615,8 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30">
-      <c r="A47" s="99"/>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A47" s="106"/>
       <c r="B47" s="25" t="s">
         <v>101</v>
       </c>
@@ -5631,7 +5631,7 @@
       <c r="E47" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="109"/>
+      <c r="F47" s="101"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5666,8 +5666,8 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30">
-      <c r="A48" s="100"/>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A48" s="107"/>
       <c r="B48" s="26" t="s">
         <v>102</v>
       </c>
@@ -5682,7 +5682,7 @@
       <c r="E48" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F48" s="110"/>
+      <c r="F48" s="102"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5717,8 +5717,8 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30">
-      <c r="A49" s="101"/>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A49" s="108"/>
       <c r="B49" s="27" t="s">
         <v>103</v>
       </c>
@@ -5733,7 +5733,7 @@
       <c r="E49" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F49" s="111"/>
+      <c r="F49" s="103"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5768,8 +5768,8 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30">
-      <c r="A50" s="94">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A50" s="109">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -5786,7 +5786,7 @@
       <c r="E50" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F50" s="107"/>
+      <c r="F50" s="99"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5821,8 +5821,8 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30">
-      <c r="A51" s="95"/>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A51" s="110"/>
       <c r="B51" s="28" t="s">
         <v>105</v>
       </c>
@@ -5837,7 +5837,7 @@
       <c r="E51" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F51" s="109"/>
+      <c r="F51" s="101"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -5872,8 +5872,8 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30">
-      <c r="A52" s="96"/>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A52" s="111"/>
       <c r="B52" s="29" t="s">
         <v>106</v>
       </c>
@@ -5888,7 +5888,7 @@
       <c r="E52" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F52" s="110"/>
+      <c r="F52" s="102"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -5923,8 +5923,8 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30">
-      <c r="A53" s="96"/>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A53" s="111"/>
       <c r="B53" s="29" t="s">
         <v>107</v>
       </c>
@@ -5939,7 +5939,7 @@
       <c r="E53" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="110"/>
+      <c r="F53" s="102"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -5974,8 +5974,8 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30">
-      <c r="A54" s="96"/>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A54" s="111"/>
       <c r="B54" s="29" t="s">
         <v>108</v>
       </c>
@@ -5990,7 +5990,7 @@
       <c r="E54" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F54" s="110"/>
+      <c r="F54" s="102"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6025,8 +6025,8 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30">
-      <c r="A55" s="97"/>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A55" s="112"/>
       <c r="B55" s="30" t="s">
         <v>109</v>
       </c>
@@ -6041,7 +6041,7 @@
       <c r="E55" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F55" s="111"/>
+      <c r="F55" s="103"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6076,8 +6076,8 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30">
-      <c r="A56" s="98">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A56" s="105">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6094,7 +6094,7 @@
       <c r="E56" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F56" s="107"/>
+      <c r="F56" s="99"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6129,8 +6129,8 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30">
-      <c r="A57" s="99"/>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A57" s="106"/>
       <c r="B57" s="25" t="s">
         <v>111</v>
       </c>
@@ -6145,7 +6145,7 @@
       <c r="E57" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F57" s="109"/>
+      <c r="F57" s="101"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6180,8 +6180,8 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30">
-      <c r="A58" s="100"/>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A58" s="107"/>
       <c r="B58" s="26" t="s">
         <v>112</v>
       </c>
@@ -6196,7 +6196,7 @@
       <c r="E58" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F58" s="110"/>
+      <c r="F58" s="102"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6231,8 +6231,8 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30">
-      <c r="A59" s="100"/>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A59" s="107"/>
       <c r="B59" s="26" t="s">
         <v>113</v>
       </c>
@@ -6247,7 +6247,7 @@
       <c r="E59" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F59" s="110"/>
+      <c r="F59" s="102"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6282,8 +6282,8 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30">
-      <c r="A60" s="100"/>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A60" s="107"/>
       <c r="B60" s="26" t="s">
         <v>114</v>
       </c>
@@ -6298,7 +6298,7 @@
       <c r="E60" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F60" s="110"/>
+      <c r="F60" s="102"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6333,8 +6333,8 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30">
-      <c r="A61" s="101"/>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A61" s="108"/>
       <c r="B61" s="27" t="s">
         <v>115</v>
       </c>
@@ -6349,7 +6349,7 @@
       <c r="E61" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F61" s="111"/>
+      <c r="F61" s="103"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6384,8 +6384,8 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30">
-      <c r="A62" s="94">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A62" s="109">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6402,7 +6402,7 @@
       <c r="E62" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F62" s="107"/>
+      <c r="F62" s="99"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6437,8 +6437,8 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30">
-      <c r="A63" s="95"/>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A63" s="110"/>
       <c r="B63" s="28" t="s">
         <v>117</v>
       </c>
@@ -6453,7 +6453,7 @@
       <c r="E63" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="109"/>
+      <c r="F63" s="101"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6488,8 +6488,8 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30">
-      <c r="A64" s="96"/>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A64" s="111"/>
       <c r="B64" s="29" t="s">
         <v>118</v>
       </c>
@@ -6504,7 +6504,7 @@
       <c r="E64" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F64" s="110"/>
+      <c r="F64" s="102"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6539,8 +6539,8 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30">
-      <c r="A65" s="96"/>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A65" s="111"/>
       <c r="B65" s="29" t="s">
         <v>119</v>
       </c>
@@ -6555,7 +6555,7 @@
       <c r="E65" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F65" s="110"/>
+      <c r="F65" s="102"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6590,8 +6590,8 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30">
-      <c r="A66" s="96"/>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A66" s="111"/>
       <c r="B66" s="29" t="s">
         <v>120</v>
       </c>
@@ -6606,7 +6606,7 @@
       <c r="E66" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F66" s="110"/>
+      <c r="F66" s="102"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6641,8 +6641,8 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30">
-      <c r="A67" s="97"/>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A67" s="112"/>
       <c r="B67" s="30" t="s">
         <v>121</v>
       </c>
@@ -6657,7 +6657,7 @@
       <c r="E67" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="111"/>
+      <c r="F67" s="103"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6692,8 +6692,8 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30">
-      <c r="A68" s="102">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A68" s="94">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -6710,7 +6710,7 @@
       <c r="E68" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F68" s="107"/>
+      <c r="F68" s="99"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6745,8 +6745,8 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30">
-      <c r="A69" s="103"/>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A69" s="95"/>
       <c r="B69" s="25" t="s">
         <v>123</v>
       </c>
@@ -6761,7 +6761,7 @@
       <c r="E69" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F69" s="109"/>
+      <c r="F69" s="101"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6796,8 +6796,8 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30">
-      <c r="A70" s="104"/>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A70" s="96"/>
       <c r="B70" s="26" t="s">
         <v>124</v>
       </c>
@@ -6812,7 +6812,7 @@
       <c r="E70" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F70" s="110"/>
+      <c r="F70" s="102"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -6847,8 +6847,8 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30">
-      <c r="A71" s="104"/>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A71" s="96"/>
       <c r="B71" s="26" t="s">
         <v>125</v>
       </c>
@@ -6863,7 +6863,7 @@
       <c r="E71" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F71" s="110"/>
+      <c r="F71" s="102"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -6898,8 +6898,8 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30">
-      <c r="A72" s="104"/>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A72" s="96"/>
       <c r="B72" s="26" t="s">
         <v>126</v>
       </c>
@@ -6914,7 +6914,7 @@
       <c r="E72" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="110"/>
+      <c r="F72" s="102"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -6949,8 +6949,8 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30">
-      <c r="A73" s="105"/>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A73" s="97"/>
       <c r="B73" s="31" t="s">
         <v>127</v>
       </c>
@@ -6965,7 +6965,7 @@
       <c r="E73" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="F73" s="112"/>
+      <c r="F73" s="104"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F74" s="19" t="s">
         <v>128</v>
       </c>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="J74" s="77" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K74" s="77" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7087,6 +7087,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7103,8 +7105,6 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10605"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/CA21BB4BE959536C/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72749073-11A9-7A4E-B559-CE4932D8174A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F226E4-83FB-4853-A4DA-BC911376248F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="130">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -450,6 +450,9 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>0x2</t>
   </si>
 </sst>
 </file>
@@ -1472,6 +1475,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1504,30 +1531,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1999,13 +2002,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.75" customWidth="1"/>
-    <col min="2" max="3" width="14.2578125" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="3" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="117" t="s">
         <v>0</v>
       </c>
@@ -2017,7 +2020,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="117"/>
       <c r="B2" s="117"/>
       <c r="C2" s="13"/>
@@ -2027,7 +2030,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="117"/>
       <c r="B3" s="117"/>
       <c r="C3" s="13"/>
@@ -2045,7 +2048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2053,7 +2056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2069,7 +2072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2077,7 +2080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2085,7 +2088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2093,7 +2096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2101,7 +2104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2109,7 +2112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2117,7 +2120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2125,7 +2128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2141,7 +2144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2149,7 +2152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2157,7 +2160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2165,7 +2168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2197,16 +2200,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.6484375" customWidth="1"/>
-    <col min="2" max="2" width="20.984375" customWidth="1"/>
-    <col min="3" max="7" width="12.10546875" customWidth="1"/>
-    <col min="9" max="9" width="22.8671875" customWidth="1"/>
-    <col min="10" max="10" width="9.55078125" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="7" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="118" t="s">
         <v>20</v>
       </c>
@@ -2217,7 +2220,7 @@
       <c r="F1" s="119"/>
       <c r="G1" s="119"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2238,7 +2241,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2265,7 +2268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2287,7 +2290,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2308,7 +2311,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2332,7 +2335,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2356,7 +2359,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2377,7 +2380,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2398,7 +2401,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2419,7 +2422,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2440,7 +2443,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2461,7 +2464,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2482,7 +2485,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2503,7 +2506,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2524,7 +2527,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2561,17 +2564,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.8359375" customWidth="1"/>
-    <col min="2" max="2" width="32.41796875" customWidth="1"/>
-    <col min="3" max="4" width="20.58203125" customWidth="1"/>
-    <col min="5" max="5" width="12.5078125" customWidth="1"/>
-    <col min="6" max="6" width="6.05078125" customWidth="1"/>
-    <col min="7" max="29" width="16.41015625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="29" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2587,7 +2590,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="98"/>
+      <c r="F1" s="106"/>
       <c r="G1" s="86" t="s">
         <v>3</v>
       </c>
@@ -2658,7 +2661,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="113">
         <v>46184</v>
       </c>
@@ -2676,7 +2679,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="99"/>
+      <c r="F2" s="107"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2750,7 +2753,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="114"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2766,7 +2769,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="108"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2840,7 +2843,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="115">
         <v>46185</v>
       </c>
@@ -2858,7 +2861,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="99"/>
+      <c r="F4" s="107"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2933,7 +2936,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="116"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -2949,7 +2952,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="100"/>
+      <c r="F5" s="108"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3024,8 +3027,8 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="105">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" s="94">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3042,7 +3045,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="99"/>
+      <c r="F6" s="107"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3117,8 +3120,8 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="106"/>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" s="95"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3133,7 +3136,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="101"/>
+      <c r="F7" s="109"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3208,8 +3211,8 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="107"/>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" s="96"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3224,7 +3227,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="102"/>
+      <c r="F8" s="110"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3299,8 +3302,8 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="108"/>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" s="97"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3315,7 +3318,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="103"/>
+      <c r="F9" s="111"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3390,8 +3393,8 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="109">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A10" s="98">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3408,7 +3411,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="99"/>
+      <c r="F10" s="107"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3481,8 +3484,8 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="110"/>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A11" s="99"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3497,7 +3500,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="101"/>
+      <c r="F11" s="109"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3572,8 +3575,8 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A12" s="111"/>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A12" s="100"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3588,7 +3591,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="102"/>
+      <c r="F12" s="110"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3663,8 +3666,8 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="112"/>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A13" s="101"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3679,7 +3682,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="103"/>
+      <c r="F13" s="111"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3754,8 +3757,8 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="105">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A14" s="94">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3772,7 +3775,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="99"/>
+      <c r="F14" s="107"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3847,8 +3850,8 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="106"/>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A15" s="95"/>
       <c r="B15" s="25" t="s">
         <v>68</v>
       </c>
@@ -3863,7 +3866,7 @@
       <c r="E15" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="101"/>
+      <c r="F15" s="109"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -3938,8 +3941,8 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A16" s="107"/>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A16" s="96"/>
       <c r="B16" s="26" t="s">
         <v>69</v>
       </c>
@@ -3954,7 +3957,7 @@
       <c r="E16" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="102"/>
+      <c r="F16" s="110"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4029,8 +4032,8 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A17" s="108"/>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A17" s="97"/>
       <c r="B17" s="27" t="s">
         <v>71</v>
       </c>
@@ -4043,9 +4046,9 @@
         <v>Uruguai</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="103"/>
+        <v>129</v>
+      </c>
+      <c r="F17" s="111"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4106,22 +4109,22 @@
       <c r="Z17" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="AA17" s="84" t="str">
+      <c r="AA17" s="84">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB17" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="93">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC17" s="88" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A18" s="109">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A18" s="98">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4138,7 +4141,7 @@
       <c r="E18" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="99"/>
+      <c r="F18" s="107"/>
       <c r="G18" s="72"/>
       <c r="H18" s="55"/>
       <c r="I18" s="55"/>
@@ -4173,8 +4176,8 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A19" s="110"/>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A19" s="99"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4189,7 +4192,7 @@
       <c r="E19" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="101"/>
+      <c r="F19" s="109"/>
       <c r="G19" s="63"/>
       <c r="H19" s="71"/>
       <c r="I19" s="71"/>
@@ -4224,8 +4227,8 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A20" s="111"/>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A20" s="100"/>
       <c r="B20" s="29" t="s">
         <v>74</v>
       </c>
@@ -4240,7 +4243,7 @@
       <c r="E20" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="102"/>
+      <c r="F20" s="110"/>
       <c r="G20" s="65"/>
       <c r="H20" s="66"/>
       <c r="I20" s="66"/>
@@ -4275,8 +4278,8 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A21" s="112"/>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A21" s="101"/>
       <c r="B21" s="30" t="s">
         <v>75</v>
       </c>
@@ -4291,7 +4294,7 @@
       <c r="E21" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="103"/>
+      <c r="F21" s="111"/>
       <c r="G21" s="74"/>
       <c r="H21" s="75"/>
       <c r="I21" s="75"/>
@@ -4326,8 +4329,8 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A22" s="105">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A22" s="94">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4344,7 +4347,7 @@
       <c r="E22" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="99"/>
+      <c r="F22" s="107"/>
       <c r="G22" s="63"/>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -4379,8 +4382,8 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A23" s="106"/>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A23" s="95"/>
       <c r="B23" s="25" t="s">
         <v>77</v>
       </c>
@@ -4395,7 +4398,7 @@
       <c r="E23" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="101"/>
+      <c r="F23" s="109"/>
       <c r="G23" s="63"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -4430,8 +4433,8 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A24" s="107"/>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A24" s="96"/>
       <c r="B24" s="26" t="s">
         <v>78</v>
       </c>
@@ -4446,7 +4449,7 @@
       <c r="E24" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="102"/>
+      <c r="F24" s="110"/>
       <c r="G24" s="65"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
@@ -4481,8 +4484,8 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A25" s="108"/>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A25" s="97"/>
       <c r="B25" s="27" t="s">
         <v>79</v>
       </c>
@@ -4497,7 +4500,7 @@
       <c r="E25" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="103"/>
+      <c r="F25" s="111"/>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -4532,8 +4535,8 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A26" s="109">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A26" s="98">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4550,7 +4553,7 @@
       <c r="E26" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="99"/>
+      <c r="F26" s="107"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4585,8 +4588,8 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A27" s="110"/>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A27" s="99"/>
       <c r="B27" s="28" t="s">
         <v>81</v>
       </c>
@@ -4601,7 +4604,7 @@
       <c r="E27" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="101"/>
+      <c r="F27" s="109"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4636,8 +4639,8 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A28" s="111"/>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A28" s="100"/>
       <c r="B28" s="29" t="s">
         <v>82</v>
       </c>
@@ -4652,7 +4655,7 @@
       <c r="E28" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="102"/>
+      <c r="F28" s="110"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4687,8 +4690,8 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A29" s="112"/>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A29" s="101"/>
       <c r="B29" s="30" t="s">
         <v>83</v>
       </c>
@@ -4703,7 +4706,7 @@
       <c r="E29" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="103"/>
+      <c r="F29" s="111"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4738,8 +4741,8 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A30" s="105">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A30" s="94">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -4756,7 +4759,7 @@
       <c r="E30" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="99"/>
+      <c r="F30" s="107"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4791,8 +4794,8 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A31" s="106"/>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A31" s="95"/>
       <c r="B31" s="25" t="s">
         <v>85</v>
       </c>
@@ -4807,7 +4810,7 @@
       <c r="E31" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F31" s="101"/>
+      <c r="F31" s="109"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4842,8 +4845,8 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A32" s="107"/>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A32" s="96"/>
       <c r="B32" s="26" t="s">
         <v>86</v>
       </c>
@@ -4858,7 +4861,7 @@
       <c r="E32" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="102"/>
+      <c r="F32" s="110"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -4893,8 +4896,8 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A33" s="108"/>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A33" s="97"/>
       <c r="B33" s="27" t="s">
         <v>87</v>
       </c>
@@ -4909,7 +4912,7 @@
       <c r="E33" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F33" s="103"/>
+      <c r="F33" s="111"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -4944,8 +4947,8 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A34" s="109">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A34" s="98">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -4962,7 +4965,7 @@
       <c r="E34" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F34" s="99"/>
+      <c r="F34" s="107"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -4997,8 +5000,8 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A35" s="110"/>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A35" s="99"/>
       <c r="B35" s="28" t="s">
         <v>89</v>
       </c>
@@ -5013,7 +5016,7 @@
       <c r="E35" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="101"/>
+      <c r="F35" s="109"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5048,8 +5051,8 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A36" s="111"/>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A36" s="100"/>
       <c r="B36" s="29" t="s">
         <v>90</v>
       </c>
@@ -5064,7 +5067,7 @@
       <c r="E36" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="102"/>
+      <c r="F36" s="110"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5099,8 +5102,8 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A37" s="112"/>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A37" s="101"/>
       <c r="B37" s="30" t="s">
         <v>91</v>
       </c>
@@ -5115,7 +5118,7 @@
       <c r="E37" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="103"/>
+      <c r="F37" s="111"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5150,8 +5153,8 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A38" s="105">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A38" s="94">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5168,7 +5171,7 @@
       <c r="E38" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="99"/>
+      <c r="F38" s="107"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5203,8 +5206,8 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A39" s="106"/>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A39" s="95"/>
       <c r="B39" s="25" t="s">
         <v>93</v>
       </c>
@@ -5219,7 +5222,7 @@
       <c r="E39" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="101"/>
+      <c r="F39" s="109"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5254,8 +5257,8 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A40" s="107"/>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A40" s="96"/>
       <c r="B40" s="26" t="s">
         <v>94</v>
       </c>
@@ -5270,7 +5273,7 @@
       <c r="E40" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F40" s="102"/>
+      <c r="F40" s="110"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5305,8 +5308,8 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A41" s="108"/>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A41" s="97"/>
       <c r="B41" s="27" t="s">
         <v>95</v>
       </c>
@@ -5321,7 +5324,7 @@
       <c r="E41" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F41" s="103"/>
+      <c r="F41" s="111"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5356,8 +5359,8 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A42" s="109">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A42" s="98">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5374,7 +5377,7 @@
       <c r="E42" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F42" s="99"/>
+      <c r="F42" s="107"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5409,8 +5412,8 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A43" s="110"/>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A43" s="99"/>
       <c r="B43" s="28" t="s">
         <v>97</v>
       </c>
@@ -5425,7 +5428,7 @@
       <c r="E43" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="101"/>
+      <c r="F43" s="109"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5460,8 +5463,8 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A44" s="111"/>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A44" s="100"/>
       <c r="B44" s="29" t="s">
         <v>98</v>
       </c>
@@ -5476,7 +5479,7 @@
       <c r="E44" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="102"/>
+      <c r="F44" s="110"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5511,8 +5514,8 @@
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A45" s="112"/>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A45" s="101"/>
       <c r="B45" s="30" t="s">
         <v>99</v>
       </c>
@@ -5527,7 +5530,7 @@
       <c r="E45" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F45" s="103"/>
+      <c r="F45" s="111"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5562,8 +5565,8 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A46" s="105">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A46" s="94">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5580,7 +5583,7 @@
       <c r="E46" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="99"/>
+      <c r="F46" s="107"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5615,8 +5618,8 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A47" s="106"/>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A47" s="95"/>
       <c r="B47" s="25" t="s">
         <v>101</v>
       </c>
@@ -5631,7 +5634,7 @@
       <c r="E47" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="101"/>
+      <c r="F47" s="109"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5666,8 +5669,8 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A48" s="107"/>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A48" s="96"/>
       <c r="B48" s="26" t="s">
         <v>102</v>
       </c>
@@ -5682,7 +5685,7 @@
       <c r="E48" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F48" s="102"/>
+      <c r="F48" s="110"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5717,8 +5720,8 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A49" s="108"/>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A49" s="97"/>
       <c r="B49" s="27" t="s">
         <v>103</v>
       </c>
@@ -5733,7 +5736,7 @@
       <c r="E49" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F49" s="103"/>
+      <c r="F49" s="111"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5768,8 +5771,8 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A50" s="109">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A50" s="98">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -5786,7 +5789,7 @@
       <c r="E50" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F50" s="99"/>
+      <c r="F50" s="107"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5821,8 +5824,8 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A51" s="110"/>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A51" s="99"/>
       <c r="B51" s="28" t="s">
         <v>105</v>
       </c>
@@ -5837,7 +5840,7 @@
       <c r="E51" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F51" s="101"/>
+      <c r="F51" s="109"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -5872,8 +5875,8 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A52" s="111"/>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A52" s="100"/>
       <c r="B52" s="29" t="s">
         <v>106</v>
       </c>
@@ -5888,7 +5891,7 @@
       <c r="E52" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F52" s="102"/>
+      <c r="F52" s="110"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -5923,8 +5926,8 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A53" s="111"/>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A53" s="100"/>
       <c r="B53" s="29" t="s">
         <v>107</v>
       </c>
@@ -5939,7 +5942,7 @@
       <c r="E53" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="102"/>
+      <c r="F53" s="110"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -5974,8 +5977,8 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A54" s="111"/>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A54" s="100"/>
       <c r="B54" s="29" t="s">
         <v>108</v>
       </c>
@@ -5990,7 +5993,7 @@
       <c r="E54" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F54" s="102"/>
+      <c r="F54" s="110"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6025,8 +6028,8 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A55" s="112"/>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A55" s="101"/>
       <c r="B55" s="30" t="s">
         <v>109</v>
       </c>
@@ -6041,7 +6044,7 @@
       <c r="E55" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F55" s="103"/>
+      <c r="F55" s="111"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6076,8 +6079,8 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A56" s="105">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A56" s="94">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6094,7 +6097,7 @@
       <c r="E56" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F56" s="99"/>
+      <c r="F56" s="107"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6129,8 +6132,8 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A57" s="106"/>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A57" s="95"/>
       <c r="B57" s="25" t="s">
         <v>111</v>
       </c>
@@ -6145,7 +6148,7 @@
       <c r="E57" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F57" s="101"/>
+      <c r="F57" s="109"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6180,8 +6183,8 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A58" s="107"/>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A58" s="96"/>
       <c r="B58" s="26" t="s">
         <v>112</v>
       </c>
@@ -6196,7 +6199,7 @@
       <c r="E58" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F58" s="102"/>
+      <c r="F58" s="110"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6231,8 +6234,8 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A59" s="107"/>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A59" s="96"/>
       <c r="B59" s="26" t="s">
         <v>113</v>
       </c>
@@ -6247,7 +6250,7 @@
       <c r="E59" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F59" s="102"/>
+      <c r="F59" s="110"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6282,8 +6285,8 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A60" s="107"/>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A60" s="96"/>
       <c r="B60" s="26" t="s">
         <v>114</v>
       </c>
@@ -6298,7 +6301,7 @@
       <c r="E60" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F60" s="102"/>
+      <c r="F60" s="110"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6333,8 +6336,8 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A61" s="108"/>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A61" s="97"/>
       <c r="B61" s="27" t="s">
         <v>115</v>
       </c>
@@ -6349,7 +6352,7 @@
       <c r="E61" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F61" s="103"/>
+      <c r="F61" s="111"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6384,8 +6387,8 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A62" s="109">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A62" s="98">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6402,7 +6405,7 @@
       <c r="E62" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F62" s="99"/>
+      <c r="F62" s="107"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6437,8 +6440,8 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A63" s="110"/>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A63" s="99"/>
       <c r="B63" s="28" t="s">
         <v>117</v>
       </c>
@@ -6453,7 +6456,7 @@
       <c r="E63" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="101"/>
+      <c r="F63" s="109"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6488,8 +6491,8 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A64" s="111"/>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A64" s="100"/>
       <c r="B64" s="29" t="s">
         <v>118</v>
       </c>
@@ -6504,7 +6507,7 @@
       <c r="E64" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F64" s="102"/>
+      <c r="F64" s="110"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6539,8 +6542,8 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A65" s="111"/>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A65" s="100"/>
       <c r="B65" s="29" t="s">
         <v>119</v>
       </c>
@@ -6555,7 +6558,7 @@
       <c r="E65" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F65" s="102"/>
+      <c r="F65" s="110"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6590,8 +6593,8 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A66" s="111"/>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A66" s="100"/>
       <c r="B66" s="29" t="s">
         <v>120</v>
       </c>
@@ -6606,7 +6609,7 @@
       <c r="E66" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F66" s="102"/>
+      <c r="F66" s="110"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6641,8 +6644,8 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A67" s="112"/>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A67" s="101"/>
       <c r="B67" s="30" t="s">
         <v>121</v>
       </c>
@@ -6657,7 +6660,7 @@
       <c r="E67" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="103"/>
+      <c r="F67" s="111"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6692,8 +6695,8 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A68" s="94">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A68" s="102">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -6710,7 +6713,7 @@
       <c r="E68" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F68" s="99"/>
+      <c r="F68" s="107"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6745,8 +6748,8 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A69" s="95"/>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A69" s="103"/>
       <c r="B69" s="25" t="s">
         <v>123</v>
       </c>
@@ -6761,7 +6764,7 @@
       <c r="E69" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F69" s="101"/>
+      <c r="F69" s="109"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6796,8 +6799,8 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A70" s="96"/>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A70" s="104"/>
       <c r="B70" s="26" t="s">
         <v>124</v>
       </c>
@@ -6812,7 +6815,7 @@
       <c r="E70" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F70" s="102"/>
+      <c r="F70" s="110"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -6847,8 +6850,8 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A71" s="96"/>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A71" s="104"/>
       <c r="B71" s="26" t="s">
         <v>125</v>
       </c>
@@ -6863,7 +6866,7 @@
       <c r="E71" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F71" s="102"/>
+      <c r="F71" s="110"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -6898,8 +6901,8 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A72" s="96"/>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A72" s="104"/>
       <c r="B72" s="26" t="s">
         <v>126</v>
       </c>
@@ -6914,7 +6917,7 @@
       <c r="E72" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="102"/>
+      <c r="F72" s="110"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -6949,8 +6952,8 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A73" s="97"/>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A73" s="105"/>
       <c r="B73" s="31" t="s">
         <v>127</v>
       </c>
@@ -6965,7 +6968,7 @@
       <c r="E73" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="F73" s="104"/>
+      <c r="F73" s="112"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7000,49 +7003,49 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F74" s="19" t="s">
         <v>128</v>
       </c>
       <c r="G74" s="77" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H74" s="77" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I74" s="77" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J74" s="77" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K74" s="77" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L74" s="77" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M74" s="77" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N74" s="77" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O74" s="77" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P74" s="77" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q74" s="77" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7050,43 +7053,45 @@
       </c>
       <c r="R74" s="77" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S74" s="77" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T74" s="77" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U74" s="77" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V74" s="77" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W74" s="77" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X74" s="77" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y74" s="77" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z74" s="77" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
@@ -7103,8 +7108,6 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F226E4-83FB-4853-A4DA-BC911376248F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612433B3-02AD-446A-A179-5AE2AF19C55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="129">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -450,9 +450,6 @@
   </si>
   <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>0x2</t>
   </si>
 </sst>
 </file>
@@ -4046,7 +4043,7 @@
         <v>Uruguai</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="F17" s="111"/>
       <c r="G17" s="68" t="s">
@@ -4109,17 +4106,17 @@
       <c r="Z17" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="AA17" s="84">
+      <c r="AA17" s="84" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB17" s="93">
+        <v/>
+      </c>
+      <c r="AB17" s="93" t="str">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v/>
       </c>
       <c r="AC17" s="88" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
+        <v/>
       </c>
       <c r="AD17" s="54"/>
     </row>
@@ -7009,43 +7006,43 @@
       </c>
       <c r="G74" s="77" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H74" s="77" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I74" s="77" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J74" s="77" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K74" s="77" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L74" s="77" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M74" s="77" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N74" s="77" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O74" s="77" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P74" s="77" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q74" s="77" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7053,48 +7050,43 @@
       </c>
       <c r="R74" s="77" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S74" s="77" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T74" s="77" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U74" s="77" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V74" s="77" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W74" s="77" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X74" s="77" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y74" s="77" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z74" s="77" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -7108,6 +7100,11 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612433B3-02AD-446A-A179-5AE2AF19C55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9973770C-D649-4FE9-B1DB-299C8325C771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -1472,6 +1472,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1496,6 +1517,18 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1507,39 +1540,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2587,7 +2587,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="106"/>
+      <c r="F1" s="94"/>
       <c r="G1" s="86" t="s">
         <v>3</v>
       </c>
@@ -2659,7 +2659,7 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="113">
+      <c r="A2" s="109">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2676,7 +2676,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="107"/>
+      <c r="F2" s="95"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="114"/>
+      <c r="A3" s="110"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2766,7 +2766,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="108"/>
+      <c r="F3" s="96"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2841,7 +2841,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="115">
+      <c r="A4" s="111">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2858,7 +2858,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="107"/>
+      <c r="F4" s="95"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2934,7 +2934,7 @@
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="116"/>
+      <c r="A5" s="112"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -2949,7 +2949,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="108"/>
+      <c r="F5" s="96"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3025,7 +3025,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="94">
+      <c r="A6" s="101">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3042,7 +3042,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="107"/>
+      <c r="F6" s="95"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3118,7 +3118,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="95"/>
+      <c r="A7" s="102"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="109"/>
+      <c r="F7" s="97"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3209,7 +3209,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="96"/>
+      <c r="A8" s="103"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3224,7 +3224,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="110"/>
+      <c r="F8" s="98"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3300,7 +3300,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="97"/>
+      <c r="A9" s="104"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3315,7 +3315,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="111"/>
+      <c r="F9" s="99"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3391,7 +3391,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="98">
+      <c r="A10" s="105">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3408,7 +3408,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="107"/>
+      <c r="F10" s="95"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3482,7 +3482,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="99"/>
+      <c r="A11" s="106"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3497,7 +3497,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="109"/>
+      <c r="F11" s="97"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3573,7 +3573,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="100"/>
+      <c r="A12" s="107"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3588,7 +3588,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="110"/>
+      <c r="F12" s="98"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3664,7 +3664,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="101"/>
+      <c r="A13" s="108"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3679,7 +3679,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="111"/>
+      <c r="F13" s="99"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3755,7 +3755,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="94">
+      <c r="A14" s="101">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3772,7 +3772,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="107"/>
+      <c r="F14" s="95"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3848,7 +3848,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="95"/>
+      <c r="A15" s="102"/>
       <c r="B15" s="25" t="s">
         <v>68</v>
       </c>
@@ -3863,7 +3863,7 @@
       <c r="E15" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="109"/>
+      <c r="F15" s="97"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -3939,7 +3939,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="96"/>
+      <c r="A16" s="103"/>
       <c r="B16" s="26" t="s">
         <v>69</v>
       </c>
@@ -3954,7 +3954,7 @@
       <c r="E16" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="110"/>
+      <c r="F16" s="98"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4030,7 +4030,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" s="97"/>
+      <c r="A17" s="104"/>
       <c r="B17" s="27" t="s">
         <v>71</v>
       </c>
@@ -4043,9 +4043,9 @@
         <v>Uruguai</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="111"/>
+        <v>50</v>
+      </c>
+      <c r="F17" s="99"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4106,22 +4106,22 @@
       <c r="Z17" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="AA17" s="84" t="str">
+      <c r="AA17" s="84">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB17" s="93" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="93">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC17" s="88" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18" s="98">
+      <c r="A18" s="105">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4138,7 +4138,7 @@
       <c r="E18" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="107"/>
+      <c r="F18" s="95"/>
       <c r="G18" s="72"/>
       <c r="H18" s="55"/>
       <c r="I18" s="55"/>
@@ -4174,7 +4174,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="99"/>
+      <c r="A19" s="106"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4189,7 +4189,7 @@
       <c r="E19" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="109"/>
+      <c r="F19" s="97"/>
       <c r="G19" s="63"/>
       <c r="H19" s="71"/>
       <c r="I19" s="71"/>
@@ -4225,7 +4225,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="100"/>
+      <c r="A20" s="107"/>
       <c r="B20" s="29" t="s">
         <v>74</v>
       </c>
@@ -4240,7 +4240,7 @@
       <c r="E20" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="110"/>
+      <c r="F20" s="98"/>
       <c r="G20" s="65"/>
       <c r="H20" s="66"/>
       <c r="I20" s="66"/>
@@ -4276,7 +4276,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" s="101"/>
+      <c r="A21" s="108"/>
       <c r="B21" s="30" t="s">
         <v>75</v>
       </c>
@@ -4291,7 +4291,7 @@
       <c r="E21" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="111"/>
+      <c r="F21" s="99"/>
       <c r="G21" s="74"/>
       <c r="H21" s="75"/>
       <c r="I21" s="75"/>
@@ -4327,7 +4327,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" s="94">
+      <c r="A22" s="101">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4344,7 +4344,7 @@
       <c r="E22" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="107"/>
+      <c r="F22" s="95"/>
       <c r="G22" s="63"/>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -4380,7 +4380,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" s="95"/>
+      <c r="A23" s="102"/>
       <c r="B23" s="25" t="s">
         <v>77</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="E23" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="109"/>
+      <c r="F23" s="97"/>
       <c r="G23" s="63"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -4431,7 +4431,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="96"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="26" t="s">
         <v>78</v>
       </c>
@@ -4446,7 +4446,7 @@
       <c r="E24" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="110"/>
+      <c r="F24" s="98"/>
       <c r="G24" s="65"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
@@ -4482,7 +4482,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25" s="97"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="27" t="s">
         <v>79</v>
       </c>
@@ -4497,7 +4497,7 @@
       <c r="E25" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="111"/>
+      <c r="F25" s="99"/>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -4533,7 +4533,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26" s="98">
+      <c r="A26" s="105">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4550,7 +4550,7 @@
       <c r="E26" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="107"/>
+      <c r="F26" s="95"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4586,7 +4586,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27" s="99"/>
+      <c r="A27" s="106"/>
       <c r="B27" s="28" t="s">
         <v>81</v>
       </c>
@@ -4601,7 +4601,7 @@
       <c r="E27" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="109"/>
+      <c r="F27" s="97"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4637,7 +4637,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" s="100"/>
+      <c r="A28" s="107"/>
       <c r="B28" s="29" t="s">
         <v>82</v>
       </c>
@@ -4652,7 +4652,7 @@
       <c r="E28" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="110"/>
+      <c r="F28" s="98"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4688,7 +4688,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29" s="101"/>
+      <c r="A29" s="108"/>
       <c r="B29" s="30" t="s">
         <v>83</v>
       </c>
@@ -4703,7 +4703,7 @@
       <c r="E29" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="111"/>
+      <c r="F29" s="99"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4739,7 +4739,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30" s="94">
+      <c r="A30" s="101">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -4756,7 +4756,7 @@
       <c r="E30" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="107"/>
+      <c r="F30" s="95"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4792,7 +4792,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A31" s="95"/>
+      <c r="A31" s="102"/>
       <c r="B31" s="25" t="s">
         <v>85</v>
       </c>
@@ -4807,7 +4807,7 @@
       <c r="E31" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F31" s="109"/>
+      <c r="F31" s="97"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4843,7 +4843,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A32" s="96"/>
+      <c r="A32" s="103"/>
       <c r="B32" s="26" t="s">
         <v>86</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="E32" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="110"/>
+      <c r="F32" s="98"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -4894,7 +4894,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A33" s="97"/>
+      <c r="A33" s="104"/>
       <c r="B33" s="27" t="s">
         <v>87</v>
       </c>
@@ -4909,7 +4909,7 @@
       <c r="E33" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F33" s="111"/>
+      <c r="F33" s="99"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -4945,7 +4945,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A34" s="98">
+      <c r="A34" s="105">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -4962,7 +4962,7 @@
       <c r="E34" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F34" s="107"/>
+      <c r="F34" s="95"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -4998,7 +4998,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A35" s="99"/>
+      <c r="A35" s="106"/>
       <c r="B35" s="28" t="s">
         <v>89</v>
       </c>
@@ -5013,7 +5013,7 @@
       <c r="E35" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="109"/>
+      <c r="F35" s="97"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5049,7 +5049,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A36" s="100"/>
+      <c r="A36" s="107"/>
       <c r="B36" s="29" t="s">
         <v>90</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="E36" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="110"/>
+      <c r="F36" s="98"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5100,7 +5100,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A37" s="101"/>
+      <c r="A37" s="108"/>
       <c r="B37" s="30" t="s">
         <v>91</v>
       </c>
@@ -5115,7 +5115,7 @@
       <c r="E37" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="111"/>
+      <c r="F37" s="99"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5151,7 +5151,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A38" s="94">
+      <c r="A38" s="101">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5168,7 +5168,7 @@
       <c r="E38" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="107"/>
+      <c r="F38" s="95"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5204,7 +5204,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A39" s="95"/>
+      <c r="A39" s="102"/>
       <c r="B39" s="25" t="s">
         <v>93</v>
       </c>
@@ -5219,7 +5219,7 @@
       <c r="E39" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="109"/>
+      <c r="F39" s="97"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5255,7 +5255,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A40" s="96"/>
+      <c r="A40" s="103"/>
       <c r="B40" s="26" t="s">
         <v>94</v>
       </c>
@@ -5270,7 +5270,7 @@
       <c r="E40" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F40" s="110"/>
+      <c r="F40" s="98"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5306,7 +5306,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A41" s="97"/>
+      <c r="A41" s="104"/>
       <c r="B41" s="27" t="s">
         <v>95</v>
       </c>
@@ -5321,7 +5321,7 @@
       <c r="E41" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F41" s="111"/>
+      <c r="F41" s="99"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5357,7 +5357,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A42" s="98">
+      <c r="A42" s="105">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5374,7 +5374,7 @@
       <c r="E42" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F42" s="107"/>
+      <c r="F42" s="95"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5410,7 +5410,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A43" s="99"/>
+      <c r="A43" s="106"/>
       <c r="B43" s="28" t="s">
         <v>97</v>
       </c>
@@ -5425,7 +5425,7 @@
       <c r="E43" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="109"/>
+      <c r="F43" s="97"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5461,7 +5461,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A44" s="100"/>
+      <c r="A44" s="107"/>
       <c r="B44" s="29" t="s">
         <v>98</v>
       </c>
@@ -5476,7 +5476,7 @@
       <c r="E44" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="110"/>
+      <c r="F44" s="98"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5512,7 +5512,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A45" s="101"/>
+      <c r="A45" s="108"/>
       <c r="B45" s="30" t="s">
         <v>99</v>
       </c>
@@ -5527,7 +5527,7 @@
       <c r="E45" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F45" s="111"/>
+      <c r="F45" s="99"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5563,7 +5563,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A46" s="94">
+      <c r="A46" s="101">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5580,7 +5580,7 @@
       <c r="E46" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="107"/>
+      <c r="F46" s="95"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5616,7 +5616,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A47" s="95"/>
+      <c r="A47" s="102"/>
       <c r="B47" s="25" t="s">
         <v>101</v>
       </c>
@@ -5631,7 +5631,7 @@
       <c r="E47" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="109"/>
+      <c r="F47" s="97"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5667,7 +5667,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A48" s="96"/>
+      <c r="A48" s="103"/>
       <c r="B48" s="26" t="s">
         <v>102</v>
       </c>
@@ -5682,7 +5682,7 @@
       <c r="E48" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F48" s="110"/>
+      <c r="F48" s="98"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5718,7 +5718,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A49" s="97"/>
+      <c r="A49" s="104"/>
       <c r="B49" s="27" t="s">
         <v>103</v>
       </c>
@@ -5733,7 +5733,7 @@
       <c r="E49" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F49" s="111"/>
+      <c r="F49" s="99"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5769,7 +5769,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A50" s="98">
+      <c r="A50" s="105">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -5786,7 +5786,7 @@
       <c r="E50" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F50" s="107"/>
+      <c r="F50" s="95"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5822,7 +5822,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A51" s="99"/>
+      <c r="A51" s="106"/>
       <c r="B51" s="28" t="s">
         <v>105</v>
       </c>
@@ -5837,7 +5837,7 @@
       <c r="E51" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F51" s="109"/>
+      <c r="F51" s="97"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -5873,7 +5873,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A52" s="100"/>
+      <c r="A52" s="107"/>
       <c r="B52" s="29" t="s">
         <v>106</v>
       </c>
@@ -5888,7 +5888,7 @@
       <c r="E52" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F52" s="110"/>
+      <c r="F52" s="98"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -5924,7 +5924,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A53" s="100"/>
+      <c r="A53" s="107"/>
       <c r="B53" s="29" t="s">
         <v>107</v>
       </c>
@@ -5939,7 +5939,7 @@
       <c r="E53" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="110"/>
+      <c r="F53" s="98"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -5975,7 +5975,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A54" s="100"/>
+      <c r="A54" s="107"/>
       <c r="B54" s="29" t="s">
         <v>108</v>
       </c>
@@ -5990,7 +5990,7 @@
       <c r="E54" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F54" s="110"/>
+      <c r="F54" s="98"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6026,7 +6026,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A55" s="101"/>
+      <c r="A55" s="108"/>
       <c r="B55" s="30" t="s">
         <v>109</v>
       </c>
@@ -6041,7 +6041,7 @@
       <c r="E55" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F55" s="111"/>
+      <c r="F55" s="99"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6077,7 +6077,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A56" s="94">
+      <c r="A56" s="101">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6094,7 +6094,7 @@
       <c r="E56" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F56" s="107"/>
+      <c r="F56" s="95"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6130,7 +6130,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A57" s="95"/>
+      <c r="A57" s="102"/>
       <c r="B57" s="25" t="s">
         <v>111</v>
       </c>
@@ -6145,7 +6145,7 @@
       <c r="E57" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F57" s="109"/>
+      <c r="F57" s="97"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6181,7 +6181,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A58" s="96"/>
+      <c r="A58" s="103"/>
       <c r="B58" s="26" t="s">
         <v>112</v>
       </c>
@@ -6196,7 +6196,7 @@
       <c r="E58" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F58" s="110"/>
+      <c r="F58" s="98"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6232,7 +6232,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A59" s="96"/>
+      <c r="A59" s="103"/>
       <c r="B59" s="26" t="s">
         <v>113</v>
       </c>
@@ -6247,7 +6247,7 @@
       <c r="E59" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F59" s="110"/>
+      <c r="F59" s="98"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6283,7 +6283,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A60" s="96"/>
+      <c r="A60" s="103"/>
       <c r="B60" s="26" t="s">
         <v>114</v>
       </c>
@@ -6298,7 +6298,7 @@
       <c r="E60" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F60" s="110"/>
+      <c r="F60" s="98"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6334,7 +6334,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A61" s="97"/>
+      <c r="A61" s="104"/>
       <c r="B61" s="27" t="s">
         <v>115</v>
       </c>
@@ -6349,7 +6349,7 @@
       <c r="E61" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F61" s="111"/>
+      <c r="F61" s="99"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6385,7 +6385,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A62" s="98">
+      <c r="A62" s="105">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6402,7 +6402,7 @@
       <c r="E62" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F62" s="107"/>
+      <c r="F62" s="95"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6438,7 +6438,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A63" s="99"/>
+      <c r="A63" s="106"/>
       <c r="B63" s="28" t="s">
         <v>117</v>
       </c>
@@ -6453,7 +6453,7 @@
       <c r="E63" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="109"/>
+      <c r="F63" s="97"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6489,7 +6489,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A64" s="100"/>
+      <c r="A64" s="107"/>
       <c r="B64" s="29" t="s">
         <v>118</v>
       </c>
@@ -6504,7 +6504,7 @@
       <c r="E64" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F64" s="110"/>
+      <c r="F64" s="98"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6540,7 +6540,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A65" s="100"/>
+      <c r="A65" s="107"/>
       <c r="B65" s="29" t="s">
         <v>119</v>
       </c>
@@ -6555,7 +6555,7 @@
       <c r="E65" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F65" s="110"/>
+      <c r="F65" s="98"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6591,7 +6591,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A66" s="100"/>
+      <c r="A66" s="107"/>
       <c r="B66" s="29" t="s">
         <v>120</v>
       </c>
@@ -6606,7 +6606,7 @@
       <c r="E66" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F66" s="110"/>
+      <c r="F66" s="98"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6642,7 +6642,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A67" s="101"/>
+      <c r="A67" s="108"/>
       <c r="B67" s="30" t="s">
         <v>121</v>
       </c>
@@ -6657,7 +6657,7 @@
       <c r="E67" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="111"/>
+      <c r="F67" s="99"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6693,7 +6693,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A68" s="102">
+      <c r="A68" s="113">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -6710,7 +6710,7 @@
       <c r="E68" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F68" s="107"/>
+      <c r="F68" s="95"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6746,7 +6746,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A69" s="103"/>
+      <c r="A69" s="114"/>
       <c r="B69" s="25" t="s">
         <v>123</v>
       </c>
@@ -6761,7 +6761,7 @@
       <c r="E69" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F69" s="109"/>
+      <c r="F69" s="97"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6797,7 +6797,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A70" s="104"/>
+      <c r="A70" s="115"/>
       <c r="B70" s="26" t="s">
         <v>124</v>
       </c>
@@ -6812,7 +6812,7 @@
       <c r="E70" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F70" s="110"/>
+      <c r="F70" s="98"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -6848,7 +6848,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A71" s="104"/>
+      <c r="A71" s="115"/>
       <c r="B71" s="26" t="s">
         <v>125</v>
       </c>
@@ -6863,7 +6863,7 @@
       <c r="E71" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F71" s="110"/>
+      <c r="F71" s="98"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -6899,7 +6899,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A72" s="104"/>
+      <c r="A72" s="115"/>
       <c r="B72" s="26" t="s">
         <v>126</v>
       </c>
@@ -6914,7 +6914,7 @@
       <c r="E72" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="110"/>
+      <c r="F72" s="98"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -6950,7 +6950,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A73" s="105"/>
+      <c r="A73" s="116"/>
       <c r="B73" s="31" t="s">
         <v>127</v>
       </c>
@@ -6965,7 +6965,7 @@
       <c r="E73" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="F73" s="112"/>
+      <c r="F73" s="100"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7087,6 +7087,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -7103,8 +7105,6 @@
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9973770C-D649-4FE9-B1DB-299C8325C771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963CBFF1-B10A-4BF6-B9DE-7652654B6E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -1472,6 +1472,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -1505,18 +1529,6 @@
     <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1528,18 +1540,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2587,7 +2587,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="94"/>
+      <c r="F1" s="102"/>
       <c r="G1" s="86" t="s">
         <v>3</v>
       </c>
@@ -2659,7 +2659,7 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="109">
+      <c r="A2" s="113">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2676,7 +2676,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="95"/>
+      <c r="F2" s="103"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="110"/>
+      <c r="A3" s="114"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2766,7 +2766,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="96"/>
+      <c r="F3" s="104"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2841,7 +2841,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="111">
+      <c r="A4" s="115">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2858,7 +2858,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="95"/>
+      <c r="F4" s="103"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2934,7 +2934,7 @@
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="112"/>
+      <c r="A5" s="116"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -2949,7 +2949,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="96"/>
+      <c r="F5" s="104"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3025,7 +3025,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="101">
+      <c r="A6" s="109">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3042,7 +3042,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="95"/>
+      <c r="F6" s="103"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3118,7 +3118,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="102"/>
+      <c r="A7" s="110"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="97"/>
+      <c r="F7" s="105"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3209,7 +3209,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="103"/>
+      <c r="A8" s="111"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3224,7 +3224,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="98"/>
+      <c r="F8" s="106"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3300,7 +3300,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="104"/>
+      <c r="A9" s="112"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3315,7 +3315,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="99"/>
+      <c r="F9" s="107"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3391,7 +3391,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="105">
+      <c r="A10" s="94">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3408,7 +3408,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="95"/>
+      <c r="F10" s="103"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3482,7 +3482,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="106"/>
+      <c r="A11" s="95"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3497,7 +3497,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="97"/>
+      <c r="F11" s="105"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3573,7 +3573,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="107"/>
+      <c r="A12" s="96"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3588,7 +3588,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="98"/>
+      <c r="F12" s="106"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3664,7 +3664,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="108"/>
+      <c r="A13" s="97"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3679,7 +3679,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="99"/>
+      <c r="F13" s="107"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3755,7 +3755,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="101">
+      <c r="A14" s="109">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3772,7 +3772,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="95"/>
+      <c r="F14" s="103"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3848,7 +3848,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="102"/>
+      <c r="A15" s="110"/>
       <c r="B15" s="25" t="s">
         <v>68</v>
       </c>
@@ -3861,9 +3861,9 @@
         <v>Nova Zelândia</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="97"/>
+        <v>63</v>
+      </c>
+      <c r="F15" s="105"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -3924,22 +3924,22 @@
       <c r="Z15" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="AA15" s="84" t="str">
+      <c r="AA15" s="84">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB15" s="93" t="str">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="93">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC15" s="88" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="103"/>
+      <c r="A16" s="111"/>
       <c r="B16" s="26" t="s">
         <v>69</v>
       </c>
@@ -3954,7 +3954,7 @@
       <c r="E16" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="98"/>
+      <c r="F16" s="106"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4030,7 +4030,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" s="104"/>
+      <c r="A17" s="112"/>
       <c r="B17" s="27" t="s">
         <v>71</v>
       </c>
@@ -4045,7 +4045,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="99"/>
+      <c r="F17" s="107"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4121,7 +4121,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18" s="105">
+      <c r="A18" s="94">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4138,7 +4138,7 @@
       <c r="E18" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="95"/>
+      <c r="F18" s="103"/>
       <c r="G18" s="72"/>
       <c r="H18" s="55"/>
       <c r="I18" s="55"/>
@@ -4174,7 +4174,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="106"/>
+      <c r="A19" s="95"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4189,7 +4189,7 @@
       <c r="E19" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="97"/>
+      <c r="F19" s="105"/>
       <c r="G19" s="63"/>
       <c r="H19" s="71"/>
       <c r="I19" s="71"/>
@@ -4225,7 +4225,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="107"/>
+      <c r="A20" s="96"/>
       <c r="B20" s="29" t="s">
         <v>74</v>
       </c>
@@ -4240,7 +4240,7 @@
       <c r="E20" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="98"/>
+      <c r="F20" s="106"/>
       <c r="G20" s="65"/>
       <c r="H20" s="66"/>
       <c r="I20" s="66"/>
@@ -4276,7 +4276,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" s="108"/>
+      <c r="A21" s="97"/>
       <c r="B21" s="30" t="s">
         <v>75</v>
       </c>
@@ -4291,7 +4291,7 @@
       <c r="E21" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="99"/>
+      <c r="F21" s="107"/>
       <c r="G21" s="74"/>
       <c r="H21" s="75"/>
       <c r="I21" s="75"/>
@@ -4327,7 +4327,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" s="101">
+      <c r="A22" s="109">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4344,7 +4344,7 @@
       <c r="E22" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="95"/>
+      <c r="F22" s="103"/>
       <c r="G22" s="63"/>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -4380,7 +4380,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" s="102"/>
+      <c r="A23" s="110"/>
       <c r="B23" s="25" t="s">
         <v>77</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="E23" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="97"/>
+      <c r="F23" s="105"/>
       <c r="G23" s="63"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -4431,7 +4431,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="103"/>
+      <c r="A24" s="111"/>
       <c r="B24" s="26" t="s">
         <v>78</v>
       </c>
@@ -4446,7 +4446,7 @@
       <c r="E24" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="98"/>
+      <c r="F24" s="106"/>
       <c r="G24" s="65"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
@@ -4482,7 +4482,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25" s="104"/>
+      <c r="A25" s="112"/>
       <c r="B25" s="27" t="s">
         <v>79</v>
       </c>
@@ -4497,7 +4497,7 @@
       <c r="E25" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="99"/>
+      <c r="F25" s="107"/>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -4533,7 +4533,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26" s="105">
+      <c r="A26" s="94">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4550,7 +4550,7 @@
       <c r="E26" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="95"/>
+      <c r="F26" s="103"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4586,7 +4586,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27" s="106"/>
+      <c r="A27" s="95"/>
       <c r="B27" s="28" t="s">
         <v>81</v>
       </c>
@@ -4601,7 +4601,7 @@
       <c r="E27" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="97"/>
+      <c r="F27" s="105"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4637,7 +4637,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" s="107"/>
+      <c r="A28" s="96"/>
       <c r="B28" s="29" t="s">
         <v>82</v>
       </c>
@@ -4652,7 +4652,7 @@
       <c r="E28" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="98"/>
+      <c r="F28" s="106"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4688,7 +4688,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29" s="108"/>
+      <c r="A29" s="97"/>
       <c r="B29" s="30" t="s">
         <v>83</v>
       </c>
@@ -4703,7 +4703,7 @@
       <c r="E29" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="99"/>
+      <c r="F29" s="107"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4739,7 +4739,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30" s="101">
+      <c r="A30" s="109">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -4756,7 +4756,7 @@
       <c r="E30" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="95"/>
+      <c r="F30" s="103"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4792,7 +4792,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A31" s="102"/>
+      <c r="A31" s="110"/>
       <c r="B31" s="25" t="s">
         <v>85</v>
       </c>
@@ -4807,7 +4807,7 @@
       <c r="E31" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F31" s="97"/>
+      <c r="F31" s="105"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4843,7 +4843,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A32" s="103"/>
+      <c r="A32" s="111"/>
       <c r="B32" s="26" t="s">
         <v>86</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="E32" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="98"/>
+      <c r="F32" s="106"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -4894,7 +4894,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A33" s="104"/>
+      <c r="A33" s="112"/>
       <c r="B33" s="27" t="s">
         <v>87</v>
       </c>
@@ -4909,7 +4909,7 @@
       <c r="E33" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F33" s="99"/>
+      <c r="F33" s="107"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -4945,7 +4945,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A34" s="105">
+      <c r="A34" s="94">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -4962,7 +4962,7 @@
       <c r="E34" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F34" s="95"/>
+      <c r="F34" s="103"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -4998,7 +4998,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A35" s="106"/>
+      <c r="A35" s="95"/>
       <c r="B35" s="28" t="s">
         <v>89</v>
       </c>
@@ -5013,7 +5013,7 @@
       <c r="E35" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="97"/>
+      <c r="F35" s="105"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5049,7 +5049,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A36" s="107"/>
+      <c r="A36" s="96"/>
       <c r="B36" s="29" t="s">
         <v>90</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="E36" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="98"/>
+      <c r="F36" s="106"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5100,7 +5100,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A37" s="108"/>
+      <c r="A37" s="97"/>
       <c r="B37" s="30" t="s">
         <v>91</v>
       </c>
@@ -5115,7 +5115,7 @@
       <c r="E37" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F37" s="99"/>
+      <c r="F37" s="107"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5151,7 +5151,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A38" s="101">
+      <c r="A38" s="109">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5168,7 +5168,7 @@
       <c r="E38" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F38" s="95"/>
+      <c r="F38" s="103"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5204,7 +5204,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A39" s="102"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="25" t="s">
         <v>93</v>
       </c>
@@ -5219,7 +5219,7 @@
       <c r="E39" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="97"/>
+      <c r="F39" s="105"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5255,7 +5255,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A40" s="103"/>
+      <c r="A40" s="111"/>
       <c r="B40" s="26" t="s">
         <v>94</v>
       </c>
@@ -5270,7 +5270,7 @@
       <c r="E40" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F40" s="98"/>
+      <c r="F40" s="106"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5306,7 +5306,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A41" s="104"/>
+      <c r="A41" s="112"/>
       <c r="B41" s="27" t="s">
         <v>95</v>
       </c>
@@ -5321,7 +5321,7 @@
       <c r="E41" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F41" s="99"/>
+      <c r="F41" s="107"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5357,7 +5357,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A42" s="105">
+      <c r="A42" s="94">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5374,7 +5374,7 @@
       <c r="E42" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F42" s="95"/>
+      <c r="F42" s="103"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5410,7 +5410,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A43" s="106"/>
+      <c r="A43" s="95"/>
       <c r="B43" s="28" t="s">
         <v>97</v>
       </c>
@@ -5425,7 +5425,7 @@
       <c r="E43" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="97"/>
+      <c r="F43" s="105"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5461,7 +5461,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A44" s="107"/>
+      <c r="A44" s="96"/>
       <c r="B44" s="29" t="s">
         <v>98</v>
       </c>
@@ -5476,7 +5476,7 @@
       <c r="E44" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="98"/>
+      <c r="F44" s="106"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5512,7 +5512,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A45" s="108"/>
+      <c r="A45" s="97"/>
       <c r="B45" s="30" t="s">
         <v>99</v>
       </c>
@@ -5527,7 +5527,7 @@
       <c r="E45" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F45" s="99"/>
+      <c r="F45" s="107"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5563,7 +5563,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A46" s="101">
+      <c r="A46" s="109">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5580,7 +5580,7 @@
       <c r="E46" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="95"/>
+      <c r="F46" s="103"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5616,7 +5616,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A47" s="102"/>
+      <c r="A47" s="110"/>
       <c r="B47" s="25" t="s">
         <v>101</v>
       </c>
@@ -5631,7 +5631,7 @@
       <c r="E47" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="97"/>
+      <c r="F47" s="105"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5667,7 +5667,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A48" s="103"/>
+      <c r="A48" s="111"/>
       <c r="B48" s="26" t="s">
         <v>102</v>
       </c>
@@ -5682,7 +5682,7 @@
       <c r="E48" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F48" s="98"/>
+      <c r="F48" s="106"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5718,7 +5718,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A49" s="104"/>
+      <c r="A49" s="112"/>
       <c r="B49" s="27" t="s">
         <v>103</v>
       </c>
@@ -5733,7 +5733,7 @@
       <c r="E49" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F49" s="99"/>
+      <c r="F49" s="107"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5769,7 +5769,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A50" s="105">
+      <c r="A50" s="94">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -5786,7 +5786,7 @@
       <c r="E50" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F50" s="95"/>
+      <c r="F50" s="103"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5822,7 +5822,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A51" s="106"/>
+      <c r="A51" s="95"/>
       <c r="B51" s="28" t="s">
         <v>105</v>
       </c>
@@ -5837,7 +5837,7 @@
       <c r="E51" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F51" s="97"/>
+      <c r="F51" s="105"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -5873,7 +5873,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A52" s="107"/>
+      <c r="A52" s="96"/>
       <c r="B52" s="29" t="s">
         <v>106</v>
       </c>
@@ -5888,7 +5888,7 @@
       <c r="E52" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F52" s="98"/>
+      <c r="F52" s="106"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -5924,7 +5924,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A53" s="107"/>
+      <c r="A53" s="96"/>
       <c r="B53" s="29" t="s">
         <v>107</v>
       </c>
@@ -5939,7 +5939,7 @@
       <c r="E53" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="98"/>
+      <c r="F53" s="106"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -5975,7 +5975,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A54" s="107"/>
+      <c r="A54" s="96"/>
       <c r="B54" s="29" t="s">
         <v>108</v>
       </c>
@@ -5990,7 +5990,7 @@
       <c r="E54" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F54" s="98"/>
+      <c r="F54" s="106"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6026,7 +6026,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A55" s="108"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="30" t="s">
         <v>109</v>
       </c>
@@ -6041,7 +6041,7 @@
       <c r="E55" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F55" s="99"/>
+      <c r="F55" s="107"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6077,7 +6077,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A56" s="101">
+      <c r="A56" s="109">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6094,7 +6094,7 @@
       <c r="E56" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F56" s="95"/>
+      <c r="F56" s="103"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6130,7 +6130,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A57" s="102"/>
+      <c r="A57" s="110"/>
       <c r="B57" s="25" t="s">
         <v>111</v>
       </c>
@@ -6145,7 +6145,7 @@
       <c r="E57" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F57" s="97"/>
+      <c r="F57" s="105"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6181,7 +6181,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A58" s="103"/>
+      <c r="A58" s="111"/>
       <c r="B58" s="26" t="s">
         <v>112</v>
       </c>
@@ -6196,7 +6196,7 @@
       <c r="E58" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F58" s="98"/>
+      <c r="F58" s="106"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6232,7 +6232,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A59" s="103"/>
+      <c r="A59" s="111"/>
       <c r="B59" s="26" t="s">
         <v>113</v>
       </c>
@@ -6247,7 +6247,7 @@
       <c r="E59" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F59" s="98"/>
+      <c r="F59" s="106"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6283,7 +6283,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A60" s="103"/>
+      <c r="A60" s="111"/>
       <c r="B60" s="26" t="s">
         <v>114</v>
       </c>
@@ -6298,7 +6298,7 @@
       <c r="E60" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F60" s="98"/>
+      <c r="F60" s="106"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6334,7 +6334,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A61" s="104"/>
+      <c r="A61" s="112"/>
       <c r="B61" s="27" t="s">
         <v>115</v>
       </c>
@@ -6349,7 +6349,7 @@
       <c r="E61" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="F61" s="99"/>
+      <c r="F61" s="107"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6385,7 +6385,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A62" s="105">
+      <c r="A62" s="94">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6402,7 +6402,7 @@
       <c r="E62" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="F62" s="95"/>
+      <c r="F62" s="103"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6438,7 +6438,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A63" s="106"/>
+      <c r="A63" s="95"/>
       <c r="B63" s="28" t="s">
         <v>117</v>
       </c>
@@ -6453,7 +6453,7 @@
       <c r="E63" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="97"/>
+      <c r="F63" s="105"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6489,7 +6489,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A64" s="107"/>
+      <c r="A64" s="96"/>
       <c r="B64" s="29" t="s">
         <v>118</v>
       </c>
@@ -6504,7 +6504,7 @@
       <c r="E64" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F64" s="98"/>
+      <c r="F64" s="106"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6540,7 +6540,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A65" s="107"/>
+      <c r="A65" s="96"/>
       <c r="B65" s="29" t="s">
         <v>119</v>
       </c>
@@ -6555,7 +6555,7 @@
       <c r="E65" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F65" s="98"/>
+      <c r="F65" s="106"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6591,7 +6591,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A66" s="107"/>
+      <c r="A66" s="96"/>
       <c r="B66" s="29" t="s">
         <v>120</v>
       </c>
@@ -6606,7 +6606,7 @@
       <c r="E66" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="F66" s="98"/>
+      <c r="F66" s="106"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6642,7 +6642,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A67" s="108"/>
+      <c r="A67" s="97"/>
       <c r="B67" s="30" t="s">
         <v>121</v>
       </c>
@@ -6657,7 +6657,7 @@
       <c r="E67" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="99"/>
+      <c r="F67" s="107"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6693,7 +6693,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A68" s="113">
+      <c r="A68" s="98">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -6710,7 +6710,7 @@
       <c r="E68" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F68" s="95"/>
+      <c r="F68" s="103"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6746,7 +6746,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A69" s="114"/>
+      <c r="A69" s="99"/>
       <c r="B69" s="25" t="s">
         <v>123</v>
       </c>
@@ -6761,7 +6761,7 @@
       <c r="E69" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="F69" s="97"/>
+      <c r="F69" s="105"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6797,7 +6797,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A70" s="115"/>
+      <c r="A70" s="100"/>
       <c r="B70" s="26" t="s">
         <v>124</v>
       </c>
@@ -6812,7 +6812,7 @@
       <c r="E70" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F70" s="98"/>
+      <c r="F70" s="106"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -6848,7 +6848,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A71" s="115"/>
+      <c r="A71" s="100"/>
       <c r="B71" s="26" t="s">
         <v>125</v>
       </c>
@@ -6863,7 +6863,7 @@
       <c r="E71" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F71" s="98"/>
+      <c r="F71" s="106"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -6899,7 +6899,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A72" s="115"/>
+      <c r="A72" s="100"/>
       <c r="B72" s="26" t="s">
         <v>126</v>
       </c>
@@ -6914,7 +6914,7 @@
       <c r="E72" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="98"/>
+      <c r="F72" s="106"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -6950,7 +6950,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A73" s="116"/>
+      <c r="A73" s="101"/>
       <c r="B73" s="31" t="s">
         <v>127</v>
       </c>
@@ -6965,7 +6965,7 @@
       <c r="E73" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="F73" s="100"/>
+      <c r="F73" s="108"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7006,11 +7006,11 @@
       </c>
       <c r="G74" s="77" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H74" s="77" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I74" s="77" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7022,11 +7022,11 @@
       </c>
       <c r="K74" s="77" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L74" s="77" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M74" s="77" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="P74" s="77" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q74" s="77" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="R74" s="77" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S74" s="77" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7087,6 +7087,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
@@ -7103,8 +7105,6 @@
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/CA21BB4BE959536C/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963CBFF1-B10A-4BF6-B9DE-7652654B6E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{972C52A7-688C-49FC-AFD0-BCCB00F98518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="130">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -266,25 +266,28 @@
     <t>Bélgica x Egito</t>
   </si>
   <si>
+    <t>Irã x Nova Zelândia</t>
+  </si>
+  <si>
+    <t>Espanha x Cabo Verde</t>
+  </si>
+  <si>
+    <t>0x0</t>
+  </si>
+  <si>
+    <t>Arábia Saudita x Uruguai</t>
+  </si>
+  <si>
+    <t>França x Senegal</t>
+  </si>
+  <si>
+    <t>3x1</t>
+  </si>
+  <si>
+    <t>Iraque x Noruega</t>
+  </si>
+  <si>
     <t>#x#</t>
-  </si>
-  <si>
-    <t>Irã x Nova Zelândia</t>
-  </si>
-  <si>
-    <t>Espanha x Cabo Verde</t>
-  </si>
-  <si>
-    <t>0x0</t>
-  </si>
-  <si>
-    <t>Arábia Saudita x Uruguai</t>
-  </si>
-  <si>
-    <t>França x Senegal</t>
-  </si>
-  <si>
-    <t>Iraque x Noruega</t>
   </si>
   <si>
     <t>Argentina x Argélia</t>
@@ -456,7 +459,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1484,6 +1487,18 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1516,18 +1531,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1590,19 +1593,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF009C3B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
@@ -1624,6 +1614,19 @@
       </fill>
       <alignment horizontal="center"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF009C3B"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1644,11 +1647,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A4:B20" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1999,13 +2002,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="3" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21">
       <c r="A1" s="117" t="s">
         <v>0</v>
       </c>
@@ -2017,7 +2020,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="117"/>
       <c r="B2" s="117"/>
       <c r="C2" s="13"/>
@@ -2027,7 +2030,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="117"/>
       <c r="B3" s="117"/>
       <c r="C3" s="13"/>
@@ -2037,7 +2040,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="26.1" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -2045,7 +2048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2053,7 +2056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2069,7 +2072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2077,7 +2080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2085,7 +2088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2093,7 +2096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2101,7 +2104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2109,7 +2112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2117,7 +2120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2125,7 +2128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2141,7 +2144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2149,7 +2152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2157,7 +2160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2165,7 +2168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2178,7 +2181,7 @@
     <mergeCell ref="A1:B3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B20">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Ok">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Ok">
       <formula>NOT(ISERROR(SEARCH("Ok",B5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2197,7 +2200,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -2206,7 +2209,7 @@
     <col min="10" max="10" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="118" t="s">
         <v>20</v>
       </c>
@@ -2217,7 +2220,7 @@
       <c r="F1" s="119"/>
       <c r="G1" s="119"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2238,7 +2241,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2265,7 +2268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2287,7 +2290,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2308,7 +2311,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2332,7 +2335,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2356,7 +2359,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2377,7 +2380,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2398,7 +2401,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2419,7 +2422,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2440,7 +2443,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2461,7 +2464,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2482,7 +2485,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2503,7 +2506,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2524,7 +2527,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2561,7 +2564,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="32.42578125" customWidth="1"/>
@@ -2571,7 +2574,7 @@
     <col min="7" max="29" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2587,7 +2590,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="102"/>
+      <c r="F1" s="106"/>
       <c r="G1" s="86" t="s">
         <v>3</v>
       </c>
@@ -2658,7 +2661,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30">
       <c r="A2" s="113">
         <v>46184</v>
       </c>
@@ -2676,7 +2679,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="103"/>
+      <c r="F2" s="107"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2750,7 +2753,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1">
       <c r="A3" s="114"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2766,7 +2769,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="104"/>
+      <c r="F3" s="108"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2840,7 +2843,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30">
       <c r="A4" s="115">
         <v>46185</v>
       </c>
@@ -2858,7 +2861,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="103"/>
+      <c r="F4" s="107"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2933,7 +2936,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30">
       <c r="A5" s="116"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -2949,7 +2952,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="104"/>
+      <c r="F5" s="108"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3024,8 +3027,8 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="109">
+    <row r="6" spans="1:30">
+      <c r="A6" s="98">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3042,7 +3045,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="103"/>
+      <c r="F6" s="107"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3117,8 +3120,8 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
+    <row r="7" spans="1:30">
+      <c r="A7" s="99"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3133,7 +3136,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="105"/>
+      <c r="F7" s="109"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3208,8 +3211,8 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="111"/>
+    <row r="8" spans="1:30">
+      <c r="A8" s="100"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3224,7 +3227,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="106"/>
+      <c r="F8" s="110"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3299,8 +3302,8 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="112"/>
+    <row r="9" spans="1:30">
+      <c r="A9" s="101"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3315,7 +3318,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="107"/>
+      <c r="F9" s="111"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3390,7 +3393,7 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30">
       <c r="A10" s="94">
         <v>46187</v>
       </c>
@@ -3408,7 +3411,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="103"/>
+      <c r="F10" s="107"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3481,7 +3484,7 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30">
       <c r="A11" s="95"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
@@ -3497,7 +3500,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="105"/>
+      <c r="F11" s="109"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3572,7 +3575,7 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30">
       <c r="A12" s="96"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
@@ -3588,7 +3591,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="106"/>
+      <c r="F12" s="110"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3663,7 +3666,7 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30">
       <c r="A13" s="97"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
@@ -3679,7 +3682,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="107"/>
+      <c r="F13" s="111"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3754,8 +3757,8 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="109">
+    <row r="14" spans="1:30">
+      <c r="A14" s="98">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3772,7 +3775,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="103"/>
+      <c r="F14" s="107"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3847,10 +3850,10 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="110"/>
+    <row r="15" spans="1:30">
+      <c r="A15" s="99"/>
       <c r="B15" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15" s="37" t="str">
         <f t="shared" si="0"/>
@@ -3863,7 +3866,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="105"/>
+      <c r="F15" s="109"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -3938,23 +3941,23 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="111"/>
+    <row r="16" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A16" s="100"/>
       <c r="B16" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Espanha</v>
+      </c>
+      <c r="D16" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Cabo Verde</v>
+      </c>
+      <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Espanha</v>
-      </c>
-      <c r="D16" s="38" t="str">
-        <f t="shared" si="1"/>
-        <v>Cabo Verde</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="106"/>
+      <c r="F16" s="110"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4029,10 +4032,10 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" s="112"/>
+    <row r="17" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A17" s="101"/>
       <c r="B17" s="27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" s="39" t="str">
         <f t="shared" si="0"/>
@@ -4045,7 +4048,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="107"/>
+      <c r="F17" s="111"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4120,60 +4123,100 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="15.75" thickBot="1">
       <c r="A18" s="94">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>França</v>
+      </c>
+      <c r="D18" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v>Senegal</v>
+      </c>
+      <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>França</v>
-      </c>
-      <c r="D18" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Senegal</v>
-      </c>
-      <c r="E18" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="103"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="55"/>
-      <c r="U18" s="73"/>
-      <c r="V18" s="73"/>
-      <c r="W18" s="73"/>
-      <c r="X18" s="73"/>
-      <c r="Y18" s="73"/>
-      <c r="Z18" s="79"/>
-      <c r="AA18" s="84" t="str">
+      <c r="F18" s="107"/>
+      <c r="G18" s="72" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="O18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="R18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="S18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="T18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="U18" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="V18" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="W18" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="X18" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y18" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z18" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA18" s="84">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB18" s="93" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="93">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC18" s="88" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30">
       <c r="A19" s="95"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
@@ -4187,29 +4230,69 @@
         <v>Noruega</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" s="105"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
-      <c r="T19" s="71"/>
-      <c r="U19" s="56"/>
-      <c r="V19" s="56"/>
-      <c r="W19" s="56"/>
-      <c r="X19" s="56"/>
-      <c r="Y19" s="56"/>
-      <c r="Z19" s="83"/>
+        <v>74</v>
+      </c>
+      <c r="F19" s="109"/>
+      <c r="G19" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="L19" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="M19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="N19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="R19" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="S19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="T19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="U19" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="V19" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="W19" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="X19" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y19" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" s="83" t="s">
+        <v>45</v>
+      </c>
       <c r="AA19" s="84" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4224,43 +4307,83 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30">
       <c r="A20" s="96"/>
       <c r="B20" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="41" t="str">
+        <f t="shared" si="0"/>
+        <v>Argentina</v>
+      </c>
+      <c r="D20" s="41" t="str">
+        <f t="shared" si="1"/>
+        <v>Argélia</v>
+      </c>
+      <c r="E20" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="41" t="str">
-        <f t="shared" si="0"/>
-        <v>Argentina</v>
-      </c>
-      <c r="D20" s="41" t="str">
-        <f t="shared" si="1"/>
-        <v>Argélia</v>
-      </c>
-      <c r="E20" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F20" s="106"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="66"/>
-      <c r="T20" s="66"/>
-      <c r="U20" s="67"/>
-      <c r="V20" s="67"/>
-      <c r="W20" s="67"/>
-      <c r="X20" s="67"/>
-      <c r="Y20" s="67"/>
-      <c r="Z20" s="81"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="K20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="L20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="M20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="N20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="R20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="S20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="T20" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="U20" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="V20" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W20" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="X20" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y20" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" s="81" t="s">
+        <v>44</v>
+      </c>
       <c r="AA20" s="84" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4275,10 +4398,10 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30">
       <c r="A21" s="97"/>
       <c r="B21" s="30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C21" s="42" t="str">
         <f t="shared" si="0"/>
@@ -4289,29 +4412,69 @@
         <v>Jordânia</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="107"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="75"/>
-      <c r="M21" s="75"/>
-      <c r="N21" s="75"/>
-      <c r="O21" s="75"/>
-      <c r="P21" s="75"/>
-      <c r="Q21" s="75"/>
-      <c r="R21" s="75"/>
-      <c r="S21" s="75"/>
-      <c r="T21" s="75"/>
-      <c r="U21" s="76"/>
-      <c r="V21" s="76"/>
-      <c r="W21" s="76"/>
-      <c r="X21" s="76"/>
-      <c r="Y21" s="76"/>
-      <c r="Z21" s="82"/>
+        <v>74</v>
+      </c>
+      <c r="F21" s="111"/>
+      <c r="G21" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="75" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="75" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="K21" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="M21" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="N21" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q21" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="R21" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="S21" s="75" t="s">
+        <v>46</v>
+      </c>
+      <c r="T21" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="U21" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="V21" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="W21" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="X21" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y21" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" s="82" t="s">
+        <v>44</v>
+      </c>
       <c r="AA21" s="84" t="str">
         <f t="shared" ref="AA21:AA73" si="5">IFERROR(VALUE(TRIM(LEFT($E21,SEARCH("x",$E21)-1))),"")</f>
         <v/>
@@ -4326,12 +4489,12 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" s="109">
+    <row r="22" spans="1:30">
+      <c r="A22" s="98">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="36" t="str">
         <f t="shared" si="0"/>
@@ -4342,9 +4505,9 @@
         <v>Rep. Dem. Congo</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F22" s="107"/>
       <c r="G22" s="63"/>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -4379,10 +4542,10 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" s="110"/>
+    <row r="23" spans="1:30">
+      <c r="A23" s="99"/>
       <c r="B23" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" s="37" t="str">
         <f t="shared" si="0"/>
@@ -4393,9 +4556,9 @@
         <v>Colômbia</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="F23" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F23" s="109"/>
       <c r="G23" s="63"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -4430,10 +4593,10 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="111"/>
+    <row r="24" spans="1:30">
+      <c r="A24" s="100"/>
       <c r="B24" s="26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="38" t="str">
         <f t="shared" si="0"/>
@@ -4444,9 +4607,9 @@
         <v>Croácia</v>
       </c>
       <c r="E24" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F24" s="110"/>
       <c r="G24" s="65"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
@@ -4481,10 +4644,10 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25" s="112"/>
+    <row r="25" spans="1:30">
+      <c r="A25" s="101"/>
       <c r="B25" s="27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" s="39" t="str">
         <f t="shared" si="0"/>
@@ -4495,9 +4658,9 @@
         <v>Panamá</v>
       </c>
       <c r="E25" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="F25" s="107"/>
+        <v>74</v>
+      </c>
+      <c r="F25" s="111"/>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -4532,12 +4695,12 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30">
       <c r="A26" s="94">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C26" s="34" t="str">
         <f t="shared" si="0"/>
@@ -4548,9 +4711,9 @@
         <v>África do Sul</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F26" s="107"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4585,10 +4748,10 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30">
       <c r="A27" s="95"/>
       <c r="B27" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" s="40" t="str">
         <f t="shared" si="0"/>
@@ -4599,9 +4762,9 @@
         <v>Coreia do Sul</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F27" s="109"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4636,10 +4799,10 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30">
       <c r="A28" s="96"/>
       <c r="B28" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" s="41" t="str">
         <f t="shared" si="0"/>
@@ -4650,9 +4813,9 @@
         <v>Bósnia e Herzeg.</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F28" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F28" s="110"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4687,10 +4850,10 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30">
       <c r="A29" s="97"/>
       <c r="B29" s="30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C29" s="42" t="str">
         <f t="shared" si="0"/>
@@ -4701,9 +4864,9 @@
         <v>Catar</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="F29" s="107"/>
+        <v>74</v>
+      </c>
+      <c r="F29" s="111"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4738,12 +4901,12 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30" s="109">
+    <row r="30" spans="1:30">
+      <c r="A30" s="98">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" s="36" t="str">
         <f t="shared" si="0"/>
@@ -4754,9 +4917,9 @@
         <v>Marrocos</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="F30" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F30" s="107"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4791,10 +4954,10 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A31" s="110"/>
+    <row r="31" spans="1:30">
+      <c r="A31" s="99"/>
       <c r="B31" s="25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C31" s="37" t="str">
         <f t="shared" si="0"/>
@@ -4805,9 +4968,9 @@
         <v>Haiti</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F31" s="109"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4842,10 +5005,10 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A32" s="111"/>
+    <row r="32" spans="1:30">
+      <c r="A32" s="100"/>
       <c r="B32" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C32" s="38" t="str">
         <f t="shared" si="0"/>
@@ -4856,9 +5019,9 @@
         <v>Austrália</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="F32" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F32" s="110"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -4893,10 +5056,10 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A33" s="112"/>
+    <row r="33" spans="1:30">
+      <c r="A33" s="101"/>
       <c r="B33" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C33" s="39" t="str">
         <f t="shared" si="0"/>
@@ -4907,9 +5070,9 @@
         <v>Paraguai</v>
       </c>
       <c r="E33" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="F33" s="107"/>
+        <v>74</v>
+      </c>
+      <c r="F33" s="111"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -4944,12 +5107,12 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30">
       <c r="A34" s="94">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C34" s="34" t="str">
         <f t="shared" si="0"/>
@@ -4960,9 +5123,9 @@
         <v>Costa do Marfim</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F34" s="107"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -4997,10 +5160,10 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30">
       <c r="A35" s="95"/>
       <c r="B35" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C35" s="40" t="str">
         <f t="shared" si="0"/>
@@ -5011,9 +5174,9 @@
         <v>Curaçao</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F35" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F35" s="109"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5048,10 +5211,10 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30">
       <c r="A36" s="96"/>
       <c r="B36" s="29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C36" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5062,9 +5225,9 @@
         <v>Suécia</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F36" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F36" s="110"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5099,10 +5262,10 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30">
       <c r="A37" s="97"/>
       <c r="B37" s="30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C37" s="42" t="str">
         <f t="shared" si="0"/>
@@ -5113,9 +5276,9 @@
         <v>Japão</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="107"/>
+        <v>74</v>
+      </c>
+      <c r="F37" s="111"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5150,12 +5313,12 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A38" s="109">
+    <row r="38" spans="1:30">
+      <c r="A38" s="98">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C38" s="36" t="str">
         <f t="shared" si="0"/>
@@ -5166,9 +5329,9 @@
         <v>Irã</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="F38" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F38" s="107"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5203,10 +5366,10 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A39" s="110"/>
+    <row r="39" spans="1:30">
+      <c r="A39" s="99"/>
       <c r="B39" s="25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="37" t="str">
         <f t="shared" si="0"/>
@@ -5217,9 +5380,9 @@
         <v>Egito</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="F39" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F39" s="109"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5254,10 +5417,10 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A40" s="111"/>
+    <row r="40" spans="1:30">
+      <c r="A40" s="100"/>
       <c r="B40" s="26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C40" s="38" t="str">
         <f t="shared" si="0"/>
@@ -5268,9 +5431,9 @@
         <v>Arábia Saudita</v>
       </c>
       <c r="E40" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="F40" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F40" s="110"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5305,10 +5468,10 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A41" s="112"/>
+    <row r="41" spans="1:30">
+      <c r="A41" s="101"/>
       <c r="B41" s="27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="39" t="str">
         <f t="shared" si="0"/>
@@ -5319,9 +5482,9 @@
         <v>Cabo Verde</v>
       </c>
       <c r="E41" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="F41" s="107"/>
+        <v>74</v>
+      </c>
+      <c r="F41" s="111"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5356,12 +5519,12 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30">
       <c r="A42" s="94">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" s="34" t="str">
         <f t="shared" si="0"/>
@@ -5372,10 +5535,12 @@
         <v>Iraque</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="F42" s="103"/>
-      <c r="G42" s="60"/>
+        <v>74</v>
+      </c>
+      <c r="F42" s="107"/>
+      <c r="G42" s="60" t="s">
+        <v>44</v>
+      </c>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
       <c r="J42" s="61"/>
@@ -5409,10 +5574,10 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30">
       <c r="A43" s="95"/>
       <c r="B43" s="28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="40" t="str">
         <f t="shared" si="0"/>
@@ -5423,9 +5588,9 @@
         <v>Senegal</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F43" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F43" s="109"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5460,10 +5625,10 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30">
       <c r="A44" s="96"/>
       <c r="B44" s="29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C44" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5474,9 +5639,9 @@
         <v>Áustria</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F44" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F44" s="110"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5511,10 +5676,10 @@
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30">
       <c r="A45" s="97"/>
       <c r="B45" s="30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="42" t="str">
         <f t="shared" si="0"/>
@@ -5525,9 +5690,9 @@
         <v>Argélia</v>
       </c>
       <c r="E45" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="F45" s="107"/>
+        <v>74</v>
+      </c>
+      <c r="F45" s="111"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5562,12 +5727,12 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A46" s="109">
+    <row r="46" spans="1:30">
+      <c r="A46" s="98">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" s="36" t="str">
         <f t="shared" si="0"/>
@@ -5578,9 +5743,9 @@
         <v>Uzbequistão</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="F46" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F46" s="107"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5615,10 +5780,10 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A47" s="110"/>
+    <row r="47" spans="1:30">
+      <c r="A47" s="99"/>
       <c r="B47" s="25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" s="37" t="str">
         <f t="shared" si="0"/>
@@ -5629,9 +5794,9 @@
         <v>Rep. Dem. Congo</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="F47" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F47" s="109"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5666,10 +5831,10 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A48" s="111"/>
+    <row r="48" spans="1:30">
+      <c r="A48" s="100"/>
       <c r="B48" s="26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C48" s="38" t="str">
         <f t="shared" si="0"/>
@@ -5680,9 +5845,9 @@
         <v>Gana</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="F48" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F48" s="110"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5717,10 +5882,10 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A49" s="112"/>
+    <row r="49" spans="1:30">
+      <c r="A49" s="101"/>
       <c r="B49" s="27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C49" s="39" t="str">
         <f t="shared" si="0"/>
@@ -5731,9 +5896,9 @@
         <v>Croácia</v>
       </c>
       <c r="E49" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="F49" s="107"/>
+        <v>74</v>
+      </c>
+      <c r="F49" s="111"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5768,12 +5933,12 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30">
       <c r="A50" s="94">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C50" s="34" t="str">
         <f t="shared" si="0"/>
@@ -5784,9 +5949,9 @@
         <v>Coreia do Sul</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="F50" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F50" s="107"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5821,10 +5986,10 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30">
       <c r="A51" s="95"/>
       <c r="B51" s="28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C51" s="40" t="str">
         <f t="shared" si="0"/>
@@ -5835,9 +6000,9 @@
         <v>México</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F51" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F51" s="109"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -5872,10 +6037,10 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30">
       <c r="A52" s="96"/>
       <c r="B52" s="29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C52" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5886,9 +6051,9 @@
         <v>Canadá</v>
       </c>
       <c r="E52" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F52" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F52" s="110"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -5923,10 +6088,10 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30">
       <c r="A53" s="96"/>
       <c r="B53" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C53" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5937,9 +6102,9 @@
         <v>Catar</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F53" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F53" s="110"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -5974,10 +6139,10 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30">
       <c r="A54" s="96"/>
       <c r="B54" s="29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C54" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5988,9 +6153,9 @@
         <v>Haiti</v>
       </c>
       <c r="E54" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F54" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F54" s="110"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6025,10 +6190,10 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30">
       <c r="A55" s="97"/>
       <c r="B55" s="30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C55" s="42" t="str">
         <f t="shared" si="0"/>
@@ -6039,9 +6204,9 @@
         <v>Brasil</v>
       </c>
       <c r="E55" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="F55" s="107"/>
+        <v>74</v>
+      </c>
+      <c r="F55" s="111"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6076,12 +6241,12 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A56" s="109">
+    <row r="56" spans="1:30">
+      <c r="A56" s="98">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C56" s="36" t="str">
         <f t="shared" si="0"/>
@@ -6092,9 +6257,9 @@
         <v>Estados Unidos</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="F56" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F56" s="107"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6129,10 +6294,10 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A57" s="110"/>
+    <row r="57" spans="1:30">
+      <c r="A57" s="99"/>
       <c r="B57" s="25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C57" s="37" t="str">
         <f t="shared" si="0"/>
@@ -6143,9 +6308,9 @@
         <v>Austrália</v>
       </c>
       <c r="E57" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="F57" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F57" s="109"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6180,10 +6345,10 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A58" s="111"/>
+    <row r="58" spans="1:30">
+      <c r="A58" s="100"/>
       <c r="B58" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C58" s="38" t="str">
         <f t="shared" si="0"/>
@@ -6194,9 +6359,9 @@
         <v>Costa do Marfim</v>
       </c>
       <c r="E58" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="F58" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F58" s="110"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6231,10 +6396,10 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A59" s="111"/>
+    <row r="59" spans="1:30">
+      <c r="A59" s="100"/>
       <c r="B59" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C59" s="38" t="str">
         <f t="shared" si="0"/>
@@ -6245,9 +6410,9 @@
         <v>Alemanha</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="F59" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F59" s="110"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6282,10 +6447,10 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A60" s="111"/>
+    <row r="60" spans="1:30">
+      <c r="A60" s="100"/>
       <c r="B60" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C60" s="38" t="str">
         <f t="shared" si="0"/>
@@ -6296,9 +6461,9 @@
         <v>Países Baixos</v>
       </c>
       <c r="E60" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="F60" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F60" s="110"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6333,10 +6498,10 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A61" s="112"/>
+    <row r="61" spans="1:30">
+      <c r="A61" s="101"/>
       <c r="B61" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C61" s="39" t="str">
         <f t="shared" si="0"/>
@@ -6347,9 +6512,9 @@
         <v>Suécia</v>
       </c>
       <c r="E61" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="F61" s="107"/>
+        <v>74</v>
+      </c>
+      <c r="F61" s="111"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6384,12 +6549,12 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30">
       <c r="A62" s="94">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C62" s="34" t="str">
         <f t="shared" si="0"/>
@@ -6400,9 +6565,9 @@
         <v>Bélgica</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="F62" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F62" s="107"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6437,10 +6602,10 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30">
       <c r="A63" s="95"/>
       <c r="B63" s="28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C63" s="40" t="str">
         <f t="shared" si="0"/>
@@ -6451,9 +6616,9 @@
         <v>Irã</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F63" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F63" s="109"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6488,10 +6653,10 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30">
       <c r="A64" s="96"/>
       <c r="B64" s="29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C64" s="41" t="str">
         <f t="shared" si="0"/>
@@ -6502,9 +6667,9 @@
         <v>Arábia Saudita</v>
       </c>
       <c r="E64" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F64" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F64" s="110"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6539,10 +6704,10 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30">
       <c r="A65" s="96"/>
       <c r="B65" s="29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C65" s="41" t="str">
         <f t="shared" si="0"/>
@@ -6553,9 +6718,9 @@
         <v>Espanha</v>
       </c>
       <c r="E65" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F65" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F65" s="110"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6590,10 +6755,10 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30">
       <c r="A66" s="96"/>
       <c r="B66" s="29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C66" s="41" t="str">
         <f t="shared" si="0"/>
@@ -6604,9 +6769,9 @@
         <v>França</v>
       </c>
       <c r="E66" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F66" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F66" s="110"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6641,10 +6806,10 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30">
       <c r="A67" s="97"/>
       <c r="B67" s="30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C67" s="42" t="str">
         <f t="shared" ref="C67:C73" si="7">TRIM(LEFT(B67,FIND(" x ",B67)-1))</f>
@@ -6655,9 +6820,9 @@
         <v>Iraque</v>
       </c>
       <c r="E67" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="F67" s="107"/>
+        <v>74</v>
+      </c>
+      <c r="F67" s="111"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6692,12 +6857,12 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A68" s="98">
+    <row r="68" spans="1:30">
+      <c r="A68" s="102">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C68" s="36" t="str">
         <f t="shared" si="7"/>
@@ -6708,9 +6873,9 @@
         <v>Áustria</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="F68" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F68" s="107"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6745,10 +6910,10 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A69" s="99"/>
+    <row r="69" spans="1:30">
+      <c r="A69" s="103"/>
       <c r="B69" s="25" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C69" s="37" t="str">
         <f t="shared" si="7"/>
@@ -6759,9 +6924,9 @@
         <v>Argentina</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="F69" s="105"/>
+        <v>74</v>
+      </c>
+      <c r="F69" s="109"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6796,10 +6961,10 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A70" s="100"/>
+    <row r="70" spans="1:30">
+      <c r="A70" s="104"/>
       <c r="B70" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C70" s="38" t="str">
         <f t="shared" si="7"/>
@@ -6810,9 +6975,9 @@
         <v>Portugal</v>
       </c>
       <c r="E70" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="F70" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F70" s="110"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -6847,10 +7012,10 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A71" s="100"/>
+    <row r="71" spans="1:30">
+      <c r="A71" s="104"/>
       <c r="B71" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C71" s="38" t="str">
         <f t="shared" si="7"/>
@@ -6861,9 +7026,9 @@
         <v>Uzbequistão</v>
       </c>
       <c r="E71" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="F71" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F71" s="110"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -6898,10 +7063,10 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A72" s="100"/>
+    <row r="72" spans="1:30">
+      <c r="A72" s="104"/>
       <c r="B72" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C72" s="38" t="str">
         <f t="shared" si="7"/>
@@ -6912,9 +7077,9 @@
         <v>Inglaterra</v>
       </c>
       <c r="E72" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="F72" s="106"/>
+        <v>74</v>
+      </c>
+      <c r="F72" s="110"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -6949,10 +7114,10 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A73" s="101"/>
+    <row r="73" spans="1:30">
+      <c r="A73" s="105"/>
       <c r="B73" s="31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C73" s="43" t="str">
         <f t="shared" si="7"/>
@@ -6963,9 +7128,9 @@
         <v>Gana</v>
       </c>
       <c r="E73" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="F73" s="108"/>
+        <v>74</v>
+      </c>
+      <c r="F73" s="112"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7000,96 +7165,93 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1">
       <c r="F74" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G74" s="77" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H74" s="77" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I74" s="77" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J74" s="77" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K74" s="77" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L74" s="77" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M74" s="77" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N74" s="77" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O74" s="77" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P74" s="77" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q74" s="77" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R74" s="77" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S74" s="77" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T74" s="77" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U74" s="77" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V74" s="77" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W74" s="77" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X74" s="77" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y74" s="77" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z74" s="77" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7105,6 +7267,9 @@
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/CA21BB4BE959536C/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{972C52A7-688C-49FC-AFD0-BCCB00F98518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC29590-3FC7-428C-B385-229D08412A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="130">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -459,7 +459,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1475,6 +1475,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1486,51 +1531,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1593,6 +1593,19 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF009C3B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
@@ -1614,19 +1627,6 @@
       </fill>
       <alignment horizontal="center"/>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF009C3B"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1647,11 +1647,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A4:B20" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2002,13 +2002,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="3" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="117" t="s">
         <v>0</v>
       </c>
@@ -2020,7 +2020,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="117"/>
       <c r="B2" s="117"/>
       <c r="C2" s="13"/>
@@ -2030,7 +2030,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="117"/>
       <c r="B3" s="117"/>
       <c r="C3" s="13"/>
@@ -2040,7 +2040,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:8" ht="26.1" customHeight="1">
+    <row r="4" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2181,7 +2181,7 @@
     <mergeCell ref="A1:B3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B20">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Ok">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Ok">
       <formula>NOT(ISERROR(SEARCH("Ok",B5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2200,7 +2200,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -2209,7 +2209,7 @@
     <col min="10" max="10" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="118" t="s">
         <v>20</v>
       </c>
@@ -2220,7 +2220,7 @@
       <c r="F1" s="119"/>
       <c r="G1" s="119"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1">
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2268,7 +2268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2311,7 +2311,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2335,7 +2335,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2359,7 +2359,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2380,7 +2380,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2401,7 +2401,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2422,7 +2422,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2443,7 +2443,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2464,7 +2464,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2485,7 +2485,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2506,7 +2506,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2527,7 +2527,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2564,7 +2564,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="32.42578125" customWidth="1"/>
@@ -2574,7 +2574,7 @@
     <col min="7" max="29" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2590,7 +2590,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="106"/>
+      <c r="F1" s="98"/>
       <c r="G1" s="86" t="s">
         <v>3</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="113">
         <v>46184</v>
       </c>
@@ -2679,7 +2679,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="107"/>
+      <c r="F2" s="99"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="114"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2769,7 +2769,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="108"/>
+      <c r="F3" s="100"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="115">
         <v>46185</v>
       </c>
@@ -2861,7 +2861,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="107"/>
+      <c r="F4" s="99"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="116"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -2952,7 +2952,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="108"/>
+      <c r="F5" s="100"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3027,8 +3027,8 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30">
-      <c r="A6" s="98">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" s="105">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3045,7 +3045,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="107"/>
+      <c r="F6" s="99"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3120,8 +3120,8 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30">
-      <c r="A7" s="99"/>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" s="106"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3136,7 +3136,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="109"/>
+      <c r="F7" s="101"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3211,8 +3211,8 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30">
-      <c r="A8" s="100"/>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" s="107"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3227,7 +3227,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="110"/>
+      <c r="F8" s="102"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3302,8 +3302,8 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30">
-      <c r="A9" s="101"/>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" s="108"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3318,7 +3318,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="111"/>
+      <c r="F9" s="103"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3393,8 +3393,8 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30">
-      <c r="A10" s="94">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A10" s="109">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3411,7 +3411,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="107"/>
+      <c r="F10" s="99"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3484,8 +3484,8 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30">
-      <c r="A11" s="95"/>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A11" s="110"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3500,7 +3500,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="109"/>
+      <c r="F11" s="101"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3575,8 +3575,8 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30">
-      <c r="A12" s="96"/>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A12" s="111"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3591,7 +3591,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="110"/>
+      <c r="F12" s="102"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3666,8 +3666,8 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30">
-      <c r="A13" s="97"/>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A13" s="112"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3682,7 +3682,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="111"/>
+      <c r="F13" s="103"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3757,8 +3757,8 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30">
-      <c r="A14" s="98">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A14" s="105">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3775,7 +3775,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="107"/>
+      <c r="F14" s="99"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3850,8 +3850,8 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30">
-      <c r="A15" s="99"/>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A15" s="106"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3866,7 +3866,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="109"/>
+      <c r="F15" s="101"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -3941,8 +3941,8 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A16" s="100"/>
+    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="107"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -3957,7 +3957,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="110"/>
+      <c r="F16" s="102"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4032,8 +4032,8 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A17" s="101"/>
+    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="108"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4048,7 +4048,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="111"/>
+      <c r="F17" s="103"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4123,8 +4123,8 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A18" s="94">
+    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="109">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4141,7 +4141,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="107"/>
+      <c r="F18" s="99"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4216,8 +4216,8 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30">
-      <c r="A19" s="95"/>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A19" s="110"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4232,7 +4232,7 @@
       <c r="E19" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="109"/>
+      <c r="F19" s="101"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4307,8 +4307,8 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30">
-      <c r="A20" s="96"/>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A20" s="111"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4323,7 +4323,7 @@
       <c r="E20" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="110"/>
+      <c r="F20" s="102"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4398,8 +4398,8 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30">
-      <c r="A21" s="97"/>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A21" s="112"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4414,7 +4414,7 @@
       <c r="E21" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="111"/>
+      <c r="F21" s="103"/>
       <c r="G21" s="74" t="s">
         <v>44</v>
       </c>
@@ -4489,8 +4489,8 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30">
-      <c r="A22" s="98">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A22" s="105">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4507,7 +4507,7 @@
       <c r="E22" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="107"/>
+      <c r="F22" s="99"/>
       <c r="G22" s="63"/>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -4542,8 +4542,8 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30">
-      <c r="A23" s="99"/>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A23" s="106"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4558,7 +4558,7 @@
       <c r="E23" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="109"/>
+      <c r="F23" s="101"/>
       <c r="G23" s="63"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -4593,8 +4593,8 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30">
-      <c r="A24" s="100"/>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A24" s="107"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4609,7 +4609,7 @@
       <c r="E24" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F24" s="110"/>
+      <c r="F24" s="102"/>
       <c r="G24" s="65"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
@@ -4644,8 +4644,8 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30">
-      <c r="A25" s="101"/>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A25" s="108"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4660,7 +4660,7 @@
       <c r="E25" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="111"/>
+      <c r="F25" s="103"/>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -4695,8 +4695,8 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30">
-      <c r="A26" s="94">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A26" s="109">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4713,7 +4713,7 @@
       <c r="E26" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="107"/>
+      <c r="F26" s="99"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4748,8 +4748,8 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30">
-      <c r="A27" s="95"/>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A27" s="110"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -4764,7 +4764,7 @@
       <c r="E27" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="109"/>
+      <c r="F27" s="101"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4799,8 +4799,8 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30">
-      <c r="A28" s="96"/>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A28" s="111"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -4815,7 +4815,7 @@
       <c r="E28" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="110"/>
+      <c r="F28" s="102"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4850,8 +4850,8 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30">
-      <c r="A29" s="97"/>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A29" s="112"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -4866,7 +4866,7 @@
       <c r="E29" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="111"/>
+      <c r="F29" s="103"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4901,8 +4901,8 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30">
-      <c r="A30" s="98">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A30" s="105">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -4919,7 +4919,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="107"/>
+      <c r="F30" s="99"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4954,8 +4954,8 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30">
-      <c r="A31" s="99"/>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A31" s="106"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -4970,7 +4970,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="109"/>
+      <c r="F31" s="101"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5005,8 +5005,8 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30">
-      <c r="A32" s="100"/>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A32" s="107"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5021,7 +5021,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="110"/>
+      <c r="F32" s="102"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5056,8 +5056,8 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30">
-      <c r="A33" s="101"/>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A33" s="108"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5072,7 +5072,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="111"/>
+      <c r="F33" s="103"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5107,8 +5107,8 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30">
-      <c r="A34" s="94">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A34" s="109">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5125,7 +5125,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="107"/>
+      <c r="F34" s="99"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5160,8 +5160,8 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30">
-      <c r="A35" s="95"/>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A35" s="110"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="109"/>
+      <c r="F35" s="101"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5211,8 +5211,8 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30">
-      <c r="A36" s="96"/>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A36" s="111"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5227,7 +5227,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="110"/>
+      <c r="F36" s="102"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5262,8 +5262,8 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30">
-      <c r="A37" s="97"/>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A37" s="112"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5278,7 +5278,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="111"/>
+      <c r="F37" s="103"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5313,8 +5313,8 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30">
-      <c r="A38" s="98">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A38" s="105">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5331,7 +5331,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="107"/>
+      <c r="F38" s="99"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5366,8 +5366,8 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30">
-      <c r="A39" s="99"/>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A39" s="106"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5382,7 +5382,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="109"/>
+      <c r="F39" s="101"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5417,8 +5417,8 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30">
-      <c r="A40" s="100"/>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A40" s="107"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5433,7 +5433,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="110"/>
+      <c r="F40" s="102"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5468,8 +5468,8 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30">
-      <c r="A41" s="101"/>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A41" s="108"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5484,7 +5484,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="111"/>
+      <c r="F41" s="103"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5519,8 +5519,8 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30">
-      <c r="A42" s="94">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A42" s="109">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5537,10 +5537,8 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="107"/>
-      <c r="G42" s="60" t="s">
-        <v>44</v>
-      </c>
+      <c r="F42" s="99"/>
+      <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
       <c r="J42" s="61"/>
@@ -5574,8 +5572,8 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30">
-      <c r="A43" s="95"/>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A43" s="110"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5590,7 +5588,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="109"/>
+      <c r="F43" s="101"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5625,8 +5623,8 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30">
-      <c r="A44" s="96"/>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A44" s="111"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -5641,7 +5639,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="110"/>
+      <c r="F44" s="102"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5676,8 +5674,8 @@
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30">
-      <c r="A45" s="97"/>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A45" s="112"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -5692,7 +5690,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="111"/>
+      <c r="F45" s="103"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5727,8 +5725,8 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30">
-      <c r="A46" s="98">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A46" s="105">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5745,7 +5743,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="107"/>
+      <c r="F46" s="99"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5780,8 +5778,8 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30">
-      <c r="A47" s="99"/>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A47" s="106"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -5796,7 +5794,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="109"/>
+      <c r="F47" s="101"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5831,8 +5829,8 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30">
-      <c r="A48" s="100"/>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A48" s="107"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -5847,7 +5845,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="110"/>
+      <c r="F48" s="102"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5882,8 +5880,8 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30">
-      <c r="A49" s="101"/>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A49" s="108"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -5898,7 +5896,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="111"/>
+      <c r="F49" s="103"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5933,8 +5931,8 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30">
-      <c r="A50" s="94">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A50" s="109">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -5951,7 +5949,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="107"/>
+      <c r="F50" s="99"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5986,8 +5984,8 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30">
-      <c r="A51" s="95"/>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A51" s="110"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6002,7 +6000,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="109"/>
+      <c r="F51" s="101"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6037,8 +6035,8 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30">
-      <c r="A52" s="96"/>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A52" s="111"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6053,7 +6051,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="110"/>
+      <c r="F52" s="102"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6088,8 +6086,8 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30">
-      <c r="A53" s="96"/>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A53" s="111"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6104,7 +6102,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="110"/>
+      <c r="F53" s="102"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6139,8 +6137,8 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30">
-      <c r="A54" s="96"/>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A54" s="111"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6155,7 +6153,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="110"/>
+      <c r="F54" s="102"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6190,8 +6188,8 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30">
-      <c r="A55" s="97"/>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A55" s="112"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6206,7 +6204,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="111"/>
+      <c r="F55" s="103"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6241,8 +6239,8 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30">
-      <c r="A56" s="98">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A56" s="105">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6259,7 +6257,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="107"/>
+      <c r="F56" s="99"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6294,8 +6292,8 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30">
-      <c r="A57" s="99"/>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A57" s="106"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6310,7 +6308,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="109"/>
+      <c r="F57" s="101"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6345,8 +6343,8 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30">
-      <c r="A58" s="100"/>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A58" s="107"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6361,7 +6359,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="110"/>
+      <c r="F58" s="102"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6396,8 +6394,8 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30">
-      <c r="A59" s="100"/>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A59" s="107"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6412,7 +6410,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="110"/>
+      <c r="F59" s="102"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6447,8 +6445,8 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30">
-      <c r="A60" s="100"/>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A60" s="107"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6463,7 +6461,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="110"/>
+      <c r="F60" s="102"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6498,8 +6496,8 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30">
-      <c r="A61" s="101"/>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A61" s="108"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6514,7 +6512,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="111"/>
+      <c r="F61" s="103"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6549,8 +6547,8 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30">
-      <c r="A62" s="94">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A62" s="109">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6567,7 +6565,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="107"/>
+      <c r="F62" s="99"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6602,8 +6600,8 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30">
-      <c r="A63" s="95"/>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A63" s="110"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -6618,7 +6616,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="109"/>
+      <c r="F63" s="101"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6653,8 +6651,8 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30">
-      <c r="A64" s="96"/>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A64" s="111"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -6669,7 +6667,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="110"/>
+      <c r="F64" s="102"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6704,8 +6702,8 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30">
-      <c r="A65" s="96"/>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A65" s="111"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -6720,7 +6718,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="110"/>
+      <c r="F65" s="102"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6755,8 +6753,8 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30">
-      <c r="A66" s="96"/>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A66" s="111"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -6771,7 +6769,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="110"/>
+      <c r="F66" s="102"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6806,8 +6804,8 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30">
-      <c r="A67" s="97"/>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A67" s="112"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -6822,7 +6820,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="111"/>
+      <c r="F67" s="103"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6857,8 +6855,8 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30">
-      <c r="A68" s="102">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A68" s="94">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -6875,7 +6873,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="107"/>
+      <c r="F68" s="99"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6910,8 +6908,8 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30">
-      <c r="A69" s="103"/>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A69" s="95"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -6926,7 +6924,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="109"/>
+      <c r="F69" s="101"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6961,8 +6959,8 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30">
-      <c r="A70" s="104"/>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A70" s="96"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -6977,7 +6975,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="110"/>
+      <c r="F70" s="102"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7012,8 +7010,8 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30">
-      <c r="A71" s="104"/>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A71" s="96"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7028,7 +7026,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="110"/>
+      <c r="F71" s="102"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7063,8 +7061,8 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30">
-      <c r="A72" s="104"/>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A72" s="96"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7079,7 +7077,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="110"/>
+      <c r="F72" s="102"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7114,8 +7112,8 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30">
-      <c r="A73" s="105"/>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A73" s="97"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7130,7 +7128,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="112"/>
+      <c r="F73" s="104"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7165,7 +7163,7 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F74" s="19" t="s">
         <v>129</v>
       </c>
@@ -7252,6 +7250,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7268,8 +7268,6 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC29590-3FC7-428C-B385-229D08412A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C0FB85-E5B5-4450-A283-F9DE1DF6E1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -1475,6 +1475,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1507,30 +1531,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2590,7 +2590,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="98"/>
+      <c r="F1" s="106"/>
       <c r="G1" s="86" t="s">
         <v>3</v>
       </c>
@@ -2679,7 +2679,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="99"/>
+      <c r="F2" s="107"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2769,7 +2769,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="108"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2861,7 +2861,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="99"/>
+      <c r="F4" s="107"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2952,7 +2952,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="100"/>
+      <c r="F5" s="108"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="105">
+      <c r="A6" s="94">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3045,7 +3045,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="99"/>
+      <c r="F6" s="107"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3121,7 +3121,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="106"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3136,7 +3136,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="101"/>
+      <c r="F7" s="109"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3212,7 +3212,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
+      <c r="A8" s="96"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3227,7 +3227,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="102"/>
+      <c r="F8" s="110"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3303,7 +3303,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="108"/>
+      <c r="A9" s="97"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3318,7 +3318,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="103"/>
+      <c r="F9" s="111"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3394,7 +3394,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="109">
+      <c r="A10" s="98">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3411,7 +3411,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="99"/>
+      <c r="F10" s="107"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3485,7 +3485,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="110"/>
+      <c r="A11" s="99"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3500,7 +3500,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="101"/>
+      <c r="F11" s="109"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3576,7 +3576,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="111"/>
+      <c r="A12" s="100"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3591,7 +3591,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="102"/>
+      <c r="F12" s="110"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3667,7 +3667,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="112"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3682,7 +3682,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="103"/>
+      <c r="F13" s="111"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3758,7 +3758,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="105">
+      <c r="A14" s="94">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3775,7 +3775,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="99"/>
+      <c r="F14" s="107"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3851,7 +3851,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="106"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3866,7 +3866,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="101"/>
+      <c r="F15" s="109"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -3942,7 +3942,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="107"/>
+      <c r="A16" s="96"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -3957,7 +3957,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="102"/>
+      <c r="F16" s="110"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4033,7 +4033,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="108"/>
+      <c r="A17" s="97"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4048,7 +4048,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="103"/>
+      <c r="F17" s="111"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4124,7 +4124,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109">
+      <c r="A18" s="98">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4141,7 +4141,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="99"/>
+      <c r="F18" s="107"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4217,7 +4217,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="110"/>
+      <c r="A19" s="99"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4232,66 +4232,66 @@
       <c r="E19" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="101"/>
+      <c r="F19" s="109"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
       <c r="H19" s="71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I19" s="71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J19" s="71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K19" s="71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L19" s="71" t="s">
         <v>46</v>
       </c>
       <c r="M19" s="71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N19" s="71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O19" s="71" t="s">
         <v>46</v>
       </c>
       <c r="P19" s="71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q19" s="71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R19" s="71" t="s">
         <v>46</v>
       </c>
       <c r="S19" s="71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T19" s="71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U19" s="56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V19" s="56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W19" s="56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X19" s="56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y19" s="56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z19" s="83" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA19" s="84" t="str">
         <f t="shared" si="2"/>
@@ -4308,7 +4308,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="111"/>
+      <c r="A20" s="100"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4323,7 +4323,7 @@
       <c r="E20" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="102"/>
+      <c r="F20" s="110"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4399,7 +4399,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" s="112"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4414,7 +4414,7 @@
       <c r="E21" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="103"/>
+      <c r="F21" s="111"/>
       <c r="G21" s="74" t="s">
         <v>44</v>
       </c>
@@ -4490,7 +4490,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" s="105">
+      <c r="A22" s="94">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4507,7 +4507,7 @@
       <c r="E22" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="99"/>
+      <c r="F22" s="107"/>
       <c r="G22" s="63"/>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -4543,7 +4543,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" s="106"/>
+      <c r="A23" s="95"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4558,7 +4558,7 @@
       <c r="E23" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="101"/>
+      <c r="F23" s="109"/>
       <c r="G23" s="63"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -4594,7 +4594,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="107"/>
+      <c r="A24" s="96"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4609,7 +4609,7 @@
       <c r="E24" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F24" s="102"/>
+      <c r="F24" s="110"/>
       <c r="G24" s="65"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
@@ -4645,7 +4645,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25" s="108"/>
+      <c r="A25" s="97"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4660,7 +4660,7 @@
       <c r="E25" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="103"/>
+      <c r="F25" s="111"/>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -4696,7 +4696,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26" s="109">
+      <c r="A26" s="98">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4713,7 +4713,7 @@
       <c r="E26" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="99"/>
+      <c r="F26" s="107"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4749,7 +4749,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27" s="110"/>
+      <c r="A27" s="99"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -4764,7 +4764,7 @@
       <c r="E27" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="101"/>
+      <c r="F27" s="109"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4800,7 +4800,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" s="111"/>
+      <c r="A28" s="100"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -4815,7 +4815,7 @@
       <c r="E28" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="102"/>
+      <c r="F28" s="110"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4851,7 +4851,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29" s="112"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -4866,7 +4866,7 @@
       <c r="E29" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="103"/>
+      <c r="F29" s="111"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4902,7 +4902,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30" s="105">
+      <c r="A30" s="94">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -4919,7 +4919,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="99"/>
+      <c r="F30" s="107"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4955,7 +4955,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A31" s="106"/>
+      <c r="A31" s="95"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -4970,7 +4970,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="101"/>
+      <c r="F31" s="109"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5006,7 +5006,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A32" s="107"/>
+      <c r="A32" s="96"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5021,7 +5021,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="102"/>
+      <c r="F32" s="110"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5057,7 +5057,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A33" s="108"/>
+      <c r="A33" s="97"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5072,7 +5072,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="103"/>
+      <c r="F33" s="111"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5108,7 +5108,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A34" s="109">
+      <c r="A34" s="98">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5125,7 +5125,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="99"/>
+      <c r="F34" s="107"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5161,7 +5161,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A35" s="110"/>
+      <c r="A35" s="99"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="101"/>
+      <c r="F35" s="109"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5212,7 +5212,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A36" s="111"/>
+      <c r="A36" s="100"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5227,7 +5227,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="102"/>
+      <c r="F36" s="110"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5263,7 +5263,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A37" s="112"/>
+      <c r="A37" s="101"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5278,7 +5278,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="103"/>
+      <c r="F37" s="111"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5314,7 +5314,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A38" s="105">
+      <c r="A38" s="94">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5331,7 +5331,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="99"/>
+      <c r="F38" s="107"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5367,7 +5367,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A39" s="106"/>
+      <c r="A39" s="95"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5382,7 +5382,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="101"/>
+      <c r="F39" s="109"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5418,7 +5418,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A40" s="107"/>
+      <c r="A40" s="96"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5433,7 +5433,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="102"/>
+      <c r="F40" s="110"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5469,7 +5469,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A41" s="108"/>
+      <c r="A41" s="97"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5484,7 +5484,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="103"/>
+      <c r="F41" s="111"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5520,7 +5520,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A42" s="109">
+      <c r="A42" s="98">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5537,7 +5537,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="99"/>
+      <c r="F42" s="107"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5573,7 +5573,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A43" s="110"/>
+      <c r="A43" s="99"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5588,7 +5588,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="101"/>
+      <c r="F43" s="109"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5624,7 +5624,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A44" s="111"/>
+      <c r="A44" s="100"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -5639,7 +5639,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="102"/>
+      <c r="F44" s="110"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5675,7 +5675,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A45" s="112"/>
+      <c r="A45" s="101"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -5690,7 +5690,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="103"/>
+      <c r="F45" s="111"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5726,7 +5726,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A46" s="105">
+      <c r="A46" s="94">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5743,7 +5743,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="99"/>
+      <c r="F46" s="107"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5779,7 +5779,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A47" s="106"/>
+      <c r="A47" s="95"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -5794,7 +5794,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="101"/>
+      <c r="F47" s="109"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5830,7 +5830,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A48" s="107"/>
+      <c r="A48" s="96"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -5845,7 +5845,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="102"/>
+      <c r="F48" s="110"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5881,7 +5881,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A49" s="108"/>
+      <c r="A49" s="97"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -5896,7 +5896,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="103"/>
+      <c r="F49" s="111"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5932,7 +5932,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A50" s="109">
+      <c r="A50" s="98">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -5949,7 +5949,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="99"/>
+      <c r="F50" s="107"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5985,7 +5985,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A51" s="110"/>
+      <c r="A51" s="99"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6000,7 +6000,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="101"/>
+      <c r="F51" s="109"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6036,7 +6036,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A52" s="111"/>
+      <c r="A52" s="100"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6051,7 +6051,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="102"/>
+      <c r="F52" s="110"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6087,7 +6087,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A53" s="111"/>
+      <c r="A53" s="100"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6102,7 +6102,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="102"/>
+      <c r="F53" s="110"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6138,7 +6138,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A54" s="111"/>
+      <c r="A54" s="100"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6153,7 +6153,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="102"/>
+      <c r="F54" s="110"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6189,7 +6189,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A55" s="112"/>
+      <c r="A55" s="101"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6204,7 +6204,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="103"/>
+      <c r="F55" s="111"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6240,7 +6240,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A56" s="105">
+      <c r="A56" s="94">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6257,7 +6257,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="99"/>
+      <c r="F56" s="107"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6293,7 +6293,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A57" s="106"/>
+      <c r="A57" s="95"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6308,7 +6308,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="101"/>
+      <c r="F57" s="109"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6344,7 +6344,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A58" s="107"/>
+      <c r="A58" s="96"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6359,7 +6359,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="102"/>
+      <c r="F58" s="110"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6395,7 +6395,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A59" s="107"/>
+      <c r="A59" s="96"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6410,7 +6410,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="102"/>
+      <c r="F59" s="110"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6446,7 +6446,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A60" s="107"/>
+      <c r="A60" s="96"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6461,7 +6461,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="102"/>
+      <c r="F60" s="110"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6497,7 +6497,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A61" s="108"/>
+      <c r="A61" s="97"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6512,7 +6512,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="103"/>
+      <c r="F61" s="111"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6548,7 +6548,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A62" s="109">
+      <c r="A62" s="98">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6565,7 +6565,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="99"/>
+      <c r="F62" s="107"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6601,7 +6601,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A63" s="110"/>
+      <c r="A63" s="99"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -6616,7 +6616,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="101"/>
+      <c r="F63" s="109"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6652,7 +6652,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A64" s="111"/>
+      <c r="A64" s="100"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -6667,7 +6667,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="102"/>
+      <c r="F64" s="110"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6703,7 +6703,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A65" s="111"/>
+      <c r="A65" s="100"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -6718,7 +6718,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="102"/>
+      <c r="F65" s="110"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6754,7 +6754,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A66" s="111"/>
+      <c r="A66" s="100"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -6769,7 +6769,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="102"/>
+      <c r="F66" s="110"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6805,7 +6805,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A67" s="112"/>
+      <c r="A67" s="101"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -6820,7 +6820,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="103"/>
+      <c r="F67" s="111"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6856,7 +6856,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A68" s="94">
+      <c r="A68" s="102">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -6873,7 +6873,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="99"/>
+      <c r="F68" s="107"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6909,7 +6909,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A69" s="95"/>
+      <c r="A69" s="103"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -6924,7 +6924,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="101"/>
+      <c r="F69" s="109"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6960,7 +6960,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A70" s="96"/>
+      <c r="A70" s="104"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -6975,7 +6975,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="102"/>
+      <c r="F70" s="110"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7011,7 +7011,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A71" s="96"/>
+      <c r="A71" s="104"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7026,7 +7026,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="102"/>
+      <c r="F71" s="110"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7062,7 +7062,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A72" s="96"/>
+      <c r="A72" s="104"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7077,7 +7077,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="102"/>
+      <c r="F72" s="110"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7113,7 +7113,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A73" s="97"/>
+      <c r="A73" s="105"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7128,7 +7128,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="104"/>
+      <c r="F73" s="112"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7250,6 +7250,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
@@ -7266,8 +7268,6 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C0FB85-E5B5-4450-A283-F9DE1DF6E1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD9291C-A334-4D5D-A298-7D6AE437C585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="131">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -453,6 +453,9 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>1x4</t>
   </si>
 </sst>
 </file>
@@ -4230,7 +4233,7 @@
         <v>Noruega</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="F19" s="109"/>
       <c r="G19" s="63" t="s">
@@ -4293,17 +4296,17 @@
       <c r="Z19" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="AA19" s="84" t="str">
+      <c r="AA19" s="84">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB19" s="93" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="93">
         <f t="shared" si="3"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AC19" s="88" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD19" s="54"/>
     </row>
@@ -7173,19 +7176,19 @@
       </c>
       <c r="H74" s="77" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I74" s="77" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J74" s="77" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K74" s="77" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L74" s="77" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7193,11 +7196,11 @@
       </c>
       <c r="M74" s="77" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N74" s="77" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O74" s="77" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7205,7 +7208,7 @@
       </c>
       <c r="P74" s="77" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q74" s="77" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7217,31 +7220,31 @@
       </c>
       <c r="S74" s="77" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T74" s="77" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U74" s="77" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V74" s="77" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W74" s="77" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X74" s="77" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y74" s="77" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z74" s="77" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7250,11 +7253,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -7268,6 +7266,11 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:Z20">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD9291C-A334-4D5D-A298-7D6AE437C585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4307025-BFA7-4252-B86B-F1E2C6AEF3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="132">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -456,13 +456,16 @@
   </si>
   <si>
     <t>1x4</t>
+  </si>
+  <si>
+    <t>3x0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -565,8 +568,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -612,6 +635,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1213,7 +1248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1418,15 +1453,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1478,6 +1504,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1502,6 +1549,18 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1514,39 +1573,6 @@
     <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1554,13 +1580,53 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1650,11 +1716,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A4:B20" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2012,10 +2078,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
+      <c r="B1" s="114"/>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
@@ -2024,8 +2090,8 @@
       <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="117"/>
-      <c r="B2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="114"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
@@ -2034,8 +2100,8 @@
       <c r="H2" s="13"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="117"/>
-      <c r="B3" s="117"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="114"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
@@ -2184,7 +2250,7 @@
     <mergeCell ref="A1:B3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B20">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Ok">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Ok">
       <formula>NOT(ISERROR(SEARCH("Ok",B5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2213,15 +2279,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -2556,7 +2622,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:E17">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$E4=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2593,79 +2659,79 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="106"/>
-      <c r="G1" s="86" t="s">
+      <c r="F1" s="91"/>
+      <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="85" t="s">
+      <c r="H1" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="85" t="s">
+      <c r="I1" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="85" t="s">
+      <c r="J1" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="85" t="s">
+      <c r="K1" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="85" t="s">
+      <c r="L1" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="85" t="s">
+      <c r="M1" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="85" t="s">
+      <c r="N1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="85" t="s">
+      <c r="O1" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="85" t="s">
+      <c r="P1" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="85" t="s">
+      <c r="Q1" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="85" t="s">
+      <c r="R1" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="85" t="s">
+      <c r="S1" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="85" t="s">
+      <c r="T1" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="85" t="s">
+      <c r="U1" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="85" t="s">
+      <c r="V1" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="85" t="s">
+      <c r="W1" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="85" t="s">
+      <c r="X1" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="85" t="s">
+      <c r="Y1" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="85" t="s">
+      <c r="Z1" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="87" t="s">
+      <c r="AA1" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="AB1" s="87" t="s">
+      <c r="AB1" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="AC1" s="89" t="s">
+      <c r="AC1" s="86" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="113">
+      <c r="A2" s="106">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2682,7 +2748,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="107"/>
+      <c r="F2" s="92"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2740,24 +2806,24 @@
       <c r="Y2" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="Z2" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="78">
+      <c r="Z2" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA2" s="75">
         <f>IFERROR(VALUE(TRIM(LEFT($E2,SEARCH("x",$E2)-1))),"")</f>
         <v>2</v>
       </c>
-      <c r="AB2" s="92">
+      <c r="AB2" s="89">
         <f>IFERROR(VALUE(TRIM(MID($E2,SEARCH("x",$E2)+1,10))),"")</f>
         <v>0</v>
       </c>
-      <c r="AC2" s="90" t="str">
+      <c r="AC2" s="87" t="str">
         <f>IF(OR($AA2="",$AB2=""),"",IF($AA2&gt;$AB2,"A",IF($AA2&lt;$AB2,"B","E")))</f>
         <v>A</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="114"/>
+      <c r="A3" s="107"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2772,7 +2838,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="108"/>
+      <c r="F3" s="93"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2830,24 +2896,24 @@
       <c r="Y3" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="80" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" s="84">
+      <c r="Z3" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA3" s="81">
         <f t="shared" ref="AA3:AA20" si="2">IFERROR(VALUE(TRIM(LEFT($E3,SEARCH("x",$E3)-1))),"")</f>
         <v>2</v>
       </c>
-      <c r="AB3" s="93">
+      <c r="AB3" s="90">
         <f t="shared" ref="AB3:AB20" si="3">IFERROR(VALUE(TRIM(MID($E3,SEARCH("x",$E3)+1,10))),"")</f>
         <v>1</v>
       </c>
-      <c r="AC3" s="88" t="str">
+      <c r="AC3" s="85" t="str">
         <f>IF(OR($AA3="",$AB3=""),"",IF($AA3&gt;$AB3,"A",IF($AA3&lt;$AB3,"B","E")))</f>
         <v>A</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="115">
+      <c r="A4" s="108">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2864,7 +2930,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="107"/>
+      <c r="F4" s="92"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2922,25 +2988,25 @@
       <c r="Y4" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="Z4" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" s="84">
+      <c r="Z4" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA4" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB4" s="93">
+      <c r="AB4" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC4" s="88" t="str">
+      <c r="AC4" s="85" t="str">
         <f t="shared" ref="AC4:AC67" si="4">IF(OR($AA4="",$AB4=""),"",IF($AA4&gt;$AB4,"A",IF($AA4&lt;$AB4,"B","E")))</f>
         <v>E</v>
       </c>
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="116"/>
+      <c r="A5" s="109"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -2955,7 +3021,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="108"/>
+      <c r="F5" s="93"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3013,25 +3079,25 @@
       <c r="Y5" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="Z5" s="80" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA5" s="84">
+      <c r="Z5" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA5" s="81">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AB5" s="93">
+      <c r="AB5" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC5" s="88" t="str">
+      <c r="AC5" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="94">
+      <c r="A6" s="98">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3048,7 +3114,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="107"/>
+      <c r="F6" s="92"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3106,25 +3172,25 @@
       <c r="Y6" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="Z6" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" s="84">
+      <c r="Z6" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA6" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB6" s="93">
+      <c r="AB6" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC6" s="88" t="str">
+      <c r="AC6" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="95"/>
+      <c r="A7" s="99"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3139,7 +3205,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="109"/>
+      <c r="F7" s="94"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3200,22 +3266,22 @@
       <c r="Z7" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="AA7" s="84">
+      <c r="AA7" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB7" s="93">
+      <c r="AB7" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC7" s="88" t="str">
+      <c r="AC7" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="96"/>
+      <c r="A8" s="100"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3230,7 +3296,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="110"/>
+      <c r="F8" s="95"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3288,25 +3354,25 @@
       <c r="Y8" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="Z8" s="81" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA8" s="84">
+      <c r="Z8" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA8" s="81">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB8" s="93">
+      <c r="AB8" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC8" s="88" t="str">
+      <c r="AC8" s="85" t="str">
         <f t="shared" si="4"/>
         <v>B</v>
       </c>
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="97"/>
+      <c r="A9" s="101"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3321,7 +3387,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="111"/>
+      <c r="F9" s="96"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3379,25 +3445,25 @@
       <c r="Y9" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="Z9" s="82" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA9" s="84">
+      <c r="Z9" s="79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA9" s="81">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AB9" s="93">
+      <c r="AB9" s="90">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC9" s="88" t="str">
+      <c r="AC9" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="98">
+      <c r="A10" s="102">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3414,7 +3480,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="107"/>
+      <c r="F10" s="92"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3470,25 +3536,25 @@
       <c r="Y10" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="Z10" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA10" s="84">
+      <c r="Z10" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA10" s="81">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="AB10" s="93">
+      <c r="AB10" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC10" s="88" t="str">
+      <c r="AC10" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="99"/>
+      <c r="A11" s="103"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3503,7 +3569,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="109"/>
+      <c r="F11" s="94"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3561,25 +3627,25 @@
       <c r="Y11" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="Z11" s="83" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA11" s="84">
+      <c r="Z11" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA11" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB11" s="93">
+      <c r="AB11" s="90">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC11" s="88" t="str">
+      <c r="AC11" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="100"/>
+      <c r="A12" s="104"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3594,7 +3660,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="110"/>
+      <c r="F12" s="95"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3652,25 +3718,25 @@
       <c r="Y12" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="Z12" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA12" s="84">
+      <c r="Z12" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA12" s="81">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AB12" s="93">
+      <c r="AB12" s="90">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="AC12" s="88" t="str">
+      <c r="AC12" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="101"/>
+      <c r="A13" s="105"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3685,7 +3751,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="111"/>
+      <c r="F13" s="96"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3743,25 +3809,25 @@
       <c r="Y13" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="Z13" s="82" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA13" s="84">
+      <c r="Z13" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA13" s="81">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="AB13" s="93">
+      <c r="AB13" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC13" s="88" t="str">
+      <c r="AC13" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="94">
+      <c r="A14" s="98">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3778,7 +3844,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="107"/>
+      <c r="F14" s="92"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3839,22 +3905,22 @@
       <c r="Z14" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="AA14" s="84">
+      <c r="AA14" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB14" s="93">
+      <c r="AB14" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC14" s="88" t="str">
+      <c r="AC14" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="95"/>
+      <c r="A15" s="99"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3869,7 +3935,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="109"/>
+      <c r="F15" s="94"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -3927,25 +3993,25 @@
       <c r="Y15" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="Z15" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA15" s="84">
+      <c r="Z15" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA15" s="81">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AB15" s="93">
+      <c r="AB15" s="90">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="AC15" s="88" t="str">
+      <c r="AC15" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="96"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -3960,7 +4026,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="110"/>
+      <c r="F16" s="95"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4021,22 +4087,22 @@
       <c r="Z16" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="AA16" s="84">
+      <c r="AA16" s="81">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB16" s="93">
+      <c r="AB16" s="90">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC16" s="88" t="str">
+      <c r="AC16" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="97"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4051,7 +4117,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="111"/>
+      <c r="F17" s="96"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4112,22 +4178,22 @@
       <c r="Z17" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="AA17" s="84">
+      <c r="AA17" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB17" s="93">
+      <c r="AB17" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC17" s="88" t="str">
+      <c r="AC17" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="98">
+      <c r="A18" s="102">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4144,7 +4210,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="107"/>
+      <c r="F18" s="92"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4202,25 +4268,25 @@
       <c r="Y18" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="Z18" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA18" s="84">
+      <c r="Z18" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA18" s="81">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="AB18" s="93">
+      <c r="AB18" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC18" s="88" t="str">
+      <c r="AC18" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="99"/>
+      <c r="A19" s="103"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4235,7 +4301,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="109"/>
+      <c r="F19" s="94"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4293,25 +4359,25 @@
       <c r="Y19" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="Z19" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA19" s="84">
+      <c r="Z19" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA19" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB19" s="93">
+      <c r="AB19" s="90">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="AC19" s="88" t="str">
+      <c r="AC19" s="85" t="str">
         <f t="shared" si="4"/>
         <v>B</v>
       </c>
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="100"/>
+      <c r="A20" s="104"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4324,9 +4390,9 @@
         <v>Argélia</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20" s="110"/>
+        <v>131</v>
+      </c>
+      <c r="F20" s="95"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4384,25 +4450,25 @@
       <c r="Y20" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="Z20" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA20" s="84" t="str">
+      <c r="Z20" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA20" s="81">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB20" s="93" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="90">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AC20" s="88" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" s="101"/>
+      <c r="A21" s="105"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4415,85 +4481,85 @@
         <v>Jordânia</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="111"/>
-      <c r="G21" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="96"/>
+      <c r="G21" s="117" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="I21" s="75" t="s">
+      <c r="I21" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="J21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="K21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="L21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="M21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="N21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="O21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="P21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="R21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="S21" s="75" t="s">
+      <c r="J21" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="K21" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="M21" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="N21" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q21" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="R21" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="S21" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="T21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="U21" s="76" t="s">
-        <v>44</v>
-      </c>
-      <c r="V21" s="76" t="s">
+      <c r="T21" s="119" t="s">
+        <v>44</v>
+      </c>
+      <c r="U21" s="120" t="s">
+        <v>44</v>
+      </c>
+      <c r="V21" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="W21" s="76" t="s">
-        <v>44</v>
-      </c>
-      <c r="X21" s="76" t="s">
+      <c r="W21" s="120" t="s">
+        <v>44</v>
+      </c>
+      <c r="X21" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="Y21" s="76" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z21" s="82" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA21" s="84" t="str">
+      <c r="Y21" s="120" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" s="122" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA21" s="81">
         <f t="shared" ref="AA21:AA73" si="5">IFERROR(VALUE(TRIM(LEFT($E21,SEARCH("x",$E21)-1))),"")</f>
-        <v/>
-      </c>
-      <c r="AB21" s="93" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="90">
         <f t="shared" ref="AB21:AB73" si="6">IFERROR(VALUE(TRIM(MID($E21,SEARCH("x",$E21)+1,10))),"")</f>
-        <v/>
-      </c>
-      <c r="AC21" s="88" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" s="94">
+    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="98">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4510,7 +4576,7 @@
       <c r="E22" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="107"/>
+      <c r="F22" s="92"/>
       <c r="G22" s="63"/>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -4530,23 +4596,23 @@
       <c r="W22" s="56"/>
       <c r="X22" s="56"/>
       <c r="Y22" s="56"/>
-      <c r="Z22" s="79"/>
-      <c r="AA22" s="84" t="str">
+      <c r="Z22" s="76"/>
+      <c r="AA22" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB22" s="93" t="str">
+      <c r="AB22" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC22" s="88" t="str">
+      <c r="AC22" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" s="95"/>
+    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="99"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4558,10 +4624,10 @@
         <f t="shared" si="1"/>
         <v>Colômbia</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="109"/>
+      <c r="F23" s="94"/>
       <c r="G23" s="63"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -4581,23 +4647,23 @@
       <c r="W23" s="56"/>
       <c r="X23" s="56"/>
       <c r="Y23" s="56"/>
-      <c r="Z23" s="83"/>
-      <c r="AA23" s="84" t="str">
+      <c r="Z23" s="80"/>
+      <c r="AA23" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB23" s="93" t="str">
+      <c r="AB23" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC23" s="88" t="str">
+      <c r="AC23" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="96"/>
+    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="100"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4609,10 +4675,10 @@
         <f t="shared" si="1"/>
         <v>Croácia</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F24" s="110"/>
+      <c r="F24" s="95"/>
       <c r="G24" s="65"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
@@ -4632,23 +4698,23 @@
       <c r="W24" s="67"/>
       <c r="X24" s="67"/>
       <c r="Y24" s="67"/>
-      <c r="Z24" s="81"/>
-      <c r="AA24" s="84" t="str">
+      <c r="Z24" s="78"/>
+      <c r="AA24" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB24" s="93" t="str">
+      <c r="AB24" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC24" s="88" t="str">
+      <c r="AC24" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A25" s="97"/>
+    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="101"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4660,10 +4726,10 @@
         <f t="shared" si="1"/>
         <v>Panamá</v>
       </c>
-      <c r="E25" s="49" t="s">
+      <c r="E25" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="111"/>
+      <c r="F25" s="96"/>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
       <c r="I25" s="69"/>
@@ -4683,23 +4749,23 @@
       <c r="W25" s="70"/>
       <c r="X25" s="70"/>
       <c r="Y25" s="70"/>
-      <c r="Z25" s="82"/>
-      <c r="AA25" s="84" t="str">
+      <c r="Z25" s="79"/>
+      <c r="AA25" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB25" s="93" t="str">
+      <c r="AB25" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC25" s="88" t="str">
+      <c r="AC25" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A26" s="98">
+    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="102">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4713,10 +4779,10 @@
         <f t="shared" si="1"/>
         <v>África do Sul</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="107"/>
+      <c r="F26" s="92"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4736,23 +4802,23 @@
       <c r="W26" s="62"/>
       <c r="X26" s="62"/>
       <c r="Y26" s="62"/>
-      <c r="Z26" s="79"/>
-      <c r="AA26" s="84" t="str">
+      <c r="Z26" s="76"/>
+      <c r="AA26" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB26" s="93" t="str">
+      <c r="AB26" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC26" s="88" t="str">
+      <c r="AC26" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A27" s="99"/>
+    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="103"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -4764,10 +4830,10 @@
         <f t="shared" si="1"/>
         <v>Coreia do Sul</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="109"/>
+      <c r="F27" s="94"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4787,23 +4853,23 @@
       <c r="W27" s="56"/>
       <c r="X27" s="56"/>
       <c r="Y27" s="56"/>
-      <c r="Z27" s="83"/>
-      <c r="AA27" s="84" t="str">
+      <c r="Z27" s="80"/>
+      <c r="AA27" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB27" s="93" t="str">
+      <c r="AB27" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC27" s="88" t="str">
+      <c r="AC27" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A28" s="100"/>
+    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="104"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -4815,10 +4881,10 @@
         <f t="shared" si="1"/>
         <v>Bósnia e Herzeg.</v>
       </c>
-      <c r="E28" s="51" t="s">
+      <c r="E28" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="110"/>
+      <c r="F28" s="95"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4838,23 +4904,23 @@
       <c r="W28" s="67"/>
       <c r="X28" s="67"/>
       <c r="Y28" s="67"/>
-      <c r="Z28" s="81"/>
-      <c r="AA28" s="84" t="str">
+      <c r="Z28" s="78"/>
+      <c r="AA28" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB28" s="93" t="str">
+      <c r="AB28" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC28" s="88" t="str">
+      <c r="AC28" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29" s="101"/>
+    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="105"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -4866,10 +4932,10 @@
         <f t="shared" si="1"/>
         <v>Catar</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="111"/>
+      <c r="F29" s="96"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4889,23 +4955,23 @@
       <c r="W29" s="70"/>
       <c r="X29" s="70"/>
       <c r="Y29" s="70"/>
-      <c r="Z29" s="82"/>
-      <c r="AA29" s="84" t="str">
+      <c r="Z29" s="79"/>
+      <c r="AA29" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB29" s="93" t="str">
+      <c r="AB29" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC29" s="88" t="str">
+      <c r="AC29" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30" s="94">
+    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="98">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -4922,7 +4988,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="107"/>
+      <c r="F30" s="92"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4942,23 +5008,23 @@
       <c r="W30" s="62"/>
       <c r="X30" s="62"/>
       <c r="Y30" s="62"/>
-      <c r="Z30" s="79"/>
-      <c r="AA30" s="84" t="str">
+      <c r="Z30" s="76"/>
+      <c r="AA30" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB30" s="93" t="str">
+      <c r="AB30" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC30" s="88" t="str">
+      <c r="AC30" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A31" s="95"/>
+      <c r="A31" s="99"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -4973,7 +5039,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="109"/>
+      <c r="F31" s="94"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4993,23 +5059,23 @@
       <c r="W31" s="56"/>
       <c r="X31" s="56"/>
       <c r="Y31" s="56"/>
-      <c r="Z31" s="83"/>
-      <c r="AA31" s="84" t="str">
+      <c r="Z31" s="80"/>
+      <c r="AA31" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB31" s="93" t="str">
+      <c r="AB31" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC31" s="88" t="str">
+      <c r="AC31" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A32" s="96"/>
+      <c r="A32" s="100"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5024,7 +5090,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="110"/>
+      <c r="F32" s="95"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5044,23 +5110,23 @@
       <c r="W32" s="67"/>
       <c r="X32" s="67"/>
       <c r="Y32" s="67"/>
-      <c r="Z32" s="81"/>
-      <c r="AA32" s="84" t="str">
+      <c r="Z32" s="78"/>
+      <c r="AA32" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB32" s="93" t="str">
+      <c r="AB32" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC32" s="88" t="str">
+      <c r="AC32" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A33" s="97"/>
+      <c r="A33" s="101"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5075,7 +5141,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="111"/>
+      <c r="F33" s="96"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5095,23 +5161,23 @@
       <c r="W33" s="70"/>
       <c r="X33" s="70"/>
       <c r="Y33" s="70"/>
-      <c r="Z33" s="82"/>
-      <c r="AA33" s="84" t="str">
+      <c r="Z33" s="79"/>
+      <c r="AA33" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB33" s="93" t="str">
+      <c r="AB33" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC33" s="88" t="str">
+      <c r="AC33" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A34" s="98">
+      <c r="A34" s="102">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5128,7 +5194,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="107"/>
+      <c r="F34" s="92"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5148,23 +5214,23 @@
       <c r="W34" s="62"/>
       <c r="X34" s="62"/>
       <c r="Y34" s="62"/>
-      <c r="Z34" s="79"/>
-      <c r="AA34" s="84" t="str">
+      <c r="Z34" s="76"/>
+      <c r="AA34" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB34" s="93" t="str">
+      <c r="AB34" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC34" s="88" t="str">
+      <c r="AC34" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A35" s="99"/>
+      <c r="A35" s="103"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5179,7 +5245,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="109"/>
+      <c r="F35" s="94"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5199,23 +5265,23 @@
       <c r="W35" s="56"/>
       <c r="X35" s="56"/>
       <c r="Y35" s="56"/>
-      <c r="Z35" s="83"/>
-      <c r="AA35" s="84" t="str">
+      <c r="Z35" s="80"/>
+      <c r="AA35" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB35" s="93" t="str">
+      <c r="AB35" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC35" s="88" t="str">
+      <c r="AC35" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A36" s="100"/>
+      <c r="A36" s="104"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5230,7 +5296,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="110"/>
+      <c r="F36" s="95"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5250,23 +5316,23 @@
       <c r="W36" s="67"/>
       <c r="X36" s="67"/>
       <c r="Y36" s="67"/>
-      <c r="Z36" s="81"/>
-      <c r="AA36" s="84" t="str">
+      <c r="Z36" s="78"/>
+      <c r="AA36" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB36" s="93" t="str">
+      <c r="AB36" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC36" s="88" t="str">
+      <c r="AC36" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A37" s="101"/>
+      <c r="A37" s="105"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5281,7 +5347,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="111"/>
+      <c r="F37" s="96"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5301,23 +5367,23 @@
       <c r="W37" s="70"/>
       <c r="X37" s="70"/>
       <c r="Y37" s="70"/>
-      <c r="Z37" s="82"/>
-      <c r="AA37" s="84" t="str">
+      <c r="Z37" s="79"/>
+      <c r="AA37" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB37" s="93" t="str">
+      <c r="AB37" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC37" s="88" t="str">
+      <c r="AC37" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A38" s="94">
+      <c r="A38" s="98">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5334,7 +5400,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="107"/>
+      <c r="F38" s="92"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5354,23 +5420,23 @@
       <c r="W38" s="62"/>
       <c r="X38" s="62"/>
       <c r="Y38" s="62"/>
-      <c r="Z38" s="79"/>
-      <c r="AA38" s="84" t="str">
+      <c r="Z38" s="76"/>
+      <c r="AA38" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB38" s="93" t="str">
+      <c r="AB38" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC38" s="88" t="str">
+      <c r="AC38" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A39" s="95"/>
+      <c r="A39" s="99"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5385,7 +5451,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="109"/>
+      <c r="F39" s="94"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5405,23 +5471,23 @@
       <c r="W39" s="56"/>
       <c r="X39" s="56"/>
       <c r="Y39" s="56"/>
-      <c r="Z39" s="83"/>
-      <c r="AA39" s="84" t="str">
+      <c r="Z39" s="80"/>
+      <c r="AA39" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB39" s="93" t="str">
+      <c r="AB39" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC39" s="88" t="str">
+      <c r="AC39" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A40" s="96"/>
+      <c r="A40" s="100"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5436,7 +5502,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="110"/>
+      <c r="F40" s="95"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5456,23 +5522,23 @@
       <c r="W40" s="67"/>
       <c r="X40" s="67"/>
       <c r="Y40" s="67"/>
-      <c r="Z40" s="81"/>
-      <c r="AA40" s="84" t="str">
+      <c r="Z40" s="78"/>
+      <c r="AA40" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB40" s="93" t="str">
+      <c r="AB40" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC40" s="88" t="str">
+      <c r="AC40" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A41" s="97"/>
+      <c r="A41" s="101"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5487,7 +5553,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="111"/>
+      <c r="F41" s="96"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5507,23 +5573,23 @@
       <c r="W41" s="70"/>
       <c r="X41" s="70"/>
       <c r="Y41" s="70"/>
-      <c r="Z41" s="82"/>
-      <c r="AA41" s="84" t="str">
+      <c r="Z41" s="79"/>
+      <c r="AA41" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB41" s="93" t="str">
+      <c r="AB41" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC41" s="88" t="str">
+      <c r="AC41" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A42" s="98">
+      <c r="A42" s="102">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5540,7 +5606,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="107"/>
+      <c r="F42" s="92"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5560,23 +5626,23 @@
       <c r="W42" s="62"/>
       <c r="X42" s="62"/>
       <c r="Y42" s="62"/>
-      <c r="Z42" s="79"/>
-      <c r="AA42" s="84" t="str">
+      <c r="Z42" s="76"/>
+      <c r="AA42" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB42" s="93" t="str">
+      <c r="AB42" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC42" s="88" t="str">
+      <c r="AC42" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A43" s="99"/>
+      <c r="A43" s="103"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5591,7 +5657,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="109"/>
+      <c r="F43" s="94"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5611,23 +5677,23 @@
       <c r="W43" s="56"/>
       <c r="X43" s="56"/>
       <c r="Y43" s="56"/>
-      <c r="Z43" s="83"/>
-      <c r="AA43" s="84" t="str">
+      <c r="Z43" s="80"/>
+      <c r="AA43" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB43" s="93" t="str">
+      <c r="AB43" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC43" s="88" t="str">
+      <c r="AC43" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A44" s="100"/>
+      <c r="A44" s="104"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -5642,7 +5708,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="110"/>
+      <c r="F44" s="95"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5662,23 +5728,23 @@
       <c r="W44" s="67"/>
       <c r="X44" s="67"/>
       <c r="Y44" s="67"/>
-      <c r="Z44" s="81"/>
-      <c r="AA44" s="84" t="str">
+      <c r="Z44" s="78"/>
+      <c r="AA44" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB44" s="93" t="str">
+      <c r="AB44" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC44" s="88" t="str">
+      <c r="AC44" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A45" s="101"/>
+      <c r="A45" s="105"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -5693,7 +5759,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="111"/>
+      <c r="F45" s="96"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5713,23 +5779,23 @@
       <c r="W45" s="70"/>
       <c r="X45" s="70"/>
       <c r="Y45" s="70"/>
-      <c r="Z45" s="82"/>
-      <c r="AA45" s="84" t="str">
+      <c r="Z45" s="79"/>
+      <c r="AA45" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB45" s="93" t="str">
+      <c r="AB45" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC45" s="88" t="str">
+      <c r="AC45" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A46" s="94">
+      <c r="A46" s="98">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5746,7 +5812,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="107"/>
+      <c r="F46" s="92"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5766,23 +5832,23 @@
       <c r="W46" s="62"/>
       <c r="X46" s="62"/>
       <c r="Y46" s="62"/>
-      <c r="Z46" s="79"/>
-      <c r="AA46" s="84" t="str">
+      <c r="Z46" s="76"/>
+      <c r="AA46" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB46" s="93" t="str">
+      <c r="AB46" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC46" s="88" t="str">
+      <c r="AC46" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A47" s="95"/>
+      <c r="A47" s="99"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -5797,7 +5863,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="109"/>
+      <c r="F47" s="94"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5817,23 +5883,23 @@
       <c r="W47" s="56"/>
       <c r="X47" s="56"/>
       <c r="Y47" s="56"/>
-      <c r="Z47" s="83"/>
-      <c r="AA47" s="84" t="str">
+      <c r="Z47" s="80"/>
+      <c r="AA47" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB47" s="93" t="str">
+      <c r="AB47" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC47" s="88" t="str">
+      <c r="AC47" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A48" s="96"/>
+      <c r="A48" s="100"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -5848,7 +5914,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="110"/>
+      <c r="F48" s="95"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5868,23 +5934,23 @@
       <c r="W48" s="67"/>
       <c r="X48" s="67"/>
       <c r="Y48" s="67"/>
-      <c r="Z48" s="81"/>
-      <c r="AA48" s="84" t="str">
+      <c r="Z48" s="78"/>
+      <c r="AA48" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB48" s="93" t="str">
+      <c r="AB48" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC48" s="88" t="str">
+      <c r="AC48" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A49" s="97"/>
+      <c r="A49" s="101"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -5899,7 +5965,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="111"/>
+      <c r="F49" s="96"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5919,23 +5985,23 @@
       <c r="W49" s="70"/>
       <c r="X49" s="70"/>
       <c r="Y49" s="70"/>
-      <c r="Z49" s="82"/>
-      <c r="AA49" s="84" t="str">
+      <c r="Z49" s="79"/>
+      <c r="AA49" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB49" s="93" t="str">
+      <c r="AB49" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC49" s="88" t="str">
+      <c r="AC49" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A50" s="98">
+      <c r="A50" s="102">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -5952,7 +6018,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="107"/>
+      <c r="F50" s="92"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5972,23 +6038,23 @@
       <c r="W50" s="62"/>
       <c r="X50" s="62"/>
       <c r="Y50" s="62"/>
-      <c r="Z50" s="79"/>
-      <c r="AA50" s="84" t="str">
+      <c r="Z50" s="76"/>
+      <c r="AA50" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB50" s="93" t="str">
+      <c r="AB50" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC50" s="88" t="str">
+      <c r="AC50" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A51" s="99"/>
+      <c r="A51" s="103"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6003,7 +6069,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="109"/>
+      <c r="F51" s="94"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6023,23 +6089,23 @@
       <c r="W51" s="56"/>
       <c r="X51" s="56"/>
       <c r="Y51" s="56"/>
-      <c r="Z51" s="83"/>
-      <c r="AA51" s="84" t="str">
+      <c r="Z51" s="80"/>
+      <c r="AA51" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB51" s="93" t="str">
+      <c r="AB51" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC51" s="88" t="str">
+      <c r="AC51" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A52" s="100"/>
+      <c r="A52" s="104"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6054,7 +6120,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="110"/>
+      <c r="F52" s="95"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6074,23 +6140,23 @@
       <c r="W52" s="67"/>
       <c r="X52" s="67"/>
       <c r="Y52" s="67"/>
-      <c r="Z52" s="81"/>
-      <c r="AA52" s="84" t="str">
+      <c r="Z52" s="78"/>
+      <c r="AA52" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB52" s="93" t="str">
+      <c r="AB52" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC52" s="88" t="str">
+      <c r="AC52" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A53" s="100"/>
+      <c r="A53" s="104"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6105,7 +6171,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="110"/>
+      <c r="F53" s="95"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6125,23 +6191,23 @@
       <c r="W53" s="67"/>
       <c r="X53" s="67"/>
       <c r="Y53" s="67"/>
-      <c r="Z53" s="81"/>
-      <c r="AA53" s="84" t="str">
+      <c r="Z53" s="78"/>
+      <c r="AA53" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB53" s="93" t="str">
+      <c r="AB53" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC53" s="88" t="str">
+      <c r="AC53" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A54" s="100"/>
+      <c r="A54" s="104"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6156,7 +6222,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="110"/>
+      <c r="F54" s="95"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6176,23 +6242,23 @@
       <c r="W54" s="67"/>
       <c r="X54" s="67"/>
       <c r="Y54" s="67"/>
-      <c r="Z54" s="81"/>
-      <c r="AA54" s="84" t="str">
+      <c r="Z54" s="78"/>
+      <c r="AA54" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB54" s="93" t="str">
+      <c r="AB54" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC54" s="88" t="str">
+      <c r="AC54" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A55" s="101"/>
+      <c r="A55" s="105"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6207,7 +6273,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="111"/>
+      <c r="F55" s="96"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6227,23 +6293,23 @@
       <c r="W55" s="70"/>
       <c r="X55" s="70"/>
       <c r="Y55" s="70"/>
-      <c r="Z55" s="82"/>
-      <c r="AA55" s="84" t="str">
+      <c r="Z55" s="79"/>
+      <c r="AA55" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB55" s="93" t="str">
+      <c r="AB55" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC55" s="88" t="str">
+      <c r="AC55" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A56" s="94">
+      <c r="A56" s="98">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6260,7 +6326,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="107"/>
+      <c r="F56" s="92"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6280,23 +6346,23 @@
       <c r="W56" s="62"/>
       <c r="X56" s="62"/>
       <c r="Y56" s="62"/>
-      <c r="Z56" s="79"/>
-      <c r="AA56" s="84" t="str">
+      <c r="Z56" s="76"/>
+      <c r="AA56" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB56" s="93" t="str">
+      <c r="AB56" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC56" s="88" t="str">
+      <c r="AC56" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A57" s="95"/>
+      <c r="A57" s="99"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6311,7 +6377,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="109"/>
+      <c r="F57" s="94"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6331,23 +6397,23 @@
       <c r="W57" s="56"/>
       <c r="X57" s="56"/>
       <c r="Y57" s="56"/>
-      <c r="Z57" s="83"/>
-      <c r="AA57" s="84" t="str">
+      <c r="Z57" s="80"/>
+      <c r="AA57" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB57" s="93" t="str">
+      <c r="AB57" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC57" s="88" t="str">
+      <c r="AC57" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A58" s="96"/>
+      <c r="A58" s="100"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6362,7 +6428,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="110"/>
+      <c r="F58" s="95"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6382,23 +6448,23 @@
       <c r="W58" s="67"/>
       <c r="X58" s="67"/>
       <c r="Y58" s="67"/>
-      <c r="Z58" s="81"/>
-      <c r="AA58" s="84" t="str">
+      <c r="Z58" s="78"/>
+      <c r="AA58" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB58" s="93" t="str">
+      <c r="AB58" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC58" s="88" t="str">
+      <c r="AC58" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A59" s="96"/>
+      <c r="A59" s="100"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6413,7 +6479,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="110"/>
+      <c r="F59" s="95"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6433,23 +6499,23 @@
       <c r="W59" s="67"/>
       <c r="X59" s="67"/>
       <c r="Y59" s="67"/>
-      <c r="Z59" s="81"/>
-      <c r="AA59" s="84" t="str">
+      <c r="Z59" s="78"/>
+      <c r="AA59" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB59" s="93" t="str">
+      <c r="AB59" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC59" s="88" t="str">
+      <c r="AC59" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A60" s="96"/>
+      <c r="A60" s="100"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6464,7 +6530,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="110"/>
+      <c r="F60" s="95"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6484,23 +6550,23 @@
       <c r="W60" s="67"/>
       <c r="X60" s="67"/>
       <c r="Y60" s="67"/>
-      <c r="Z60" s="81"/>
-      <c r="AA60" s="84" t="str">
+      <c r="Z60" s="78"/>
+      <c r="AA60" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB60" s="93" t="str">
+      <c r="AB60" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC60" s="88" t="str">
+      <c r="AC60" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A61" s="97"/>
+      <c r="A61" s="101"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6515,7 +6581,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="111"/>
+      <c r="F61" s="96"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6535,23 +6601,23 @@
       <c r="W61" s="70"/>
       <c r="X61" s="70"/>
       <c r="Y61" s="70"/>
-      <c r="Z61" s="82"/>
-      <c r="AA61" s="84" t="str">
+      <c r="Z61" s="79"/>
+      <c r="AA61" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB61" s="93" t="str">
+      <c r="AB61" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC61" s="88" t="str">
+      <c r="AC61" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A62" s="98">
+      <c r="A62" s="102">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6568,7 +6634,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="107"/>
+      <c r="F62" s="92"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6588,23 +6654,23 @@
       <c r="W62" s="62"/>
       <c r="X62" s="62"/>
       <c r="Y62" s="62"/>
-      <c r="Z62" s="79"/>
-      <c r="AA62" s="84" t="str">
+      <c r="Z62" s="76"/>
+      <c r="AA62" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB62" s="93" t="str">
+      <c r="AB62" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC62" s="88" t="str">
+      <c r="AC62" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A63" s="99"/>
+      <c r="A63" s="103"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -6619,7 +6685,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="109"/>
+      <c r="F63" s="94"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6639,23 +6705,23 @@
       <c r="W63" s="56"/>
       <c r="X63" s="56"/>
       <c r="Y63" s="56"/>
-      <c r="Z63" s="83"/>
-      <c r="AA63" s="84" t="str">
+      <c r="Z63" s="80"/>
+      <c r="AA63" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB63" s="93" t="str">
+      <c r="AB63" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC63" s="88" t="str">
+      <c r="AC63" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A64" s="100"/>
+      <c r="A64" s="104"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -6670,7 +6736,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="110"/>
+      <c r="F64" s="95"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6690,23 +6756,23 @@
       <c r="W64" s="67"/>
       <c r="X64" s="67"/>
       <c r="Y64" s="67"/>
-      <c r="Z64" s="81"/>
-      <c r="AA64" s="84" t="str">
+      <c r="Z64" s="78"/>
+      <c r="AA64" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB64" s="93" t="str">
+      <c r="AB64" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC64" s="88" t="str">
+      <c r="AC64" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A65" s="100"/>
+      <c r="A65" s="104"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -6721,7 +6787,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="110"/>
+      <c r="F65" s="95"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6741,23 +6807,23 @@
       <c r="W65" s="67"/>
       <c r="X65" s="67"/>
       <c r="Y65" s="67"/>
-      <c r="Z65" s="81"/>
-      <c r="AA65" s="84" t="str">
+      <c r="Z65" s="78"/>
+      <c r="AA65" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB65" s="93" t="str">
+      <c r="AB65" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC65" s="88" t="str">
+      <c r="AC65" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A66" s="100"/>
+      <c r="A66" s="104"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -6772,7 +6838,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="110"/>
+      <c r="F66" s="95"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6792,23 +6858,23 @@
       <c r="W66" s="67"/>
       <c r="X66" s="67"/>
       <c r="Y66" s="67"/>
-      <c r="Z66" s="81"/>
-      <c r="AA66" s="84" t="str">
+      <c r="Z66" s="78"/>
+      <c r="AA66" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB66" s="93" t="str">
+      <c r="AB66" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC66" s="88" t="str">
+      <c r="AC66" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A67" s="101"/>
+      <c r="A67" s="105"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -6823,7 +6889,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="111"/>
+      <c r="F67" s="96"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6843,23 +6909,23 @@
       <c r="W67" s="70"/>
       <c r="X67" s="70"/>
       <c r="Y67" s="70"/>
-      <c r="Z67" s="82"/>
-      <c r="AA67" s="84" t="str">
+      <c r="Z67" s="79"/>
+      <c r="AA67" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB67" s="93" t="str">
+      <c r="AB67" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC67" s="88" t="str">
+      <c r="AC67" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A68" s="102">
+      <c r="A68" s="110">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -6876,7 +6942,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="107"/>
+      <c r="F68" s="92"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6896,23 +6962,23 @@
       <c r="W68" s="62"/>
       <c r="X68" s="62"/>
       <c r="Y68" s="62"/>
-      <c r="Z68" s="79"/>
-      <c r="AA68" s="84" t="str">
+      <c r="Z68" s="76"/>
+      <c r="AA68" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB68" s="93" t="str">
+      <c r="AB68" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC68" s="88" t="str">
+      <c r="AC68" s="85" t="str">
         <f t="shared" ref="AC68:AC73" si="9">IF(OR($AA68="",$AB68=""),"",IF($AA68&gt;$AB68,"A",IF($AA68&lt;$AB68,"B","E")))</f>
         <v/>
       </c>
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A69" s="103"/>
+      <c r="A69" s="111"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -6927,7 +6993,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="109"/>
+      <c r="F69" s="94"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6947,23 +7013,23 @@
       <c r="W69" s="56"/>
       <c r="X69" s="56"/>
       <c r="Y69" s="56"/>
-      <c r="Z69" s="83"/>
-      <c r="AA69" s="84" t="str">
+      <c r="Z69" s="80"/>
+      <c r="AA69" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB69" s="93" t="str">
+      <c r="AB69" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC69" s="88" t="str">
+      <c r="AC69" s="85" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A70" s="104"/>
+      <c r="A70" s="112"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -6978,7 +7044,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="110"/>
+      <c r="F70" s="95"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -6998,23 +7064,23 @@
       <c r="W70" s="67"/>
       <c r="X70" s="67"/>
       <c r="Y70" s="67"/>
-      <c r="Z70" s="81"/>
-      <c r="AA70" s="84" t="str">
+      <c r="Z70" s="78"/>
+      <c r="AA70" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB70" s="93" t="str">
+      <c r="AB70" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC70" s="88" t="str">
+      <c r="AC70" s="85" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A71" s="104"/>
+      <c r="A71" s="112"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7029,7 +7095,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="110"/>
+      <c r="F71" s="95"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7049,23 +7115,23 @@
       <c r="W71" s="67"/>
       <c r="X71" s="67"/>
       <c r="Y71" s="67"/>
-      <c r="Z71" s="81"/>
-      <c r="AA71" s="84" t="str">
+      <c r="Z71" s="78"/>
+      <c r="AA71" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB71" s="93" t="str">
+      <c r="AB71" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC71" s="88" t="str">
+      <c r="AC71" s="85" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A72" s="104"/>
+      <c r="A72" s="112"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7080,7 +7146,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="110"/>
+      <c r="F72" s="95"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7100,23 +7166,23 @@
       <c r="W72" s="67"/>
       <c r="X72" s="67"/>
       <c r="Y72" s="67"/>
-      <c r="Z72" s="81"/>
-      <c r="AA72" s="84" t="str">
+      <c r="Z72" s="78"/>
+      <c r="AA72" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB72" s="93" t="str">
+      <c r="AB72" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC72" s="88" t="str">
+      <c r="AC72" s="85" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A73" s="105"/>
+      <c r="A73" s="113"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7131,7 +7197,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="112"/>
+      <c r="F73" s="97"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7151,16 +7217,16 @@
       <c r="W73" s="70"/>
       <c r="X73" s="70"/>
       <c r="Y73" s="70"/>
-      <c r="Z73" s="82"/>
-      <c r="AA73" s="84" t="str">
+      <c r="Z73" s="79"/>
+      <c r="AA73" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB73" s="93" t="str">
+      <c r="AB73" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC73" s="91" t="str">
+      <c r="AC73" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7170,89 +7236,91 @@
       <c r="F74" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="G74" s="77" cm="1">
+      <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="H74" s="74" cm="1">
+        <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="I74" s="74" cm="1">
+        <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="J74" s="74" cm="1">
+        <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>12</v>
+      </c>
+      <c r="K74" s="74" cm="1">
+        <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="L74" s="74" cm="1">
+        <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>9</v>
+      </c>
+      <c r="M74" s="74" cm="1">
+        <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>9</v>
+      </c>
+      <c r="N74" s="74" cm="1">
+        <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>11</v>
+      </c>
+      <c r="O74" s="74" cm="1">
+        <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>7</v>
+      </c>
+      <c r="P74" s="74" cm="1">
+        <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>11</v>
+      </c>
+      <c r="Q74" s="74" cm="1">
+        <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="R74" s="74" cm="1">
+        <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="S74" s="74" cm="1">
+        <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>7</v>
+      </c>
+      <c r="T74" s="74" cm="1">
+        <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="U74" s="74" cm="1">
+        <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="V74" s="74" cm="1">
+        <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>7</v>
+      </c>
+      <c r="W74" s="74" cm="1">
+        <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="X74" s="74" cm="1">
+        <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
         <v>6</v>
       </c>
-      <c r="H74" s="77" cm="1">
-        <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
-      </c>
-      <c r="I74" s="77" cm="1">
-        <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
-      </c>
-      <c r="J74" s="77" cm="1">
-        <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+      <c r="Y74" s="74" cm="1">
+        <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
         <v>10</v>
       </c>
-      <c r="K74" s="77" cm="1">
-        <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+      <c r="Z74" s="74" cm="1">
+        <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
         <v>8</v>
-      </c>
-      <c r="L74" s="77" cm="1">
-        <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
-      </c>
-      <c r="M74" s="77" cm="1">
-        <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
-      </c>
-      <c r="N74" s="77" cm="1">
-        <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
-      </c>
-      <c r="O74" s="77" cm="1">
-        <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
-      </c>
-      <c r="P74" s="77" cm="1">
-        <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
-      </c>
-      <c r="Q74" s="77" cm="1">
-        <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
-      </c>
-      <c r="R74" s="77" cm="1">
-        <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
-      </c>
-      <c r="S74" s="77" cm="1">
-        <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
-      </c>
-      <c r="T74" s="77" cm="1">
-        <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
-      </c>
-      <c r="U74" s="77" cm="1">
-        <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
-      </c>
-      <c r="V74" s="77" cm="1">
-        <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
-      </c>
-      <c r="W74" s="77" cm="1">
-        <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
-      </c>
-      <c r="X74" s="77" cm="1">
-        <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
-      </c>
-      <c r="Y74" s="77" cm="1">
-        <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
-      </c>
-      <c r="Z74" s="77" cm="1">
-        <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -7269,13 +7337,14 @@
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
   </mergeCells>
-  <conditionalFormatting sqref="G2:Z20">
+  <phoneticPr fontId="15" type="noConversion"/>
+  <conditionalFormatting sqref="G2:Z73">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND($AC2&lt;&gt;"",G2=$AC2)</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:Z73">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>AND($AC2&lt;&gt;"",G2&lt;&gt;"",G2&lt;&gt;$AC2)</formula>
     </cfRule>

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10605"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/CA21BB4BE959536C/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B0C2E18-616C-C444-935C-494F4F498835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B650BD8-9408-41CE-95F4-F99CDD5D524A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="132">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -242,36 +242,54 @@
     <t>Alemanha x Curaçao</t>
   </si>
   <si>
+    <t>7x1</t>
+  </si>
+  <si>
+    <t>Costa do Marfim x Equador</t>
+  </si>
+  <si>
+    <t>1x0</t>
+  </si>
+  <si>
+    <t>Países Baixos x Japão</t>
+  </si>
+  <si>
+    <t>2x2</t>
+  </si>
+  <si>
+    <t>Suécia x Tunísia</t>
+  </si>
+  <si>
+    <t>5x1</t>
+  </si>
+  <si>
+    <t>Bélgica x Egito</t>
+  </si>
+  <si>
+    <t>Irã x Nova Zelândia</t>
+  </si>
+  <si>
+    <t>Espanha x Cabo Verde</t>
+  </si>
+  <si>
+    <t>0x0</t>
+  </si>
+  <si>
+    <t>Arábia Saudita x Uruguai</t>
+  </si>
+  <si>
+    <t>França x Senegal</t>
+  </si>
+  <si>
+    <t>3x1</t>
+  </si>
+  <si>
+    <t>Iraque x Noruega</t>
+  </si>
+  <si>
     <t>#x#</t>
   </si>
   <si>
-    <t>Costa do Marfim x Equador</t>
-  </si>
-  <si>
-    <t>Países Baixos x Japão</t>
-  </si>
-  <si>
-    <t>Suécia x Tunísia</t>
-  </si>
-  <si>
-    <t>Bélgica x Egito</t>
-  </si>
-  <si>
-    <t>Irã x Nova Zelândia</t>
-  </si>
-  <si>
-    <t>Espanha x Cabo Verde</t>
-  </si>
-  <si>
-    <t>Arábia Saudita x Uruguai</t>
-  </si>
-  <si>
-    <t>França x Senegal</t>
-  </si>
-  <si>
-    <t>Iraque x Noruega</t>
-  </si>
-  <si>
     <t>Argentina x Argélia</t>
   </si>
   <si>
@@ -437,26 +455,17 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>7x1</t>
-  </si>
-  <si>
-    <t>2x2</t>
-  </si>
-  <si>
-    <t>1x0</t>
-  </si>
-  <si>
-    <t>5x1</t>
-  </si>
-  <si>
-    <t>0x0</t>
+    <t>1x4</t>
+  </si>
+  <si>
+    <t>3x0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -559,8 +568,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -606,6 +642,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1207,7 +1255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1412,15 +1460,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1472,6 +1511,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1504,30 +1603,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1554,7 +1629,51 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1644,11 +1763,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="A4:B20" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1999,17 +2118,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.75" customWidth="1"/>
-    <col min="2" max="3" width="14.2578125" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="3" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="117" t="s">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
+      <c r="B1" s="126"/>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
@@ -2017,9 +2136,9 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="117"/>
-      <c r="B2" s="117"/>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="126"/>
+      <c r="B2" s="126"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
@@ -2027,9 +2146,9 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="117"/>
-      <c r="B3" s="117"/>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="126"/>
+      <c r="B3" s="126"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
@@ -2045,7 +2164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2053,7 +2172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2069,7 +2188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2077,7 +2196,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2085,7 +2204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2093,7 +2212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2101,7 +2220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2109,7 +2228,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2117,7 +2236,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2125,7 +2244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2133,7 +2252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2141,7 +2260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2149,7 +2268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2157,7 +2276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2165,7 +2284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2178,7 +2297,7 @@
     <mergeCell ref="A1:B3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B20">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Ok">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Ok">
       <formula>NOT(ISERROR(SEARCH("Ok",B5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2197,27 +2316,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.6484375" customWidth="1"/>
-    <col min="2" max="2" width="20.984375" customWidth="1"/>
-    <col min="3" max="7" width="12.10546875" customWidth="1"/>
-    <col min="9" max="9" width="22.8671875" customWidth="1"/>
-    <col min="10" max="10" width="9.55078125" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="7" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="118" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-    </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+    </row>
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2238,7 +2357,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2265,7 +2384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2287,7 +2406,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2308,7 +2427,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2332,7 +2451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2356,7 +2475,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2377,7 +2496,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2398,7 +2517,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2419,7 +2538,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2440,7 +2559,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2461,7 +2580,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2482,7 +2601,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2503,7 +2622,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2524,7 +2643,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2550,7 +2669,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:E17">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$E4=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2561,17 +2680,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.8359375" customWidth="1"/>
-    <col min="2" max="2" width="32.41796875" customWidth="1"/>
-    <col min="3" max="4" width="20.58203125" customWidth="1"/>
-    <col min="5" max="5" width="12.5078125" customWidth="1"/>
-    <col min="6" max="6" width="6.05078125" customWidth="1"/>
-    <col min="7" max="29" width="16.41015625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="29" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2587,79 +2706,79 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="98"/>
-      <c r="G1" s="86" t="s">
+      <c r="F1" s="115"/>
+      <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="85" t="s">
+      <c r="H1" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="85" t="s">
+      <c r="I1" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="85" t="s">
+      <c r="J1" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="85" t="s">
+      <c r="K1" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="85" t="s">
+      <c r="L1" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="85" t="s">
+      <c r="M1" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="85" t="s">
+      <c r="N1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="85" t="s">
+      <c r="O1" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="85" t="s">
+      <c r="P1" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="85" t="s">
+      <c r="Q1" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="85" t="s">
+      <c r="R1" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="85" t="s">
+      <c r="S1" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="85" t="s">
+      <c r="T1" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="85" t="s">
+      <c r="U1" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="85" t="s">
+      <c r="V1" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="85" t="s">
+      <c r="W1" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="85" t="s">
+      <c r="X1" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="85" t="s">
+      <c r="Y1" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="85" t="s">
+      <c r="Z1" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="87" t="s">
+      <c r="AA1" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="AB1" s="87" t="s">
+      <c r="AB1" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="AC1" s="89" t="s">
+      <c r="AC1" s="86" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A2" s="113">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2" s="122">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2676,7 +2795,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="99"/>
+      <c r="F2" s="116"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2734,24 +2853,24 @@
       <c r="Y2" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="Z2" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="78">
+      <c r="Z2" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA2" s="75">
         <f>IFERROR(VALUE(TRIM(LEFT($E2,SEARCH("x",$E2)-1))),"")</f>
         <v>2</v>
       </c>
-      <c r="AB2" s="92">
+      <c r="AB2" s="89">
         <f>IFERROR(VALUE(TRIM(MID($E2,SEARCH("x",$E2)+1,10))),"")</f>
         <v>0</v>
       </c>
-      <c r="AC2" s="90" t="str">
+      <c r="AC2" s="87" t="str">
         <f>IF(OR($AA2="",$AB2=""),"",IF($AA2&gt;$AB2,"A",IF($AA2&lt;$AB2,"B","E")))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="114"/>
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2766,7 +2885,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="117"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2824,24 +2943,24 @@
       <c r="Y3" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="80" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" s="84">
+      <c r="Z3" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA3" s="81">
         <f t="shared" ref="AA3:AA20" si="2">IFERROR(VALUE(TRIM(LEFT($E3,SEARCH("x",$E3)-1))),"")</f>
         <v>2</v>
       </c>
-      <c r="AB3" s="93">
+      <c r="AB3" s="90">
         <f t="shared" ref="AB3:AB20" si="3">IFERROR(VALUE(TRIM(MID($E3,SEARCH("x",$E3)+1,10))),"")</f>
         <v>1</v>
       </c>
-      <c r="AC3" s="88" t="str">
+      <c r="AC3" s="85" t="str">
         <f>IF(OR($AA3="",$AB3=""),"",IF($AA3&gt;$AB3,"A",IF($AA3&lt;$AB3,"B","E")))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A4" s="115">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4" s="124">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2858,7 +2977,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="99"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -2916,25 +3035,25 @@
       <c r="Y4" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="Z4" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" s="84">
+      <c r="Z4" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA4" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB4" s="93">
+      <c r="AB4" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC4" s="88" t="str">
+      <c r="AC4" s="85" t="str">
         <f t="shared" ref="AC4:AC67" si="4">IF(OR($AA4="",$AB4=""),"",IF($AA4&gt;$AB4,"A",IF($AA4&lt;$AB4,"B","E")))</f>
         <v>E</v>
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A5" s="116"/>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -2949,7 +3068,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="100"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3007,25 +3126,25 @@
       <c r="Y5" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="Z5" s="80" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA5" s="84">
+      <c r="Z5" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA5" s="81">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AB5" s="93">
+      <c r="AB5" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC5" s="88" t="str">
+      <c r="AC5" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="105">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" s="107">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3042,7 +3161,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="99"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3100,25 +3219,25 @@
       <c r="Y6" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="Z6" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" s="84">
+      <c r="Z6" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA6" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB6" s="93">
+      <c r="AB6" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC6" s="88" t="str">
+      <c r="AC6" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="106"/>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" s="108"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3133,7 +3252,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="101"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3194,22 +3313,22 @@
       <c r="Z7" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="AA7" s="84">
+      <c r="AA7" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB7" s="93">
+      <c r="AB7" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC7" s="88" t="str">
+      <c r="AC7" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="107"/>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" s="109"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3224,7 +3343,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="102"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3282,25 +3401,25 @@
       <c r="Y8" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="Z8" s="81" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA8" s="84">
+      <c r="Z8" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA8" s="81">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB8" s="93">
+      <c r="AB8" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC8" s="88" t="str">
+      <c r="AC8" s="85" t="str">
         <f t="shared" si="4"/>
         <v>B</v>
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="108"/>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" s="110"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3315,7 +3434,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="103"/>
+      <c r="F9" s="120"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3373,25 +3492,25 @@
       <c r="Y9" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="Z9" s="82" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA9" s="84">
+      <c r="Z9" s="79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA9" s="81">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AB9" s="93">
+      <c r="AB9" s="90">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC9" s="88" t="str">
+      <c r="AC9" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="109">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A10" s="103">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3406,9 +3525,9 @@
         <v>Curaçao</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="99"/>
+        <v>59</v>
+      </c>
+      <c r="F10" s="116"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3464,25 +3583,25 @@
       <c r="Y10" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="Z10" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA10" s="84">
+      <c r="Z10" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA10" s="81">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="AB10" s="93">
+      <c r="AB10" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC10" s="88" t="str">
+      <c r="AC10" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="110"/>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A11" s="104"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3495,9 +3614,9 @@
         <v>Equador</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="F11" s="101"/>
+        <v>61</v>
+      </c>
+      <c r="F11" s="118"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3555,27 +3674,27 @@
       <c r="Y11" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="Z11" s="83" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA11" s="84">
+      <c r="Z11" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA11" s="81">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AB11" s="93">
+      <c r="AB11" s="90">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC11" s="88" t="str">
+      <c r="AC11" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A12" s="111"/>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A12" s="105"/>
       <c r="B12" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="41" t="str">
         <f t="shared" si="0"/>
@@ -3586,9 +3705,9 @@
         <v>Japão</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="102"/>
+        <v>63</v>
+      </c>
+      <c r="F12" s="119"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3646,27 +3765,27 @@
       <c r="Y12" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="Z12" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA12" s="84">
+      <c r="Z12" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA12" s="81">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AB12" s="93">
+      <c r="AB12" s="90">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="AC12" s="88" t="str">
+      <c r="AC12" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="112"/>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A13" s="106"/>
       <c r="B13" s="30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C13" s="42" t="str">
         <f t="shared" si="0"/>
@@ -3677,9 +3796,9 @@
         <v>Tunísia</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="F13" s="103"/>
+        <v>65</v>
+      </c>
+      <c r="F13" s="120"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3737,29 +3856,29 @@
       <c r="Y13" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="Z13" s="82" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA13" s="84">
+      <c r="Z13" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA13" s="81">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="AB13" s="93">
+      <c r="AB13" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC13" s="88" t="str">
+      <c r="AC13" s="85" t="str">
         <f t="shared" si="4"/>
         <v>A</v>
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="105">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A14" s="107">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C14" s="36" t="str">
         <f t="shared" si="0"/>
@@ -3770,47 +3889,87 @@
         <v>Egito</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="99"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="61"/>
-      <c r="N14" s="61"/>
-      <c r="O14" s="61"/>
-      <c r="P14" s="61"/>
-      <c r="Q14" s="61"/>
-      <c r="R14" s="61"/>
-      <c r="S14" s="61"/>
-      <c r="T14" s="61"/>
-      <c r="U14" s="62"/>
-      <c r="V14" s="62"/>
-      <c r="W14" s="62"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
-      <c r="Z14" s="79"/>
-      <c r="AA14" s="84" t="str">
+        <v>50</v>
+      </c>
+      <c r="F14" s="116"/>
+      <c r="G14" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="O14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="R14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="S14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="T14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="U14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="V14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="W14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="X14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA14" s="81">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB14" s="93" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="90">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AC14" s="88" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="106"/>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A15" s="108"/>
       <c r="B15" s="25" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C15" s="37" t="str">
         <f t="shared" si="0"/>
@@ -3821,47 +3980,87 @@
         <v>Nova Zelândia</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="101"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-      <c r="T15" s="71"/>
-      <c r="U15" s="56"/>
-      <c r="V15" s="56"/>
-      <c r="W15" s="56"/>
-      <c r="X15" s="56"/>
-      <c r="Y15" s="56"/>
-      <c r="Z15" s="83"/>
-      <c r="AA15" s="84" t="str">
+        <v>63</v>
+      </c>
+      <c r="F15" s="118"/>
+      <c r="G15" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="L15" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q15" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="R15" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="S15" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="T15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="U15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="V15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="W15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="X15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y15" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z15" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA15" s="81">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB15" s="93" t="str">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="90">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AC15" s="88" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC15" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A16" s="107"/>
+    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="109"/>
       <c r="B16" s="26" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C16" s="38" t="str">
         <f t="shared" si="0"/>
@@ -3872,87 +4071,87 @@
         <v>Cabo Verde</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="102"/>
+        <v>69</v>
+      </c>
+      <c r="F16" s="119"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="K16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="L16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="M16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="N16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="O16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="P16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="R16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="S16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="T16" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="U16" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="V16" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="W16" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="X16" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y16" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z16" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA16" s="84">
+      <c r="H16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="K16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="O16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="R16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="S16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="T16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="U16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="V16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="W16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="X16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA16" s="81">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB16" s="93">
+      <c r="AB16" s="90">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC16" s="88" t="str">
+      <c r="AC16" s="85" t="str">
         <f t="shared" si="4"/>
         <v>E</v>
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A17" s="108"/>
+    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="110"/>
       <c r="B17" s="27" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C17" s="39" t="str">
         <f t="shared" si="0"/>
@@ -3963,49 +4162,89 @@
         <v>Uruguai</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="103"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="69"/>
-      <c r="P17" s="69"/>
-      <c r="Q17" s="69"/>
-      <c r="R17" s="69"/>
-      <c r="S17" s="69"/>
-      <c r="T17" s="69"/>
-      <c r="U17" s="70"/>
-      <c r="V17" s="70"/>
-      <c r="W17" s="70"/>
-      <c r="X17" s="70"/>
-      <c r="Y17" s="70"/>
-      <c r="Z17" s="82"/>
-      <c r="AA17" s="84" t="str">
+        <v>50</v>
+      </c>
+      <c r="F17" s="120"/>
+      <c r="G17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="M17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="N17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="O17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="P17" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q17" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="R17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="S17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="T17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="U17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="V17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="W17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="X17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z17" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA17" s="81">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB17" s="93" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="90">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AC17" s="88" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A18" s="109">
+    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="103">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C18" s="34" t="str">
         <f t="shared" si="0"/>
@@ -4016,47 +4255,87 @@
         <v>Senegal</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="99"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="55"/>
-      <c r="U18" s="73"/>
-      <c r="V18" s="73"/>
-      <c r="W18" s="73"/>
-      <c r="X18" s="73"/>
-      <c r="Y18" s="73"/>
-      <c r="Z18" s="79"/>
-      <c r="AA18" s="84" t="str">
+        <v>72</v>
+      </c>
+      <c r="F18" s="116"/>
+      <c r="G18" s="72" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="O18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="R18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="S18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="T18" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="U18" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="V18" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="W18" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="X18" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y18" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z18" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA18" s="81">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB18" s="93" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="90">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AC18" s="88" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A19" s="110"/>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A19" s="104"/>
       <c r="B19" s="28" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C19" s="40" t="str">
         <f t="shared" si="0"/>
@@ -4067,47 +4346,87 @@
         <v>Noruega</v>
       </c>
       <c r="E19" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="101"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
-      <c r="T19" s="71"/>
-      <c r="U19" s="56"/>
-      <c r="V19" s="56"/>
-      <c r="W19" s="56"/>
-      <c r="X19" s="56"/>
-      <c r="Y19" s="56"/>
-      <c r="Z19" s="83"/>
-      <c r="AA19" s="84" t="str">
+        <v>130</v>
+      </c>
+      <c r="F19" s="118"/>
+      <c r="G19" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="L19" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="M19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="N19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="O19" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="R19" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="S19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="T19" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="U19" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="V19" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="W19" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="X19" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y19" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z19" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA19" s="81">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB19" s="93" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="90">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AC19" s="88" t="str">
+        <v>4</v>
+      </c>
+      <c r="AC19" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A20" s="111"/>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A20" s="105"/>
       <c r="B20" s="29" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C20" s="41" t="str">
         <f t="shared" si="0"/>
@@ -4118,47 +4437,87 @@
         <v>Argélia</v>
       </c>
       <c r="E20" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="102"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="66"/>
-      <c r="T20" s="66"/>
-      <c r="U20" s="67"/>
-      <c r="V20" s="67"/>
-      <c r="W20" s="67"/>
-      <c r="X20" s="67"/>
-      <c r="Y20" s="67"/>
-      <c r="Z20" s="81"/>
-      <c r="AA20" s="84" t="str">
+        <v>131</v>
+      </c>
+      <c r="F20" s="119"/>
+      <c r="G20" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="K20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="L20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="M20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="N20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="R20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="S20" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="T20" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="U20" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="V20" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W20" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="X20" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y20" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA20" s="81">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="AB20" s="93" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="90">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AC20" s="88" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A21" s="112"/>
+    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="106"/>
       <c r="B21" s="30" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C21" s="42" t="str">
         <f t="shared" si="0"/>
@@ -4169,49 +4528,89 @@
         <v>Jordânia</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="103"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="75"/>
-      <c r="M21" s="75"/>
-      <c r="N21" s="75"/>
-      <c r="O21" s="75"/>
-      <c r="P21" s="75"/>
-      <c r="Q21" s="75"/>
-      <c r="R21" s="75"/>
-      <c r="S21" s="75"/>
-      <c r="T21" s="75"/>
-      <c r="U21" s="76"/>
-      <c r="V21" s="76"/>
-      <c r="W21" s="76"/>
-      <c r="X21" s="76"/>
-      <c r="Y21" s="76"/>
-      <c r="Z21" s="82"/>
-      <c r="AA21" s="84" t="str">
+        <v>72</v>
+      </c>
+      <c r="F21" s="120"/>
+      <c r="G21" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="92" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="92" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="K21" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="M21" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="N21" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q21" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="R21" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="S21" s="92" t="s">
+        <v>46</v>
+      </c>
+      <c r="T21" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="U21" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="V21" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="W21" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="X21" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y21" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA21" s="81">
         <f t="shared" ref="AA21:AA73" si="5">IFERROR(VALUE(TRIM(LEFT($E21,SEARCH("x",$E21)-1))),"")</f>
-        <v/>
-      </c>
-      <c r="AB21" s="93" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="90">
         <f t="shared" ref="AB21:AB73" si="6">IFERROR(VALUE(TRIM(MID($E21,SEARCH("x",$E21)+1,10))),"")</f>
-        <v/>
-      </c>
-      <c r="AC21" s="88" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A22" s="105">
+    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="107">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C22" s="36" t="str">
         <f t="shared" si="0"/>
@@ -4222,47 +4621,87 @@
         <v>Rep. Dem. Congo</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="99"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="71"/>
-      <c r="T22" s="71"/>
-      <c r="U22" s="56"/>
-      <c r="V22" s="56"/>
-      <c r="W22" s="56"/>
-      <c r="X22" s="56"/>
-      <c r="Y22" s="56"/>
-      <c r="Z22" s="79"/>
-      <c r="AA22" s="84" t="str">
+        <v>50</v>
+      </c>
+      <c r="F22" s="116"/>
+      <c r="G22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="M22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="N22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="O22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="P22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="R22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="S22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="T22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="U22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="V22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="W22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="X22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA22" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB22" s="93" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="90">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AC22" s="88" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A23" s="106"/>
+    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="108"/>
       <c r="B23" s="25" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C23" s="37" t="str">
         <f t="shared" si="0"/>
@@ -4272,48 +4711,88 @@
         <f t="shared" si="1"/>
         <v>Colômbia</v>
       </c>
-      <c r="E23" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" s="101"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="71"/>
-      <c r="S23" s="71"/>
-      <c r="T23" s="71"/>
-      <c r="U23" s="56"/>
-      <c r="V23" s="56"/>
-      <c r="W23" s="56"/>
-      <c r="X23" s="56"/>
-      <c r="Y23" s="56"/>
-      <c r="Z23" s="83"/>
-      <c r="AA23" s="84" t="str">
+      <c r="E23" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="118"/>
+      <c r="G23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="L23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="M23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="N23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="O23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="P23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="R23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="S23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="T23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="U23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="V23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="W23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="X23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA23" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB23" s="93" t="str">
+      <c r="AB23" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC23" s="88" t="str">
+      <c r="AC23" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A24" s="107"/>
+    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="109"/>
       <c r="B24" s="26" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C24" s="38" t="str">
         <f t="shared" si="0"/>
@@ -4323,48 +4802,88 @@
         <f t="shared" si="1"/>
         <v>Croácia</v>
       </c>
-      <c r="E24" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="102"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
-      <c r="U24" s="67"/>
-      <c r="V24" s="67"/>
-      <c r="W24" s="67"/>
-      <c r="X24" s="67"/>
-      <c r="Y24" s="67"/>
-      <c r="Z24" s="81"/>
-      <c r="AA24" s="84" t="str">
+      <c r="E24" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="119"/>
+      <c r="G24" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="L24" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="M24" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="N24" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="O24" s="98" t="s">
+        <v>46</v>
+      </c>
+      <c r="P24" s="98" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q24" s="98" t="s">
+        <v>45</v>
+      </c>
+      <c r="R24" s="98" t="s">
+        <v>44</v>
+      </c>
+      <c r="S24" s="98" t="s">
+        <v>45</v>
+      </c>
+      <c r="T24" s="98" t="s">
+        <v>46</v>
+      </c>
+      <c r="U24" s="99" t="s">
+        <v>44</v>
+      </c>
+      <c r="V24" s="99" t="s">
+        <v>44</v>
+      </c>
+      <c r="W24" s="99" t="s">
+        <v>46</v>
+      </c>
+      <c r="X24" s="99" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y24" s="99" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z24" s="100" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB24" s="93" t="str">
+      <c r="AB24" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC24" s="88" t="str">
+      <c r="AC24" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A25" s="108"/>
+    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="110"/>
       <c r="B25" s="27" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C25" s="39" t="str">
         <f t="shared" si="0"/>
@@ -4374,50 +4893,90 @@
         <f t="shared" si="1"/>
         <v>Panamá</v>
       </c>
-      <c r="E25" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" s="103"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="69"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="69"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="69"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="69"/>
-      <c r="T25" s="69"/>
-      <c r="U25" s="70"/>
-      <c r="V25" s="70"/>
-      <c r="W25" s="70"/>
-      <c r="X25" s="70"/>
-      <c r="Y25" s="70"/>
-      <c r="Z25" s="82"/>
-      <c r="AA25" s="84" t="str">
+      <c r="E25" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" s="120"/>
+      <c r="G25" s="101" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="102" t="s">
+        <v>46</v>
+      </c>
+      <c r="K25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="L25" s="102" t="s">
+        <v>46</v>
+      </c>
+      <c r="M25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="N25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="O25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="P25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="R25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="S25" s="102" t="s">
+        <v>46</v>
+      </c>
+      <c r="T25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="U25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="V25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="W25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="X25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" s="102" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA25" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB25" s="93" t="str">
+      <c r="AB25" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC25" s="88" t="str">
+      <c r="AC25" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A26" s="109">
+    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="103">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C26" s="34" t="str">
         <f t="shared" si="0"/>
@@ -4427,10 +4986,10 @@
         <f t="shared" si="1"/>
         <v>África do Sul</v>
       </c>
-      <c r="E26" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="99"/>
+      <c r="E26" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="116"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4450,25 +5009,25 @@
       <c r="W26" s="62"/>
       <c r="X26" s="62"/>
       <c r="Y26" s="62"/>
-      <c r="Z26" s="79"/>
-      <c r="AA26" s="84" t="str">
+      <c r="Z26" s="76"/>
+      <c r="AA26" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB26" s="93" t="str">
+      <c r="AB26" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC26" s="88" t="str">
+      <c r="AC26" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A27" s="110"/>
+    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="104"/>
       <c r="B27" s="28" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C27" s="40" t="str">
         <f t="shared" si="0"/>
@@ -4478,10 +5037,10 @@
         <f t="shared" si="1"/>
         <v>Coreia do Sul</v>
       </c>
-      <c r="E27" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="101"/>
+      <c r="E27" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="118"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -4501,25 +5060,25 @@
       <c r="W27" s="56"/>
       <c r="X27" s="56"/>
       <c r="Y27" s="56"/>
-      <c r="Z27" s="83"/>
-      <c r="AA27" s="84" t="str">
+      <c r="Z27" s="80"/>
+      <c r="AA27" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB27" s="93" t="str">
+      <c r="AB27" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC27" s="88" t="str">
+      <c r="AC27" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A28" s="111"/>
+    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="105"/>
       <c r="B28" s="29" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C28" s="41" t="str">
         <f t="shared" si="0"/>
@@ -4529,10 +5088,10 @@
         <f t="shared" si="1"/>
         <v>Bósnia e Herzeg.</v>
       </c>
-      <c r="E28" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="102"/>
+      <c r="E28" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="119"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -4552,25 +5111,25 @@
       <c r="W28" s="67"/>
       <c r="X28" s="67"/>
       <c r="Y28" s="67"/>
-      <c r="Z28" s="81"/>
-      <c r="AA28" s="84" t="str">
+      <c r="Z28" s="78"/>
+      <c r="AA28" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB28" s="93" t="str">
+      <c r="AB28" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC28" s="88" t="str">
+      <c r="AC28" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A29" s="112"/>
+    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="106"/>
       <c r="B29" s="30" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C29" s="42" t="str">
         <f t="shared" si="0"/>
@@ -4580,10 +5139,10 @@
         <f t="shared" si="1"/>
         <v>Catar</v>
       </c>
-      <c r="E29" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="103"/>
+      <c r="E29" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="120"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -4603,27 +5162,27 @@
       <c r="W29" s="70"/>
       <c r="X29" s="70"/>
       <c r="Y29" s="70"/>
-      <c r="Z29" s="82"/>
-      <c r="AA29" s="84" t="str">
+      <c r="Z29" s="79"/>
+      <c r="AA29" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB29" s="93" t="str">
+      <c r="AB29" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC29" s="88" t="str">
+      <c r="AC29" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A30" s="105">
+    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="107">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C30" s="36" t="str">
         <f t="shared" si="0"/>
@@ -4634,9 +5193,9 @@
         <v>Marrocos</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="99"/>
+        <v>74</v>
+      </c>
+      <c r="F30" s="116"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -4656,25 +5215,25 @@
       <c r="W30" s="62"/>
       <c r="X30" s="62"/>
       <c r="Y30" s="62"/>
-      <c r="Z30" s="79"/>
-      <c r="AA30" s="84" t="str">
+      <c r="Z30" s="76"/>
+      <c r="AA30" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB30" s="93" t="str">
+      <c r="AB30" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC30" s="88" t="str">
+      <c r="AC30" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A31" s="106"/>
+    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="108"/>
       <c r="B31" s="25" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C31" s="37" t="str">
         <f t="shared" si="0"/>
@@ -4685,9 +5244,9 @@
         <v>Haiti</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F31" s="101"/>
+        <v>74</v>
+      </c>
+      <c r="F31" s="118"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4707,25 +5266,25 @@
       <c r="W31" s="56"/>
       <c r="X31" s="56"/>
       <c r="Y31" s="56"/>
-      <c r="Z31" s="83"/>
-      <c r="AA31" s="84" t="str">
+      <c r="Z31" s="80"/>
+      <c r="AA31" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB31" s="93" t="str">
+      <c r="AB31" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC31" s="88" t="str">
+      <c r="AC31" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A32" s="107"/>
+    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="109"/>
       <c r="B32" s="26" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C32" s="38" t="str">
         <f t="shared" si="0"/>
@@ -4736,9 +5295,9 @@
         <v>Austrália</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F32" s="119"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -4758,25 +5317,25 @@
       <c r="W32" s="67"/>
       <c r="X32" s="67"/>
       <c r="Y32" s="67"/>
-      <c r="Z32" s="81"/>
-      <c r="AA32" s="84" t="str">
+      <c r="Z32" s="78"/>
+      <c r="AA32" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB32" s="93" t="str">
+      <c r="AB32" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC32" s="88" t="str">
+      <c r="AC32" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A33" s="108"/>
+    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="110"/>
       <c r="B33" s="27" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C33" s="39" t="str">
         <f t="shared" si="0"/>
@@ -4787,9 +5346,9 @@
         <v>Paraguai</v>
       </c>
       <c r="E33" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F33" s="120"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -4809,27 +5368,27 @@
       <c r="W33" s="70"/>
       <c r="X33" s="70"/>
       <c r="Y33" s="70"/>
-      <c r="Z33" s="82"/>
-      <c r="AA33" s="84" t="str">
+      <c r="Z33" s="79"/>
+      <c r="AA33" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB33" s="93" t="str">
+      <c r="AB33" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC33" s="88" t="str">
+      <c r="AC33" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A34" s="109">
+    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="103">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C34" s="34" t="str">
         <f t="shared" si="0"/>
@@ -4840,9 +5399,9 @@
         <v>Costa do Marfim</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" s="99"/>
+        <v>74</v>
+      </c>
+      <c r="F34" s="116"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -4862,25 +5421,25 @@
       <c r="W34" s="62"/>
       <c r="X34" s="62"/>
       <c r="Y34" s="62"/>
-      <c r="Z34" s="79"/>
-      <c r="AA34" s="84" t="str">
+      <c r="Z34" s="76"/>
+      <c r="AA34" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB34" s="93" t="str">
+      <c r="AB34" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC34" s="88" t="str">
+      <c r="AC34" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A35" s="110"/>
+    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="104"/>
       <c r="B35" s="28" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C35" s="40" t="str">
         <f t="shared" si="0"/>
@@ -4891,9 +5450,9 @@
         <v>Curaçao</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F35" s="101"/>
+        <v>74</v>
+      </c>
+      <c r="F35" s="118"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -4913,25 +5472,25 @@
       <c r="W35" s="56"/>
       <c r="X35" s="56"/>
       <c r="Y35" s="56"/>
-      <c r="Z35" s="83"/>
-      <c r="AA35" s="84" t="str">
+      <c r="Z35" s="80"/>
+      <c r="AA35" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB35" s="93" t="str">
+      <c r="AB35" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC35" s="88" t="str">
+      <c r="AC35" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A36" s="111"/>
+    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="105"/>
       <c r="B36" s="29" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C36" s="41" t="str">
         <f t="shared" si="0"/>
@@ -4942,9 +5501,9 @@
         <v>Suécia</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F36" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F36" s="119"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -4964,25 +5523,25 @@
       <c r="W36" s="67"/>
       <c r="X36" s="67"/>
       <c r="Y36" s="67"/>
-      <c r="Z36" s="81"/>
-      <c r="AA36" s="84" t="str">
+      <c r="Z36" s="78"/>
+      <c r="AA36" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB36" s="93" t="str">
+      <c r="AB36" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC36" s="88" t="str">
+      <c r="AC36" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A37" s="112"/>
+    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="106"/>
       <c r="B37" s="30" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C37" s="42" t="str">
         <f t="shared" si="0"/>
@@ -4993,9 +5552,9 @@
         <v>Japão</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F37" s="120"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5015,27 +5574,27 @@
       <c r="W37" s="70"/>
       <c r="X37" s="70"/>
       <c r="Y37" s="70"/>
-      <c r="Z37" s="82"/>
-      <c r="AA37" s="84" t="str">
+      <c r="Z37" s="79"/>
+      <c r="AA37" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB37" s="93" t="str">
+      <c r="AB37" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC37" s="88" t="str">
+      <c r="AC37" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A38" s="105">
+    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="107">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C38" s="36" t="str">
         <f t="shared" si="0"/>
@@ -5046,9 +5605,9 @@
         <v>Irã</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" s="99"/>
+        <v>74</v>
+      </c>
+      <c r="F38" s="116"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5068,25 +5627,25 @@
       <c r="W38" s="62"/>
       <c r="X38" s="62"/>
       <c r="Y38" s="62"/>
-      <c r="Z38" s="79"/>
-      <c r="AA38" s="84" t="str">
+      <c r="Z38" s="76"/>
+      <c r="AA38" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB38" s="93" t="str">
+      <c r="AB38" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC38" s="88" t="str">
+      <c r="AC38" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A39" s="106"/>
+    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="108"/>
       <c r="B39" s="25" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C39" s="37" t="str">
         <f t="shared" si="0"/>
@@ -5097,9 +5656,9 @@
         <v>Egito</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="101"/>
+        <v>74</v>
+      </c>
+      <c r="F39" s="118"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5119,25 +5678,25 @@
       <c r="W39" s="56"/>
       <c r="X39" s="56"/>
       <c r="Y39" s="56"/>
-      <c r="Z39" s="83"/>
-      <c r="AA39" s="84" t="str">
+      <c r="Z39" s="80"/>
+      <c r="AA39" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB39" s="93" t="str">
+      <c r="AB39" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC39" s="88" t="str">
+      <c r="AC39" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A40" s="107"/>
+    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="109"/>
       <c r="B40" s="26" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C40" s="38" t="str">
         <f t="shared" si="0"/>
@@ -5148,9 +5707,9 @@
         <v>Arábia Saudita</v>
       </c>
       <c r="E40" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F40" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F40" s="119"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5170,25 +5729,25 @@
       <c r="W40" s="67"/>
       <c r="X40" s="67"/>
       <c r="Y40" s="67"/>
-      <c r="Z40" s="81"/>
-      <c r="AA40" s="84" t="str">
+      <c r="Z40" s="78"/>
+      <c r="AA40" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB40" s="93" t="str">
+      <c r="AB40" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC40" s="88" t="str">
+      <c r="AC40" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A41" s="108"/>
+    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="110"/>
       <c r="B41" s="27" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C41" s="39" t="str">
         <f t="shared" si="0"/>
@@ -5199,9 +5758,9 @@
         <v>Cabo Verde</v>
       </c>
       <c r="E41" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F41" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F41" s="120"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5221,27 +5780,27 @@
       <c r="W41" s="70"/>
       <c r="X41" s="70"/>
       <c r="Y41" s="70"/>
-      <c r="Z41" s="82"/>
-      <c r="AA41" s="84" t="str">
+      <c r="Z41" s="79"/>
+      <c r="AA41" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB41" s="93" t="str">
+      <c r="AB41" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC41" s="88" t="str">
+      <c r="AC41" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A42" s="109">
+    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="103">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C42" s="34" t="str">
         <f t="shared" si="0"/>
@@ -5252,9 +5811,9 @@
         <v>Iraque</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F42" s="99"/>
+        <v>74</v>
+      </c>
+      <c r="F42" s="116"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5274,25 +5833,25 @@
       <c r="W42" s="62"/>
       <c r="X42" s="62"/>
       <c r="Y42" s="62"/>
-      <c r="Z42" s="79"/>
-      <c r="AA42" s="84" t="str">
+      <c r="Z42" s="76"/>
+      <c r="AA42" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB42" s="93" t="str">
+      <c r="AB42" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC42" s="88" t="str">
+      <c r="AC42" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A43" s="110"/>
+    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="104"/>
       <c r="B43" s="28" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C43" s="40" t="str">
         <f t="shared" si="0"/>
@@ -5303,9 +5862,9 @@
         <v>Senegal</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F43" s="101"/>
+        <v>74</v>
+      </c>
+      <c r="F43" s="118"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5325,25 +5884,25 @@
       <c r="W43" s="56"/>
       <c r="X43" s="56"/>
       <c r="Y43" s="56"/>
-      <c r="Z43" s="83"/>
-      <c r="AA43" s="84" t="str">
+      <c r="Z43" s="80"/>
+      <c r="AA43" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB43" s="93" t="str">
+      <c r="AB43" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC43" s="88" t="str">
+      <c r="AC43" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A44" s="111"/>
+    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="105"/>
       <c r="B44" s="29" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C44" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5354,9 +5913,9 @@
         <v>Áustria</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F44" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F44" s="119"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5376,25 +5935,25 @@
       <c r="W44" s="67"/>
       <c r="X44" s="67"/>
       <c r="Y44" s="67"/>
-      <c r="Z44" s="81"/>
-      <c r="AA44" s="84" t="str">
+      <c r="Z44" s="78"/>
+      <c r="AA44" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB44" s="93" t="str">
+      <c r="AB44" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC44" s="88" t="str">
+      <c r="AC44" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A45" s="112"/>
+    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="106"/>
       <c r="B45" s="30" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C45" s="42" t="str">
         <f t="shared" si="0"/>
@@ -5405,9 +5964,9 @@
         <v>Argélia</v>
       </c>
       <c r="E45" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F45" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F45" s="120"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5427,27 +5986,27 @@
       <c r="W45" s="70"/>
       <c r="X45" s="70"/>
       <c r="Y45" s="70"/>
-      <c r="Z45" s="82"/>
-      <c r="AA45" s="84" t="str">
+      <c r="Z45" s="79"/>
+      <c r="AA45" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB45" s="93" t="str">
+      <c r="AB45" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC45" s="88" t="str">
+      <c r="AC45" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A46" s="105">
+    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="107">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C46" s="36" t="str">
         <f t="shared" si="0"/>
@@ -5458,9 +6017,9 @@
         <v>Uzbequistão</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="99"/>
+        <v>74</v>
+      </c>
+      <c r="F46" s="116"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -5480,25 +6039,25 @@
       <c r="W46" s="62"/>
       <c r="X46" s="62"/>
       <c r="Y46" s="62"/>
-      <c r="Z46" s="79"/>
-      <c r="AA46" s="84" t="str">
+      <c r="Z46" s="76"/>
+      <c r="AA46" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB46" s="93" t="str">
+      <c r="AB46" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC46" s="88" t="str">
+      <c r="AC46" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A47" s="106"/>
+    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="108"/>
       <c r="B47" s="25" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C47" s="37" t="str">
         <f t="shared" si="0"/>
@@ -5509,9 +6068,9 @@
         <v>Rep. Dem. Congo</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F47" s="101"/>
+        <v>74</v>
+      </c>
+      <c r="F47" s="118"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -5531,25 +6090,25 @@
       <c r="W47" s="56"/>
       <c r="X47" s="56"/>
       <c r="Y47" s="56"/>
-      <c r="Z47" s="83"/>
-      <c r="AA47" s="84" t="str">
+      <c r="Z47" s="80"/>
+      <c r="AA47" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB47" s="93" t="str">
+      <c r="AB47" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC47" s="88" t="str">
+      <c r="AC47" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A48" s="107"/>
+    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="109"/>
       <c r="B48" s="26" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C48" s="38" t="str">
         <f t="shared" si="0"/>
@@ -5560,9 +6119,9 @@
         <v>Gana</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F48" s="119"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -5582,25 +6141,25 @@
       <c r="W48" s="67"/>
       <c r="X48" s="67"/>
       <c r="Y48" s="67"/>
-      <c r="Z48" s="81"/>
-      <c r="AA48" s="84" t="str">
+      <c r="Z48" s="78"/>
+      <c r="AA48" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB48" s="93" t="str">
+      <c r="AB48" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC48" s="88" t="str">
+      <c r="AC48" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A49" s="108"/>
+    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="110"/>
       <c r="B49" s="27" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C49" s="39" t="str">
         <f t="shared" si="0"/>
@@ -5611,9 +6170,9 @@
         <v>Croácia</v>
       </c>
       <c r="E49" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F49" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F49" s="120"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -5633,27 +6192,27 @@
       <c r="W49" s="70"/>
       <c r="X49" s="70"/>
       <c r="Y49" s="70"/>
-      <c r="Z49" s="82"/>
-      <c r="AA49" s="84" t="str">
+      <c r="Z49" s="79"/>
+      <c r="AA49" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB49" s="93" t="str">
+      <c r="AB49" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC49" s="88" t="str">
+      <c r="AC49" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A50" s="109">
+    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="103">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C50" s="34" t="str">
         <f t="shared" si="0"/>
@@ -5664,9 +6223,9 @@
         <v>Coreia do Sul</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F50" s="99"/>
+        <v>74</v>
+      </c>
+      <c r="F50" s="116"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -5686,25 +6245,25 @@
       <c r="W50" s="62"/>
       <c r="X50" s="62"/>
       <c r="Y50" s="62"/>
-      <c r="Z50" s="79"/>
-      <c r="AA50" s="84" t="str">
+      <c r="Z50" s="76"/>
+      <c r="AA50" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB50" s="93" t="str">
+      <c r="AB50" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC50" s="88" t="str">
+      <c r="AC50" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A51" s="110"/>
+    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="104"/>
       <c r="B51" s="28" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C51" s="40" t="str">
         <f t="shared" si="0"/>
@@ -5715,9 +6274,9 @@
         <v>México</v>
       </c>
       <c r="E51" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F51" s="101"/>
+        <v>74</v>
+      </c>
+      <c r="F51" s="118"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -5737,25 +6296,25 @@
       <c r="W51" s="56"/>
       <c r="X51" s="56"/>
       <c r="Y51" s="56"/>
-      <c r="Z51" s="83"/>
-      <c r="AA51" s="84" t="str">
+      <c r="Z51" s="80"/>
+      <c r="AA51" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB51" s="93" t="str">
+      <c r="AB51" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC51" s="88" t="str">
+      <c r="AC51" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A52" s="111"/>
+    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="105"/>
       <c r="B52" s="29" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C52" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5766,9 +6325,9 @@
         <v>Canadá</v>
       </c>
       <c r="E52" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F52" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F52" s="119"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -5788,25 +6347,25 @@
       <c r="W52" s="67"/>
       <c r="X52" s="67"/>
       <c r="Y52" s="67"/>
-      <c r="Z52" s="81"/>
-      <c r="AA52" s="84" t="str">
+      <c r="Z52" s="78"/>
+      <c r="AA52" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB52" s="93" t="str">
+      <c r="AB52" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC52" s="88" t="str">
+      <c r="AC52" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A53" s="111"/>
+    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="105"/>
       <c r="B53" s="29" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C53" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5817,9 +6376,9 @@
         <v>Catar</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F53" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F53" s="119"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -5839,25 +6398,25 @@
       <c r="W53" s="67"/>
       <c r="X53" s="67"/>
       <c r="Y53" s="67"/>
-      <c r="Z53" s="81"/>
-      <c r="AA53" s="84" t="str">
+      <c r="Z53" s="78"/>
+      <c r="AA53" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB53" s="93" t="str">
+      <c r="AB53" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC53" s="88" t="str">
+      <c r="AC53" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A54" s="111"/>
+    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="105"/>
       <c r="B54" s="29" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C54" s="41" t="str">
         <f t="shared" si="0"/>
@@ -5868,9 +6427,9 @@
         <v>Haiti</v>
       </c>
       <c r="E54" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F54" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F54" s="119"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -5890,25 +6449,25 @@
       <c r="W54" s="67"/>
       <c r="X54" s="67"/>
       <c r="Y54" s="67"/>
-      <c r="Z54" s="81"/>
-      <c r="AA54" s="84" t="str">
+      <c r="Z54" s="78"/>
+      <c r="AA54" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB54" s="93" t="str">
+      <c r="AB54" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC54" s="88" t="str">
+      <c r="AC54" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A55" s="112"/>
+    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="106"/>
       <c r="B55" s="30" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C55" s="42" t="str">
         <f t="shared" si="0"/>
@@ -5919,9 +6478,9 @@
         <v>Brasil</v>
       </c>
       <c r="E55" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F55" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F55" s="120"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -5941,27 +6500,27 @@
       <c r="W55" s="70"/>
       <c r="X55" s="70"/>
       <c r="Y55" s="70"/>
-      <c r="Z55" s="82"/>
-      <c r="AA55" s="84" t="str">
+      <c r="Z55" s="79"/>
+      <c r="AA55" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB55" s="93" t="str">
+      <c r="AB55" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC55" s="88" t="str">
+      <c r="AC55" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A56" s="105">
+    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="107">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C56" s="36" t="str">
         <f t="shared" si="0"/>
@@ -5972,9 +6531,9 @@
         <v>Estados Unidos</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F56" s="99"/>
+        <v>74</v>
+      </c>
+      <c r="F56" s="116"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -5994,25 +6553,25 @@
       <c r="W56" s="62"/>
       <c r="X56" s="62"/>
       <c r="Y56" s="62"/>
-      <c r="Z56" s="79"/>
-      <c r="AA56" s="84" t="str">
+      <c r="Z56" s="76"/>
+      <c r="AA56" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB56" s="93" t="str">
+      <c r="AB56" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC56" s="88" t="str">
+      <c r="AC56" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A57" s="106"/>
+    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="108"/>
       <c r="B57" s="25" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C57" s="37" t="str">
         <f t="shared" si="0"/>
@@ -6023,9 +6582,9 @@
         <v>Austrália</v>
       </c>
       <c r="E57" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F57" s="101"/>
+        <v>74</v>
+      </c>
+      <c r="F57" s="118"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6045,25 +6604,25 @@
       <c r="W57" s="56"/>
       <c r="X57" s="56"/>
       <c r="Y57" s="56"/>
-      <c r="Z57" s="83"/>
-      <c r="AA57" s="84" t="str">
+      <c r="Z57" s="80"/>
+      <c r="AA57" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB57" s="93" t="str">
+      <c r="AB57" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC57" s="88" t="str">
+      <c r="AC57" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A58" s="107"/>
+    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="109"/>
       <c r="B58" s="26" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C58" s="38" t="str">
         <f t="shared" si="0"/>
@@ -6074,9 +6633,9 @@
         <v>Costa do Marfim</v>
       </c>
       <c r="E58" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F58" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F58" s="119"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6096,25 +6655,25 @@
       <c r="W58" s="67"/>
       <c r="X58" s="67"/>
       <c r="Y58" s="67"/>
-      <c r="Z58" s="81"/>
-      <c r="AA58" s="84" t="str">
+      <c r="Z58" s="78"/>
+      <c r="AA58" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB58" s="93" t="str">
+      <c r="AB58" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC58" s="88" t="str">
+      <c r="AC58" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A59" s="107"/>
+    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="109"/>
       <c r="B59" s="26" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C59" s="38" t="str">
         <f t="shared" si="0"/>
@@ -6125,9 +6684,9 @@
         <v>Alemanha</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F59" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F59" s="119"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6147,25 +6706,25 @@
       <c r="W59" s="67"/>
       <c r="X59" s="67"/>
       <c r="Y59" s="67"/>
-      <c r="Z59" s="81"/>
-      <c r="AA59" s="84" t="str">
+      <c r="Z59" s="78"/>
+      <c r="AA59" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB59" s="93" t="str">
+      <c r="AB59" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC59" s="88" t="str">
+      <c r="AC59" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A60" s="107"/>
+    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="109"/>
       <c r="B60" s="26" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C60" s="38" t="str">
         <f t="shared" si="0"/>
@@ -6176,9 +6735,9 @@
         <v>Países Baixos</v>
       </c>
       <c r="E60" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F60" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F60" s="119"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6198,25 +6757,25 @@
       <c r="W60" s="67"/>
       <c r="X60" s="67"/>
       <c r="Y60" s="67"/>
-      <c r="Z60" s="81"/>
-      <c r="AA60" s="84" t="str">
+      <c r="Z60" s="78"/>
+      <c r="AA60" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB60" s="93" t="str">
+      <c r="AB60" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC60" s="88" t="str">
+      <c r="AC60" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A61" s="108"/>
+    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="110"/>
       <c r="B61" s="27" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C61" s="39" t="str">
         <f t="shared" si="0"/>
@@ -6227,9 +6786,9 @@
         <v>Suécia</v>
       </c>
       <c r="E61" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F61" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F61" s="120"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6249,27 +6808,27 @@
       <c r="W61" s="70"/>
       <c r="X61" s="70"/>
       <c r="Y61" s="70"/>
-      <c r="Z61" s="82"/>
-      <c r="AA61" s="84" t="str">
+      <c r="Z61" s="79"/>
+      <c r="AA61" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB61" s="93" t="str">
+      <c r="AB61" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC61" s="88" t="str">
+      <c r="AC61" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A62" s="109">
+    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="103">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C62" s="34" t="str">
         <f t="shared" si="0"/>
@@ -6280,9 +6839,9 @@
         <v>Bélgica</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="F62" s="99"/>
+        <v>74</v>
+      </c>
+      <c r="F62" s="116"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6302,25 +6861,25 @@
       <c r="W62" s="62"/>
       <c r="X62" s="62"/>
       <c r="Y62" s="62"/>
-      <c r="Z62" s="79"/>
-      <c r="AA62" s="84" t="str">
+      <c r="Z62" s="76"/>
+      <c r="AA62" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB62" s="93" t="str">
+      <c r="AB62" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC62" s="88" t="str">
+      <c r="AC62" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A63" s="110"/>
+    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="104"/>
       <c r="B63" s="28" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C63" s="40" t="str">
         <f t="shared" si="0"/>
@@ -6331,9 +6890,9 @@
         <v>Irã</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F63" s="101"/>
+        <v>74</v>
+      </c>
+      <c r="F63" s="118"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6353,25 +6912,25 @@
       <c r="W63" s="56"/>
       <c r="X63" s="56"/>
       <c r="Y63" s="56"/>
-      <c r="Z63" s="83"/>
-      <c r="AA63" s="84" t="str">
+      <c r="Z63" s="80"/>
+      <c r="AA63" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB63" s="93" t="str">
+      <c r="AB63" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC63" s="88" t="str">
+      <c r="AC63" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A64" s="111"/>
+    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="105"/>
       <c r="B64" s="29" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C64" s="41" t="str">
         <f t="shared" si="0"/>
@@ -6382,9 +6941,9 @@
         <v>Arábia Saudita</v>
       </c>
       <c r="E64" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F64" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F64" s="119"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6404,25 +6963,25 @@
       <c r="W64" s="67"/>
       <c r="X64" s="67"/>
       <c r="Y64" s="67"/>
-      <c r="Z64" s="81"/>
-      <c r="AA64" s="84" t="str">
+      <c r="Z64" s="78"/>
+      <c r="AA64" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB64" s="93" t="str">
+      <c r="AB64" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC64" s="88" t="str">
+      <c r="AC64" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A65" s="111"/>
+    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="105"/>
       <c r="B65" s="29" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C65" s="41" t="str">
         <f t="shared" si="0"/>
@@ -6433,9 +6992,9 @@
         <v>Espanha</v>
       </c>
       <c r="E65" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F65" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F65" s="119"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6455,25 +7014,25 @@
       <c r="W65" s="67"/>
       <c r="X65" s="67"/>
       <c r="Y65" s="67"/>
-      <c r="Z65" s="81"/>
-      <c r="AA65" s="84" t="str">
+      <c r="Z65" s="78"/>
+      <c r="AA65" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB65" s="93" t="str">
+      <c r="AB65" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC65" s="88" t="str">
+      <c r="AC65" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A66" s="111"/>
+    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="105"/>
       <c r="B66" s="29" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C66" s="41" t="str">
         <f t="shared" si="0"/>
@@ -6484,9 +7043,9 @@
         <v>França</v>
       </c>
       <c r="E66" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F66" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F66" s="119"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -6506,25 +7065,25 @@
       <c r="W66" s="67"/>
       <c r="X66" s="67"/>
       <c r="Y66" s="67"/>
-      <c r="Z66" s="81"/>
-      <c r="AA66" s="84" t="str">
+      <c r="Z66" s="78"/>
+      <c r="AA66" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB66" s="93" t="str">
+      <c r="AB66" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC66" s="88" t="str">
+      <c r="AC66" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A67" s="112"/>
+    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="106"/>
       <c r="B67" s="30" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C67" s="42" t="str">
         <f t="shared" ref="C67:C73" si="7">TRIM(LEFT(B67,FIND(" x ",B67)-1))</f>
@@ -6535,9 +7094,9 @@
         <v>Iraque</v>
       </c>
       <c r="E67" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="F67" s="103"/>
+        <v>74</v>
+      </c>
+      <c r="F67" s="120"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -6557,27 +7116,27 @@
       <c r="W67" s="70"/>
       <c r="X67" s="70"/>
       <c r="Y67" s="70"/>
-      <c r="Z67" s="82"/>
-      <c r="AA67" s="84" t="str">
+      <c r="Z67" s="79"/>
+      <c r="AA67" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB67" s="93" t="str">
+      <c r="AB67" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC67" s="88" t="str">
+      <c r="AC67" s="85" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A68" s="94">
+    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="111">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C68" s="36" t="str">
         <f t="shared" si="7"/>
@@ -6588,9 +7147,9 @@
         <v>Áustria</v>
       </c>
       <c r="E68" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="F68" s="99"/>
+        <v>74</v>
+      </c>
+      <c r="F68" s="116"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -6610,25 +7169,25 @@
       <c r="W68" s="62"/>
       <c r="X68" s="62"/>
       <c r="Y68" s="62"/>
-      <c r="Z68" s="79"/>
-      <c r="AA68" s="84" t="str">
+      <c r="Z68" s="76"/>
+      <c r="AA68" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB68" s="93" t="str">
+      <c r="AB68" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC68" s="88" t="str">
+      <c r="AC68" s="85" t="str">
         <f t="shared" ref="AC68:AC73" si="9">IF(OR($AA68="",$AB68=""),"",IF($AA68&gt;$AB68,"A",IF($AA68&lt;$AB68,"B","E")))</f>
         <v/>
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A69" s="95"/>
+    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C69" s="37" t="str">
         <f t="shared" si="7"/>
@@ -6639,9 +7198,9 @@
         <v>Argentina</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F69" s="101"/>
+        <v>74</v>
+      </c>
+      <c r="F69" s="118"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -6661,25 +7220,25 @@
       <c r="W69" s="56"/>
       <c r="X69" s="56"/>
       <c r="Y69" s="56"/>
-      <c r="Z69" s="83"/>
-      <c r="AA69" s="84" t="str">
+      <c r="Z69" s="80"/>
+      <c r="AA69" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB69" s="93" t="str">
+      <c r="AB69" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC69" s="88" t="str">
+      <c r="AC69" s="85" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A70" s="96"/>
+    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C70" s="38" t="str">
         <f t="shared" si="7"/>
@@ -6690,9 +7249,9 @@
         <v>Portugal</v>
       </c>
       <c r="E70" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F70" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F70" s="119"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -6712,25 +7271,25 @@
       <c r="W70" s="67"/>
       <c r="X70" s="67"/>
       <c r="Y70" s="67"/>
-      <c r="Z70" s="81"/>
-      <c r="AA70" s="84" t="str">
+      <c r="Z70" s="78"/>
+      <c r="AA70" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB70" s="93" t="str">
+      <c r="AB70" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC70" s="88" t="str">
+      <c r="AC70" s="85" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A71" s="96"/>
+    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C71" s="38" t="str">
         <f t="shared" si="7"/>
@@ -6741,9 +7300,9 @@
         <v>Uzbequistão</v>
       </c>
       <c r="E71" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F71" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F71" s="119"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -6763,25 +7322,25 @@
       <c r="W71" s="67"/>
       <c r="X71" s="67"/>
       <c r="Y71" s="67"/>
-      <c r="Z71" s="81"/>
-      <c r="AA71" s="84" t="str">
+      <c r="Z71" s="78"/>
+      <c r="AA71" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB71" s="93" t="str">
+      <c r="AB71" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC71" s="88" t="str">
+      <c r="AC71" s="85" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A72" s="96"/>
+    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C72" s="38" t="str">
         <f t="shared" si="7"/>
@@ -6792,9 +7351,9 @@
         <v>Inglaterra</v>
       </c>
       <c r="E72" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F72" s="102"/>
+        <v>74</v>
+      </c>
+      <c r="F72" s="119"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -6814,25 +7373,25 @@
       <c r="W72" s="67"/>
       <c r="X72" s="67"/>
       <c r="Y72" s="67"/>
-      <c r="Z72" s="81"/>
-      <c r="AA72" s="84" t="str">
+      <c r="Z72" s="78"/>
+      <c r="AA72" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB72" s="93" t="str">
+      <c r="AB72" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC72" s="88" t="str">
+      <c r="AC72" s="85" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A73" s="97"/>
+    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C73" s="43" t="str">
         <f t="shared" si="7"/>
@@ -6843,9 +7402,9 @@
         <v>Gana</v>
       </c>
       <c r="E73" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="F73" s="104"/>
+        <v>74</v>
+      </c>
+      <c r="F73" s="121"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -6865,108 +7424,111 @@
       <c r="W73" s="70"/>
       <c r="X73" s="70"/>
       <c r="Y73" s="70"/>
-      <c r="Z73" s="82"/>
-      <c r="AA73" s="84" t="str">
+      <c r="Z73" s="79"/>
+      <c r="AA73" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AB73" s="93" t="str">
+      <c r="AB73" s="90" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AC73" s="91" t="str">
+      <c r="AC73" s="88" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F74" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="G74" s="77" cm="1">
+        <v>129</v>
+      </c>
+      <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
-      </c>
-      <c r="H74" s="77" cm="1">
+        <v>8</v>
+      </c>
+      <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
-      </c>
-      <c r="I74" s="77" cm="1">
+        <v>8</v>
+      </c>
+      <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="J74" s="74" cm="1">
+        <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>12</v>
+      </c>
+      <c r="K74" s="74" cm="1">
+        <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="L74" s="74" cm="1">
+        <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>9</v>
+      </c>
+      <c r="M74" s="74" cm="1">
+        <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>9</v>
+      </c>
+      <c r="N74" s="74" cm="1">
+        <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>11</v>
+      </c>
+      <c r="O74" s="74" cm="1">
+        <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
         <v>7</v>
       </c>
-      <c r="J74" s="77" cm="1">
-        <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+      <c r="P74" s="74" cm="1">
+        <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>11</v>
+      </c>
+      <c r="Q74" s="74" cm="1">
+        <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="R74" s="74" cm="1">
+        <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="S74" s="74" cm="1">
+        <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
         <v>7</v>
       </c>
-      <c r="K74" s="77" cm="1">
-        <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
-      </c>
-      <c r="L74" s="77" cm="1">
-        <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
-      </c>
-      <c r="M74" s="77" cm="1">
-        <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
-      </c>
-      <c r="N74" s="77" cm="1">
-        <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+      <c r="T74" s="74" cm="1">
+        <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="U74" s="74" cm="1">
+        <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="V74" s="74" cm="1">
+        <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
         <v>7</v>
       </c>
-      <c r="O74" s="77" cm="1">
-        <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
-      </c>
-      <c r="P74" s="77" cm="1">
-        <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+      <c r="W74" s="74" cm="1">
+        <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
+        <v>10</v>
+      </c>
+      <c r="X74" s="74" cm="1">
+        <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
         <v>6</v>
       </c>
-      <c r="Q74" s="77" cm="1">
-        <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
-      </c>
-      <c r="R74" s="77" cm="1">
-        <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
-      </c>
-      <c r="S74" s="77" cm="1">
-        <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
-      </c>
-      <c r="T74" s="77" cm="1">
-        <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
-      </c>
-      <c r="U74" s="77" cm="1">
-        <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
-      </c>
-      <c r="V74" s="77" cm="1">
-        <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>4</v>
-      </c>
-      <c r="W74" s="77" cm="1">
-        <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
-      </c>
-      <c r="X74" s="77" cm="1">
-        <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>3</v>
-      </c>
-      <c r="Y74" s="77" cm="1">
+      <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
-      </c>
-      <c r="Z74" s="77" cm="1">
+        <v>10</v>
+      </c>
+      <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
@@ -6982,16 +7544,30 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
-  <conditionalFormatting sqref="G2:Z20">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <phoneticPr fontId="15" type="noConversion"/>
+  <conditionalFormatting sqref="G2:Z21 G26:Z73">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>AND($AC2&lt;&gt;"",G2=$AC2)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>AND($AC2&lt;&gt;"",G2&lt;&gt;"",G2&lt;&gt;$AC2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:Z22">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>AND($AC22&lt;&gt;"",G22=$AC22)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>AND($AC22&lt;&gt;"",G22&lt;&gt;"",G22&lt;&gt;$AC22)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23:Z23">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>AND($AC23&lt;&gt;"",G23=$AC23)</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>AND($AC2&lt;&gt;"",G2&lt;&gt;"",G2&lt;&gt;$AC2)</formula>
+      <formula>AND($AC23&lt;&gt;"",G23&lt;&gt;"",G23&lt;&gt;$AC23)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B650BD8-9408-41CE-95F4-F99CDD5D524A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0136432-9CDA-4C27-B040-D383894AB123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -4803,7 +4803,7 @@
         <v>Croácia</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
@@ -4866,17 +4866,17 @@
       <c r="Z24" s="100" t="s">
         <v>45</v>
       </c>
-      <c r="AA24" s="81" t="str">
+      <c r="AA24" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB24" s="90" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC24" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD24" s="54"/>
     </row>
@@ -7445,35 +7445,35 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7501,11 +7501,11 @@
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7526,11 +7526,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7544,30 +7539,21 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
-  <conditionalFormatting sqref="G2:Z21 G26:Z73">
-    <cfRule type="expression" dxfId="3" priority="5">
+  <conditionalFormatting sqref="G2:Z73">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND($AC2&lt;&gt;"",G2=$AC2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:Z73">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>AND($AC2&lt;&gt;"",G2&lt;&gt;"",G2&lt;&gt;$AC2)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22:Z22">
-    <cfRule type="expression" dxfId="5" priority="3">
-      <formula>AND($AC22&lt;&gt;"",G22=$AC22)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>AND($AC22&lt;&gt;"",G22&lt;&gt;"",G22&lt;&gt;$AC22)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G23:Z23">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>AND($AC23&lt;&gt;"",G23=$AC23)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>AND($AC23&lt;&gt;"",G23&lt;&gt;"",G23&lt;&gt;$AC23)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0136432-9CDA-4C27-B040-D383894AB123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEC07F8-97B1-4D42-B77D-FB4E63DFA76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -1547,6 +1547,51 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1558,51 +1603,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1629,51 +1629,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1763,11 +1719,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A4:B20" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2297,7 +2253,7 @@
     <mergeCell ref="A1:B3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B20">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Ok">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Ok">
       <formula>NOT(ISERROR(SEARCH("Ok",B5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2669,7 +2625,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:E17">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$E4=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2706,7 +2662,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="115"/>
+      <c r="F1" s="107"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2795,7 +2751,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="116"/>
+      <c r="F2" s="108"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2885,7 +2841,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="117"/>
+      <c r="F3" s="109"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2977,7 +2933,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="116"/>
+      <c r="F4" s="108"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3068,7 +3024,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="117"/>
+      <c r="F5" s="109"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3144,7 +3100,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="107">
+      <c r="A6" s="114">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3161,7 +3117,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="116"/>
+      <c r="F6" s="108"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3237,7 +3193,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="108"/>
+      <c r="A7" s="115"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3252,7 +3208,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="118"/>
+      <c r="F7" s="110"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3328,7 +3284,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="109"/>
+      <c r="A8" s="116"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3343,7 +3299,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="119"/>
+      <c r="F8" s="111"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3419,7 +3375,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="110"/>
+      <c r="A9" s="117"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3434,7 +3390,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="120"/>
+      <c r="F9" s="112"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3510,7 +3466,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="103">
+      <c r="A10" s="118">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3527,7 +3483,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="116"/>
+      <c r="F10" s="108"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3601,7 +3557,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="104"/>
+      <c r="A11" s="119"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3616,7 +3572,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="110"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3692,7 +3648,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="105"/>
+      <c r="A12" s="120"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3707,7 +3663,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="119"/>
+      <c r="F12" s="111"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3783,7 +3739,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="106"/>
+      <c r="A13" s="121"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3798,7 +3754,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="120"/>
+      <c r="F13" s="112"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3874,7 +3830,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="107">
+      <c r="A14" s="114">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3891,7 +3847,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="116"/>
+      <c r="F14" s="108"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3967,7 +3923,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="108"/>
+      <c r="A15" s="115"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3982,7 +3938,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="118"/>
+      <c r="F15" s="110"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4058,7 +4014,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="109"/>
+      <c r="A16" s="116"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4073,7 +4029,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="119"/>
+      <c r="F16" s="111"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4149,7 +4105,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="110"/>
+      <c r="A17" s="117"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4164,7 +4120,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="120"/>
+      <c r="F17" s="112"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4240,7 +4196,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="103">
+      <c r="A18" s="118">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4257,7 +4213,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="116"/>
+      <c r="F18" s="108"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4333,7 +4289,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="104"/>
+      <c r="A19" s="119"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4348,7 +4304,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="118"/>
+      <c r="F19" s="110"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4424,7 +4380,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="105"/>
+      <c r="A20" s="120"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4439,7 +4395,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="119"/>
+      <c r="F20" s="111"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4515,7 +4471,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="106"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4530,7 +4486,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="120"/>
+      <c r="F21" s="112"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4606,7 +4562,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="107">
+      <c r="A22" s="114">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4623,7 +4579,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="116"/>
+      <c r="F22" s="108"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4699,7 +4655,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="108"/>
+      <c r="A23" s="115"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4714,7 +4670,7 @@
       <c r="E23" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="118"/>
+      <c r="F23" s="110"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4790,7 +4746,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="109"/>
+      <c r="A24" s="116"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4803,9 +4759,9 @@
         <v>Croácia</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="119"/>
+        <v>50</v>
+      </c>
+      <c r="F24" s="111"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4872,16 +4828,16 @@
       </c>
       <c r="AB24" s="90">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24" s="85" t="str">
         <f t="shared" si="4"/>
-        <v>A</v>
+        <v>E</v>
       </c>
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="110"/>
+      <c r="A25" s="117"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4896,7 +4852,7 @@
       <c r="E25" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="120"/>
+      <c r="F25" s="112"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4972,7 +4928,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="103">
+      <c r="A26" s="118">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4989,7 +4945,7 @@
       <c r="E26" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="116"/>
+      <c r="F26" s="108"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -5025,7 +4981,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="104"/>
+      <c r="A27" s="119"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5040,7 +4996,7 @@
       <c r="E27" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="118"/>
+      <c r="F27" s="110"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -5076,7 +5032,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="105"/>
+      <c r="A28" s="120"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5091,7 +5047,7 @@
       <c r="E28" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="119"/>
+      <c r="F28" s="111"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -5127,7 +5083,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="106"/>
+      <c r="A29" s="121"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5142,7 +5098,7 @@
       <c r="E29" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="120"/>
+      <c r="F29" s="112"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -5178,7 +5134,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="107">
+      <c r="A30" s="114">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5195,7 +5151,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="116"/>
+      <c r="F30" s="108"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -5231,7 +5187,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="108"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5246,7 +5202,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="118"/>
+      <c r="F31" s="110"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5282,7 +5238,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="109"/>
+      <c r="A32" s="116"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5297,7 +5253,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="119"/>
+      <c r="F32" s="111"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5333,7 +5289,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="110"/>
+      <c r="A33" s="117"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5348,7 +5304,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="120"/>
+      <c r="F33" s="112"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5384,7 +5340,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="103">
+      <c r="A34" s="118">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5401,7 +5357,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="116"/>
+      <c r="F34" s="108"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5437,7 +5393,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="104"/>
+      <c r="A35" s="119"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5452,7 +5408,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="118"/>
+      <c r="F35" s="110"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5488,7 +5444,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="105"/>
+      <c r="A36" s="120"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5503,7 +5459,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="111"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5539,7 +5495,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="106"/>
+      <c r="A37" s="121"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5554,7 +5510,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="120"/>
+      <c r="F37" s="112"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5590,7 +5546,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="107">
+      <c r="A38" s="114">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5607,7 +5563,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="116"/>
+      <c r="F38" s="108"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5643,7 +5599,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="108"/>
+      <c r="A39" s="115"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5658,7 +5614,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="118"/>
+      <c r="F39" s="110"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5694,7 +5650,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="109"/>
+      <c r="A40" s="116"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5709,7 +5665,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="119"/>
+      <c r="F40" s="111"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5745,7 +5701,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="110"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5760,7 +5716,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="120"/>
+      <c r="F41" s="112"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5796,7 +5752,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="103">
+      <c r="A42" s="118">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5813,7 +5769,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="116"/>
+      <c r="F42" s="108"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5849,7 +5805,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="104"/>
+      <c r="A43" s="119"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5864,7 +5820,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="118"/>
+      <c r="F43" s="110"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5900,7 +5856,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="105"/>
+      <c r="A44" s="120"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -5915,7 +5871,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="119"/>
+      <c r="F44" s="111"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5951,7 +5907,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="106"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -5966,7 +5922,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="120"/>
+      <c r="F45" s="112"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6002,7 +5958,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="107">
+      <c r="A46" s="114">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6019,7 +5975,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="116"/>
+      <c r="F46" s="108"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6055,7 +6011,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="108"/>
+      <c r="A47" s="115"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6070,7 +6026,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="118"/>
+      <c r="F47" s="110"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6106,7 +6062,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="109"/>
+      <c r="A48" s="116"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6121,7 +6077,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="119"/>
+      <c r="F48" s="111"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6157,7 +6113,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="110"/>
+      <c r="A49" s="117"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6172,7 +6128,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="120"/>
+      <c r="F49" s="112"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6208,7 +6164,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="103">
+      <c r="A50" s="118">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6225,7 +6181,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="116"/>
+      <c r="F50" s="108"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6261,7 +6217,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="104"/>
+      <c r="A51" s="119"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6276,7 +6232,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="118"/>
+      <c r="F51" s="110"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6312,7 +6268,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="105"/>
+      <c r="A52" s="120"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6327,7 +6283,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="119"/>
+      <c r="F52" s="111"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6363,7 +6319,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="105"/>
+      <c r="A53" s="120"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6378,7 +6334,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="119"/>
+      <c r="F53" s="111"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6414,7 +6370,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="105"/>
+      <c r="A54" s="120"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6429,7 +6385,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="119"/>
+      <c r="F54" s="111"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6465,7 +6421,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="106"/>
+      <c r="A55" s="121"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6480,7 +6436,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="120"/>
+      <c r="F55" s="112"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6516,7 +6472,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="107">
+      <c r="A56" s="114">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6533,7 +6489,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="116"/>
+      <c r="F56" s="108"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6569,7 +6525,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="108"/>
+      <c r="A57" s="115"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6584,7 +6540,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="118"/>
+      <c r="F57" s="110"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6620,7 +6576,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="109"/>
+      <c r="A58" s="116"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6635,7 +6591,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="119"/>
+      <c r="F58" s="111"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6671,7 +6627,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="109"/>
+      <c r="A59" s="116"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6686,7 +6642,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="119"/>
+      <c r="F59" s="111"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6722,7 +6678,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="109"/>
+      <c r="A60" s="116"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6737,7 +6693,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="119"/>
+      <c r="F60" s="111"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6773,7 +6729,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="110"/>
+      <c r="A61" s="117"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6788,7 +6744,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="120"/>
+      <c r="F61" s="112"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6824,7 +6780,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="103">
+      <c r="A62" s="118">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6841,7 +6797,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="116"/>
+      <c r="F62" s="108"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6877,7 +6833,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="104"/>
+      <c r="A63" s="119"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -6892,7 +6848,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="118"/>
+      <c r="F63" s="110"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6928,7 +6884,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="105"/>
+      <c r="A64" s="120"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -6943,7 +6899,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="119"/>
+      <c r="F64" s="111"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6979,7 +6935,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="105"/>
+      <c r="A65" s="120"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -6994,7 +6950,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="119"/>
+      <c r="F65" s="111"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7030,7 +6986,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="105"/>
+      <c r="A66" s="120"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7045,7 +7001,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="119"/>
+      <c r="F66" s="111"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7081,7 +7037,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="106"/>
+      <c r="A67" s="121"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7096,7 +7052,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="120"/>
+      <c r="F67" s="112"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7132,7 +7088,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="111">
+      <c r="A68" s="103">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7149,7 +7105,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="116"/>
+      <c r="F68" s="108"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7185,7 +7141,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="112"/>
+      <c r="A69" s="104"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7200,7 +7156,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="118"/>
+      <c r="F69" s="110"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7236,7 +7192,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="113"/>
+      <c r="A70" s="105"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7251,7 +7207,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="119"/>
+      <c r="F70" s="111"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7287,7 +7243,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="113"/>
+      <c r="A71" s="105"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7302,7 +7258,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="119"/>
+      <c r="F71" s="111"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7338,7 +7294,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="113"/>
+      <c r="A72" s="105"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7353,7 +7309,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="119"/>
+      <c r="F72" s="111"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7389,7 +7345,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="114"/>
+      <c r="A73" s="106"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7404,7 +7360,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="121"/>
+      <c r="F73" s="113"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7445,43 +7401,43 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7489,7 +7445,7 @@
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7497,27 +7453,27 @@
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7526,6 +7482,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7542,16 +7500,12 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND($AC2&lt;&gt;"",G2=$AC2)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:Z73">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>AND($AC2&lt;&gt;"",G2&lt;&gt;"",G2&lt;&gt;$AC2)</formula>
     </cfRule>

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEC07F8-97B1-4D42-B77D-FB4E63DFA76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9642BA0-7958-4014-AFA8-FCE524CFFAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -1547,6 +1547,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1579,30 +1603,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2662,7 +2662,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="107"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2751,7 +2751,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="108"/>
+      <c r="F2" s="116"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="109"/>
+      <c r="F3" s="117"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2933,7 +2933,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3024,7 +3024,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="109"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3100,7 +3100,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="114">
+      <c r="A6" s="103">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3117,7 +3117,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3193,7 +3193,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="115"/>
+      <c r="A7" s="104"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3208,7 +3208,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="110"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3284,7 +3284,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="116"/>
+      <c r="A8" s="105"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3299,7 +3299,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="111"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3375,7 +3375,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="117"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3390,7 +3390,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="112"/>
+      <c r="F9" s="120"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3466,7 +3466,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="118">
+      <c r="A10" s="107">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3483,7 +3483,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="116"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3557,7 +3557,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="119"/>
+      <c r="A11" s="108"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3572,7 +3572,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="110"/>
+      <c r="F11" s="118"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3648,7 +3648,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="120"/>
+      <c r="A12" s="109"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3663,7 +3663,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="111"/>
+      <c r="F12" s="119"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3739,7 +3739,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="121"/>
+      <c r="A13" s="110"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3754,7 +3754,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="112"/>
+      <c r="F13" s="120"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3830,7 +3830,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="114">
+      <c r="A14" s="103">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3847,7 +3847,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="108"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3923,7 +3923,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="115"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3938,7 +3938,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="110"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4014,7 +4014,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="116"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4029,7 +4029,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="111"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4105,7 +4105,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="117"/>
+      <c r="A17" s="106"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4120,7 +4120,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="112"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4196,7 +4196,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="118">
+      <c r="A18" s="107">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4213,7 +4213,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="108"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4289,7 +4289,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="119"/>
+      <c r="A19" s="108"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4304,7 +4304,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="110"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4380,7 +4380,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="120"/>
+      <c r="A20" s="109"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="111"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4471,7 +4471,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="121"/>
+      <c r="A21" s="110"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4486,7 +4486,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="112"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4562,7 +4562,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="114">
+      <c r="A22" s="103">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4579,7 +4579,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="108"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4655,7 +4655,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="115"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4670,7 +4670,7 @@
       <c r="E23" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="110"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4746,7 +4746,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="116"/>
+      <c r="A24" s="105"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4759,9 +4759,9 @@
         <v>Croácia</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" s="111"/>
+        <v>63</v>
+      </c>
+      <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4824,11 +4824,11 @@
       </c>
       <c r="AA24" s="81">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB24" s="90">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC24" s="85" t="str">
         <f t="shared" si="4"/>
@@ -4837,7 +4837,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="117"/>
+      <c r="A25" s="106"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4852,7 +4852,7 @@
       <c r="E25" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="112"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4928,7 +4928,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="118">
+      <c r="A26" s="107">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4945,7 +4945,7 @@
       <c r="E26" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="108"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4981,7 +4981,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="119"/>
+      <c r="A27" s="108"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -4996,7 +4996,7 @@
       <c r="E27" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="110"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -5032,7 +5032,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="120"/>
+      <c r="A28" s="109"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5047,7 +5047,7 @@
       <c r="E28" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="111"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -5083,7 +5083,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="121"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5098,7 +5098,7 @@
       <c r="E29" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="112"/>
+      <c r="F29" s="120"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -5134,7 +5134,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="114">
+      <c r="A30" s="103">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5151,7 +5151,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="108"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -5187,7 +5187,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="115"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5202,7 +5202,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="110"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5238,7 +5238,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="116"/>
+      <c r="A32" s="105"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5253,7 +5253,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="111"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5289,7 +5289,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="117"/>
+      <c r="A33" s="106"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5304,7 +5304,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="112"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5340,7 +5340,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="118">
+      <c r="A34" s="107">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5357,7 +5357,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="108"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5393,7 +5393,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="119"/>
+      <c r="A35" s="108"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5408,7 +5408,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="110"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5444,7 +5444,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="120"/>
+      <c r="A36" s="109"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5459,7 +5459,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="111"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5495,7 +5495,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="121"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5510,7 +5510,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="112"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5546,7 +5546,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="114">
+      <c r="A38" s="103">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5563,7 +5563,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="108"/>
+      <c r="F38" s="116"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5599,7 +5599,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="115"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5614,7 +5614,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="110"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5650,7 +5650,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="116"/>
+      <c r="A40" s="105"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5665,7 +5665,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="111"/>
+      <c r="F40" s="119"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5701,7 +5701,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="117"/>
+      <c r="A41" s="106"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5716,7 +5716,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="112"/>
+      <c r="F41" s="120"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5752,7 +5752,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="118">
+      <c r="A42" s="107">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5769,7 +5769,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="108"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5805,7 +5805,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="119"/>
+      <c r="A43" s="108"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5820,7 +5820,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="110"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5856,7 +5856,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="120"/>
+      <c r="A44" s="109"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -5871,7 +5871,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="111"/>
+      <c r="F44" s="119"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5907,7 +5907,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="121"/>
+      <c r="A45" s="110"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -5922,7 +5922,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="112"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5958,7 +5958,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="114">
+      <c r="A46" s="103">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5975,7 +5975,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="108"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6011,7 +6011,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="115"/>
+      <c r="A47" s="104"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6026,7 +6026,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="110"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6062,7 +6062,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="116"/>
+      <c r="A48" s="105"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6077,7 +6077,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="111"/>
+      <c r="F48" s="119"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6113,7 +6113,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="117"/>
+      <c r="A49" s="106"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6128,7 +6128,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="112"/>
+      <c r="F49" s="120"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6164,7 +6164,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="118">
+      <c r="A50" s="107">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6181,7 +6181,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="108"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6217,7 +6217,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="119"/>
+      <c r="A51" s="108"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6232,7 +6232,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="110"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6268,7 +6268,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="120"/>
+      <c r="A52" s="109"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6283,7 +6283,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="111"/>
+      <c r="F52" s="119"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6319,7 +6319,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="120"/>
+      <c r="A53" s="109"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6334,7 +6334,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="111"/>
+      <c r="F53" s="119"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6370,7 +6370,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="120"/>
+      <c r="A54" s="109"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6385,7 +6385,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="111"/>
+      <c r="F54" s="119"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6421,7 +6421,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="121"/>
+      <c r="A55" s="110"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6436,7 +6436,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="112"/>
+      <c r="F55" s="120"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6472,7 +6472,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="114">
+      <c r="A56" s="103">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6489,7 +6489,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="108"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6525,7 +6525,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="115"/>
+      <c r="A57" s="104"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6540,7 +6540,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="110"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6576,7 +6576,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="116"/>
+      <c r="A58" s="105"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6591,7 +6591,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="111"/>
+      <c r="F58" s="119"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6627,7 +6627,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="116"/>
+      <c r="A59" s="105"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6642,7 +6642,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="111"/>
+      <c r="F59" s="119"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6678,7 +6678,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="116"/>
+      <c r="A60" s="105"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6693,7 +6693,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="111"/>
+      <c r="F60" s="119"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6729,7 +6729,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="117"/>
+      <c r="A61" s="106"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6744,7 +6744,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="112"/>
+      <c r="F61" s="120"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6780,7 +6780,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="118">
+      <c r="A62" s="107">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6797,7 +6797,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="108"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6833,7 +6833,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="119"/>
+      <c r="A63" s="108"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -6848,7 +6848,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="110"/>
+      <c r="F63" s="118"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6884,7 +6884,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="120"/>
+      <c r="A64" s="109"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -6899,7 +6899,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="111"/>
+      <c r="F64" s="119"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6935,7 +6935,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="120"/>
+      <c r="A65" s="109"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -6950,7 +6950,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="111"/>
+      <c r="F65" s="119"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6986,7 +6986,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="120"/>
+      <c r="A66" s="109"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7001,7 +7001,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="111"/>
+      <c r="F66" s="119"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7037,7 +7037,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="121"/>
+      <c r="A67" s="110"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7052,7 +7052,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="112"/>
+      <c r="F67" s="120"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7088,7 +7088,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="103">
+      <c r="A68" s="111">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7105,7 +7105,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="108"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7141,7 +7141,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="104"/>
+      <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7156,7 +7156,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="110"/>
+      <c r="F69" s="118"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7192,7 +7192,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="105"/>
+      <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7207,7 +7207,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="111"/>
+      <c r="F70" s="119"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7243,7 +7243,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="105"/>
+      <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7258,7 +7258,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="111"/>
+      <c r="F71" s="119"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7294,7 +7294,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="105"/>
+      <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7309,7 +7309,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="111"/>
+      <c r="F72" s="119"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7345,7 +7345,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="106"/>
+      <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7360,7 +7360,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="113"/>
+      <c r="F73" s="121"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7482,6 +7482,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
@@ -7498,8 +7500,6 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9642BA0-7958-4014-AFA8-FCE524CFFAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8BA5E0-8AA3-4100-835F-D772534524D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="133">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -459,6 +459,9 @@
   </si>
   <si>
     <t>3x0</t>
+  </si>
+  <si>
+    <t>3x2</t>
   </si>
 </sst>
 </file>
@@ -4759,7 +4762,7 @@
         <v>Croácia</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
@@ -4824,7 +4827,7 @@
       </c>
       <c r="AA24" s="81">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB24" s="90">
         <f t="shared" si="6"/>
@@ -4832,7 +4835,7 @@
       </c>
       <c r="AC24" s="85" t="str">
         <f t="shared" si="4"/>
-        <v>E</v>
+        <v>A</v>
       </c>
       <c r="AD24" s="54"/>
     </row>
@@ -7401,43 +7404,43 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7445,7 +7448,7 @@
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7453,27 +7456,27 @@
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7482,11 +7485,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -7500,6 +7498,11 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8BA5E0-8AA3-4100-835F-D772534524D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FFC5181-A7E0-44CC-A927-643B61F590A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -461,7 +461,7 @@
     <t>3x0</t>
   </si>
   <si>
-    <t>3x2</t>
+    <t>4x2</t>
   </si>
 </sst>
 </file>
@@ -1550,6 +1550,27 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1574,6 +1595,18 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1585,39 +1618,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2665,7 +2665,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="115"/>
+      <c r="F1" s="103"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2737,7 +2737,7 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="122">
+      <c r="A2" s="118">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2754,7 +2754,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="116"/>
+      <c r="F2" s="104"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2829,7 +2829,7 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="123"/>
+      <c r="A3" s="119"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2844,7 +2844,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="117"/>
+      <c r="F3" s="105"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2919,7 +2919,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="124">
+      <c r="A4" s="120">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2936,7 +2936,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="116"/>
+      <c r="F4" s="104"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3012,7 +3012,7 @@
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="125"/>
+      <c r="A5" s="121"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -3027,7 +3027,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="117"/>
+      <c r="F5" s="105"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3103,7 +3103,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="103">
+      <c r="A6" s="110">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3120,7 +3120,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="116"/>
+      <c r="F6" s="104"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3196,7 +3196,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3211,7 +3211,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="118"/>
+      <c r="F7" s="106"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3287,7 +3287,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="105"/>
+      <c r="A8" s="112"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3302,7 +3302,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="119"/>
+      <c r="F8" s="107"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3378,7 +3378,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="106"/>
+      <c r="A9" s="113"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3393,7 +3393,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="120"/>
+      <c r="F9" s="108"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3469,7 +3469,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="107">
+      <c r="A10" s="114">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3486,7 +3486,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="116"/>
+      <c r="F10" s="104"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3560,7 +3560,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="108"/>
+      <c r="A11" s="115"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3575,7 +3575,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="106"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3651,7 +3651,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="109"/>
+      <c r="A12" s="116"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3666,7 +3666,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="119"/>
+      <c r="F12" s="107"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3742,7 +3742,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="110"/>
+      <c r="A13" s="117"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3757,7 +3757,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="120"/>
+      <c r="F13" s="108"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3833,7 +3833,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="103">
+      <c r="A14" s="110">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3850,7 +3850,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="116"/>
+      <c r="F14" s="104"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3926,7 +3926,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="104"/>
+      <c r="A15" s="111"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3941,7 +3941,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="118"/>
+      <c r="F15" s="106"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4017,7 +4017,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="105"/>
+      <c r="A16" s="112"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4032,7 +4032,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="119"/>
+      <c r="F16" s="107"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4108,7 +4108,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="106"/>
+      <c r="A17" s="113"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4123,7 +4123,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="120"/>
+      <c r="F17" s="108"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4199,7 +4199,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="107">
+      <c r="A18" s="114">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4216,7 +4216,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="116"/>
+      <c r="F18" s="104"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4292,7 +4292,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="108"/>
+      <c r="A19" s="115"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4307,7 +4307,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="118"/>
+      <c r="F19" s="106"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4383,7 +4383,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="109"/>
+      <c r="A20" s="116"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4398,7 +4398,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="119"/>
+      <c r="F20" s="107"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="110"/>
+      <c r="A21" s="117"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4489,7 +4489,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="120"/>
+      <c r="F21" s="108"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4565,7 +4565,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="103">
+      <c r="A22" s="110">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4582,7 +4582,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="116"/>
+      <c r="F22" s="104"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4658,7 +4658,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="104"/>
+      <c r="A23" s="111"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4673,7 +4673,7 @@
       <c r="E23" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="118"/>
+      <c r="F23" s="106"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4749,7 +4749,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="105"/>
+      <c r="A24" s="112"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4764,7 +4764,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="119"/>
+      <c r="F24" s="107"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="AA24" s="81">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB24" s="90">
         <f t="shared" si="6"/>
@@ -4840,7 +4840,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="106"/>
+      <c r="A25" s="113"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4855,7 +4855,7 @@
       <c r="E25" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="120"/>
+      <c r="F25" s="108"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4931,7 +4931,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="107">
+      <c r="A26" s="114">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4948,7 +4948,7 @@
       <c r="E26" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="116"/>
+      <c r="F26" s="104"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4984,7 +4984,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="108"/>
+      <c r="A27" s="115"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -4999,7 +4999,7 @@
       <c r="E27" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="118"/>
+      <c r="F27" s="106"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -5035,7 +5035,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="109"/>
+      <c r="A28" s="116"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5050,7 +5050,7 @@
       <c r="E28" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="119"/>
+      <c r="F28" s="107"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -5086,7 +5086,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="110"/>
+      <c r="A29" s="117"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5101,7 +5101,7 @@
       <c r="E29" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="120"/>
+      <c r="F29" s="108"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -5137,7 +5137,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="103">
+      <c r="A30" s="110">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5154,7 +5154,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="116"/>
+      <c r="F30" s="104"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -5190,7 +5190,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="104"/>
+      <c r="A31" s="111"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5205,7 +5205,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="118"/>
+      <c r="F31" s="106"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5241,7 +5241,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="105"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5256,7 +5256,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="119"/>
+      <c r="F32" s="107"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5292,7 +5292,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="106"/>
+      <c r="A33" s="113"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5307,7 +5307,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="120"/>
+      <c r="F33" s="108"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5343,7 +5343,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="107">
+      <c r="A34" s="114">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5360,7 +5360,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="116"/>
+      <c r="F34" s="104"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5396,7 +5396,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="108"/>
+      <c r="A35" s="115"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5411,7 +5411,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="118"/>
+      <c r="F35" s="106"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5447,7 +5447,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="109"/>
+      <c r="A36" s="116"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5462,7 +5462,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="107"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5498,7 +5498,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="110"/>
+      <c r="A37" s="117"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5513,7 +5513,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="120"/>
+      <c r="F37" s="108"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5549,7 +5549,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="103">
+      <c r="A38" s="110">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5566,7 +5566,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="116"/>
+      <c r="F38" s="104"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5602,7 +5602,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="104"/>
+      <c r="A39" s="111"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5617,7 +5617,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="118"/>
+      <c r="F39" s="106"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5653,7 +5653,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="105"/>
+      <c r="A40" s="112"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5668,7 +5668,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="119"/>
+      <c r="F40" s="107"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5704,7 +5704,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="106"/>
+      <c r="A41" s="113"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5719,7 +5719,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="120"/>
+      <c r="F41" s="108"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5755,7 +5755,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="107">
+      <c r="A42" s="114">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5772,7 +5772,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="116"/>
+      <c r="F42" s="104"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5808,7 +5808,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="108"/>
+      <c r="A43" s="115"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5823,7 +5823,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="118"/>
+      <c r="F43" s="106"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5859,7 +5859,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="109"/>
+      <c r="A44" s="116"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -5874,7 +5874,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="119"/>
+      <c r="F44" s="107"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5910,7 +5910,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="110"/>
+      <c r="A45" s="117"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -5925,7 +5925,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="120"/>
+      <c r="F45" s="108"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5961,7 +5961,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="103">
+      <c r="A46" s="110">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5978,7 +5978,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="116"/>
+      <c r="F46" s="104"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6014,7 +6014,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="104"/>
+      <c r="A47" s="111"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6029,7 +6029,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="118"/>
+      <c r="F47" s="106"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6065,7 +6065,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="105"/>
+      <c r="A48" s="112"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6080,7 +6080,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="119"/>
+      <c r="F48" s="107"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6116,7 +6116,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="106"/>
+      <c r="A49" s="113"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6131,7 +6131,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="120"/>
+      <c r="F49" s="108"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6167,7 +6167,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="107">
+      <c r="A50" s="114">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6184,7 +6184,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="116"/>
+      <c r="F50" s="104"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6220,7 +6220,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="108"/>
+      <c r="A51" s="115"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6235,7 +6235,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="118"/>
+      <c r="F51" s="106"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6271,7 +6271,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="109"/>
+      <c r="A52" s="116"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6286,7 +6286,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="119"/>
+      <c r="F52" s="107"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6322,7 +6322,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="109"/>
+      <c r="A53" s="116"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6337,7 +6337,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="119"/>
+      <c r="F53" s="107"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6373,7 +6373,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="109"/>
+      <c r="A54" s="116"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6388,7 +6388,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="119"/>
+      <c r="F54" s="107"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6424,7 +6424,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="110"/>
+      <c r="A55" s="117"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6439,7 +6439,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="120"/>
+      <c r="F55" s="108"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6475,7 +6475,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="103">
+      <c r="A56" s="110">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6492,7 +6492,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="116"/>
+      <c r="F56" s="104"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6528,7 +6528,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="104"/>
+      <c r="A57" s="111"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6543,7 +6543,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="118"/>
+      <c r="F57" s="106"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6579,7 +6579,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="105"/>
+      <c r="A58" s="112"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6594,7 +6594,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="119"/>
+      <c r="F58" s="107"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6630,7 +6630,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="105"/>
+      <c r="A59" s="112"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6645,7 +6645,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="119"/>
+      <c r="F59" s="107"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6681,7 +6681,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="105"/>
+      <c r="A60" s="112"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6696,7 +6696,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="119"/>
+      <c r="F60" s="107"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6732,7 +6732,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="106"/>
+      <c r="A61" s="113"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6747,7 +6747,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="120"/>
+      <c r="F61" s="108"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6783,7 +6783,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="107">
+      <c r="A62" s="114">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6800,7 +6800,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="116"/>
+      <c r="F62" s="104"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6836,7 +6836,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="108"/>
+      <c r="A63" s="115"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -6851,7 +6851,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="118"/>
+      <c r="F63" s="106"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6887,7 +6887,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="109"/>
+      <c r="A64" s="116"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -6902,7 +6902,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="119"/>
+      <c r="F64" s="107"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6938,7 +6938,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="109"/>
+      <c r="A65" s="116"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -6953,7 +6953,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="119"/>
+      <c r="F65" s="107"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6989,7 +6989,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="109"/>
+      <c r="A66" s="116"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7004,7 +7004,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="119"/>
+      <c r="F66" s="107"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7040,7 +7040,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="110"/>
+      <c r="A67" s="117"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7055,7 +7055,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="120"/>
+      <c r="F67" s="108"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7091,7 +7091,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="111">
+      <c r="A68" s="122">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7108,7 +7108,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="116"/>
+      <c r="F68" s="104"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7144,7 +7144,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="112"/>
+      <c r="A69" s="123"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7159,7 +7159,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="118"/>
+      <c r="F69" s="106"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7195,7 +7195,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="113"/>
+      <c r="A70" s="124"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7210,7 +7210,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="119"/>
+      <c r="F70" s="107"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7246,7 +7246,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="113"/>
+      <c r="A71" s="124"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7261,7 +7261,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="119"/>
+      <c r="F71" s="107"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7297,7 +7297,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="113"/>
+      <c r="A72" s="124"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7312,7 +7312,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="119"/>
+      <c r="F72" s="107"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7348,7 +7348,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="114"/>
+      <c r="A73" s="125"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7363,7 +7363,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="121"/>
+      <c r="F73" s="109"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7485,6 +7485,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -7501,8 +7503,6 @@
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FFC5181-A7E0-44CC-A927-643B61F590A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6015B5-79DD-432D-8F1F-5A314E0DBFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -1550,6 +1550,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -1583,18 +1607,6 @@
     <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1606,18 +1618,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2665,7 +2665,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="103"/>
+      <c r="F1" s="111"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2737,7 +2737,7 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="118">
+      <c r="A2" s="122">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2754,7 +2754,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="104"/>
+      <c r="F2" s="112"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2829,7 +2829,7 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
+      <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2844,7 +2844,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="105"/>
+      <c r="F3" s="113"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2919,7 +2919,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="120">
+      <c r="A4" s="124">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2936,7 +2936,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="104"/>
+      <c r="F4" s="112"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3012,7 +3012,7 @@
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="121"/>
+      <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -3027,7 +3027,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="105"/>
+      <c r="F5" s="113"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3103,7 +3103,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="110">
+      <c r="A6" s="118">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3120,7 +3120,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="104"/>
+      <c r="F6" s="112"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3196,7 +3196,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="111"/>
+      <c r="A7" s="119"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3211,7 +3211,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="106"/>
+      <c r="F7" s="114"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3287,7 +3287,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="112"/>
+      <c r="A8" s="120"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3302,7 +3302,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="107"/>
+      <c r="F8" s="115"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3378,7 +3378,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="113"/>
+      <c r="A9" s="121"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3393,7 +3393,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="116"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3469,7 +3469,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="114">
+      <c r="A10" s="103">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3486,7 +3486,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="104"/>
+      <c r="F10" s="112"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3560,7 +3560,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="115"/>
+      <c r="A11" s="104"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3575,7 +3575,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="106"/>
+      <c r="F11" s="114"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3651,7 +3651,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="116"/>
+      <c r="A12" s="105"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3666,7 +3666,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="107"/>
+      <c r="F12" s="115"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3742,7 +3742,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="117"/>
+      <c r="A13" s="106"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3757,7 +3757,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="108"/>
+      <c r="F13" s="116"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3833,7 +3833,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="110">
+      <c r="A14" s="118">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3850,7 +3850,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="104"/>
+      <c r="F14" s="112"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3926,7 +3926,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="111"/>
+      <c r="A15" s="119"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3941,7 +3941,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="106"/>
+      <c r="F15" s="114"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4017,7 +4017,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="112"/>
+      <c r="A16" s="120"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4032,7 +4032,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="107"/>
+      <c r="F16" s="115"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4108,7 +4108,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="113"/>
+      <c r="A17" s="121"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4123,7 +4123,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="108"/>
+      <c r="F17" s="116"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4199,7 +4199,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="114">
+      <c r="A18" s="103">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4216,7 +4216,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="104"/>
+      <c r="F18" s="112"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4292,7 +4292,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="115"/>
+      <c r="A19" s="104"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4307,7 +4307,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="106"/>
+      <c r="F19" s="114"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4383,7 +4383,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="116"/>
+      <c r="A20" s="105"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4398,7 +4398,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="107"/>
+      <c r="F20" s="115"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="117"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4489,7 +4489,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="108"/>
+      <c r="F21" s="116"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4565,7 +4565,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="110">
+      <c r="A22" s="118">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4582,7 +4582,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="104"/>
+      <c r="F22" s="112"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4658,7 +4658,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="111"/>
+      <c r="A23" s="119"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4673,7 +4673,7 @@
       <c r="E23" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="106"/>
+      <c r="F23" s="114"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4749,7 +4749,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="112"/>
+      <c r="A24" s="120"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4764,7 +4764,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="107"/>
+      <c r="F24" s="115"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4840,7 +4840,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="113"/>
+      <c r="A25" s="121"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4853,9 +4853,9 @@
         <v>Panamá</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="108"/>
+        <v>61</v>
+      </c>
+      <c r="F25" s="116"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4916,22 +4916,22 @@
       <c r="Z25" s="102" t="s">
         <v>44</v>
       </c>
-      <c r="AA25" s="81" t="str">
+      <c r="AA25" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB25" s="90" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC25" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="114">
+      <c r="A26" s="103">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4948,7 +4948,7 @@
       <c r="E26" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="104"/>
+      <c r="F26" s="112"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4984,7 +4984,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="115"/>
+      <c r="A27" s="104"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -4999,7 +4999,7 @@
       <c r="E27" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="106"/>
+      <c r="F27" s="114"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -5035,7 +5035,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="116"/>
+      <c r="A28" s="105"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5050,7 +5050,7 @@
       <c r="E28" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="107"/>
+      <c r="F28" s="115"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -5086,7 +5086,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5101,7 +5101,7 @@
       <c r="E29" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="108"/>
+      <c r="F29" s="116"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -5137,7 +5137,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="110">
+      <c r="A30" s="118">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5154,7 +5154,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="104"/>
+      <c r="F30" s="112"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -5190,7 +5190,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="111"/>
+      <c r="A31" s="119"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5205,7 +5205,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="106"/>
+      <c r="F31" s="114"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5241,7 +5241,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="112"/>
+      <c r="A32" s="120"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5256,7 +5256,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="107"/>
+      <c r="F32" s="115"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5292,7 +5292,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="113"/>
+      <c r="A33" s="121"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5307,7 +5307,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="108"/>
+      <c r="F33" s="116"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5343,7 +5343,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="114">
+      <c r="A34" s="103">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5360,7 +5360,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="104"/>
+      <c r="F34" s="112"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5396,7 +5396,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="115"/>
+      <c r="A35" s="104"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5411,7 +5411,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="106"/>
+      <c r="F35" s="114"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5447,7 +5447,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="116"/>
+      <c r="A36" s="105"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5462,7 +5462,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="107"/>
+      <c r="F36" s="115"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5498,7 +5498,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="117"/>
+      <c r="A37" s="106"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5513,7 +5513,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="108"/>
+      <c r="F37" s="116"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5549,7 +5549,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="110">
+      <c r="A38" s="118">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5566,7 +5566,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="104"/>
+      <c r="F38" s="112"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5602,7 +5602,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="111"/>
+      <c r="A39" s="119"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5617,7 +5617,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="106"/>
+      <c r="F39" s="114"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5653,7 +5653,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="112"/>
+      <c r="A40" s="120"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5668,7 +5668,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="107"/>
+      <c r="F40" s="115"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5704,7 +5704,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="113"/>
+      <c r="A41" s="121"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5719,7 +5719,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="108"/>
+      <c r="F41" s="116"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5755,7 +5755,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="114">
+      <c r="A42" s="103">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5772,7 +5772,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="104"/>
+      <c r="F42" s="112"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5808,7 +5808,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="115"/>
+      <c r="A43" s="104"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5823,7 +5823,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="106"/>
+      <c r="F43" s="114"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5859,7 +5859,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="116"/>
+      <c r="A44" s="105"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -5874,7 +5874,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="107"/>
+      <c r="F44" s="115"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5910,7 +5910,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="117"/>
+      <c r="A45" s="106"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -5925,7 +5925,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="108"/>
+      <c r="F45" s="116"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5961,7 +5961,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="110">
+      <c r="A46" s="118">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5978,7 +5978,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="104"/>
+      <c r="F46" s="112"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6014,7 +6014,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="111"/>
+      <c r="A47" s="119"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6029,7 +6029,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="106"/>
+      <c r="F47" s="114"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6065,7 +6065,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="112"/>
+      <c r="A48" s="120"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6080,7 +6080,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="107"/>
+      <c r="F48" s="115"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6116,7 +6116,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="113"/>
+      <c r="A49" s="121"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6131,7 +6131,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="108"/>
+      <c r="F49" s="116"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6167,7 +6167,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="114">
+      <c r="A50" s="103">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6184,7 +6184,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="104"/>
+      <c r="F50" s="112"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6220,7 +6220,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="115"/>
+      <c r="A51" s="104"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6235,7 +6235,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="106"/>
+      <c r="F51" s="114"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6271,7 +6271,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="116"/>
+      <c r="A52" s="105"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6286,7 +6286,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="107"/>
+      <c r="F52" s="115"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6322,7 +6322,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="116"/>
+      <c r="A53" s="105"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6337,7 +6337,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="107"/>
+      <c r="F53" s="115"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6373,7 +6373,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="116"/>
+      <c r="A54" s="105"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6388,7 +6388,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="107"/>
+      <c r="F54" s="115"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6424,7 +6424,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="117"/>
+      <c r="A55" s="106"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6439,7 +6439,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="108"/>
+      <c r="F55" s="116"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6475,7 +6475,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="110">
+      <c r="A56" s="118">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6492,7 +6492,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="104"/>
+      <c r="F56" s="112"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6528,7 +6528,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="111"/>
+      <c r="A57" s="119"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6543,7 +6543,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="106"/>
+      <c r="F57" s="114"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6579,7 +6579,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="112"/>
+      <c r="A58" s="120"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6594,7 +6594,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="107"/>
+      <c r="F58" s="115"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6630,7 +6630,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="112"/>
+      <c r="A59" s="120"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6645,7 +6645,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="107"/>
+      <c r="F59" s="115"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6681,7 +6681,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="112"/>
+      <c r="A60" s="120"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6696,7 +6696,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="107"/>
+      <c r="F60" s="115"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6732,7 +6732,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="113"/>
+      <c r="A61" s="121"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6747,7 +6747,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="108"/>
+      <c r="F61" s="116"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6783,7 +6783,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="114">
+      <c r="A62" s="103">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6800,7 +6800,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="104"/>
+      <c r="F62" s="112"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6836,7 +6836,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="115"/>
+      <c r="A63" s="104"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -6851,7 +6851,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="106"/>
+      <c r="F63" s="114"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6887,7 +6887,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="116"/>
+      <c r="A64" s="105"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -6902,7 +6902,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="107"/>
+      <c r="F64" s="115"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6938,7 +6938,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="116"/>
+      <c r="A65" s="105"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -6953,7 +6953,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="107"/>
+      <c r="F65" s="115"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6989,7 +6989,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="116"/>
+      <c r="A66" s="105"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7004,7 +7004,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="107"/>
+      <c r="F66" s="115"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7040,7 +7040,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="117"/>
+      <c r="A67" s="106"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7055,7 +7055,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="108"/>
+      <c r="F67" s="116"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7091,7 +7091,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="122">
+      <c r="A68" s="107">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7108,7 +7108,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="104"/>
+      <c r="F68" s="112"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7144,7 +7144,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="123"/>
+      <c r="A69" s="108"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7159,7 +7159,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="106"/>
+      <c r="F69" s="114"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7195,7 +7195,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="124"/>
+      <c r="A70" s="109"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7210,7 +7210,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="107"/>
+      <c r="F70" s="115"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7246,7 +7246,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="124"/>
+      <c r="A71" s="109"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7261,7 +7261,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="107"/>
+      <c r="F71" s="115"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7297,7 +7297,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="124"/>
+      <c r="A72" s="109"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7312,7 +7312,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="107"/>
+      <c r="F72" s="115"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7348,7 +7348,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="125"/>
+      <c r="A73" s="110"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7363,7 +7363,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="109"/>
+      <c r="F73" s="117"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7404,15 +7404,15 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7428,27 +7428,27 @@
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7456,35 +7456,37 @@
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
@@ -7501,8 +7503,6 @@
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1562,6 +1562,18 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1594,18 +1606,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2665,7 +2665,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="111"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2754,7 +2754,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="112"/>
+      <c r="F2" s="116"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2844,7 +2844,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="113"/>
+      <c r="F3" s="117"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2936,7 +2936,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="112"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3027,7 +3027,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="113"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3103,7 +3103,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="118">
+      <c r="A6" s="107">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3120,7 +3120,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="112"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3196,7 +3196,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="119"/>
+      <c r="A7" s="108"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3211,7 +3211,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="114"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3287,7 +3287,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="120"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3302,7 +3302,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="115"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3378,7 +3378,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="121"/>
+      <c r="A9" s="110"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3393,7 +3393,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="116"/>
+      <c r="F9" s="120"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3486,7 +3486,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="112"/>
+      <c r="F10" s="116"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3575,7 +3575,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="114"/>
+      <c r="F11" s="118"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3666,7 +3666,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="115"/>
+      <c r="F12" s="119"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3757,7 +3757,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="116"/>
+      <c r="F13" s="120"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3833,7 +3833,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="118">
+      <c r="A14" s="107">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3850,7 +3850,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="112"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3926,7 +3926,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="119"/>
+      <c r="A15" s="108"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3941,7 +3941,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="114"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4017,7 +4017,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="120"/>
+      <c r="A16" s="109"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4032,7 +4032,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="115"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4108,7 +4108,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="121"/>
+      <c r="A17" s="110"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4123,7 +4123,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="116"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4216,7 +4216,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="112"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4307,7 +4307,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="114"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4398,7 +4398,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="115"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4489,7 +4489,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="116"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4565,7 +4565,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="118">
+      <c r="A22" s="107">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4582,7 +4582,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="112"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4658,7 +4658,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="119"/>
+      <c r="A23" s="108"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4673,7 +4673,7 @@
       <c r="E23" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="114"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4749,7 +4749,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="120"/>
+      <c r="A24" s="109"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4764,7 +4764,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="115"/>
+      <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4840,7 +4840,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="121"/>
+      <c r="A25" s="110"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4855,7 +4855,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="116"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4948,7 +4948,7 @@
       <c r="E26" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="112"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="60"/>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -4999,7 +4999,7 @@
       <c r="E27" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="114"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="63"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -5050,7 +5050,7 @@
       <c r="E28" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="115"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="65"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
@@ -5101,7 +5101,7 @@
       <c r="E29" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="116"/>
+      <c r="F29" s="120"/>
       <c r="G29" s="68"/>
       <c r="H29" s="69"/>
       <c r="I29" s="69"/>
@@ -5137,7 +5137,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="118">
+      <c r="A30" s="107">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5154,7 +5154,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="112"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -5190,7 +5190,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="119"/>
+      <c r="A31" s="108"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5205,7 +5205,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="114"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5241,7 +5241,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="120"/>
+      <c r="A32" s="109"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5256,7 +5256,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="115"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5292,7 +5292,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="121"/>
+      <c r="A33" s="110"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5307,7 +5307,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="116"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5360,7 +5360,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="112"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5411,7 +5411,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="114"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5462,7 +5462,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="115"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5513,7 +5513,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="116"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5549,7 +5549,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="118">
+      <c r="A38" s="107">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5566,7 +5566,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="112"/>
+      <c r="F38" s="116"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5602,7 +5602,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="119"/>
+      <c r="A39" s="108"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5617,7 +5617,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="114"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5653,7 +5653,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="120"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5668,7 +5668,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="115"/>
+      <c r="F40" s="119"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5704,7 +5704,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="121"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5719,7 +5719,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="116"/>
+      <c r="F41" s="120"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5772,7 +5772,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="112"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5823,7 +5823,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="114"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5874,7 +5874,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="115"/>
+      <c r="F44" s="119"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5925,7 +5925,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="116"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5961,7 +5961,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="118">
+      <c r="A46" s="107">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5978,7 +5978,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="112"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6014,7 +6014,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="119"/>
+      <c r="A47" s="108"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6029,7 +6029,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="114"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6065,7 +6065,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="120"/>
+      <c r="A48" s="109"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6080,7 +6080,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="115"/>
+      <c r="F48" s="119"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6116,7 +6116,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="121"/>
+      <c r="A49" s="110"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6131,7 +6131,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="116"/>
+      <c r="F49" s="120"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6184,7 +6184,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="112"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6235,7 +6235,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="114"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6286,7 +6286,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="115"/>
+      <c r="F52" s="119"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6337,7 +6337,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="115"/>
+      <c r="F53" s="119"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6388,7 +6388,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="115"/>
+      <c r="F54" s="119"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6439,7 +6439,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="116"/>
+      <c r="F55" s="120"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6475,7 +6475,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="118">
+      <c r="A56" s="107">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6492,7 +6492,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="112"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6528,7 +6528,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="119"/>
+      <c r="A57" s="108"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6543,7 +6543,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="114"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6579,7 +6579,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="120"/>
+      <c r="A58" s="109"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6594,7 +6594,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="115"/>
+      <c r="F58" s="119"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6630,7 +6630,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="120"/>
+      <c r="A59" s="109"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6645,7 +6645,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="115"/>
+      <c r="F59" s="119"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6681,7 +6681,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="120"/>
+      <c r="A60" s="109"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6696,7 +6696,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="115"/>
+      <c r="F60" s="119"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6732,7 +6732,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="121"/>
+      <c r="A61" s="110"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6747,7 +6747,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="116"/>
+      <c r="F61" s="120"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6800,7 +6800,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="112"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6851,7 +6851,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="114"/>
+      <c r="F63" s="118"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6902,7 +6902,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="115"/>
+      <c r="F64" s="119"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6953,7 +6953,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="115"/>
+      <c r="F65" s="119"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7004,7 +7004,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="115"/>
+      <c r="F66" s="119"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7055,7 +7055,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="116"/>
+      <c r="F67" s="120"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7091,7 +7091,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="107">
+      <c r="A68" s="111">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7108,7 +7108,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="112"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7144,7 +7144,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="108"/>
+      <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7159,7 +7159,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="114"/>
+      <c r="F69" s="118"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7195,7 +7195,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="109"/>
+      <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7210,7 +7210,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="115"/>
+      <c r="F70" s="119"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7246,7 +7246,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="109"/>
+      <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7261,7 +7261,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="115"/>
+      <c r="F71" s="119"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7297,7 +7297,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="109"/>
+      <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7312,7 +7312,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="115"/>
+      <c r="F72" s="119"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7348,7 +7348,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="110"/>
+      <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7363,7 +7363,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="117"/>
+      <c r="F73" s="121"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7485,6 +7485,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
@@ -7501,8 +7503,6 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6015B5-79DD-432D-8F1F-5A314E0DBFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3BB09F-C02B-470C-BD61-7347A8787CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="134">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -462,6 +462,9 @@
   </si>
   <si>
     <t>4x2</t>
+  </si>
+  <si>
+    <t>1x3</t>
   </si>
 </sst>
 </file>
@@ -4671,7 +4674,7 @@
         <v>Colômbia</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="F23" s="118"/>
       <c r="G23" s="63" t="s">
@@ -4734,17 +4737,17 @@
       <c r="Z23" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="AA23" s="81" t="str">
+      <c r="AA23" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB23" s="90" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AC23" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD23" s="54"/>
     </row>
@@ -7404,15 +7407,15 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7420,76 +7423,71 @@
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7503,6 +7501,11 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3BB09F-C02B-470C-BD61-7347A8787CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AF6FBF-09E5-42EB-B3B2-548EAECD1274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="134">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -1553,6 +1553,51 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1564,51 +1609,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2668,7 +2668,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="115"/>
+      <c r="F1" s="107"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2757,7 +2757,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="116"/>
+      <c r="F2" s="108"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2847,7 +2847,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="117"/>
+      <c r="F3" s="109"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2939,7 +2939,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="116"/>
+      <c r="F4" s="108"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3030,7 +3030,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="117"/>
+      <c r="F5" s="109"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3106,7 +3106,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="107">
+      <c r="A6" s="114">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3123,7 +3123,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="116"/>
+      <c r="F6" s="108"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3199,7 +3199,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="108"/>
+      <c r="A7" s="115"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3214,7 +3214,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="118"/>
+      <c r="F7" s="110"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3290,7 +3290,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="109"/>
+      <c r="A8" s="116"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="119"/>
+      <c r="F8" s="111"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3381,7 +3381,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="110"/>
+      <c r="A9" s="117"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3396,7 +3396,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="120"/>
+      <c r="F9" s="112"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3472,7 +3472,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="103">
+      <c r="A10" s="118">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3489,7 +3489,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="116"/>
+      <c r="F10" s="108"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3563,7 +3563,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="104"/>
+      <c r="A11" s="119"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3578,7 +3578,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="110"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3654,7 +3654,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="105"/>
+      <c r="A12" s="120"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3669,7 +3669,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="119"/>
+      <c r="F12" s="111"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3745,7 +3745,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="106"/>
+      <c r="A13" s="121"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3760,7 +3760,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="120"/>
+      <c r="F13" s="112"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3836,7 +3836,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="107">
+      <c r="A14" s="114">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3853,7 +3853,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="116"/>
+      <c r="F14" s="108"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3929,7 +3929,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="108"/>
+      <c r="A15" s="115"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3944,7 +3944,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="118"/>
+      <c r="F15" s="110"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4020,7 +4020,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="109"/>
+      <c r="A16" s="116"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4035,7 +4035,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="119"/>
+      <c r="F16" s="111"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4111,7 +4111,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="110"/>
+      <c r="A17" s="117"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4126,7 +4126,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="120"/>
+      <c r="F17" s="112"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4202,7 +4202,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="103">
+      <c r="A18" s="118">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4219,7 +4219,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="116"/>
+      <c r="F18" s="108"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4295,7 +4295,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="104"/>
+      <c r="A19" s="119"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4310,7 +4310,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="118"/>
+      <c r="F19" s="110"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4386,7 +4386,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="105"/>
+      <c r="A20" s="120"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4401,7 +4401,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="119"/>
+      <c r="F20" s="111"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4477,7 +4477,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="106"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4492,7 +4492,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="120"/>
+      <c r="F21" s="112"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4568,7 +4568,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="107">
+      <c r="A22" s="114">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4585,7 +4585,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="116"/>
+      <c r="F22" s="108"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4661,7 +4661,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="108"/>
+      <c r="A23" s="115"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4676,7 +4676,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="118"/>
+      <c r="F23" s="110"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4752,7 +4752,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="109"/>
+      <c r="A24" s="116"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4767,7 +4767,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="119"/>
+      <c r="F24" s="111"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4843,7 +4843,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="110"/>
+      <c r="A25" s="117"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="120"/>
+      <c r="F25" s="112"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4934,7 +4934,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="103">
+      <c r="A26" s="118">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4949,45 +4949,85 @@
         <v>África do Sul</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="116"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="61"/>
-      <c r="O26" s="61"/>
-      <c r="P26" s="61"/>
-      <c r="Q26" s="61"/>
-      <c r="R26" s="61"/>
-      <c r="S26" s="61"/>
-      <c r="T26" s="61"/>
-      <c r="U26" s="62"/>
-      <c r="V26" s="62"/>
-      <c r="W26" s="62"/>
-      <c r="X26" s="62"/>
-      <c r="Y26" s="62"/>
-      <c r="Z26" s="76"/>
-      <c r="AA26" s="81" t="str">
+        <v>50</v>
+      </c>
+      <c r="F26" s="108"/>
+      <c r="G26" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="K26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="L26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="M26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="N26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="O26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="P26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="R26" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="S26" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="T26" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="U26" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="V26" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="W26" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="X26" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y26" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA26" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB26" s="90" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC26" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="104"/>
+      <c r="A27" s="119"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5002,26 +5042,64 @@
       <c r="E27" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="118"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="71"/>
-      <c r="S27" s="71"/>
-      <c r="T27" s="71"/>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="56"/>
-      <c r="Y27" s="56"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="J27" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K27" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="L27" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="M27" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="N27" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O27" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="P27" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q27" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="R27" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="S27" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="T27" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="U27" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="V27" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="W27" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="X27" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y27" s="56" t="s">
+        <v>45</v>
+      </c>
       <c r="Z27" s="80"/>
       <c r="AA27" s="81" t="str">
         <f t="shared" si="5"/>
@@ -5038,7 +5116,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="105"/>
+      <c r="A28" s="120"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5053,26 +5131,64 @@
       <c r="E28" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="119"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
-      <c r="U28" s="67"/>
-      <c r="V28" s="67"/>
-      <c r="W28" s="67"/>
-      <c r="X28" s="67"/>
-      <c r="Y28" s="67"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I28" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="K28" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="L28" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="M28" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="N28" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O28" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="P28" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q28" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="R28" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="S28" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="T28" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="U28" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="V28" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W28" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="X28" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y28" s="67" t="s">
+        <v>44</v>
+      </c>
       <c r="Z28" s="78"/>
       <c r="AA28" s="81" t="str">
         <f t="shared" si="5"/>
@@ -5089,7 +5205,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="106"/>
+      <c r="A29" s="121"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5104,26 +5220,64 @@
       <c r="E29" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="120"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="69"/>
-      <c r="L29" s="69"/>
-      <c r="M29" s="69"/>
-      <c r="N29" s="69"/>
-      <c r="O29" s="69"/>
-      <c r="P29" s="69"/>
-      <c r="Q29" s="69"/>
-      <c r="R29" s="69"/>
-      <c r="S29" s="69"/>
-      <c r="T29" s="69"/>
-      <c r="U29" s="70"/>
-      <c r="V29" s="70"/>
-      <c r="W29" s="70"/>
-      <c r="X29" s="70"/>
-      <c r="Y29" s="70"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="I29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="J29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="K29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="L29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="M29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="N29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="O29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="P29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="R29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="S29" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="T29" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="U29" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="V29" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="W29" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="X29" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y29" s="70" t="s">
+        <v>44</v>
+      </c>
       <c r="Z29" s="79"/>
       <c r="AA29" s="81" t="str">
         <f t="shared" si="5"/>
@@ -5140,7 +5294,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="107">
+      <c r="A30" s="114">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5157,7 +5311,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="116"/>
+      <c r="F30" s="108"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -5193,7 +5347,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="108"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5208,7 +5362,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="118"/>
+      <c r="F31" s="110"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5244,7 +5398,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="109"/>
+      <c r="A32" s="116"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5259,7 +5413,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="119"/>
+      <c r="F32" s="111"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5295,7 +5449,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="110"/>
+      <c r="A33" s="117"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5310,7 +5464,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="120"/>
+      <c r="F33" s="112"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5346,7 +5500,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="103">
+      <c r="A34" s="118">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5363,7 +5517,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="116"/>
+      <c r="F34" s="108"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5399,7 +5553,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="104"/>
+      <c r="A35" s="119"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5414,7 +5568,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="118"/>
+      <c r="F35" s="110"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5450,7 +5604,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="105"/>
+      <c r="A36" s="120"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5465,7 +5619,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="111"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5501,7 +5655,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="106"/>
+      <c r="A37" s="121"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5516,7 +5670,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="120"/>
+      <c r="F37" s="112"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5552,7 +5706,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="107">
+      <c r="A38" s="114">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5569,7 +5723,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="116"/>
+      <c r="F38" s="108"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5605,7 +5759,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="108"/>
+      <c r="A39" s="115"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5620,7 +5774,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="118"/>
+      <c r="F39" s="110"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5656,7 +5810,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="109"/>
+      <c r="A40" s="116"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5671,7 +5825,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="119"/>
+      <c r="F40" s="111"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5707,7 +5861,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="110"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5722,7 +5876,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="120"/>
+      <c r="F41" s="112"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5758,7 +5912,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="103">
+      <c r="A42" s="118">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5775,7 +5929,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="116"/>
+      <c r="F42" s="108"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5811,7 +5965,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="104"/>
+      <c r="A43" s="119"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5826,7 +5980,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="118"/>
+      <c r="F43" s="110"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -5862,7 +6016,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="105"/>
+      <c r="A44" s="120"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -5877,7 +6031,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="119"/>
+      <c r="F44" s="111"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -5913,7 +6067,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="106"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -5928,7 +6082,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="120"/>
+      <c r="F45" s="112"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -5964,7 +6118,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="107">
+      <c r="A46" s="114">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -5981,7 +6135,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="116"/>
+      <c r="F46" s="108"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6017,7 +6171,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="108"/>
+      <c r="A47" s="115"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6032,7 +6186,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="118"/>
+      <c r="F47" s="110"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6068,7 +6222,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="109"/>
+      <c r="A48" s="116"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6083,7 +6237,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="119"/>
+      <c r="F48" s="111"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6119,7 +6273,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="110"/>
+      <c r="A49" s="117"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6134,7 +6288,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="120"/>
+      <c r="F49" s="112"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6170,7 +6324,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="103">
+      <c r="A50" s="118">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6187,7 +6341,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="116"/>
+      <c r="F50" s="108"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6223,7 +6377,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="104"/>
+      <c r="A51" s="119"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6238,7 +6392,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="118"/>
+      <c r="F51" s="110"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6274,7 +6428,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="105"/>
+      <c r="A52" s="120"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6289,7 +6443,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="119"/>
+      <c r="F52" s="111"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6325,7 +6479,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="105"/>
+      <c r="A53" s="120"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6340,7 +6494,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="119"/>
+      <c r="F53" s="111"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6376,7 +6530,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="105"/>
+      <c r="A54" s="120"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6391,7 +6545,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="119"/>
+      <c r="F54" s="111"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6427,7 +6581,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="106"/>
+      <c r="A55" s="121"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6442,7 +6596,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="120"/>
+      <c r="F55" s="112"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6478,7 +6632,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="107">
+      <c r="A56" s="114">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6495,7 +6649,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="116"/>
+      <c r="F56" s="108"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6531,7 +6685,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="108"/>
+      <c r="A57" s="115"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6546,7 +6700,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="118"/>
+      <c r="F57" s="110"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6582,7 +6736,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="109"/>
+      <c r="A58" s="116"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6597,7 +6751,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="119"/>
+      <c r="F58" s="111"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6633,7 +6787,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="109"/>
+      <c r="A59" s="116"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6648,7 +6802,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="119"/>
+      <c r="F59" s="111"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6684,7 +6838,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="109"/>
+      <c r="A60" s="116"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6699,7 +6853,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="119"/>
+      <c r="F60" s="111"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6735,7 +6889,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="110"/>
+      <c r="A61" s="117"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6750,7 +6904,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="120"/>
+      <c r="F61" s="112"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6786,7 +6940,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="103">
+      <c r="A62" s="118">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6803,7 +6957,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="116"/>
+      <c r="F62" s="108"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6839,7 +6993,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="104"/>
+      <c r="A63" s="119"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -6854,7 +7008,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="118"/>
+      <c r="F63" s="110"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -6890,7 +7044,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="105"/>
+      <c r="A64" s="120"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -6905,7 +7059,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="119"/>
+      <c r="F64" s="111"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -6941,7 +7095,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="105"/>
+      <c r="A65" s="120"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -6956,7 +7110,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="119"/>
+      <c r="F65" s="111"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -6992,7 +7146,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="105"/>
+      <c r="A66" s="120"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7007,7 +7161,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="119"/>
+      <c r="F66" s="111"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7043,7 +7197,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="106"/>
+      <c r="A67" s="121"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7058,7 +7212,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="120"/>
+      <c r="F67" s="112"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7094,7 +7248,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="111">
+      <c r="A68" s="103">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7111,7 +7265,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="116"/>
+      <c r="F68" s="108"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7147,7 +7301,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="112"/>
+      <c r="A69" s="104"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7162,7 +7316,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="118"/>
+      <c r="F69" s="110"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7198,7 +7352,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="113"/>
+      <c r="A70" s="105"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7213,7 +7367,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="119"/>
+      <c r="F70" s="111"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7249,7 +7403,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="113"/>
+      <c r="A71" s="105"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7264,7 +7418,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="119"/>
+      <c r="F71" s="111"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7300,7 +7454,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="113"/>
+      <c r="A72" s="105"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7315,7 +7469,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="119"/>
+      <c r="F72" s="111"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7351,7 +7505,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="114"/>
+      <c r="A73" s="106"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7366,7 +7520,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="121"/>
+      <c r="F73" s="113"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7451,11 +7605,11 @@
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7488,6 +7642,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7504,8 +7660,6 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10605"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AF6FBF-09E5-42EB-B3B2-548EAECD1274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B6711BC-E01D-0248-8B4C-0A48308E9B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -1553,6 +1553,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1585,30 +1609,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2080,13 +2080,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="3" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.75" customWidth="1"/>
+    <col min="2" max="3" width="14.2578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
@@ -2098,7 +2098,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="126"/>
       <c r="B2" s="126"/>
       <c r="C2" s="13"/>
@@ -2108,7 +2108,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="126"/>
       <c r="B3" s="126"/>
       <c r="C3" s="13"/>
@@ -2126,7 +2126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2278,16 +2278,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="7" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="22.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.6484375" customWidth="1"/>
+    <col min="2" max="2" width="20.984375" customWidth="1"/>
+    <col min="3" max="7" width="12.10546875" customWidth="1"/>
+    <col min="9" max="9" width="22.8671875" customWidth="1"/>
+    <col min="10" max="10" width="9.55078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="127" t="s">
         <v>20</v>
       </c>
@@ -2298,7 +2298,7 @@
       <c r="F1" s="128"/>
       <c r="G1" s="128"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2346,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2389,7 +2389,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2413,7 +2413,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2437,7 +2437,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2458,7 +2458,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2479,7 +2479,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2500,7 +2500,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2521,7 +2521,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2542,7 +2542,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2563,7 +2563,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2584,7 +2584,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2605,7 +2605,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2642,17 +2642,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="29" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.8359375" customWidth="1"/>
+    <col min="2" max="2" width="32.41796875" customWidth="1"/>
+    <col min="3" max="4" width="20.58203125" customWidth="1"/>
+    <col min="5" max="5" width="12.5078125" customWidth="1"/>
+    <col min="6" max="6" width="6.05078125" customWidth="1"/>
+    <col min="7" max="29" width="16.41015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2668,7 +2668,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="107"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="122">
         <v>46184</v>
       </c>
@@ -2757,7 +2757,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="108"/>
+      <c r="F2" s="116"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2847,7 +2847,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="109"/>
+      <c r="F3" s="117"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="124">
         <v>46185</v>
       </c>
@@ -2939,7 +2939,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -3030,7 +3030,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="109"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3105,8 +3105,8 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="114">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A6" s="103">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3123,7 +3123,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3198,8 +3198,8 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="115"/>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A7" s="104"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3214,7 +3214,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="110"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3289,8 +3289,8 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="116"/>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A8" s="105"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="111"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3380,8 +3380,8 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="117"/>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A9" s="106"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3396,7 +3396,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="112"/>
+      <c r="F9" s="120"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3471,8 +3471,8 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="118">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A10" s="107">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3489,7 +3489,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="116"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3562,8 +3562,8 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="119"/>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A11" s="108"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3578,7 +3578,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="110"/>
+      <c r="F11" s="118"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3653,8 +3653,8 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="120"/>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A12" s="109"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3669,7 +3669,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="111"/>
+      <c r="F12" s="119"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3744,8 +3744,8 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="121"/>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A13" s="110"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3760,7 +3760,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="112"/>
+      <c r="F13" s="120"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3835,8 +3835,8 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="114">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A14" s="103">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3853,7 +3853,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="108"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3928,8 +3928,8 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="115"/>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A15" s="104"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3944,7 +3944,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="110"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4019,8 +4019,8 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="116"/>
+    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="105"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4035,7 +4035,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="111"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4110,8 +4110,8 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="117"/>
+    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="106"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4126,7 +4126,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="112"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4201,8 +4201,8 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="118">
+    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="107">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4219,7 +4219,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="108"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4294,8 +4294,8 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="119"/>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A19" s="108"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4310,7 +4310,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="110"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4385,8 +4385,8 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="120"/>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A20" s="109"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4401,7 +4401,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="111"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4476,8 +4476,8 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="121"/>
+    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="110"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4492,7 +4492,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="112"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4567,8 +4567,8 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="114">
+    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="103">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4585,7 +4585,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="108"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4660,8 +4660,8 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="115"/>
+    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="104"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4676,7 +4676,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="110"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4751,8 +4751,8 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="116"/>
+    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="105"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4767,7 +4767,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="111"/>
+      <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4842,8 +4842,8 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="117"/>
+    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="106"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="112"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4933,8 +4933,8 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="118">
+    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="107">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4951,7 +4951,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="108"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5026,8 +5026,8 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="119"/>
+    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="108"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5040,9 +5040,9 @@
         <v>Coreia do Sul</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="110"/>
+        <v>52</v>
+      </c>
+      <c r="F27" s="118"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5101,22 +5101,22 @@
         <v>45</v>
       </c>
       <c r="Z27" s="80"/>
-      <c r="AA27" s="81" t="str">
+      <c r="AA27" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB27" s="90" t="str">
+        <v>4</v>
+      </c>
+      <c r="AB27" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC27" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="120"/>
+    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="109"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5131,7 +5131,7 @@
       <c r="E28" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="111"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5204,8 +5204,8 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="121"/>
+    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="110"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5220,7 +5220,7 @@
       <c r="E29" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="112"/>
+      <c r="F29" s="120"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5293,8 +5293,8 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="114">
+    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="103">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5311,7 +5311,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="108"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -5346,8 +5346,8 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="115"/>
+    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="104"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5362,7 +5362,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="110"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5397,8 +5397,8 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="116"/>
+    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="105"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5413,7 +5413,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="111"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5448,8 +5448,8 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="117"/>
+    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="106"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5464,7 +5464,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="112"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5499,8 +5499,8 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="118">
+    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="107">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5517,7 +5517,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="108"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5552,8 +5552,8 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="119"/>
+    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="108"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5568,7 +5568,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="110"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5603,8 +5603,8 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="120"/>
+    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="109"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5619,7 +5619,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="111"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5654,8 +5654,8 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="121"/>
+    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="110"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5670,7 +5670,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="112"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5705,8 +5705,8 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="114">
+    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="103">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5723,7 +5723,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="108"/>
+      <c r="F38" s="116"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5758,8 +5758,8 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="115"/>
+    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="104"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5774,7 +5774,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="110"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5809,8 +5809,8 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="116"/>
+    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="105"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5825,7 +5825,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="111"/>
+      <c r="F40" s="119"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5860,8 +5860,8 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="117"/>
+    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="106"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5876,7 +5876,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="112"/>
+      <c r="F41" s="120"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5911,8 +5911,8 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="118">
+    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="107">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5929,7 +5929,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="108"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5964,8 +5964,8 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="119"/>
+    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="108"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5980,7 +5980,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="110"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6015,8 +6015,8 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="120"/>
+    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="109"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6031,7 +6031,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="111"/>
+      <c r="F44" s="119"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6066,8 +6066,8 @@
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="121"/>
+    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="110"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6082,7 +6082,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="112"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6117,8 +6117,8 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="114">
+    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="103">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6135,7 +6135,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="108"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6170,8 +6170,8 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="115"/>
+    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="104"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6186,7 +6186,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="110"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6221,8 +6221,8 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="116"/>
+    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="105"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6237,7 +6237,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="111"/>
+      <c r="F48" s="119"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6272,8 +6272,8 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="117"/>
+    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="106"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6288,7 +6288,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="112"/>
+      <c r="F49" s="120"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6323,8 +6323,8 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="118">
+    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="107">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6341,7 +6341,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="108"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6376,8 +6376,8 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="119"/>
+    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="108"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6392,7 +6392,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="110"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6427,8 +6427,8 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="120"/>
+    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="109"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6443,7 +6443,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="111"/>
+      <c r="F52" s="119"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6478,8 +6478,8 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="120"/>
+    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="109"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6494,7 +6494,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="111"/>
+      <c r="F53" s="119"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6529,8 +6529,8 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="120"/>
+    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="109"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6545,7 +6545,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="111"/>
+      <c r="F54" s="119"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6580,8 +6580,8 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="121"/>
+    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="110"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6596,7 +6596,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="112"/>
+      <c r="F55" s="120"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6631,8 +6631,8 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="114">
+    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="103">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6649,7 +6649,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="108"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6684,8 +6684,8 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="115"/>
+    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="104"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6700,7 +6700,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="110"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6735,8 +6735,8 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="116"/>
+    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="105"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6751,7 +6751,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="111"/>
+      <c r="F58" s="119"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6786,8 +6786,8 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="116"/>
+    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="105"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6802,7 +6802,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="111"/>
+      <c r="F59" s="119"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6837,8 +6837,8 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="116"/>
+    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="105"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6853,7 +6853,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="111"/>
+      <c r="F60" s="119"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6888,8 +6888,8 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="117"/>
+    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="106"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6904,7 +6904,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="112"/>
+      <c r="F61" s="120"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6939,8 +6939,8 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="118">
+    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="107">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6957,7 +6957,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="108"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6992,8 +6992,8 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="119"/>
+    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="108"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7008,7 +7008,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="110"/>
+      <c r="F63" s="118"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7043,8 +7043,8 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="120"/>
+    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="109"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7059,7 +7059,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="111"/>
+      <c r="F64" s="119"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7094,8 +7094,8 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="120"/>
+    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="109"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7110,7 +7110,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="111"/>
+      <c r="F65" s="119"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7145,8 +7145,8 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="120"/>
+    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="109"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7161,7 +7161,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="111"/>
+      <c r="F66" s="119"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7196,8 +7196,8 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="121"/>
+    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="110"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7212,7 +7212,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="112"/>
+      <c r="F67" s="120"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7247,8 +7247,8 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="103">
+    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="111">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7265,7 +7265,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="108"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7300,8 +7300,8 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="104"/>
+    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7316,7 +7316,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="110"/>
+      <c r="F69" s="118"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7351,8 +7351,8 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="105"/>
+    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7367,7 +7367,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="111"/>
+      <c r="F70" s="119"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7402,8 +7402,8 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="105"/>
+    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7418,7 +7418,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="111"/>
+      <c r="F71" s="119"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7453,8 +7453,8 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="105"/>
+    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7469,7 +7469,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="111"/>
+      <c r="F72" s="119"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7504,8 +7504,8 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="106"/>
+    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7520,7 +7520,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="113"/>
+      <c r="F73" s="121"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7555,17 +7555,17 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F74" s="19" t="s">
         <v>129</v>
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7585,15 +7585,15 @@
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7642,9 +7642,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -7660,6 +7657,9 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B6711BC-E01D-0248-8B4C-0A48308E9B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37701A7C-15B7-674B-B9AC-1F61166B76E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -5040,7 +5040,7 @@
         <v>Coreia do Sul</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="F27" s="118"/>
       <c r="G27" s="63" t="s">
@@ -5101,17 +5101,17 @@
         <v>45</v>
       </c>
       <c r="Z27" s="80"/>
-      <c r="AA27" s="81">
+      <c r="AA27" s="81" t="str">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="AB27" s="90">
+        <v/>
+      </c>
+      <c r="AB27" s="90" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="AC27" s="85" t="str">
         <f t="shared" si="4"/>
-        <v>A</v>
+        <v/>
       </c>
       <c r="AD27" s="54"/>
     </row>
@@ -5129,7 +5129,7 @@
         <v>Bósnia e Herzeg.</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="F28" s="119"/>
       <c r="G28" s="65" t="s">
@@ -5190,17 +5190,17 @@
         <v>44</v>
       </c>
       <c r="Z28" s="78"/>
-      <c r="AA28" s="81" t="str">
+      <c r="AA28" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB28" s="90" t="str">
+        <v>4</v>
+      </c>
+      <c r="AB28" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC28" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD28" s="54"/>
     </row>
@@ -7577,11 +7577,11 @@
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7621,19 +7621,19 @@
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37701A7C-15B7-674B-B9AC-1F61166B76E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F8A0DF4-D264-BE46-ABC0-6B5005978ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="136">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -465,6 +465,9 @@
   </si>
   <si>
     <t>1x3</t>
+  </si>
+  <si>
+    <t>6x0</t>
   </si>
 </sst>
 </file>
@@ -1553,6 +1556,27 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1577,6 +1601,18 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1588,39 +1624,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2668,7 +2671,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="115"/>
+      <c r="F1" s="103"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2740,7 +2743,7 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A2" s="122">
+      <c r="A2" s="118">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2757,7 +2760,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="116"/>
+      <c r="F2" s="104"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2832,7 +2835,7 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="123"/>
+      <c r="A3" s="119"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2847,7 +2850,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="117"/>
+      <c r="F3" s="105"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2922,7 +2925,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A4" s="124">
+      <c r="A4" s="120">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2939,7 +2942,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="116"/>
+      <c r="F4" s="104"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3015,7 +3018,7 @@
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A5" s="125"/>
+      <c r="A5" s="121"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -3030,7 +3033,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="117"/>
+      <c r="F5" s="105"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3106,7 +3109,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="103">
+      <c r="A6" s="110">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3123,7 +3126,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="116"/>
+      <c r="F6" s="104"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3199,7 +3202,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="104"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3214,7 +3217,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="118"/>
+      <c r="F7" s="106"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3290,7 +3293,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="105"/>
+      <c r="A8" s="112"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3305,7 +3308,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="119"/>
+      <c r="F8" s="107"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3381,7 +3384,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="106"/>
+      <c r="A9" s="113"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3396,7 +3399,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="120"/>
+      <c r="F9" s="108"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3472,7 +3475,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="107">
+      <c r="A10" s="114">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3489,7 +3492,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="116"/>
+      <c r="F10" s="104"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3563,7 +3566,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="108"/>
+      <c r="A11" s="115"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3578,7 +3581,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="106"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3654,7 +3657,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A12" s="109"/>
+      <c r="A12" s="116"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3669,7 +3672,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="119"/>
+      <c r="F12" s="107"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3745,7 +3748,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="110"/>
+      <c r="A13" s="117"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3760,7 +3763,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="120"/>
+      <c r="F13" s="108"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3836,7 +3839,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="103">
+      <c r="A14" s="110">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3853,7 +3856,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="116"/>
+      <c r="F14" s="104"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3929,7 +3932,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="104"/>
+      <c r="A15" s="111"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3944,7 +3947,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="118"/>
+      <c r="F15" s="106"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4020,7 +4023,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="105"/>
+      <c r="A16" s="112"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4035,7 +4038,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="119"/>
+      <c r="F16" s="107"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4111,7 +4114,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="106"/>
+      <c r="A17" s="113"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4126,7 +4129,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="120"/>
+      <c r="F17" s="108"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4202,7 +4205,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="107">
+      <c r="A18" s="114">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4219,7 +4222,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="116"/>
+      <c r="F18" s="104"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4295,7 +4298,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A19" s="108"/>
+      <c r="A19" s="115"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4310,7 +4313,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="118"/>
+      <c r="F19" s="106"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4386,7 +4389,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A20" s="109"/>
+      <c r="A20" s="116"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4401,7 +4404,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="119"/>
+      <c r="F20" s="107"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4477,7 +4480,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="110"/>
+      <c r="A21" s="117"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4492,7 +4495,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="120"/>
+      <c r="F21" s="108"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4568,7 +4571,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="103">
+      <c r="A22" s="110">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4585,7 +4588,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="116"/>
+      <c r="F22" s="104"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4661,7 +4664,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="104"/>
+      <c r="A23" s="111"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4676,7 +4679,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="118"/>
+      <c r="F23" s="106"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4752,7 +4755,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="105"/>
+      <c r="A24" s="112"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4767,7 +4770,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="119"/>
+      <c r="F24" s="107"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4843,7 +4846,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="106"/>
+      <c r="A25" s="113"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4858,7 +4861,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="120"/>
+      <c r="F25" s="108"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4934,7 +4937,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="107">
+      <c r="A26" s="114">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4951,7 +4954,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="116"/>
+      <c r="F26" s="104"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5027,7 +5030,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="108"/>
+      <c r="A27" s="115"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5042,7 +5045,7 @@
       <c r="E27" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="118"/>
+      <c r="F27" s="106"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5116,7 +5119,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="109"/>
+      <c r="A28" s="116"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5131,7 +5134,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="119"/>
+      <c r="F28" s="107"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5205,7 +5208,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="110"/>
+      <c r="A29" s="117"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5218,9 +5221,9 @@
         <v>Catar</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="120"/>
+        <v>134</v>
+      </c>
+      <c r="F29" s="108"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5279,22 +5282,22 @@
         <v>44</v>
       </c>
       <c r="Z29" s="79"/>
-      <c r="AA29" s="81" t="str">
+      <c r="AA29" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB29" s="90" t="str">
+        <v>6</v>
+      </c>
+      <c r="AB29" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC29" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="103">
+      <c r="A30" s="110">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5311,7 +5314,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="116"/>
+      <c r="F30" s="104"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -5347,7 +5350,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="104"/>
+      <c r="A31" s="111"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5362,7 +5365,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="118"/>
+      <c r="F31" s="106"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5398,7 +5401,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="105"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5413,7 +5416,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="119"/>
+      <c r="F32" s="107"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5449,7 +5452,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="106"/>
+      <c r="A33" s="113"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5464,7 +5467,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="120"/>
+      <c r="F33" s="108"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5500,7 +5503,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="107">
+      <c r="A34" s="114">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5517,7 +5520,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="116"/>
+      <c r="F34" s="104"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5553,7 +5556,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="108"/>
+      <c r="A35" s="115"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5568,7 +5571,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="118"/>
+      <c r="F35" s="106"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5604,7 +5607,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="109"/>
+      <c r="A36" s="116"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5619,7 +5622,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="107"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5655,7 +5658,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="110"/>
+      <c r="A37" s="117"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5670,7 +5673,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="120"/>
+      <c r="F37" s="108"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5706,7 +5709,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="103">
+      <c r="A38" s="110">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5723,7 +5726,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="116"/>
+      <c r="F38" s="104"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5759,7 +5762,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="104"/>
+      <c r="A39" s="111"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5774,7 +5777,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="118"/>
+      <c r="F39" s="106"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5810,7 +5813,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="105"/>
+      <c r="A40" s="112"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5825,7 +5828,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="119"/>
+      <c r="F40" s="107"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5861,7 +5864,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="106"/>
+      <c r="A41" s="113"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5876,7 +5879,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="120"/>
+      <c r="F41" s="108"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5912,7 +5915,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="107">
+      <c r="A42" s="114">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5929,7 +5932,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="116"/>
+      <c r="F42" s="104"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5965,7 +5968,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="108"/>
+      <c r="A43" s="115"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5980,7 +5983,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="118"/>
+      <c r="F43" s="106"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6016,7 +6019,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="109"/>
+      <c r="A44" s="116"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6031,7 +6034,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="119"/>
+      <c r="F44" s="107"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6067,7 +6070,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="110"/>
+      <c r="A45" s="117"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6082,7 +6085,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="120"/>
+      <c r="F45" s="108"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6118,7 +6121,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="103">
+      <c r="A46" s="110">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6135,7 +6138,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="116"/>
+      <c r="F46" s="104"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6171,7 +6174,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="104"/>
+      <c r="A47" s="111"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6186,7 +6189,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="118"/>
+      <c r="F47" s="106"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6222,7 +6225,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="105"/>
+      <c r="A48" s="112"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6237,7 +6240,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="119"/>
+      <c r="F48" s="107"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6273,7 +6276,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="106"/>
+      <c r="A49" s="113"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6288,7 +6291,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="120"/>
+      <c r="F49" s="108"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6324,7 +6327,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="107">
+      <c r="A50" s="114">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6341,7 +6344,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="116"/>
+      <c r="F50" s="104"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6377,7 +6380,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="108"/>
+      <c r="A51" s="115"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6392,7 +6395,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="118"/>
+      <c r="F51" s="106"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6428,7 +6431,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="109"/>
+      <c r="A52" s="116"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6443,7 +6446,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="119"/>
+      <c r="F52" s="107"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6479,7 +6482,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="109"/>
+      <c r="A53" s="116"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6494,7 +6497,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="119"/>
+      <c r="F53" s="107"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6530,7 +6533,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="109"/>
+      <c r="A54" s="116"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6545,7 +6548,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="119"/>
+      <c r="F54" s="107"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6581,7 +6584,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="110"/>
+      <c r="A55" s="117"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6596,7 +6599,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="120"/>
+      <c r="F55" s="108"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6632,7 +6635,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="103">
+      <c r="A56" s="110">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6649,7 +6652,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="116"/>
+      <c r="F56" s="104"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6685,7 +6688,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="104"/>
+      <c r="A57" s="111"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6700,7 +6703,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="118"/>
+      <c r="F57" s="106"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6736,7 +6739,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="105"/>
+      <c r="A58" s="112"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6751,7 +6754,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="119"/>
+      <c r="F58" s="107"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6787,7 +6790,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="105"/>
+      <c r="A59" s="112"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6802,7 +6805,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="119"/>
+      <c r="F59" s="107"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6838,7 +6841,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="105"/>
+      <c r="A60" s="112"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6853,7 +6856,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="119"/>
+      <c r="F60" s="107"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6889,7 +6892,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="106"/>
+      <c r="A61" s="113"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6904,7 +6907,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="120"/>
+      <c r="F61" s="108"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6940,7 +6943,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="107">
+      <c r="A62" s="114">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6957,7 +6960,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="116"/>
+      <c r="F62" s="104"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6993,7 +6996,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="108"/>
+      <c r="A63" s="115"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7008,7 +7011,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="118"/>
+      <c r="F63" s="106"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7044,7 +7047,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
+      <c r="A64" s="116"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7059,7 +7062,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="119"/>
+      <c r="F64" s="107"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7095,7 +7098,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="109"/>
+      <c r="A65" s="116"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7110,7 +7113,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="119"/>
+      <c r="F65" s="107"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7146,7 +7149,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="109"/>
+      <c r="A66" s="116"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7161,7 +7164,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="119"/>
+      <c r="F66" s="107"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7197,7 +7200,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="110"/>
+      <c r="A67" s="117"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7212,7 +7215,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="120"/>
+      <c r="F67" s="108"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7248,7 +7251,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="111">
+      <c r="A68" s="122">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7265,7 +7268,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="116"/>
+      <c r="F68" s="104"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7301,7 +7304,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="112"/>
+      <c r="A69" s="123"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7316,7 +7319,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="118"/>
+      <c r="F69" s="106"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7352,7 +7355,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="113"/>
+      <c r="A70" s="124"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7367,7 +7370,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="119"/>
+      <c r="F70" s="107"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7403,7 +7406,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="113"/>
+      <c r="A71" s="124"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7418,7 +7421,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="119"/>
+      <c r="F71" s="107"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7454,7 +7457,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="113"/>
+      <c r="A72" s="124"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7469,7 +7472,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="119"/>
+      <c r="F72" s="107"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7505,7 +7508,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="114"/>
+      <c r="A73" s="125"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7520,7 +7523,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="121"/>
+      <c r="F73" s="109"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7561,51 +7564,51 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7613,15 +7616,15 @@
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7633,7 +7636,7 @@
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7642,6 +7645,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -7658,8 +7663,6 @@
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F8A0DF4-D264-BE46-ABC0-6B5005978ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AD9DE09-E21B-004B-B4A8-1E1793E08758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="135">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -1556,6 +1556,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -1589,18 +1613,6 @@
     <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1612,18 +1624,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2671,7 +2671,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="103"/>
+      <c r="F1" s="111"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2743,7 +2743,7 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A2" s="118">
+      <c r="A2" s="122">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2760,7 +2760,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="104"/>
+      <c r="F2" s="112"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2835,7 +2835,7 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="119"/>
+      <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2850,7 +2850,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="105"/>
+      <c r="F3" s="113"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2925,7 +2925,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A4" s="120">
+      <c r="A4" s="124">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2942,7 +2942,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="104"/>
+      <c r="F4" s="112"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3018,7 +3018,7 @@
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A5" s="121"/>
+      <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -3033,7 +3033,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="105"/>
+      <c r="F5" s="113"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3109,7 +3109,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="110">
+      <c r="A6" s="118">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3126,7 +3126,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="104"/>
+      <c r="F6" s="112"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="111"/>
+      <c r="A7" s="119"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="106"/>
+      <c r="F7" s="114"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3293,7 +3293,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="112"/>
+      <c r="A8" s="120"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="107"/>
+      <c r="F8" s="115"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3384,7 +3384,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="113"/>
+      <c r="A9" s="121"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3399,7 +3399,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="116"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3475,7 +3475,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="114">
+      <c r="A10" s="103">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3492,7 +3492,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="104"/>
+      <c r="F10" s="112"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3566,7 +3566,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="115"/>
+      <c r="A11" s="104"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3581,7 +3581,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="106"/>
+      <c r="F11" s="114"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3657,7 +3657,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A12" s="116"/>
+      <c r="A12" s="105"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3672,7 +3672,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="107"/>
+      <c r="F12" s="115"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3748,7 +3748,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="117"/>
+      <c r="A13" s="106"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3763,7 +3763,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="108"/>
+      <c r="F13" s="116"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3839,7 +3839,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="110">
+      <c r="A14" s="118">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3856,7 +3856,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="104"/>
+      <c r="F14" s="112"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3932,7 +3932,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="111"/>
+      <c r="A15" s="119"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="106"/>
+      <c r="F15" s="114"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4023,7 +4023,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="112"/>
+      <c r="A16" s="120"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="107"/>
+      <c r="F16" s="115"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4114,7 +4114,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="113"/>
+      <c r="A17" s="121"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4129,7 +4129,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="108"/>
+      <c r="F17" s="116"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4205,7 +4205,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="114">
+      <c r="A18" s="103">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4222,7 +4222,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="104"/>
+      <c r="F18" s="112"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4298,7 +4298,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A19" s="115"/>
+      <c r="A19" s="104"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="106"/>
+      <c r="F19" s="114"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4389,7 +4389,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A20" s="116"/>
+      <c r="A20" s="105"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4404,7 +4404,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="107"/>
+      <c r="F20" s="115"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4480,7 +4480,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="117"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4495,7 +4495,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="108"/>
+      <c r="F21" s="116"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4571,7 +4571,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="110">
+      <c r="A22" s="118">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4588,7 +4588,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="104"/>
+      <c r="F22" s="112"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="111"/>
+      <c r="A23" s="119"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4679,7 +4679,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="106"/>
+      <c r="F23" s="114"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="112"/>
+      <c r="A24" s="120"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4770,7 +4770,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="107"/>
+      <c r="F24" s="115"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4846,7 +4846,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="113"/>
+      <c r="A25" s="121"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4861,7 +4861,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="108"/>
+      <c r="F25" s="116"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="114">
+      <c r="A26" s="103">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4954,7 +4954,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="104"/>
+      <c r="F26" s="112"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5030,7 +5030,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="115"/>
+      <c r="A27" s="104"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5043,9 +5043,9 @@
         <v>Coreia do Sul</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="106"/>
+        <v>61</v>
+      </c>
+      <c r="F27" s="114"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5104,22 +5104,22 @@
         <v>45</v>
       </c>
       <c r="Z27" s="80"/>
-      <c r="AA27" s="81" t="str">
+      <c r="AA27" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB27" s="90" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC27" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="116"/>
+      <c r="A28" s="105"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5134,7 +5134,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="107"/>
+      <c r="F28" s="115"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="117"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5223,7 +5223,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="108"/>
+      <c r="F29" s="116"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5297,7 +5297,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="110">
+      <c r="A30" s="118">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5314,7 +5314,7 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="104"/>
+      <c r="F30" s="112"/>
       <c r="G30" s="60"/>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -5350,7 +5350,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="111"/>
+      <c r="A31" s="119"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5365,7 +5365,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="106"/>
+      <c r="F31" s="114"/>
       <c r="G31" s="63"/>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -5401,7 +5401,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="112"/>
+      <c r="A32" s="120"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5416,7 +5416,7 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="107"/>
+      <c r="F32" s="115"/>
       <c r="G32" s="65"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
@@ -5452,7 +5452,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="113"/>
+      <c r="A33" s="121"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5467,7 +5467,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="108"/>
+      <c r="F33" s="116"/>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
       <c r="I33" s="69"/>
@@ -5503,7 +5503,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="114">
+      <c r="A34" s="103">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5520,7 +5520,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="104"/>
+      <c r="F34" s="112"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5556,7 +5556,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="115"/>
+      <c r="A35" s="104"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5571,7 +5571,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="106"/>
+      <c r="F35" s="114"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5607,7 +5607,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="116"/>
+      <c r="A36" s="105"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5622,7 +5622,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="107"/>
+      <c r="F36" s="115"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5658,7 +5658,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="117"/>
+      <c r="A37" s="106"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5673,7 +5673,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="108"/>
+      <c r="F37" s="116"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5709,7 +5709,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="110">
+      <c r="A38" s="118">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5726,7 +5726,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="104"/>
+      <c r="F38" s="112"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5762,7 +5762,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="111"/>
+      <c r="A39" s="119"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5777,7 +5777,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="106"/>
+      <c r="F39" s="114"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5813,7 +5813,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="112"/>
+      <c r="A40" s="120"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5828,7 +5828,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="107"/>
+      <c r="F40" s="115"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5864,7 +5864,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113"/>
+      <c r="A41" s="121"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5879,7 +5879,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="108"/>
+      <c r="F41" s="116"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5915,7 +5915,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="114">
+      <c r="A42" s="103">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5932,7 +5932,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="104"/>
+      <c r="F42" s="112"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5968,7 +5968,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="115"/>
+      <c r="A43" s="104"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5983,7 +5983,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="106"/>
+      <c r="F43" s="114"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6019,7 +6019,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="116"/>
+      <c r="A44" s="105"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6034,7 +6034,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="107"/>
+      <c r="F44" s="115"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6070,7 +6070,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="117"/>
+      <c r="A45" s="106"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6085,7 +6085,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="108"/>
+      <c r="F45" s="116"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6121,7 +6121,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="110">
+      <c r="A46" s="118">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6138,7 +6138,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="104"/>
+      <c r="F46" s="112"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6174,7 +6174,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="111"/>
+      <c r="A47" s="119"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6189,7 +6189,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="106"/>
+      <c r="F47" s="114"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6225,7 +6225,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="112"/>
+      <c r="A48" s="120"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6240,7 +6240,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="107"/>
+      <c r="F48" s="115"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6276,7 +6276,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="113"/>
+      <c r="A49" s="121"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6291,7 +6291,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="108"/>
+      <c r="F49" s="116"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6327,7 +6327,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="114">
+      <c r="A50" s="103">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6344,7 +6344,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="104"/>
+      <c r="F50" s="112"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6380,7 +6380,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="115"/>
+      <c r="A51" s="104"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6395,7 +6395,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="106"/>
+      <c r="F51" s="114"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6431,7 +6431,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="116"/>
+      <c r="A52" s="105"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6446,7 +6446,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="107"/>
+      <c r="F52" s="115"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6482,7 +6482,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="116"/>
+      <c r="A53" s="105"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6497,7 +6497,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="107"/>
+      <c r="F53" s="115"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6533,7 +6533,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="116"/>
+      <c r="A54" s="105"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6548,7 +6548,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="107"/>
+      <c r="F54" s="115"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6584,7 +6584,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="117"/>
+      <c r="A55" s="106"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6599,7 +6599,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="108"/>
+      <c r="F55" s="116"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6635,7 +6635,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="110">
+      <c r="A56" s="118">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6652,7 +6652,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="104"/>
+      <c r="F56" s="112"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6688,7 +6688,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="111"/>
+      <c r="A57" s="119"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6703,7 +6703,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="106"/>
+      <c r="F57" s="114"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6739,7 +6739,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="112"/>
+      <c r="A58" s="120"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6754,7 +6754,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="107"/>
+      <c r="F58" s="115"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6790,7 +6790,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="112"/>
+      <c r="A59" s="120"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6805,7 +6805,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="107"/>
+      <c r="F59" s="115"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6841,7 +6841,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="112"/>
+      <c r="A60" s="120"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6856,7 +6856,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="107"/>
+      <c r="F60" s="115"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6892,7 +6892,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="113"/>
+      <c r="A61" s="121"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6907,7 +6907,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="108"/>
+      <c r="F61" s="116"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6943,7 +6943,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="114">
+      <c r="A62" s="103">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6960,7 +6960,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="104"/>
+      <c r="F62" s="112"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6996,7 +6996,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="115"/>
+      <c r="A63" s="104"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7011,7 +7011,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="106"/>
+      <c r="F63" s="114"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7047,7 +7047,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="116"/>
+      <c r="A64" s="105"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7062,7 +7062,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="107"/>
+      <c r="F64" s="115"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7098,7 +7098,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="116"/>
+      <c r="A65" s="105"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7113,7 +7113,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="107"/>
+      <c r="F65" s="115"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7149,7 +7149,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="116"/>
+      <c r="A66" s="105"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7164,7 +7164,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="107"/>
+      <c r="F66" s="115"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7200,7 +7200,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="117"/>
+      <c r="A67" s="106"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7215,7 +7215,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="108"/>
+      <c r="F67" s="116"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7251,7 +7251,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="122">
+      <c r="A68" s="107">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7268,7 +7268,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="104"/>
+      <c r="F68" s="112"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7304,7 +7304,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="123"/>
+      <c r="A69" s="108"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7319,7 +7319,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="106"/>
+      <c r="F69" s="114"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7355,7 +7355,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="124"/>
+      <c r="A70" s="109"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7370,7 +7370,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="107"/>
+      <c r="F70" s="115"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7406,7 +7406,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="124"/>
+      <c r="A71" s="109"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7421,7 +7421,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="107"/>
+      <c r="F71" s="115"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7457,7 +7457,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="124"/>
+      <c r="A72" s="109"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7472,7 +7472,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="107"/>
+      <c r="F72" s="115"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7508,7 +7508,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="125"/>
+      <c r="A73" s="110"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7523,7 +7523,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="109"/>
+      <c r="F73" s="117"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7564,11 +7564,11 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7588,15 +7588,15 @@
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7645,6 +7645,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
@@ -7661,8 +7663,6 @@
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="135">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -1568,6 +1568,18 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1600,18 +1612,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2671,7 +2671,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="111"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2760,7 +2760,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="112"/>
+      <c r="F2" s="116"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2850,7 +2850,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="113"/>
+      <c r="F3" s="117"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2942,7 +2942,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="112"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3033,7 +3033,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="113"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3109,7 +3109,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="118">
+      <c r="A6" s="107">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3126,7 +3126,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="112"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="119"/>
+      <c r="A7" s="108"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="114"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3293,7 +3293,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="120"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="115"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3384,7 +3384,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="121"/>
+      <c r="A9" s="110"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3399,7 +3399,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="116"/>
+      <c r="F9" s="120"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3492,7 +3492,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="112"/>
+      <c r="F10" s="116"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3581,7 +3581,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="114"/>
+      <c r="F11" s="118"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3672,7 +3672,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="115"/>
+      <c r="F12" s="119"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3763,7 +3763,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="116"/>
+      <c r="F13" s="120"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3839,7 +3839,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="118">
+      <c r="A14" s="107">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3856,7 +3856,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="112"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3932,7 +3932,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="119"/>
+      <c r="A15" s="108"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="114"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4023,7 +4023,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="120"/>
+      <c r="A16" s="109"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="115"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4114,7 +4114,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="121"/>
+      <c r="A17" s="110"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4129,7 +4129,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="116"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4222,7 +4222,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="112"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="114"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4404,7 +4404,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="115"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4495,7 +4495,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="116"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4571,7 +4571,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="118">
+      <c r="A22" s="107">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4588,7 +4588,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="112"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="119"/>
+      <c r="A23" s="108"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4679,7 +4679,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="114"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="120"/>
+      <c r="A24" s="109"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4770,7 +4770,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="115"/>
+      <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4846,7 +4846,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="121"/>
+      <c r="A25" s="110"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4861,7 +4861,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="116"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4954,7 +4954,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="112"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5045,7 +5045,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="114"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5134,7 +5134,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="115"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5223,7 +5223,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="116"/>
+      <c r="F29" s="120"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5297,7 +5297,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="118">
+      <c r="A30" s="107">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5314,27 +5314,65 @@
       <c r="E30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="112"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="61"/>
-      <c r="R30" s="61"/>
+      <c r="F30" s="116"/>
+      <c r="G30" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="J30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="K30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="L30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="M30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="N30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="O30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="P30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="R30" s="61" t="s">
+        <v>45</v>
+      </c>
       <c r="S30" s="61"/>
-      <c r="T30" s="61"/>
-      <c r="U30" s="62"/>
-      <c r="V30" s="62"/>
-      <c r="W30" s="62"/>
-      <c r="X30" s="62"/>
-      <c r="Y30" s="62"/>
-      <c r="Z30" s="76"/>
+      <c r="T30" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="U30" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="V30" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="W30" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="X30" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y30" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z30" s="76" t="s">
+        <v>45</v>
+      </c>
       <c r="AA30" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5350,7 +5388,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="119"/>
+      <c r="A31" s="108"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5365,27 +5403,65 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="114"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
+      <c r="F31" s="118"/>
+      <c r="G31" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="I31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="L31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="M31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="N31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="P31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="R31" s="71" t="s">
+        <v>44</v>
+      </c>
       <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="56"/>
-      <c r="V31" s="56"/>
-      <c r="W31" s="56"/>
-      <c r="X31" s="56"/>
-      <c r="Y31" s="56"/>
-      <c r="Z31" s="80"/>
+      <c r="T31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="U31" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="V31" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="W31" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="X31" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y31" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" s="80" t="s">
+        <v>44</v>
+      </c>
       <c r="AA31" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5401,7 +5477,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="120"/>
+      <c r="A32" s="109"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5416,27 +5492,65 @@
       <c r="E32" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="115"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="66"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="66"/>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="66"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="K32" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="L32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="M32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="N32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="P32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="R32" s="66" t="s">
+        <v>44</v>
+      </c>
       <c r="S32" s="66"/>
-      <c r="T32" s="66"/>
-      <c r="U32" s="67"/>
-      <c r="V32" s="67"/>
-      <c r="W32" s="67"/>
-      <c r="X32" s="67"/>
-      <c r="Y32" s="67"/>
-      <c r="Z32" s="78"/>
+      <c r="T32" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="U32" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="V32" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W32" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="X32" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y32" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" s="78" t="s">
+        <v>44</v>
+      </c>
       <c r="AA32" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5452,7 +5566,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="121"/>
+      <c r="A33" s="110"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5467,27 +5581,65 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="116"/>
-      <c r="G33" s="68"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="69"/>
-      <c r="M33" s="69"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="69"/>
-      <c r="P33" s="69"/>
-      <c r="Q33" s="69"/>
-      <c r="R33" s="69"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="I33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="K33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="L33" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="M33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="N33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="O33" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="P33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q33" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="R33" s="69" t="s">
+        <v>44</v>
+      </c>
       <c r="S33" s="69"/>
-      <c r="T33" s="69"/>
-      <c r="U33" s="70"/>
-      <c r="V33" s="70"/>
-      <c r="W33" s="70"/>
-      <c r="X33" s="70"/>
-      <c r="Y33" s="70"/>
-      <c r="Z33" s="79"/>
+      <c r="T33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="U33" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="V33" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="W33" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="X33" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y33" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" s="79" t="s">
+        <v>45</v>
+      </c>
       <c r="AA33" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5520,7 +5672,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="112"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5571,7 +5723,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="114"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5622,7 +5774,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="115"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5673,7 +5825,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="116"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5709,7 +5861,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="118">
+      <c r="A38" s="107">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5726,7 +5878,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="112"/>
+      <c r="F38" s="116"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5762,7 +5914,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="119"/>
+      <c r="A39" s="108"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5777,7 +5929,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="114"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5813,7 +5965,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="120"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5828,7 +5980,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="115"/>
+      <c r="F40" s="119"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5864,7 +6016,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="121"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5879,7 +6031,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="116"/>
+      <c r="F41" s="120"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5932,7 +6084,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="112"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5983,7 +6135,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="114"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6034,7 +6186,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="115"/>
+      <c r="F44" s="119"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6085,7 +6237,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="116"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6121,7 +6273,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="118">
+      <c r="A46" s="107">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6138,7 +6290,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="112"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6174,7 +6326,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="119"/>
+      <c r="A47" s="108"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6189,7 +6341,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="114"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6225,7 +6377,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="120"/>
+      <c r="A48" s="109"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6240,7 +6392,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="115"/>
+      <c r="F48" s="119"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6276,7 +6428,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="121"/>
+      <c r="A49" s="110"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6291,7 +6443,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="116"/>
+      <c r="F49" s="120"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6344,7 +6496,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="112"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6395,7 +6547,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="114"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6446,7 +6598,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="115"/>
+      <c r="F52" s="119"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6497,7 +6649,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="115"/>
+      <c r="F53" s="119"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6548,7 +6700,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="115"/>
+      <c r="F54" s="119"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6599,7 +6751,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="116"/>
+      <c r="F55" s="120"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6635,7 +6787,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="118">
+      <c r="A56" s="107">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6652,7 +6804,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="112"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6688,7 +6840,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="119"/>
+      <c r="A57" s="108"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6703,7 +6855,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="114"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6739,7 +6891,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="120"/>
+      <c r="A58" s="109"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6754,7 +6906,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="115"/>
+      <c r="F58" s="119"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6790,7 +6942,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="120"/>
+      <c r="A59" s="109"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6805,7 +6957,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="115"/>
+      <c r="F59" s="119"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6841,7 +6993,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="120"/>
+      <c r="A60" s="109"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6856,7 +7008,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="115"/>
+      <c r="F60" s="119"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6892,7 +7044,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="121"/>
+      <c r="A61" s="110"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6907,7 +7059,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="116"/>
+      <c r="F61" s="120"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6960,7 +7112,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="112"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7011,7 +7163,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="114"/>
+      <c r="F63" s="118"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7062,7 +7214,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="115"/>
+      <c r="F64" s="119"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7113,7 +7265,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="115"/>
+      <c r="F65" s="119"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7164,7 +7316,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="115"/>
+      <c r="F66" s="119"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7215,7 +7367,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="116"/>
+      <c r="F67" s="120"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7251,7 +7403,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="107">
+      <c r="A68" s="111">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7268,7 +7420,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="112"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7304,7 +7456,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="108"/>
+      <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7319,7 +7471,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="114"/>
+      <c r="F69" s="118"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7355,7 +7507,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="109"/>
+      <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7370,7 +7522,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="115"/>
+      <c r="F70" s="119"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7406,7 +7558,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="109"/>
+      <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7421,7 +7573,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="115"/>
+      <c r="F71" s="119"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7457,7 +7609,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="109"/>
+      <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7472,7 +7624,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="115"/>
+      <c r="F72" s="119"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7508,7 +7660,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="110"/>
+      <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7523,7 +7675,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="117"/>
+      <c r="F73" s="121"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7645,6 +7797,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
@@ -7661,8 +7815,6 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -5490,7 +5490,7 @@
         <v>Austrália</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F32" s="119"/>
       <c r="G32" s="65" t="s">
@@ -5551,17 +5551,17 @@
       <c r="Z32" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="AA32" s="81" t="str">
+      <c r="AA32" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB32" s="90" t="str">
+        <v>2</v>
+      </c>
+      <c r="AB32" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC32" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD32" s="54"/>
     </row>
@@ -7716,19 +7716,19 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7736,31 +7736,31 @@
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7772,36 +7772,31 @@
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7815,6 +7810,11 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="135">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -1556,6 +1556,51 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1567,51 +1612,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2671,7 +2671,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="115"/>
+      <c r="F1" s="107"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2760,7 +2760,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="116"/>
+      <c r="F2" s="108"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2850,7 +2850,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="117"/>
+      <c r="F3" s="109"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2942,7 +2942,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="116"/>
+      <c r="F4" s="108"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3033,7 +3033,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="117"/>
+      <c r="F5" s="109"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3109,7 +3109,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="107">
+      <c r="A6" s="114">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3126,7 +3126,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="116"/>
+      <c r="F6" s="108"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="108"/>
+      <c r="A7" s="115"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="118"/>
+      <c r="F7" s="110"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3293,7 +3293,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="109"/>
+      <c r="A8" s="116"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="119"/>
+      <c r="F8" s="111"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3384,7 +3384,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="110"/>
+      <c r="A9" s="117"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3399,7 +3399,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="120"/>
+      <c r="F9" s="112"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3475,7 +3475,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="103">
+      <c r="A10" s="118">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3492,7 +3492,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="116"/>
+      <c r="F10" s="108"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3566,7 +3566,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="104"/>
+      <c r="A11" s="119"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3581,7 +3581,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="110"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3657,7 +3657,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A12" s="105"/>
+      <c r="A12" s="120"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3672,7 +3672,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="119"/>
+      <c r="F12" s="111"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3748,7 +3748,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="106"/>
+      <c r="A13" s="121"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3763,7 +3763,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="120"/>
+      <c r="F13" s="112"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3839,7 +3839,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="107">
+      <c r="A14" s="114">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3856,7 +3856,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="116"/>
+      <c r="F14" s="108"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3932,7 +3932,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="108"/>
+      <c r="A15" s="115"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="118"/>
+      <c r="F15" s="110"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4023,7 +4023,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="109"/>
+      <c r="A16" s="116"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="119"/>
+      <c r="F16" s="111"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4114,7 +4114,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="110"/>
+      <c r="A17" s="117"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4129,7 +4129,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="120"/>
+      <c r="F17" s="112"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4205,7 +4205,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="103">
+      <c r="A18" s="118">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4222,7 +4222,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="116"/>
+      <c r="F18" s="108"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4298,7 +4298,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A19" s="104"/>
+      <c r="A19" s="119"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="118"/>
+      <c r="F19" s="110"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4389,7 +4389,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A20" s="105"/>
+      <c r="A20" s="120"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4404,7 +4404,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="119"/>
+      <c r="F20" s="111"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4480,7 +4480,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="106"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4495,7 +4495,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="120"/>
+      <c r="F21" s="112"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4571,7 +4571,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="107">
+      <c r="A22" s="114">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4588,7 +4588,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="116"/>
+      <c r="F22" s="108"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="108"/>
+      <c r="A23" s="115"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4679,7 +4679,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="118"/>
+      <c r="F23" s="110"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="109"/>
+      <c r="A24" s="116"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4770,7 +4770,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="119"/>
+      <c r="F24" s="111"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4846,7 +4846,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="110"/>
+      <c r="A25" s="117"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4861,7 +4861,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="120"/>
+      <c r="F25" s="112"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="103">
+      <c r="A26" s="118">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4954,7 +4954,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="116"/>
+      <c r="F26" s="108"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5030,7 +5030,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="104"/>
+      <c r="A27" s="119"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5045,7 +5045,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="118"/>
+      <c r="F27" s="110"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5119,7 +5119,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="105"/>
+      <c r="A28" s="120"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5134,7 +5134,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="119"/>
+      <c r="F28" s="111"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="106"/>
+      <c r="A29" s="121"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5223,7 +5223,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="120"/>
+      <c r="F29" s="112"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5297,7 +5297,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="107">
+      <c r="A30" s="114">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5312,9 +5312,9 @@
         <v>Marrocos</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="116"/>
+        <v>56</v>
+      </c>
+      <c r="F30" s="108"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5373,22 +5373,22 @@
       <c r="Z30" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="AA30" s="81" t="str">
+      <c r="AA30" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB30" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC30" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="108"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="E31" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="118"/>
+      <c r="F31" s="110"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5440,7 +5440,9 @@
       <c r="R31" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="S31" s="71"/>
+      <c r="S31" s="71" t="s">
+        <v>44</v>
+      </c>
       <c r="T31" s="71" t="s">
         <v>44</v>
       </c>
@@ -5477,7 +5479,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="109"/>
+      <c r="A32" s="116"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5492,7 +5494,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="119"/>
+      <c r="F32" s="111"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5566,7 +5568,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="110"/>
+      <c r="A33" s="117"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5581,7 +5583,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="120"/>
+      <c r="F33" s="112"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5618,7 +5620,9 @@
       <c r="R33" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="S33" s="69"/>
+      <c r="S33" s="69" t="s">
+        <v>46</v>
+      </c>
       <c r="T33" s="69" t="s">
         <v>44</v>
       </c>
@@ -5655,7 +5659,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="103">
+      <c r="A34" s="118">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5672,7 +5676,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="116"/>
+      <c r="F34" s="108"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5708,7 +5712,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="104"/>
+      <c r="A35" s="119"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5723,7 +5727,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="118"/>
+      <c r="F35" s="110"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5759,7 +5763,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="105"/>
+      <c r="A36" s="120"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5774,7 +5778,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="111"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5810,7 +5814,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="106"/>
+      <c r="A37" s="121"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5825,7 +5829,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="120"/>
+      <c r="F37" s="112"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5861,7 +5865,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="107">
+      <c r="A38" s="114">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5878,7 +5882,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="116"/>
+      <c r="F38" s="108"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5914,7 +5918,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="108"/>
+      <c r="A39" s="115"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5929,7 +5933,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="118"/>
+      <c r="F39" s="110"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5965,7 +5969,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="109"/>
+      <c r="A40" s="116"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5980,7 +5984,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="119"/>
+      <c r="F40" s="111"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -6016,7 +6020,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="110"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6031,7 +6035,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="120"/>
+      <c r="F41" s="112"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -6067,7 +6071,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="103">
+      <c r="A42" s="118">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6084,7 +6088,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="116"/>
+      <c r="F42" s="108"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -6120,7 +6124,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="104"/>
+      <c r="A43" s="119"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6135,7 +6139,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="118"/>
+      <c r="F43" s="110"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6171,7 +6175,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="105"/>
+      <c r="A44" s="120"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6186,7 +6190,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="119"/>
+      <c r="F44" s="111"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6222,7 +6226,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="106"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6237,7 +6241,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="120"/>
+      <c r="F45" s="112"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6273,7 +6277,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="107">
+      <c r="A46" s="114">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6290,7 +6294,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="116"/>
+      <c r="F46" s="108"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6326,7 +6330,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="108"/>
+      <c r="A47" s="115"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6341,7 +6345,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="118"/>
+      <c r="F47" s="110"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6377,7 +6381,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="109"/>
+      <c r="A48" s="116"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6392,7 +6396,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="119"/>
+      <c r="F48" s="111"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6428,7 +6432,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="110"/>
+      <c r="A49" s="117"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6443,7 +6447,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="120"/>
+      <c r="F49" s="112"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6479,7 +6483,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="103">
+      <c r="A50" s="118">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6496,7 +6500,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="116"/>
+      <c r="F50" s="108"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6532,7 +6536,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="104"/>
+      <c r="A51" s="119"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6547,7 +6551,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="118"/>
+      <c r="F51" s="110"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6583,7 +6587,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="105"/>
+      <c r="A52" s="120"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6598,7 +6602,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="119"/>
+      <c r="F52" s="111"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6634,7 +6638,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="105"/>
+      <c r="A53" s="120"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6649,7 +6653,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="119"/>
+      <c r="F53" s="111"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6685,7 +6689,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="105"/>
+      <c r="A54" s="120"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6700,7 +6704,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="119"/>
+      <c r="F54" s="111"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6736,7 +6740,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="106"/>
+      <c r="A55" s="121"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6751,7 +6755,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="120"/>
+      <c r="F55" s="112"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6787,7 +6791,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="107">
+      <c r="A56" s="114">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6804,7 +6808,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="116"/>
+      <c r="F56" s="108"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6840,7 +6844,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="108"/>
+      <c r="A57" s="115"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6855,7 +6859,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="118"/>
+      <c r="F57" s="110"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6891,7 +6895,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="109"/>
+      <c r="A58" s="116"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6906,7 +6910,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="119"/>
+      <c r="F58" s="111"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6942,7 +6946,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="109"/>
+      <c r="A59" s="116"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6957,7 +6961,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="119"/>
+      <c r="F59" s="111"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6993,7 +6997,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="109"/>
+      <c r="A60" s="116"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7008,7 +7012,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="119"/>
+      <c r="F60" s="111"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7044,7 +7048,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="110"/>
+      <c r="A61" s="117"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7059,7 +7063,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="120"/>
+      <c r="F61" s="112"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7095,7 +7099,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="103">
+      <c r="A62" s="118">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7112,7 +7116,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="116"/>
+      <c r="F62" s="108"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7148,7 +7152,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="104"/>
+      <c r="A63" s="119"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7163,7 +7167,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="118"/>
+      <c r="F63" s="110"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7199,7 +7203,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="105"/>
+      <c r="A64" s="120"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7214,7 +7218,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="119"/>
+      <c r="F64" s="111"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7250,7 +7254,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="105"/>
+      <c r="A65" s="120"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7265,7 +7269,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="119"/>
+      <c r="F65" s="111"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7301,7 +7305,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="105"/>
+      <c r="A66" s="120"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7316,7 +7320,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="119"/>
+      <c r="F66" s="111"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7352,7 +7356,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="106"/>
+      <c r="A67" s="121"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7367,7 +7371,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="120"/>
+      <c r="F67" s="112"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7403,7 +7407,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="111">
+      <c r="A68" s="103">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7420,7 +7424,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="116"/>
+      <c r="F68" s="108"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7456,7 +7460,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="112"/>
+      <c r="A69" s="104"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7471,7 +7475,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="118"/>
+      <c r="F69" s="110"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7507,7 +7511,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="113"/>
+      <c r="A70" s="105"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7522,7 +7526,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="119"/>
+      <c r="F70" s="111"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7558,7 +7562,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="113"/>
+      <c r="A71" s="105"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7573,7 +7577,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="119"/>
+      <c r="F71" s="111"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7609,7 +7613,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="113"/>
+      <c r="A72" s="105"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7624,7 +7628,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="119"/>
+      <c r="F72" s="111"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7660,7 +7664,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="114"/>
+      <c r="A73" s="106"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7675,7 +7679,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="121"/>
+      <c r="F73" s="113"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7716,51 +7720,51 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7772,31 +7776,33 @@
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7813,8 +7819,6 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1556,6 +1556,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1588,30 +1612,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2671,7 +2671,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="107"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2760,7 +2760,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="108"/>
+      <c r="F2" s="116"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2850,7 +2850,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="109"/>
+      <c r="F3" s="117"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2942,7 +2942,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3033,7 +3033,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="109"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3109,7 +3109,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="114">
+      <c r="A6" s="103">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3126,7 +3126,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="115"/>
+      <c r="A7" s="104"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="110"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3293,7 +3293,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="116"/>
+      <c r="A8" s="105"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="111"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3384,7 +3384,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="117"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3399,7 +3399,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="112"/>
+      <c r="F9" s="120"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3475,7 +3475,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="118">
+      <c r="A10" s="107">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3492,7 +3492,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="116"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3566,7 +3566,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="119"/>
+      <c r="A11" s="108"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3581,7 +3581,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="110"/>
+      <c r="F11" s="118"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3657,7 +3657,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A12" s="120"/>
+      <c r="A12" s="109"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3672,7 +3672,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="111"/>
+      <c r="F12" s="119"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3748,7 +3748,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="121"/>
+      <c r="A13" s="110"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3763,7 +3763,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="112"/>
+      <c r="F13" s="120"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3839,7 +3839,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="114">
+      <c r="A14" s="103">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3856,7 +3856,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="108"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3932,7 +3932,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="115"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="110"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4023,7 +4023,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="116"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="111"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4114,7 +4114,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="117"/>
+      <c r="A17" s="106"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4129,7 +4129,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="112"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4205,7 +4205,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="118">
+      <c r="A18" s="107">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4222,7 +4222,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="108"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4298,7 +4298,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A19" s="119"/>
+      <c r="A19" s="108"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="110"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4389,7 +4389,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A20" s="120"/>
+      <c r="A20" s="109"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4404,7 +4404,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="111"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4480,7 +4480,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="121"/>
+      <c r="A21" s="110"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4495,7 +4495,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="112"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4571,7 +4571,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="114">
+      <c r="A22" s="103">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4588,7 +4588,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="108"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="115"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4679,7 +4679,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="110"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="116"/>
+      <c r="A24" s="105"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4770,7 +4770,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="111"/>
+      <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4846,7 +4846,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="117"/>
+      <c r="A25" s="106"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4861,7 +4861,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="112"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="118">
+      <c r="A26" s="107">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4954,7 +4954,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="108"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5030,7 +5030,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="119"/>
+      <c r="A27" s="108"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5045,7 +5045,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="110"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5119,7 +5119,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="120"/>
+      <c r="A28" s="109"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5134,7 +5134,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="111"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="121"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5223,7 +5223,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="112"/>
+      <c r="F29" s="120"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5297,7 +5297,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="114">
+      <c r="A30" s="103">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5314,7 +5314,7 @@
       <c r="E30" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="108"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5388,7 +5388,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="115"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5401,9 +5401,9 @@
         <v>Haiti</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" s="110"/>
+        <v>131</v>
+      </c>
+      <c r="F31" s="118"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5464,22 +5464,22 @@
       <c r="Z31" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="AA31" s="81" t="str">
+      <c r="AA31" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB31" s="90" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB31" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC31" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="116"/>
+      <c r="A32" s="105"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5494,7 +5494,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="111"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5568,7 +5568,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="117"/>
+      <c r="A33" s="106"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5583,7 +5583,7 @@
       <c r="E33" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="112"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5659,7 +5659,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="118">
+      <c r="A34" s="107">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5676,7 +5676,7 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="108"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="60"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -5712,7 +5712,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="119"/>
+      <c r="A35" s="108"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5727,7 +5727,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="110"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="63"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -5763,7 +5763,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="120"/>
+      <c r="A36" s="109"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5778,7 +5778,7 @@
       <c r="E36" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="111"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="65"/>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -5814,7 +5814,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="121"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5829,7 +5829,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="112"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="68"/>
       <c r="H37" s="69"/>
       <c r="I37" s="69"/>
@@ -5865,7 +5865,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="114">
+      <c r="A38" s="103">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5882,7 +5882,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="108"/>
+      <c r="F38" s="116"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5918,7 +5918,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="115"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5933,7 +5933,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="110"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5969,7 +5969,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="116"/>
+      <c r="A40" s="105"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5984,7 +5984,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="111"/>
+      <c r="F40" s="119"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -6020,7 +6020,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="117"/>
+      <c r="A41" s="106"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6035,7 +6035,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="112"/>
+      <c r="F41" s="120"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -6071,7 +6071,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="118">
+      <c r="A42" s="107">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6088,7 +6088,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="108"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -6124,7 +6124,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="119"/>
+      <c r="A43" s="108"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6139,7 +6139,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="110"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6175,7 +6175,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="120"/>
+      <c r="A44" s="109"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6190,7 +6190,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="111"/>
+      <c r="F44" s="119"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6226,7 +6226,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="121"/>
+      <c r="A45" s="110"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6241,7 +6241,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="112"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6277,7 +6277,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="114">
+      <c r="A46" s="103">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6294,7 +6294,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="108"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6330,7 +6330,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="115"/>
+      <c r="A47" s="104"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6345,7 +6345,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="110"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6381,7 +6381,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="116"/>
+      <c r="A48" s="105"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6396,7 +6396,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="111"/>
+      <c r="F48" s="119"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6432,7 +6432,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="117"/>
+      <c r="A49" s="106"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6447,7 +6447,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="112"/>
+      <c r="F49" s="120"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6483,7 +6483,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="118">
+      <c r="A50" s="107">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6500,7 +6500,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="108"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6536,7 +6536,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="119"/>
+      <c r="A51" s="108"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6551,7 +6551,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="110"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6587,7 +6587,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="120"/>
+      <c r="A52" s="109"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6602,7 +6602,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="111"/>
+      <c r="F52" s="119"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6638,7 +6638,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="120"/>
+      <c r="A53" s="109"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6653,7 +6653,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="111"/>
+      <c r="F53" s="119"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6689,7 +6689,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="120"/>
+      <c r="A54" s="109"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6704,7 +6704,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="111"/>
+      <c r="F54" s="119"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6740,7 +6740,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="121"/>
+      <c r="A55" s="110"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6755,7 +6755,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="112"/>
+      <c r="F55" s="120"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6791,7 +6791,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="114">
+      <c r="A56" s="103">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6808,7 +6808,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="108"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6844,7 +6844,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="115"/>
+      <c r="A57" s="104"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6859,7 +6859,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="110"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6895,7 +6895,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="116"/>
+      <c r="A58" s="105"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6910,7 +6910,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="111"/>
+      <c r="F58" s="119"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6946,7 +6946,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="116"/>
+      <c r="A59" s="105"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6961,7 +6961,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="111"/>
+      <c r="F59" s="119"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6997,7 +6997,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="116"/>
+      <c r="A60" s="105"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7012,7 +7012,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="111"/>
+      <c r="F60" s="119"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7048,7 +7048,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="117"/>
+      <c r="A61" s="106"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7063,7 +7063,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="112"/>
+      <c r="F61" s="120"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7099,7 +7099,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="118">
+      <c r="A62" s="107">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7116,7 +7116,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="108"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7152,7 +7152,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="119"/>
+      <c r="A63" s="108"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7167,7 +7167,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="110"/>
+      <c r="F63" s="118"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7203,7 +7203,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="120"/>
+      <c r="A64" s="109"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7218,7 +7218,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="111"/>
+      <c r="F64" s="119"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7254,7 +7254,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="120"/>
+      <c r="A65" s="109"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7269,7 +7269,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="111"/>
+      <c r="F65" s="119"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7305,7 +7305,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="120"/>
+      <c r="A66" s="109"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7320,7 +7320,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="111"/>
+      <c r="F66" s="119"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7356,7 +7356,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="121"/>
+      <c r="A67" s="110"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7371,7 +7371,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="112"/>
+      <c r="F67" s="120"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7407,7 +7407,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="103">
+      <c r="A68" s="111">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7424,7 +7424,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="108"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7460,7 +7460,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="104"/>
+      <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7475,7 +7475,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="110"/>
+      <c r="F69" s="118"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7511,7 +7511,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="105"/>
+      <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7526,7 +7526,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="111"/>
+      <c r="F70" s="119"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7562,7 +7562,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="105"/>
+      <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7577,7 +7577,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="111"/>
+      <c r="F71" s="119"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7613,7 +7613,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="105"/>
+      <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7628,7 +7628,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="111"/>
+      <c r="F72" s="119"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7664,7 +7664,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="106"/>
+      <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7679,7 +7679,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="113"/>
+      <c r="F73" s="121"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7720,87 +7720,89 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
@@ -7817,8 +7819,6 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -5581,7 +5581,7 @@
         <v>Paraguai</v>
       </c>
       <c r="E33" s="49" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F33" s="120"/>
       <c r="G33" s="68" t="s">
@@ -5644,17 +5644,17 @@
       <c r="Z33" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="AA33" s="81" t="str">
+      <c r="AA33" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB33" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC33" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD33" s="54"/>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7784,11 +7784,11 @@
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7796,16 +7796,11 @@
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -7819,6 +7814,11 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AF6FBF-09E5-42EB-B3B2-548EAECD1274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79E2BB6-9501-41A6-AABB-CE8957188572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="135">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -465,6 +465,9 @@
   </si>
   <si>
     <t>1x3</t>
+  </si>
+  <si>
+    <t>6x0</t>
   </si>
 </sst>
 </file>
@@ -1553,6 +1556,63 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1564,63 +1624,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2668,7 +2671,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="107"/>
+      <c r="F1" s="103"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2740,7 +2743,7 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="122">
+      <c r="A2" s="118">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2757,7 +2760,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="108"/>
+      <c r="F2" s="104"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2832,7 +2835,7 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="123"/>
+      <c r="A3" s="119"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2847,7 +2850,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="109"/>
+      <c r="F3" s="105"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2922,7 +2925,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="124">
+      <c r="A4" s="120">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2939,7 +2942,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="104"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3015,7 +3018,7 @@
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="125"/>
+      <c r="A5" s="121"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -3030,7 +3033,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="109"/>
+      <c r="F5" s="105"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3106,7 +3109,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="114">
+      <c r="A6" s="110">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3123,7 +3126,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="104"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3199,7 +3202,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="115"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3214,7 +3217,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="110"/>
+      <c r="F7" s="106"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3290,7 +3293,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="116"/>
+      <c r="A8" s="112"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3305,7 +3308,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="111"/>
+      <c r="F8" s="107"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3381,7 +3384,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="117"/>
+      <c r="A9" s="113"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3396,7 +3399,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="112"/>
+      <c r="F9" s="108"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3472,7 +3475,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="118">
+      <c r="A10" s="114">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3489,7 +3492,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="104"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3563,7 +3566,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="119"/>
+      <c r="A11" s="115"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3578,7 +3581,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="110"/>
+      <c r="F11" s="106"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3654,7 +3657,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="120"/>
+      <c r="A12" s="116"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3669,7 +3672,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="111"/>
+      <c r="F12" s="107"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3745,7 +3748,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="121"/>
+      <c r="A13" s="117"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3760,7 +3763,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="112"/>
+      <c r="F13" s="108"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3836,7 +3839,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="114">
+      <c r="A14" s="110">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3853,7 +3856,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="108"/>
+      <c r="F14" s="104"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3929,7 +3932,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="115"/>
+      <c r="A15" s="111"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3944,7 +3947,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="110"/>
+      <c r="F15" s="106"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4020,7 +4023,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="116"/>
+      <c r="A16" s="112"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4035,7 +4038,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="111"/>
+      <c r="F16" s="107"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4111,7 +4114,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="117"/>
+      <c r="A17" s="113"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4126,7 +4129,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="112"/>
+      <c r="F17" s="108"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4202,7 +4205,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="118">
+      <c r="A18" s="114">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4219,7 +4222,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="108"/>
+      <c r="F18" s="104"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4295,7 +4298,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="119"/>
+      <c r="A19" s="115"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4310,7 +4313,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="110"/>
+      <c r="F19" s="106"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4386,7 +4389,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="120"/>
+      <c r="A20" s="116"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4401,7 +4404,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="111"/>
+      <c r="F20" s="107"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4477,7 +4480,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="121"/>
+      <c r="A21" s="117"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4492,7 +4495,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="112"/>
+      <c r="F21" s="108"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4568,7 +4571,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="114">
+      <c r="A22" s="110">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4585,7 +4588,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="108"/>
+      <c r="F22" s="104"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4661,7 +4664,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="115"/>
+      <c r="A23" s="111"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4676,7 +4679,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="110"/>
+      <c r="F23" s="106"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4752,7 +4755,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="116"/>
+      <c r="A24" s="112"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4767,7 +4770,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="111"/>
+      <c r="F24" s="107"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4843,7 +4846,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="117"/>
+      <c r="A25" s="113"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4858,7 +4861,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="112"/>
+      <c r="F25" s="108"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4934,7 +4937,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="118">
+      <c r="A26" s="114">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4951,7 +4954,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="108"/>
+      <c r="F26" s="104"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5027,7 +5030,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="119"/>
+      <c r="A27" s="115"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5040,9 +5043,9 @@
         <v>Coreia do Sul</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="110"/>
+        <v>61</v>
+      </c>
+      <c r="F27" s="106"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5101,22 +5104,22 @@
         <v>45</v>
       </c>
       <c r="Z27" s="80"/>
-      <c r="AA27" s="81" t="str">
+      <c r="AA27" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB27" s="90" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC27" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="120"/>
+      <c r="A28" s="116"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5129,9 +5132,9 @@
         <v>Bósnia e Herzeg.</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="111"/>
+        <v>52</v>
+      </c>
+      <c r="F28" s="107"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5190,22 +5193,22 @@
         <v>44</v>
       </c>
       <c r="Z28" s="78"/>
-      <c r="AA28" s="81" t="str">
+      <c r="AA28" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB28" s="90" t="str">
+        <v>4</v>
+      </c>
+      <c r="AB28" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC28" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="121"/>
+      <c r="A29" s="117"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5218,9 +5221,9 @@
         <v>Catar</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="112"/>
+        <v>134</v>
+      </c>
+      <c r="F29" s="108"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5279,22 +5282,22 @@
         <v>44</v>
       </c>
       <c r="Z29" s="79"/>
-      <c r="AA29" s="81" t="str">
+      <c r="AA29" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB29" s="90" t="str">
+        <v>6</v>
+      </c>
+      <c r="AB29" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC29" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="114">
+      <c r="A30" s="110">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5309,45 +5312,83 @@
         <v>Marrocos</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="108"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="61"/>
-      <c r="R30" s="61"/>
+        <v>56</v>
+      </c>
+      <c r="F30" s="104"/>
+      <c r="G30" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="J30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="K30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="L30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="M30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="N30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="O30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="P30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q30" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="R30" s="61" t="s">
+        <v>45</v>
+      </c>
       <c r="S30" s="61"/>
-      <c r="T30" s="61"/>
-      <c r="U30" s="62"/>
-      <c r="V30" s="62"/>
-      <c r="W30" s="62"/>
-      <c r="X30" s="62"/>
-      <c r="Y30" s="62"/>
-      <c r="Z30" s="76"/>
-      <c r="AA30" s="81" t="str">
+      <c r="T30" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="U30" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="V30" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="W30" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="X30" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y30" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z30" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA30" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB30" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC30" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="115"/>
+      <c r="A31" s="111"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5360,45 +5401,85 @@
         <v>Haiti</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" s="110"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="56"/>
-      <c r="V31" s="56"/>
-      <c r="W31" s="56"/>
-      <c r="X31" s="56"/>
-      <c r="Y31" s="56"/>
-      <c r="Z31" s="80"/>
-      <c r="AA31" s="81" t="str">
+        <v>131</v>
+      </c>
+      <c r="F31" s="106"/>
+      <c r="G31" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="I31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="L31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="M31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="N31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="P31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="R31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="S31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="T31" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="U31" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="V31" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="W31" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="X31" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y31" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z31" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA31" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB31" s="90" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB31" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC31" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="116"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5411,45 +5492,83 @@
         <v>Austrália</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" s="111"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="66"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="66"/>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="66"/>
+        <v>43</v>
+      </c>
+      <c r="F32" s="107"/>
+      <c r="G32" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="K32" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="L32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="M32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="N32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="P32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q32" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="R32" s="66" t="s">
+        <v>44</v>
+      </c>
       <c r="S32" s="66"/>
-      <c r="T32" s="66"/>
-      <c r="U32" s="67"/>
-      <c r="V32" s="67"/>
-      <c r="W32" s="67"/>
-      <c r="X32" s="67"/>
-      <c r="Y32" s="67"/>
-      <c r="Z32" s="78"/>
-      <c r="AA32" s="81" t="str">
+      <c r="T32" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="U32" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="V32" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W32" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="X32" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y32" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z32" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA32" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB32" s="90" t="str">
+        <v>2</v>
+      </c>
+      <c r="AB32" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC32" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="117"/>
+      <c r="A33" s="113"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5462,45 +5581,85 @@
         <v>Paraguai</v>
       </c>
       <c r="E33" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="112"/>
-      <c r="G33" s="68"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="69"/>
-      <c r="M33" s="69"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="69"/>
-      <c r="P33" s="69"/>
-      <c r="Q33" s="69"/>
-      <c r="R33" s="69"/>
-      <c r="S33" s="69"/>
-      <c r="T33" s="69"/>
-      <c r="U33" s="70"/>
-      <c r="V33" s="70"/>
-      <c r="W33" s="70"/>
-      <c r="X33" s="70"/>
-      <c r="Y33" s="70"/>
-      <c r="Z33" s="79"/>
-      <c r="AA33" s="81" t="str">
+        <v>56</v>
+      </c>
+      <c r="F33" s="108"/>
+      <c r="G33" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="I33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="K33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="L33" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="M33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="N33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="O33" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="P33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q33" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="R33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="S33" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="T33" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="U33" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="V33" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="W33" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="X33" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y33" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" s="79" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB33" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC33" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="118">
+      <c r="A34" s="114">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5517,27 +5676,67 @@
       <c r="E34" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="108"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="61"/>
-      <c r="N34" s="61"/>
-      <c r="O34" s="61"/>
-      <c r="P34" s="61"/>
-      <c r="Q34" s="61"/>
-      <c r="R34" s="61"/>
-      <c r="S34" s="61"/>
-      <c r="T34" s="61"/>
-      <c r="U34" s="62"/>
-      <c r="V34" s="62"/>
-      <c r="W34" s="62"/>
-      <c r="X34" s="62"/>
-      <c r="Y34" s="62"/>
-      <c r="Z34" s="76"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="K34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="L34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="M34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="N34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="O34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="P34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="R34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="S34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="T34" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="U34" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="V34" s="62" t="s">
+        <v>46</v>
+      </c>
+      <c r="W34" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="X34" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y34" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z34" s="76" t="s">
+        <v>46</v>
+      </c>
       <c r="AA34" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5553,7 +5752,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="119"/>
+      <c r="A35" s="115"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5568,27 +5767,65 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="110"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="71"/>
-      <c r="O35" s="71"/>
-      <c r="P35" s="71"/>
+      <c r="F35" s="106"/>
+      <c r="G35" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="I35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="L35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="M35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="N35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="P35" s="71" t="s">
+        <v>44</v>
+      </c>
       <c r="Q35" s="71"/>
-      <c r="R35" s="71"/>
-      <c r="S35" s="71"/>
-      <c r="T35" s="71"/>
-      <c r="U35" s="56"/>
-      <c r="V35" s="56"/>
-      <c r="W35" s="56"/>
-      <c r="X35" s="56"/>
-      <c r="Y35" s="56"/>
-      <c r="Z35" s="80"/>
+      <c r="R35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="S35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="T35" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="U35" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="V35" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="W35" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="X35" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y35" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" s="80" t="s">
+        <v>46</v>
+      </c>
       <c r="AA35" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5604,7 +5841,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="120"/>
+      <c r="A36" s="116"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5617,45 +5854,85 @@
         <v>Suécia</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="F36" s="111"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="66"/>
-      <c r="J36" s="66"/>
-      <c r="K36" s="66"/>
-      <c r="L36" s="66"/>
-      <c r="M36" s="66"/>
-      <c r="N36" s="66"/>
-      <c r="O36" s="66"/>
-      <c r="P36" s="66"/>
-      <c r="Q36" s="66"/>
-      <c r="R36" s="66"/>
-      <c r="S36" s="66"/>
-      <c r="T36" s="66"/>
-      <c r="U36" s="67"/>
-      <c r="V36" s="67"/>
-      <c r="W36" s="67"/>
-      <c r="X36" s="67"/>
-      <c r="Y36" s="67"/>
-      <c r="Z36" s="78"/>
-      <c r="AA36" s="81" t="str">
+        <v>65</v>
+      </c>
+      <c r="F36" s="107"/>
+      <c r="G36" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H36" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="J36" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="K36" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="L36" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="M36" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="N36" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O36" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="P36" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q36" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="R36" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="S36" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="T36" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="U36" s="67" t="s">
+        <v>46</v>
+      </c>
+      <c r="V36" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W36" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="X36" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y36" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z36" s="78" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA36" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB36" s="90" t="str">
+        <v>5</v>
+      </c>
+      <c r="AB36" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC36" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="121"/>
+      <c r="A37" s="117"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5670,27 +5947,67 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="112"/>
-      <c r="G37" s="68"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="69"/>
-      <c r="P37" s="69"/>
-      <c r="Q37" s="69"/>
-      <c r="R37" s="69"/>
-      <c r="S37" s="69"/>
-      <c r="T37" s="69"/>
-      <c r="U37" s="70"/>
-      <c r="V37" s="70"/>
-      <c r="W37" s="70"/>
-      <c r="X37" s="70"/>
-      <c r="Y37" s="70"/>
-      <c r="Z37" s="79"/>
+      <c r="F37" s="108"/>
+      <c r="G37" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="H37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="J37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="K37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="L37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="M37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="N37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="O37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="P37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q37" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="R37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="S37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="T37" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="U37" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="V37" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="W37" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="X37" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y37" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z37" s="79" t="s">
+        <v>45</v>
+      </c>
       <c r="AA37" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -5706,7 +6023,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="114">
+      <c r="A38" s="110">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -5723,7 +6040,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="108"/>
+      <c r="F38" s="104"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -5759,7 +6076,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="115"/>
+      <c r="A39" s="111"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -5774,7 +6091,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="110"/>
+      <c r="F39" s="106"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -5810,7 +6127,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="116"/>
+      <c r="A40" s="112"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -5825,7 +6142,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="111"/>
+      <c r="F40" s="107"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -5861,7 +6178,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="117"/>
+      <c r="A41" s="113"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -5876,7 +6193,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="112"/>
+      <c r="F41" s="108"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -5912,7 +6229,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="118">
+      <c r="A42" s="114">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -5929,7 +6246,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="108"/>
+      <c r="F42" s="104"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -5965,7 +6282,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="119"/>
+      <c r="A43" s="115"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -5980,7 +6297,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="110"/>
+      <c r="F43" s="106"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6016,7 +6333,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="120"/>
+      <c r="A44" s="116"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6031,7 +6348,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="111"/>
+      <c r="F44" s="107"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6067,7 +6384,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="121"/>
+      <c r="A45" s="117"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6082,7 +6399,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="112"/>
+      <c r="F45" s="108"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6118,7 +6435,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="114">
+      <c r="A46" s="110">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6135,7 +6452,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="108"/>
+      <c r="F46" s="104"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6171,7 +6488,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="115"/>
+      <c r="A47" s="111"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6186,7 +6503,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="110"/>
+      <c r="F47" s="106"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6222,7 +6539,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="116"/>
+      <c r="A48" s="112"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6237,7 +6554,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="111"/>
+      <c r="F48" s="107"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6273,7 +6590,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="117"/>
+      <c r="A49" s="113"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6288,7 +6605,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="112"/>
+      <c r="F49" s="108"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6324,7 +6641,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="118">
+      <c r="A50" s="114">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6341,7 +6658,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="108"/>
+      <c r="F50" s="104"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6377,7 +6694,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="119"/>
+      <c r="A51" s="115"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6392,7 +6709,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="110"/>
+      <c r="F51" s="106"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6428,7 +6745,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="120"/>
+      <c r="A52" s="116"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6443,7 +6760,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="111"/>
+      <c r="F52" s="107"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6479,7 +6796,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="120"/>
+      <c r="A53" s="116"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6494,7 +6811,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="111"/>
+      <c r="F53" s="107"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6530,7 +6847,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="120"/>
+      <c r="A54" s="116"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6545,7 +6862,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="111"/>
+      <c r="F54" s="107"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6581,7 +6898,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="121"/>
+      <c r="A55" s="117"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6596,7 +6913,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="112"/>
+      <c r="F55" s="108"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6632,7 +6949,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="114">
+      <c r="A56" s="110">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6649,7 +6966,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="108"/>
+      <c r="F56" s="104"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -6685,7 +7002,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="115"/>
+      <c r="A57" s="111"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -6700,7 +7017,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="110"/>
+      <c r="F57" s="106"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -6736,7 +7053,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="116"/>
+      <c r="A58" s="112"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -6751,7 +7068,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="111"/>
+      <c r="F58" s="107"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -6787,7 +7104,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="116"/>
+      <c r="A59" s="112"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -6802,7 +7119,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="111"/>
+      <c r="F59" s="107"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -6838,7 +7155,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="116"/>
+      <c r="A60" s="112"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -6853,7 +7170,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="111"/>
+      <c r="F60" s="107"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -6889,7 +7206,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="117"/>
+      <c r="A61" s="113"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -6904,7 +7221,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="112"/>
+      <c r="F61" s="108"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -6940,7 +7257,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="118">
+      <c r="A62" s="114">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -6957,7 +7274,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="108"/>
+      <c r="F62" s="104"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -6993,7 +7310,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="119"/>
+      <c r="A63" s="115"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7008,7 +7325,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="110"/>
+      <c r="F63" s="106"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7044,7 +7361,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="120"/>
+      <c r="A64" s="116"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7059,7 +7376,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="111"/>
+      <c r="F64" s="107"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7095,7 +7412,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="120"/>
+      <c r="A65" s="116"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7110,7 +7427,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="111"/>
+      <c r="F65" s="107"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7146,7 +7463,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="120"/>
+      <c r="A66" s="116"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7161,7 +7478,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="111"/>
+      <c r="F66" s="107"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7197,7 +7514,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="121"/>
+      <c r="A67" s="117"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7212,7 +7529,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="112"/>
+      <c r="F67" s="108"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7248,7 +7565,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="103">
+      <c r="A68" s="122">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7265,7 +7582,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="108"/>
+      <c r="F68" s="104"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7301,7 +7618,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="104"/>
+      <c r="A69" s="123"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7316,7 +7633,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="110"/>
+      <c r="F69" s="106"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7352,7 +7669,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="105"/>
+      <c r="A70" s="124"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7367,7 +7684,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="111"/>
+      <c r="F70" s="107"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7403,7 +7720,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="105"/>
+      <c r="A71" s="124"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7418,7 +7735,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="111"/>
+      <c r="F71" s="107"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7454,7 +7771,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="105"/>
+      <c r="A72" s="124"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7469,7 +7786,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="111"/>
+      <c r="F72" s="107"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7505,7 +7822,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="106"/>
+      <c r="A73" s="125"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7520,7 +7837,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="113"/>
+      <c r="F73" s="109"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7561,88 +7878,87 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
@@ -7660,6 +7976,7 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79E2BB6-9501-41A6-AABB-CE8957188572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E587E295-29DD-4C6C-AF5F-161E9983B3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -1556,6 +1556,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -1589,18 +1613,6 @@
     <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1612,18 +1624,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2671,7 +2671,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="103"/>
+      <c r="F1" s="111"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2743,7 +2743,7 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="118">
+      <c r="A2" s="122">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2760,7 +2760,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="104"/>
+      <c r="F2" s="112"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2835,7 +2835,7 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
+      <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2850,7 +2850,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="105"/>
+      <c r="F3" s="113"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2925,7 +2925,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="120">
+      <c r="A4" s="124">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2942,7 +2942,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="104"/>
+      <c r="F4" s="112"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3018,7 +3018,7 @@
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="121"/>
+      <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -3033,7 +3033,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="105"/>
+      <c r="F5" s="113"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3109,7 +3109,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="110">
+      <c r="A6" s="118">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3126,7 +3126,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="104"/>
+      <c r="F6" s="112"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="111"/>
+      <c r="A7" s="119"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="106"/>
+      <c r="F7" s="114"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3293,7 +3293,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="112"/>
+      <c r="A8" s="120"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="107"/>
+      <c r="F8" s="115"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3384,7 +3384,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="113"/>
+      <c r="A9" s="121"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3399,7 +3399,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="116"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3475,7 +3475,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="114">
+      <c r="A10" s="103">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3492,7 +3492,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="104"/>
+      <c r="F10" s="112"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3566,7 +3566,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="115"/>
+      <c r="A11" s="104"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3581,7 +3581,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="106"/>
+      <c r="F11" s="114"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3657,7 +3657,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="116"/>
+      <c r="A12" s="105"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3672,7 +3672,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="107"/>
+      <c r="F12" s="115"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3748,7 +3748,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="117"/>
+      <c r="A13" s="106"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3763,7 +3763,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="108"/>
+      <c r="F13" s="116"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3839,7 +3839,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="110">
+      <c r="A14" s="118">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3856,7 +3856,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="104"/>
+      <c r="F14" s="112"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3932,7 +3932,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="111"/>
+      <c r="A15" s="119"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="106"/>
+      <c r="F15" s="114"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4023,7 +4023,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="112"/>
+      <c r="A16" s="120"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="107"/>
+      <c r="F16" s="115"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4114,7 +4114,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="113"/>
+      <c r="A17" s="121"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4129,7 +4129,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="108"/>
+      <c r="F17" s="116"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4205,7 +4205,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="114">
+      <c r="A18" s="103">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4222,7 +4222,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="104"/>
+      <c r="F18" s="112"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4298,7 +4298,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="115"/>
+      <c r="A19" s="104"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="106"/>
+      <c r="F19" s="114"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4389,7 +4389,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="116"/>
+      <c r="A20" s="105"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4404,7 +4404,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="107"/>
+      <c r="F20" s="115"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4480,7 +4480,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="117"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4495,7 +4495,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="108"/>
+      <c r="F21" s="116"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4571,7 +4571,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="110">
+      <c r="A22" s="118">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4588,7 +4588,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="104"/>
+      <c r="F22" s="112"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="111"/>
+      <c r="A23" s="119"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4679,7 +4679,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="106"/>
+      <c r="F23" s="114"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="112"/>
+      <c r="A24" s="120"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4770,7 +4770,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="107"/>
+      <c r="F24" s="115"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4846,7 +4846,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="113"/>
+      <c r="A25" s="121"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4861,7 +4861,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="108"/>
+      <c r="F25" s="116"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="114">
+      <c r="A26" s="103">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4954,7 +4954,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="104"/>
+      <c r="F26" s="112"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5030,7 +5030,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="115"/>
+      <c r="A27" s="104"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5045,7 +5045,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="106"/>
+      <c r="F27" s="114"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5119,7 +5119,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="116"/>
+      <c r="A28" s="105"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5134,7 +5134,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="107"/>
+      <c r="F28" s="115"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5223,7 +5223,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="108"/>
+      <c r="F29" s="116"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5297,7 +5297,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="110">
+      <c r="A30" s="118">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5314,7 +5314,7 @@
       <c r="E30" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="104"/>
+      <c r="F30" s="112"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5388,7 +5388,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="111"/>
+      <c r="A31" s="119"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="E31" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="106"/>
+      <c r="F31" s="114"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5479,7 +5479,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="112"/>
+      <c r="A32" s="120"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5494,7 +5494,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="107"/>
+      <c r="F32" s="115"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5568,7 +5568,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="113"/>
+      <c r="A33" s="121"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5583,7 +5583,7 @@
       <c r="E33" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="108"/>
+      <c r="F33" s="116"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5659,7 +5659,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="114">
+      <c r="A34" s="103">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5674,9 +5674,9 @@
         <v>Costa do Marfim</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="F34" s="104"/>
+        <v>56</v>
+      </c>
+      <c r="F34" s="112"/>
       <c r="G34" s="60" t="s">
         <v>44</v>
       </c>
@@ -5737,22 +5737,22 @@
       <c r="Z34" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="AA34" s="81" t="str">
+      <c r="AA34" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB34" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC34" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="115"/>
+      <c r="A35" s="104"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5767,7 +5767,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="106"/>
+      <c r="F35" s="114"/>
       <c r="G35" s="63" t="s">
         <v>44</v>
       </c>
@@ -5841,7 +5841,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="116"/>
+      <c r="A36" s="105"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5856,7 +5856,7 @@
       <c r="E36" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="107"/>
+      <c r="F36" s="115"/>
       <c r="G36" s="65" t="s">
         <v>44</v>
       </c>
@@ -5932,7 +5932,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="117"/>
+      <c r="A37" s="106"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5947,7 +5947,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="108"/>
+      <c r="F37" s="116"/>
       <c r="G37" s="68" t="s">
         <v>45</v>
       </c>
@@ -6023,7 +6023,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="110">
+      <c r="A38" s="118">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -6040,7 +6040,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="104"/>
+      <c r="F38" s="112"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -6076,7 +6076,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="111"/>
+      <c r="A39" s="119"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -6091,7 +6091,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="106"/>
+      <c r="F39" s="114"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -6127,7 +6127,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="112"/>
+      <c r="A40" s="120"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -6142,7 +6142,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="107"/>
+      <c r="F40" s="115"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -6178,7 +6178,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="113"/>
+      <c r="A41" s="121"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6193,7 +6193,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="108"/>
+      <c r="F41" s="116"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -6229,7 +6229,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="114">
+      <c r="A42" s="103">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6246,7 +6246,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="104"/>
+      <c r="F42" s="112"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -6282,7 +6282,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="115"/>
+      <c r="A43" s="104"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6297,7 +6297,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="106"/>
+      <c r="F43" s="114"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6333,7 +6333,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="116"/>
+      <c r="A44" s="105"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6348,7 +6348,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="107"/>
+      <c r="F44" s="115"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6384,7 +6384,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="117"/>
+      <c r="A45" s="106"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6399,7 +6399,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="108"/>
+      <c r="F45" s="116"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6435,7 +6435,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="110">
+      <c r="A46" s="118">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6452,7 +6452,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="104"/>
+      <c r="F46" s="112"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6488,7 +6488,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="111"/>
+      <c r="A47" s="119"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6503,7 +6503,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="106"/>
+      <c r="F47" s="114"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6539,7 +6539,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="112"/>
+      <c r="A48" s="120"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6554,7 +6554,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="107"/>
+      <c r="F48" s="115"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6590,7 +6590,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="113"/>
+      <c r="A49" s="121"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6605,7 +6605,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="108"/>
+      <c r="F49" s="116"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6641,7 +6641,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="114">
+      <c r="A50" s="103">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6658,7 +6658,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="104"/>
+      <c r="F50" s="112"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6694,7 +6694,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="115"/>
+      <c r="A51" s="104"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6709,7 +6709,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="106"/>
+      <c r="F51" s="114"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6745,7 +6745,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="116"/>
+      <c r="A52" s="105"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6760,7 +6760,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="107"/>
+      <c r="F52" s="115"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6796,7 +6796,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="116"/>
+      <c r="A53" s="105"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6811,7 +6811,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="107"/>
+      <c r="F53" s="115"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6847,7 +6847,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="116"/>
+      <c r="A54" s="105"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6862,7 +6862,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="107"/>
+      <c r="F54" s="115"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6898,7 +6898,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="117"/>
+      <c r="A55" s="106"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6913,7 +6913,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="108"/>
+      <c r="F55" s="116"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6949,7 +6949,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="110">
+      <c r="A56" s="118">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6966,7 +6966,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="104"/>
+      <c r="F56" s="112"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -7002,7 +7002,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="111"/>
+      <c r="A57" s="119"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -7017,7 +7017,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="106"/>
+      <c r="F57" s="114"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -7053,7 +7053,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="112"/>
+      <c r="A58" s="120"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -7068,7 +7068,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="107"/>
+      <c r="F58" s="115"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -7104,7 +7104,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="112"/>
+      <c r="A59" s="120"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -7119,7 +7119,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="107"/>
+      <c r="F59" s="115"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -7155,7 +7155,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="112"/>
+      <c r="A60" s="120"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7170,7 +7170,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="107"/>
+      <c r="F60" s="115"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7206,7 +7206,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="113"/>
+      <c r="A61" s="121"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7221,7 +7221,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="108"/>
+      <c r="F61" s="116"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7257,7 +7257,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="114">
+      <c r="A62" s="103">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7274,7 +7274,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="104"/>
+      <c r="F62" s="112"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7310,7 +7310,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="115"/>
+      <c r="A63" s="104"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7325,7 +7325,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="106"/>
+      <c r="F63" s="114"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7361,7 +7361,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="116"/>
+      <c r="A64" s="105"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7376,7 +7376,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="107"/>
+      <c r="F64" s="115"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7412,7 +7412,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="116"/>
+      <c r="A65" s="105"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7427,7 +7427,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="107"/>
+      <c r="F65" s="115"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7463,7 +7463,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="116"/>
+      <c r="A66" s="105"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7478,7 +7478,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="107"/>
+      <c r="F66" s="115"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7514,7 +7514,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="117"/>
+      <c r="A67" s="106"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7529,7 +7529,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="108"/>
+      <c r="F67" s="116"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7565,7 +7565,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="122">
+      <c r="A68" s="107">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7582,7 +7582,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="104"/>
+      <c r="F68" s="112"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7618,7 +7618,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="123"/>
+      <c r="A69" s="108"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7633,7 +7633,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="106"/>
+      <c r="F69" s="114"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7669,7 +7669,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="124"/>
+      <c r="A70" s="109"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7684,7 +7684,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="107"/>
+      <c r="F70" s="115"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7720,7 +7720,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="124"/>
+      <c r="A71" s="109"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7735,7 +7735,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="107"/>
+      <c r="F71" s="115"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7771,7 +7771,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="124"/>
+      <c r="A72" s="109"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7786,7 +7786,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="107"/>
+      <c r="F72" s="115"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7822,7 +7822,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="125"/>
+      <c r="A73" s="110"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7837,7 +7837,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="109"/>
+      <c r="F73" s="117"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7959,6 +7959,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
@@ -7975,8 +7977,6 @@
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\BolaoCopa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E587E295-29DD-4C6C-AF5F-161E9983B3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76ADBD4-52A2-4D49-A371-690F36A51538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
   <sheets>
     <sheet name="Pagamentos" sheetId="1" r:id="rId1"/>
@@ -474,7 +474,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1568,6 +1568,18 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1600,18 +1612,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2083,13 +2083,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="3" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.75" customWidth="1"/>
+    <col min="2" max="3" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="20.25">
       <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
@@ -2101,7 +2101,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="126"/>
       <c r="B2" s="126"/>
       <c r="C2" s="13"/>
@@ -2111,7 +2111,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="126"/>
       <c r="B3" s="126"/>
       <c r="C3" s="13"/>
@@ -2121,7 +2121,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="26.1" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="15">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="15">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="15">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="15">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="15">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="15">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="15">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="15">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="15">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2281,16 +2281,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="7" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="22.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="3" max="7" width="12.125" customWidth="1"/>
+    <col min="9" max="9" width="22.875" customWidth="1"/>
+    <col min="10" max="10" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="127" t="s">
         <v>20</v>
       </c>
@@ -2301,7 +2301,7 @@
       <c r="F1" s="128"/>
       <c r="G1" s="128"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2349,7 +2349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="15">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2392,7 +2392,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2416,7 +2416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="15">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2440,7 +2440,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2461,7 +2461,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2482,7 +2482,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="15">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2503,7 +2503,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2524,7 +2524,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="15">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2545,7 +2545,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="15">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2566,7 +2566,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2587,7 +2587,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2608,7 +2608,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="15">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2645,17 +2645,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="2" width="32.375" customWidth="1"/>
+    <col min="3" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="12.625" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="29" width="16.42578125" customWidth="1"/>
+    <col min="7" max="29" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2671,7 +2671,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="111"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15">
       <c r="A2" s="122">
         <v>46184</v>
       </c>
@@ -2760,7 +2760,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="112"/>
+      <c r="F2" s="116"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1">
       <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2850,7 +2850,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="113"/>
+      <c r="F3" s="117"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15">
       <c r="A4" s="124">
         <v>46185</v>
       </c>
@@ -2942,7 +2942,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="112"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="15">
       <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -3033,7 +3033,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="113"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3108,8 +3108,8 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="118">
+    <row r="6" spans="1:30" ht="15">
+      <c r="A6" s="107">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3126,7 +3126,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="112"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3201,8 +3201,8 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="119"/>
+    <row r="7" spans="1:30" ht="15">
+      <c r="A7" s="108"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="114"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3292,8 +3292,8 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="120"/>
+    <row r="8" spans="1:30" ht="15">
+      <c r="A8" s="109"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="115"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3383,8 +3383,8 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="121"/>
+    <row r="9" spans="1:30" ht="15">
+      <c r="A9" s="110"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3399,7 +3399,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="116"/>
+      <c r="F9" s="120"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="15">
       <c r="A10" s="103">
         <v>46187</v>
       </c>
@@ -3492,7 +3492,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="112"/>
+      <c r="F10" s="116"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="15">
       <c r="A11" s="104"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
@@ -3581,7 +3581,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="114"/>
+      <c r="F11" s="118"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="15">
       <c r="A12" s="105"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
@@ -3672,7 +3672,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="115"/>
+      <c r="F12" s="119"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="15">
       <c r="A13" s="106"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
@@ -3763,7 +3763,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="116"/>
+      <c r="F13" s="120"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3838,8 +3838,8 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="118">
+    <row r="14" spans="1:30" ht="15">
+      <c r="A14" s="107">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3856,7 +3856,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="112"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3931,8 +3931,8 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="119"/>
+    <row r="15" spans="1:30" ht="15">
+      <c r="A15" s="108"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3947,7 +3947,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="114"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4022,8 +4022,8 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="120"/>
+    <row r="16" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A16" s="109"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="115"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4113,8 +4113,8 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="121"/>
+    <row r="17" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A17" s="110"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4129,7 +4129,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="116"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" ht="15.75" thickBot="1">
       <c r="A18" s="103">
         <v>46189</v>
       </c>
@@ -4222,7 +4222,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="112"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="15">
       <c r="A19" s="104"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
@@ -4313,7 +4313,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="114"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="15">
       <c r="A20" s="105"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
@@ -4404,7 +4404,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="115"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" ht="15.75" thickBot="1">
       <c r="A21" s="106"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
@@ -4495,7 +4495,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="116"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4570,8 +4570,8 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="118">
+    <row r="22" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A22" s="107">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4588,7 +4588,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="112"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4663,8 +4663,8 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="119"/>
+    <row r="23" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A23" s="108"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4679,7 +4679,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="114"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4754,8 +4754,8 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="120"/>
+    <row r="24" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A24" s="109"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4770,7 +4770,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="115"/>
+      <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4845,8 +4845,8 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="121"/>
+    <row r="25" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A25" s="110"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4861,7 +4861,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="116"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" ht="15.75" thickBot="1">
       <c r="A26" s="103">
         <v>46191</v>
       </c>
@@ -4954,7 +4954,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="112"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" ht="15.75" thickBot="1">
       <c r="A27" s="104"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
@@ -5045,7 +5045,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="114"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" ht="15.75" thickBot="1">
       <c r="A28" s="105"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
@@ -5134,7 +5134,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="115"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" ht="15.75" thickBot="1">
       <c r="A29" s="106"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
@@ -5223,7 +5223,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="116"/>
+      <c r="F29" s="120"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5296,8 +5296,8 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="118">
+    <row r="30" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A30" s="107">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5314,7 +5314,7 @@
       <c r="E30" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="112"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5387,8 +5387,8 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="119"/>
+    <row r="31" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A31" s="108"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="E31" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="114"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5478,8 +5478,8 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="120"/>
+    <row r="32" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A32" s="109"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5494,7 +5494,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="115"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5567,8 +5567,8 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="121"/>
+    <row r="33" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A33" s="110"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5583,7 +5583,7 @@
       <c r="E33" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="116"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" ht="15.75" thickBot="1">
       <c r="A34" s="103">
         <v>46193</v>
       </c>
@@ -5674,9 +5674,9 @@
         <v>Costa do Marfim</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="F34" s="112"/>
+        <v>48</v>
+      </c>
+      <c r="F34" s="116"/>
       <c r="G34" s="60" t="s">
         <v>44</v>
       </c>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AA34" s="81">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB34" s="90">
         <f t="shared" si="6"/>
@@ -5747,11 +5747,11 @@
       </c>
       <c r="AC34" s="85" t="str">
         <f t="shared" si="4"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:30" ht="15.75" thickBot="1">
       <c r="A35" s="104"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
@@ -5767,7 +5767,7 @@
       <c r="E35" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="114"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="63" t="s">
         <v>44</v>
       </c>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" ht="15.75" thickBot="1">
       <c r="A36" s="105"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
@@ -5856,7 +5856,7 @@
       <c r="E36" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="115"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="65" t="s">
         <v>44</v>
       </c>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" ht="15.75" thickBot="1">
       <c r="A37" s="106"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
@@ -5947,7 +5947,7 @@
       <c r="E37" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F37" s="116"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="68" t="s">
         <v>45</v>
       </c>
@@ -6022,8 +6022,8 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="118">
+    <row r="38" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A38" s="107">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -6040,7 +6040,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="112"/>
+      <c r="F38" s="116"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -6075,8 +6075,8 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="119"/>
+    <row r="39" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A39" s="108"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -6091,7 +6091,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="114"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -6126,8 +6126,8 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="120"/>
+    <row r="40" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A40" s="109"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -6142,7 +6142,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="115"/>
+      <c r="F40" s="119"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -6177,8 +6177,8 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="121"/>
+    <row r="41" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A41" s="110"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6193,7 +6193,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="116"/>
+      <c r="F41" s="120"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:30" ht="15.75" thickBot="1">
       <c r="A42" s="103">
         <v>46195</v>
       </c>
@@ -6246,7 +6246,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="112"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" ht="15.75" thickBot="1">
       <c r="A43" s="104"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
@@ -6297,7 +6297,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="114"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:30" ht="15.75" thickBot="1">
       <c r="A44" s="105"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
@@ -6348,7 +6348,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="115"/>
+      <c r="F44" s="119"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:30" ht="15.75" thickBot="1">
       <c r="A45" s="106"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
@@ -6399,7 +6399,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="116"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6434,8 +6434,8 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="118">
+    <row r="46" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A46" s="107">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6452,7 +6452,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="112"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6487,8 +6487,8 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="119"/>
+    <row r="47" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A47" s="108"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6503,7 +6503,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="114"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6538,8 +6538,8 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="120"/>
+    <row r="48" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A48" s="109"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6554,7 +6554,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="115"/>
+      <c r="F48" s="119"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6589,8 +6589,8 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="121"/>
+    <row r="49" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A49" s="110"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6605,7 +6605,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="116"/>
+      <c r="F49" s="120"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:30" ht="15.75" thickBot="1">
       <c r="A50" s="103">
         <v>46197</v>
       </c>
@@ -6658,7 +6658,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="112"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:30" ht="15.75" thickBot="1">
       <c r="A51" s="104"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
@@ -6709,7 +6709,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="114"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:30" ht="15.75" thickBot="1">
       <c r="A52" s="105"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
@@ -6760,7 +6760,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="115"/>
+      <c r="F52" s="119"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6795,7 +6795,7 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:30" ht="15.75" thickBot="1">
       <c r="A53" s="105"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
@@ -6811,7 +6811,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="115"/>
+      <c r="F53" s="119"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:30" ht="15.75" thickBot="1">
       <c r="A54" s="105"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
@@ -6862,7 +6862,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="115"/>
+      <c r="F54" s="119"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:30" ht="15.75" thickBot="1">
       <c r="A55" s="106"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
@@ -6913,7 +6913,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="116"/>
+      <c r="F55" s="120"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6948,8 +6948,8 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="118">
+    <row r="56" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A56" s="107">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6966,7 +6966,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="112"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -7001,8 +7001,8 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="119"/>
+    <row r="57" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A57" s="108"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -7017,7 +7017,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="114"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -7052,8 +7052,8 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="120"/>
+    <row r="58" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A58" s="109"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -7068,7 +7068,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="115"/>
+      <c r="F58" s="119"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -7103,8 +7103,8 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="120"/>
+    <row r="59" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A59" s="109"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -7119,7 +7119,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="115"/>
+      <c r="F59" s="119"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -7154,8 +7154,8 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="120"/>
+    <row r="60" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A60" s="109"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7170,7 +7170,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="115"/>
+      <c r="F60" s="119"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7205,8 +7205,8 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="121"/>
+    <row r="61" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A61" s="110"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7221,7 +7221,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="116"/>
+      <c r="F61" s="120"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:30" ht="15.75" thickBot="1">
       <c r="A62" s="103">
         <v>46199</v>
       </c>
@@ -7274,7 +7274,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="112"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:30" ht="15.75" thickBot="1">
       <c r="A63" s="104"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
@@ -7325,7 +7325,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="114"/>
+      <c r="F63" s="118"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:30" ht="15.75" thickBot="1">
       <c r="A64" s="105"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
@@ -7376,7 +7376,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="115"/>
+      <c r="F64" s="119"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:30" ht="15.75" thickBot="1">
       <c r="A65" s="105"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
@@ -7427,7 +7427,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="115"/>
+      <c r="F65" s="119"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:30" ht="15.75" thickBot="1">
       <c r="A66" s="105"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
@@ -7478,7 +7478,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="115"/>
+      <c r="F66" s="119"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:30" ht="15.75" thickBot="1">
       <c r="A67" s="106"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
@@ -7529,7 +7529,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="116"/>
+      <c r="F67" s="120"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7564,8 +7564,8 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="107">
+    <row r="68" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A68" s="111">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7582,7 +7582,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="112"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7617,8 +7617,8 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="108"/>
+    <row r="69" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7633,7 +7633,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="114"/>
+      <c r="F69" s="118"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7668,8 +7668,8 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="109"/>
+    <row r="70" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7684,7 +7684,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="115"/>
+      <c r="F70" s="119"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7719,8 +7719,8 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="109"/>
+    <row r="71" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7735,7 +7735,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="115"/>
+      <c r="F71" s="119"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7770,8 +7770,8 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="109"/>
+    <row r="72" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7786,7 +7786,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="115"/>
+      <c r="F72" s="119"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7821,8 +7821,8 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="110"/>
+    <row r="73" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7837,7 +7837,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="117"/>
+      <c r="F73" s="121"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7872,69 +7872,69 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
       <c r="F74" s="19" t="s">
         <v>129</v>
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7942,15 +7942,15 @@
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7959,6 +7959,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
@@ -7975,8 +7977,6 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76ADBD4-52A2-4D49-A371-690F36A51538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C730CC09-110A-43CD-AB71-B9D05483112F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="135">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -5765,7 +5765,7 @@
         <v>Curaçao</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F35" s="118"/>
       <c r="G35" s="63" t="s">
@@ -5798,7 +5798,9 @@
       <c r="P35" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="Q35" s="71"/>
+      <c r="Q35" s="71" t="s">
+        <v>44</v>
+      </c>
       <c r="R35" s="71" t="s">
         <v>44</v>
       </c>
@@ -5826,17 +5828,17 @@
       <c r="Z35" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="AA35" s="81" t="str">
+      <c r="AA35" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB35" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC35" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD35" s="54"/>
     </row>
@@ -7954,16 +7956,11 @@
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7977,6 +7974,11 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C730CC09-110A-43CD-AB71-B9D05483112F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A50F6B-2028-47CB-B28A-A5CA73C6C750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="136">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -468,6 +468,9 @@
   </si>
   <si>
     <t>6x0</t>
+  </si>
+  <si>
+    <t>0x4</t>
   </si>
 </sst>
 </file>
@@ -1556,6 +1559,51 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1567,51 +1615,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2671,7 +2674,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="115"/>
+      <c r="F1" s="107"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2760,7 +2763,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="116"/>
+      <c r="F2" s="108"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2850,7 +2853,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="117"/>
+      <c r="F3" s="109"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2942,7 +2945,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="116"/>
+      <c r="F4" s="108"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3033,7 +3036,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="117"/>
+      <c r="F5" s="109"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3109,7 +3112,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" ht="15">
-      <c r="A6" s="107">
+      <c r="A6" s="114">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3126,7 +3129,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="116"/>
+      <c r="F6" s="108"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3202,7 +3205,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" ht="15">
-      <c r="A7" s="108"/>
+      <c r="A7" s="115"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3217,7 +3220,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="118"/>
+      <c r="F7" s="110"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3293,7 +3296,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" ht="15">
-      <c r="A8" s="109"/>
+      <c r="A8" s="116"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3308,7 +3311,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="119"/>
+      <c r="F8" s="111"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3384,7 +3387,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" ht="15">
-      <c r="A9" s="110"/>
+      <c r="A9" s="117"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3399,7 +3402,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="120"/>
+      <c r="F9" s="112"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3475,7 +3478,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" ht="15">
-      <c r="A10" s="103">
+      <c r="A10" s="118">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3492,7 +3495,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="116"/>
+      <c r="F10" s="108"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3566,7 +3569,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" ht="15">
-      <c r="A11" s="104"/>
+      <c r="A11" s="119"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3581,7 +3584,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="110"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3657,7 +3660,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" ht="15">
-      <c r="A12" s="105"/>
+      <c r="A12" s="120"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3672,7 +3675,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="119"/>
+      <c r="F12" s="111"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3748,7 +3751,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" ht="15">
-      <c r="A13" s="106"/>
+      <c r="A13" s="121"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3763,7 +3766,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="120"/>
+      <c r="F13" s="112"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3839,7 +3842,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" ht="15">
-      <c r="A14" s="107">
+      <c r="A14" s="114">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3856,7 +3859,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="116"/>
+      <c r="F14" s="108"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3932,7 +3935,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" ht="15">
-      <c r="A15" s="108"/>
+      <c r="A15" s="115"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3947,7 +3950,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="118"/>
+      <c r="F15" s="110"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4023,7 +4026,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A16" s="109"/>
+      <c r="A16" s="116"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4038,7 +4041,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="119"/>
+      <c r="F16" s="111"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4114,7 +4117,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A17" s="110"/>
+      <c r="A17" s="117"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4129,7 +4132,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="120"/>
+      <c r="F17" s="112"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4205,7 +4208,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A18" s="103">
+      <c r="A18" s="118">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4222,7 +4225,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="116"/>
+      <c r="F18" s="108"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4298,7 +4301,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" ht="15">
-      <c r="A19" s="104"/>
+      <c r="A19" s="119"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4313,7 +4316,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="118"/>
+      <c r="F19" s="110"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4389,7 +4392,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" ht="15">
-      <c r="A20" s="105"/>
+      <c r="A20" s="120"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4404,7 +4407,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="119"/>
+      <c r="F20" s="111"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4480,7 +4483,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A21" s="106"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4495,7 +4498,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="120"/>
+      <c r="F21" s="112"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4571,7 +4574,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A22" s="107">
+      <c r="A22" s="114">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4588,7 +4591,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="116"/>
+      <c r="F22" s="108"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4664,7 +4667,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A23" s="108"/>
+      <c r="A23" s="115"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4679,7 +4682,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="118"/>
+      <c r="F23" s="110"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4755,7 +4758,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A24" s="109"/>
+      <c r="A24" s="116"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4770,7 +4773,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="119"/>
+      <c r="F24" s="111"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4846,7 +4849,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A25" s="110"/>
+      <c r="A25" s="117"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4861,7 +4864,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="120"/>
+      <c r="F25" s="112"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4937,7 +4940,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A26" s="103">
+      <c r="A26" s="118">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4954,7 +4957,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="116"/>
+      <c r="F26" s="108"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5030,7 +5033,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A27" s="104"/>
+      <c r="A27" s="119"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5045,7 +5048,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="118"/>
+      <c r="F27" s="110"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5119,7 +5122,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A28" s="105"/>
+      <c r="A28" s="120"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5134,7 +5137,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="119"/>
+      <c r="F28" s="111"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5208,7 +5211,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A29" s="106"/>
+      <c r="A29" s="121"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5223,7 +5226,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="120"/>
+      <c r="F29" s="112"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5297,7 +5300,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A30" s="107">
+      <c r="A30" s="114">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5314,7 +5317,7 @@
       <c r="E30" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="116"/>
+      <c r="F30" s="108"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5388,7 +5391,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A31" s="108"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5403,7 +5406,7 @@
       <c r="E31" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="118"/>
+      <c r="F31" s="110"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5479,7 +5482,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A32" s="109"/>
+      <c r="A32" s="116"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5494,7 +5497,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="119"/>
+      <c r="F32" s="111"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5568,7 +5571,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A33" s="110"/>
+      <c r="A33" s="117"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5583,7 +5586,7 @@
       <c r="E33" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="120"/>
+      <c r="F33" s="112"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5659,7 +5662,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A34" s="103">
+      <c r="A34" s="118">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5676,7 +5679,7 @@
       <c r="E34" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="116"/>
+      <c r="F34" s="108"/>
       <c r="G34" s="60" t="s">
         <v>44</v>
       </c>
@@ -5752,7 +5755,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A35" s="104"/>
+      <c r="A35" s="119"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5767,7 +5770,7 @@
       <c r="E35" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="118"/>
+      <c r="F35" s="110"/>
       <c r="G35" s="63" t="s">
         <v>44</v>
       </c>
@@ -5843,7 +5846,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A36" s="105"/>
+      <c r="A36" s="120"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5858,7 +5861,7 @@
       <c r="E36" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="111"/>
       <c r="G36" s="65" t="s">
         <v>44</v>
       </c>
@@ -5934,7 +5937,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A37" s="106"/>
+      <c r="A37" s="121"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5947,9 +5950,9 @@
         <v>Japão</v>
       </c>
       <c r="E37" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="F37" s="120"/>
+        <v>135</v>
+      </c>
+      <c r="F37" s="112"/>
       <c r="G37" s="68" t="s">
         <v>45</v>
       </c>
@@ -6010,22 +6013,22 @@
       <c r="Z37" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="AA37" s="81" t="str">
+      <c r="AA37" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB37" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AC37" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A38" s="107">
+      <c r="A38" s="114">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -6042,7 +6045,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="116"/>
+      <c r="F38" s="108"/>
       <c r="G38" s="60"/>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -6078,7 +6081,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A39" s="108"/>
+      <c r="A39" s="115"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -6093,7 +6096,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="118"/>
+      <c r="F39" s="110"/>
       <c r="G39" s="63"/>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -6129,7 +6132,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A40" s="109"/>
+      <c r="A40" s="116"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -6144,7 +6147,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="119"/>
+      <c r="F40" s="111"/>
       <c r="G40" s="65"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -6180,7 +6183,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A41" s="110"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6195,7 +6198,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="120"/>
+      <c r="F41" s="112"/>
       <c r="G41" s="68"/>
       <c r="H41" s="69"/>
       <c r="I41" s="69"/>
@@ -6231,7 +6234,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A42" s="103">
+      <c r="A42" s="118">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6248,7 +6251,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="116"/>
+      <c r="F42" s="108"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -6284,7 +6287,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A43" s="104"/>
+      <c r="A43" s="119"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6299,7 +6302,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="118"/>
+      <c r="F43" s="110"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6335,7 +6338,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A44" s="105"/>
+      <c r="A44" s="120"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6350,7 +6353,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="119"/>
+      <c r="F44" s="111"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6386,7 +6389,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A45" s="106"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6401,7 +6404,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="120"/>
+      <c r="F45" s="112"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6437,7 +6440,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A46" s="107">
+      <c r="A46" s="114">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6454,7 +6457,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="116"/>
+      <c r="F46" s="108"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6490,7 +6493,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A47" s="108"/>
+      <c r="A47" s="115"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6505,7 +6508,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="118"/>
+      <c r="F47" s="110"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6541,7 +6544,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A48" s="109"/>
+      <c r="A48" s="116"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6556,7 +6559,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="119"/>
+      <c r="F48" s="111"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6592,7 +6595,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A49" s="110"/>
+      <c r="A49" s="117"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6607,7 +6610,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="120"/>
+      <c r="F49" s="112"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6643,7 +6646,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A50" s="103">
+      <c r="A50" s="118">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6660,7 +6663,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="116"/>
+      <c r="F50" s="108"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6696,7 +6699,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A51" s="104"/>
+      <c r="A51" s="119"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6711,7 +6714,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="118"/>
+      <c r="F51" s="110"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6747,7 +6750,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A52" s="105"/>
+      <c r="A52" s="120"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6762,7 +6765,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="119"/>
+      <c r="F52" s="111"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6798,7 +6801,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A53" s="105"/>
+      <c r="A53" s="120"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6813,7 +6816,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="119"/>
+      <c r="F53" s="111"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6849,7 +6852,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A54" s="105"/>
+      <c r="A54" s="120"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6864,7 +6867,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="119"/>
+      <c r="F54" s="111"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6900,7 +6903,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A55" s="106"/>
+      <c r="A55" s="121"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6915,7 +6918,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="120"/>
+      <c r="F55" s="112"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6951,7 +6954,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A56" s="107">
+      <c r="A56" s="114">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6968,7 +6971,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="116"/>
+      <c r="F56" s="108"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -7004,7 +7007,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A57" s="108"/>
+      <c r="A57" s="115"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -7019,7 +7022,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="118"/>
+      <c r="F57" s="110"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -7055,7 +7058,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A58" s="109"/>
+      <c r="A58" s="116"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -7070,7 +7073,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="119"/>
+      <c r="F58" s="111"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -7106,7 +7109,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A59" s="109"/>
+      <c r="A59" s="116"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -7121,7 +7124,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="119"/>
+      <c r="F59" s="111"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -7157,7 +7160,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A60" s="109"/>
+      <c r="A60" s="116"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7172,7 +7175,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="119"/>
+      <c r="F60" s="111"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7208,7 +7211,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A61" s="110"/>
+      <c r="A61" s="117"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7223,7 +7226,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="120"/>
+      <c r="F61" s="112"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7259,7 +7262,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A62" s="103">
+      <c r="A62" s="118">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7276,7 +7279,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="116"/>
+      <c r="F62" s="108"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7312,7 +7315,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A63" s="104"/>
+      <c r="A63" s="119"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7327,7 +7330,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="118"/>
+      <c r="F63" s="110"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7363,7 +7366,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A64" s="105"/>
+      <c r="A64" s="120"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7378,7 +7381,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="119"/>
+      <c r="F64" s="111"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7414,7 +7417,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A65" s="105"/>
+      <c r="A65" s="120"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7429,7 +7432,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="119"/>
+      <c r="F65" s="111"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7465,7 +7468,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A66" s="105"/>
+      <c r="A66" s="120"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7480,7 +7483,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="119"/>
+      <c r="F66" s="111"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7516,7 +7519,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A67" s="106"/>
+      <c r="A67" s="121"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7531,7 +7534,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="120"/>
+      <c r="F67" s="112"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7567,7 +7570,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A68" s="111">
+      <c r="A68" s="103">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7584,7 +7587,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="116"/>
+      <c r="F68" s="108"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7620,7 +7623,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A69" s="112"/>
+      <c r="A69" s="104"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7635,7 +7638,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="118"/>
+      <c r="F69" s="110"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7671,7 +7674,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A70" s="113"/>
+      <c r="A70" s="105"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7686,7 +7689,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="119"/>
+      <c r="F70" s="111"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7722,7 +7725,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A71" s="113"/>
+      <c r="A71" s="105"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7737,7 +7740,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="119"/>
+      <c r="F71" s="111"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7773,7 +7776,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A72" s="113"/>
+      <c r="A72" s="105"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7788,7 +7791,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="119"/>
+      <c r="F72" s="111"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7824,7 +7827,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A73" s="114"/>
+      <c r="A73" s="106"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7839,7 +7842,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="121"/>
+      <c r="F73" s="113"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7880,43 +7883,43 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -7924,43 +7927,45 @@
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -7977,8 +7982,6 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A50F6B-2028-47CB-B28A-A5CA73C6C750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060AF2B1-C37B-473D-A352-2F7B957FF956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="136">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -1267,7 +1267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1559,6 +1559,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1593,30 +1617,6 @@
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1635,13 +1635,38 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1731,11 +1756,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}" name="BolaoCopa" displayName="BolaoCopa" ref="A4:B20" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A4:B20" xr:uid="{49FA96F6-1C29-4184-8466-79C03B42EAD6}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{377F1B03-9BE9-462A-A1BC-1F8EE6567180}" name="Participantes" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{EF301B8F-51D1-4897-A7D7-3E56DAA9D6FC}" name="Pago" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2265,7 +2290,7 @@
     <mergeCell ref="A1:B3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B20">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Ok">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Ok">
       <formula>NOT(ISERROR(SEARCH("Ok",B5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2637,7 +2662,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:E17">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$E4=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2674,7 +2699,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="107"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2763,7 +2788,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="108"/>
+      <c r="F2" s="116"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2853,7 +2878,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="109"/>
+      <c r="F3" s="117"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2945,7 +2970,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3036,7 +3061,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="109"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3112,7 +3137,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" ht="15">
-      <c r="A6" s="114">
+      <c r="A6" s="103">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3129,7 +3154,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3205,7 +3230,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" ht="15">
-      <c r="A7" s="115"/>
+      <c r="A7" s="104"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3220,7 +3245,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="110"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3296,7 +3321,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" ht="15">
-      <c r="A8" s="116"/>
+      <c r="A8" s="105"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3311,7 +3336,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="111"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3387,7 +3412,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" ht="15">
-      <c r="A9" s="117"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3402,7 +3427,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="112"/>
+      <c r="F9" s="120"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3478,7 +3503,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" ht="15">
-      <c r="A10" s="118">
+      <c r="A10" s="107">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3495,7 +3520,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="116"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3569,7 +3594,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" ht="15">
-      <c r="A11" s="119"/>
+      <c r="A11" s="108"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3584,7 +3609,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="110"/>
+      <c r="F11" s="118"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3660,7 +3685,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" ht="15">
-      <c r="A12" s="120"/>
+      <c r="A12" s="109"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3675,7 +3700,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="111"/>
+      <c r="F12" s="119"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3751,7 +3776,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" ht="15">
-      <c r="A13" s="121"/>
+      <c r="A13" s="110"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3766,7 +3791,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="112"/>
+      <c r="F13" s="120"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3842,7 +3867,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" ht="15">
-      <c r="A14" s="114">
+      <c r="A14" s="103">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3859,7 +3884,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="108"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3935,7 +3960,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" ht="15">
-      <c r="A15" s="115"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3950,7 +3975,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="110"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4026,7 +4051,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A16" s="116"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4041,7 +4066,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="111"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4117,7 +4142,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A17" s="117"/>
+      <c r="A17" s="106"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4132,7 +4157,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="112"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4208,7 +4233,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A18" s="118">
+      <c r="A18" s="107">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4225,7 +4250,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="108"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4301,7 +4326,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" ht="15">
-      <c r="A19" s="119"/>
+      <c r="A19" s="108"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4316,7 +4341,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="110"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4392,7 +4417,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" ht="15">
-      <c r="A20" s="120"/>
+      <c r="A20" s="109"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4407,7 +4432,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="111"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4483,7 +4508,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A21" s="121"/>
+      <c r="A21" s="110"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4498,7 +4523,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="112"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4574,7 +4599,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A22" s="114">
+      <c r="A22" s="103">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4591,7 +4616,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="108"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4667,7 +4692,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A23" s="115"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4682,7 +4707,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="110"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4758,7 +4783,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A24" s="116"/>
+      <c r="A24" s="105"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4773,7 +4798,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="111"/>
+      <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4849,7 +4874,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A25" s="117"/>
+      <c r="A25" s="106"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4864,7 +4889,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="112"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4940,7 +4965,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A26" s="118">
+      <c r="A26" s="107">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4957,7 +4982,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="108"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5033,7 +5058,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A27" s="119"/>
+      <c r="A27" s="108"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5048,7 +5073,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="110"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5122,7 +5147,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A28" s="120"/>
+      <c r="A28" s="109"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5137,7 +5162,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="111"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5211,7 +5236,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A29" s="121"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5226,7 +5251,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="112"/>
+      <c r="F29" s="120"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5300,7 +5325,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A30" s="114">
+      <c r="A30" s="103">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5317,7 +5342,7 @@
       <c r="E30" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="108"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5391,7 +5416,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A31" s="115"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5406,7 +5431,7 @@
       <c r="E31" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="110"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5482,7 +5507,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A32" s="116"/>
+      <c r="A32" s="105"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5497,7 +5522,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="111"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5571,7 +5596,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A33" s="117"/>
+      <c r="A33" s="106"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5586,7 +5611,7 @@
       <c r="E33" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="112"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5662,7 +5687,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A34" s="118">
+      <c r="A34" s="107">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5679,7 +5704,7 @@
       <c r="E34" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="108"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="60" t="s">
         <v>44</v>
       </c>
@@ -5755,7 +5780,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A35" s="119"/>
+      <c r="A35" s="108"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5770,7 +5795,7 @@
       <c r="E35" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="110"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="63" t="s">
         <v>44</v>
       </c>
@@ -5846,7 +5871,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A36" s="120"/>
+      <c r="A36" s="109"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5861,7 +5886,7 @@
       <c r="E36" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="111"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="65" t="s">
         <v>44</v>
       </c>
@@ -5937,7 +5962,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A37" s="121"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5952,7 +5977,7 @@
       <c r="E37" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="112"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="68" t="s">
         <v>45</v>
       </c>
@@ -6028,7 +6053,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A38" s="114">
+      <c r="A38" s="103">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -6045,27 +6070,61 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="108"/>
-      <c r="G38" s="60"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="61"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
+      <c r="F38" s="116"/>
+      <c r="G38" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="I38" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="K38" s="61" t="s">
+        <v>44</v>
+      </c>
       <c r="L38" s="61"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="61"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="61"/>
+      <c r="M38" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="N38" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="O38" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="P38" s="61" t="s">
+        <v>44</v>
+      </c>
       <c r="Q38" s="61"/>
       <c r="R38" s="61"/>
-      <c r="S38" s="61"/>
-      <c r="T38" s="61"/>
-      <c r="U38" s="62"/>
-      <c r="V38" s="62"/>
-      <c r="W38" s="62"/>
-      <c r="X38" s="62"/>
-      <c r="Y38" s="62"/>
-      <c r="Z38" s="76"/>
+      <c r="S38" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="T38" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="U38" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="V38" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="W38" s="62" t="s">
+        <v>46</v>
+      </c>
+      <c r="X38" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y38" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" s="76" t="s">
+        <v>46</v>
+      </c>
       <c r="AA38" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6081,7 +6140,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A39" s="115"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -6096,27 +6155,61 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="110"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="H39" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="I39" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="J39" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="K39" s="71" t="s">
+        <v>46</v>
+      </c>
       <c r="L39" s="71"/>
-      <c r="M39" s="71"/>
-      <c r="N39" s="71"/>
-      <c r="O39" s="71"/>
-      <c r="P39" s="71"/>
+      <c r="M39" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="N39" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="O39" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="P39" s="71" t="s">
+        <v>45</v>
+      </c>
       <c r="Q39" s="71"/>
       <c r="R39" s="71"/>
-      <c r="S39" s="71"/>
-      <c r="T39" s="71"/>
-      <c r="U39" s="56"/>
-      <c r="V39" s="56"/>
-      <c r="W39" s="56"/>
-      <c r="X39" s="56"/>
-      <c r="Y39" s="56"/>
-      <c r="Z39" s="80"/>
+      <c r="S39" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="T39" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="U39" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="V39" s="129" t="s">
+        <v>45</v>
+      </c>
+      <c r="W39" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="X39" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y39" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z39" s="80" t="s">
+        <v>45</v>
+      </c>
       <c r="AA39" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6132,7 +6225,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A40" s="116"/>
+      <c r="A40" s="105"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -6147,27 +6240,61 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="111"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="66"/>
+      <c r="F40" s="119"/>
+      <c r="G40" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H40" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I40" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="J40" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="K40" s="66" t="s">
+        <v>44</v>
+      </c>
       <c r="L40" s="66"/>
-      <c r="M40" s="66"/>
-      <c r="N40" s="66"/>
-      <c r="O40" s="66"/>
-      <c r="P40" s="66"/>
+      <c r="M40" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="N40" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O40" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="P40" s="66" t="s">
+        <v>44</v>
+      </c>
       <c r="Q40" s="66"/>
       <c r="R40" s="66"/>
-      <c r="S40" s="66"/>
-      <c r="T40" s="66"/>
-      <c r="U40" s="67"/>
-      <c r="V40" s="67"/>
-      <c r="W40" s="67"/>
-      <c r="X40" s="67"/>
-      <c r="Y40" s="67"/>
-      <c r="Z40" s="78"/>
+      <c r="S40" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="T40" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="U40" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="V40" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W40" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="X40" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y40" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z40" s="78" t="s">
+        <v>44</v>
+      </c>
       <c r="AA40" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6183,7 +6310,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A41" s="117"/>
+      <c r="A41" s="106"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6198,27 +6325,61 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="112"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="I41" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="J41" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="K41" s="69" t="s">
+        <v>44</v>
+      </c>
       <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="69"/>
-      <c r="P41" s="69"/>
+      <c r="M41" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="N41" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="O41" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="P41" s="69" t="s">
+        <v>44</v>
+      </c>
       <c r="Q41" s="69"/>
       <c r="R41" s="69"/>
-      <c r="S41" s="69"/>
-      <c r="T41" s="69"/>
-      <c r="U41" s="70"/>
-      <c r="V41" s="70"/>
-      <c r="W41" s="70"/>
-      <c r="X41" s="70"/>
-      <c r="Y41" s="70"/>
-      <c r="Z41" s="79"/>
+      <c r="S41" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="T41" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="U41" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="V41" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="W41" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="X41" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y41" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z41" s="79" t="s">
+        <v>46</v>
+      </c>
       <c r="AA41" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6234,7 +6395,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A42" s="118">
+      <c r="A42" s="107">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6251,7 +6412,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="108"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -6287,7 +6448,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A43" s="119"/>
+      <c r="A43" s="108"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6302,7 +6463,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="110"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6338,7 +6499,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A44" s="120"/>
+      <c r="A44" s="109"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6353,7 +6514,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="111"/>
+      <c r="F44" s="119"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6389,7 +6550,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A45" s="121"/>
+      <c r="A45" s="110"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6404,7 +6565,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="112"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6440,7 +6601,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A46" s="114">
+      <c r="A46" s="103">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6457,7 +6618,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="108"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6493,7 +6654,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A47" s="115"/>
+      <c r="A47" s="104"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6508,7 +6669,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="110"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6544,7 +6705,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A48" s="116"/>
+      <c r="A48" s="105"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6559,7 +6720,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="111"/>
+      <c r="F48" s="119"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6595,7 +6756,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A49" s="117"/>
+      <c r="A49" s="106"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6610,7 +6771,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="112"/>
+      <c r="F49" s="120"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6646,7 +6807,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A50" s="118">
+      <c r="A50" s="107">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6663,7 +6824,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="108"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6699,7 +6860,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A51" s="119"/>
+      <c r="A51" s="108"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6714,7 +6875,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="110"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6750,7 +6911,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A52" s="120"/>
+      <c r="A52" s="109"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6765,7 +6926,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="111"/>
+      <c r="F52" s="119"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6801,7 +6962,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A53" s="120"/>
+      <c r="A53" s="109"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6816,7 +6977,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="111"/>
+      <c r="F53" s="119"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -6834,7 +6995,6 @@
       <c r="U53" s="67"/>
       <c r="V53" s="67"/>
       <c r="W53" s="67"/>
-      <c r="X53" s="67"/>
       <c r="Y53" s="67"/>
       <c r="Z53" s="78"/>
       <c r="AA53" s="81" t="str">
@@ -6852,7 +7012,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A54" s="120"/>
+      <c r="A54" s="109"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -6867,7 +7027,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="111"/>
+      <c r="F54" s="119"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -6903,7 +7063,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A55" s="121"/>
+      <c r="A55" s="110"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -6918,7 +7078,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="112"/>
+      <c r="F55" s="120"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -6954,7 +7114,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A56" s="114">
+      <c r="A56" s="103">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -6971,7 +7131,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="108"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -7007,7 +7167,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A57" s="115"/>
+      <c r="A57" s="104"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -7022,7 +7182,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="110"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -7058,7 +7218,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A58" s="116"/>
+      <c r="A58" s="105"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -7073,7 +7233,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="111"/>
+      <c r="F58" s="119"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -7109,7 +7269,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A59" s="116"/>
+      <c r="A59" s="105"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -7124,7 +7284,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="111"/>
+      <c r="F59" s="119"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -7160,7 +7320,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A60" s="116"/>
+      <c r="A60" s="105"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7175,7 +7335,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="111"/>
+      <c r="F60" s="119"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7211,7 +7371,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A61" s="117"/>
+      <c r="A61" s="106"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7226,7 +7386,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="112"/>
+      <c r="F61" s="120"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7262,7 +7422,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A62" s="118">
+      <c r="A62" s="107">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7279,7 +7439,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="108"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7315,7 +7475,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A63" s="119"/>
+      <c r="A63" s="108"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7330,7 +7490,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="110"/>
+      <c r="F63" s="118"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7366,7 +7526,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A64" s="120"/>
+      <c r="A64" s="109"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7381,7 +7541,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="111"/>
+      <c r="F64" s="119"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7417,7 +7577,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A65" s="120"/>
+      <c r="A65" s="109"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7432,7 +7592,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="111"/>
+      <c r="F65" s="119"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7468,7 +7628,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A66" s="120"/>
+      <c r="A66" s="109"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7483,7 +7643,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="111"/>
+      <c r="F66" s="119"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7519,7 +7679,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A67" s="121"/>
+      <c r="A67" s="110"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7534,7 +7694,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="112"/>
+      <c r="F67" s="120"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7570,7 +7730,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A68" s="103">
+      <c r="A68" s="111">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7587,7 +7747,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="108"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7623,7 +7783,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A69" s="104"/>
+      <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7638,7 +7798,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="110"/>
+      <c r="F69" s="118"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7674,7 +7834,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A70" s="105"/>
+      <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7689,7 +7849,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="111"/>
+      <c r="F70" s="119"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7725,7 +7885,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A71" s="105"/>
+      <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7740,7 +7900,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="111"/>
+      <c r="F71" s="119"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7776,7 +7936,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A72" s="105"/>
+      <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7791,7 +7951,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="111"/>
+      <c r="F72" s="119"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7827,7 +7987,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1">
-      <c r="A73" s="106"/>
+      <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7842,7 +8002,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="113"/>
+      <c r="F73" s="121"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -7964,6 +8124,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
@@ -7980,20 +8142,26 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
-  <conditionalFormatting sqref="G2:Z73">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="G54:Z73 G53:W53 Y53:Z53 G2:Z37 G40:Z52 G38:U39 W38:Z39 V39">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND($AC2&lt;&gt;"",G2=$AC2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND($AC2&lt;&gt;"",G2&lt;&gt;"",G2&lt;&gt;$AC2)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V38">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>AND($AC39&lt;&gt;"",V38=$AC39)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>AND($AC39&lt;&gt;"",V38&lt;&gt;"",V38&lt;&gt;$AC39)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:Z73" xr:uid="{5B8CAFB9-760C-4EAE-8934-296EE66D380D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Z73 X2:X52 X54:X73 W39 G40:W73 G39:U39 G2:W38" xr:uid="{5B8CAFB9-760C-4EAE-8934-296EE66D380D}">
       <formula1>"A,B,E"</formula1>
     </dataValidation>
   </dataValidations>

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -477,7 +477,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1267,7 +1267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1635,9 +1635,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2111,13 +2108,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.75" customWidth="1"/>
-    <col min="2" max="3" width="14.25" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="3" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.25">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
@@ -2129,7 +2126,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="126"/>
       <c r="B2" s="126"/>
       <c r="C2" s="13"/>
@@ -2139,7 +2136,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="126"/>
       <c r="B3" s="126"/>
       <c r="C3" s="13"/>
@@ -2149,7 +2146,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:8" ht="26.1" customHeight="1">
+    <row r="4" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -2157,7 +2154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2165,7 +2162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2173,7 +2170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2181,7 +2178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2189,7 +2186,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2197,7 +2194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2205,7 +2202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2213,7 +2210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2221,7 +2218,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2229,7 +2226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2237,7 +2234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2245,7 +2242,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2253,7 +2250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2261,7 +2258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2269,7 +2266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2277,7 +2274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2309,16 +2306,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="7" width="12.125" customWidth="1"/>
-    <col min="9" max="9" width="22.875" customWidth="1"/>
-    <col min="10" max="10" width="9.625" customWidth="1"/>
+    <col min="3" max="7" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="127" t="s">
         <v>20</v>
       </c>
@@ -2329,7 +2326,7 @@
       <c r="F1" s="128"/>
       <c r="G1" s="128"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1">
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2350,7 +2347,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" ht="15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2377,7 +2374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2399,7 +2396,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" ht="15">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2420,7 +2417,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2444,7 +2441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2468,7 +2465,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2489,7 +2486,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2510,7 +2507,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2531,7 +2528,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2552,7 +2549,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2573,7 +2570,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2594,7 +2591,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2615,7 +2612,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2636,7 +2633,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2673,17 +2670,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="2" width="32.375" customWidth="1"/>
-    <col min="3" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="5" width="12.625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="29" width="16.375" customWidth="1"/>
+    <col min="7" max="29" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2770,7 +2767,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="122">
         <v>46184</v>
       </c>
@@ -2862,7 +2859,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2952,7 +2949,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="15">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="124">
         <v>46185</v>
       </c>
@@ -3045,7 +3042,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" ht="15">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -3136,7 +3133,7 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" ht="15">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="103">
         <v>46186</v>
       </c>
@@ -3229,7 +3226,7 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" ht="15">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="104"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
@@ -3320,7 +3317,7 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" ht="15">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="105"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
@@ -3411,7 +3408,7 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" ht="15">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="106"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
@@ -3502,7 +3499,7 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" ht="15">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="107">
         <v>46187</v>
       </c>
@@ -3593,7 +3590,7 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" ht="15">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="108"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
@@ -3684,7 +3681,7 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" ht="15">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="109"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
@@ -3775,7 +3772,7 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" ht="15">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="110"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
@@ -3866,7 +3863,7 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" ht="15">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="103">
         <v>46188</v>
       </c>
@@ -3959,7 +3956,7 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" ht="15">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="104"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
@@ -4050,7 +4047,7 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1">
+    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="105"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
@@ -4141,7 +4138,7 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" thickBot="1">
+    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="106"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
@@ -4232,7 +4229,7 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" thickBot="1">
+    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="107">
         <v>46189</v>
       </c>
@@ -4325,7 +4322,7 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" ht="15">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="108"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
@@ -4416,7 +4413,7 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" ht="15">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="109"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
@@ -4507,7 +4504,7 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" ht="15.75" thickBot="1">
+    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="110"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
@@ -4598,7 +4595,7 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" ht="15.75" thickBot="1">
+    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="103">
         <v>46190</v>
       </c>
@@ -4691,7 +4688,7 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" ht="15.75" thickBot="1">
+    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="104"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
@@ -4782,7 +4779,7 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" ht="15.75" thickBot="1">
+    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="105"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
@@ -4873,7 +4870,7 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" ht="15.75" thickBot="1">
+    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="106"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
@@ -4964,7 +4961,7 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" ht="15.75" thickBot="1">
+    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="107">
         <v>46191</v>
       </c>
@@ -5057,7 +5054,7 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" ht="15.75" thickBot="1">
+    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="108"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
@@ -5146,7 +5143,7 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" ht="15.75" thickBot="1">
+    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="109"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
@@ -5235,7 +5232,7 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" ht="15.75" thickBot="1">
+    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="110"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
@@ -5324,7 +5321,7 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" ht="15.75" thickBot="1">
+    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="103">
         <v>46192</v>
       </c>
@@ -5415,7 +5412,7 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" ht="15.75" thickBot="1">
+    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="104"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
@@ -5506,7 +5503,7 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" ht="15.75" thickBot="1">
+    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="105"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
@@ -5595,7 +5592,7 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" ht="15.75" thickBot="1">
+    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="106"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
@@ -5686,7 +5683,7 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" ht="15.75" thickBot="1">
+    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="107">
         <v>46193</v>
       </c>
@@ -5779,7 +5776,7 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" ht="15.75" thickBot="1">
+    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="108"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
@@ -5870,7 +5867,7 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" ht="15.75" thickBot="1">
+    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="109"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
@@ -5961,7 +5958,7 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" ht="15.75" thickBot="1">
+    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="110"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
@@ -6052,7 +6049,7 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" ht="15.75" thickBot="1">
+    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="103">
         <v>46194</v>
       </c>
@@ -6139,7 +6136,7 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" ht="15.75" thickBot="1">
+    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="104"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
@@ -6195,7 +6192,7 @@
       <c r="U39" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="V39" s="129" t="s">
+      <c r="V39" s="59" t="s">
         <v>45</v>
       </c>
       <c r="W39" s="56" t="s">
@@ -6224,7 +6221,7 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" ht="15.75" thickBot="1">
+    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="105"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
@@ -6309,7 +6306,7 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" ht="15.75" thickBot="1">
+    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="106"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
@@ -6394,7 +6391,7 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" ht="15.75" thickBot="1">
+    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="107">
         <v>46195</v>
       </c>
@@ -6447,7 +6444,7 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" ht="15.75" thickBot="1">
+    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="108"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
@@ -6498,7 +6495,7 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30" ht="15.75" thickBot="1">
+    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="109"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
@@ -6549,7 +6546,7 @@
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30" ht="15.75" thickBot="1">
+    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="110"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
@@ -6600,7 +6597,7 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30" ht="15.75" thickBot="1">
+    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="103">
         <v>46196</v>
       </c>
@@ -6653,7 +6650,7 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30" ht="15.75" thickBot="1">
+    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="104"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
@@ -6704,7 +6701,7 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30" ht="15.75" thickBot="1">
+    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="105"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
@@ -6755,7 +6752,7 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30" ht="15.75" thickBot="1">
+    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="106"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
@@ -6806,7 +6803,7 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30" ht="15.75" thickBot="1">
+    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="107">
         <v>46197</v>
       </c>
@@ -6859,7 +6856,7 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30" ht="15.75" thickBot="1">
+    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="108"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
@@ -6910,7 +6907,7 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30" ht="15.75" thickBot="1">
+    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="109"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
@@ -6961,7 +6958,7 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30" ht="15.75" thickBot="1">
+    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="109"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
@@ -7011,7 +7008,7 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30" ht="15.75" thickBot="1">
+    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="109"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
@@ -7062,7 +7059,7 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30" ht="15.75" thickBot="1">
+    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="110"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
@@ -7113,7 +7110,7 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30" ht="15.75" thickBot="1">
+    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="103">
         <v>46198</v>
       </c>
@@ -7166,7 +7163,7 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30" ht="15.75" thickBot="1">
+    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="104"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
@@ -7217,7 +7214,7 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30" ht="15.75" thickBot="1">
+    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="105"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
@@ -7268,7 +7265,7 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30" ht="15.75" thickBot="1">
+    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="105"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
@@ -7319,7 +7316,7 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30" ht="15.75" thickBot="1">
+    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="105"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
@@ -7370,7 +7367,7 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30" ht="15.75" thickBot="1">
+    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="106"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
@@ -7421,7 +7418,7 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30" ht="15.75" thickBot="1">
+    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="107">
         <v>46199</v>
       </c>
@@ -7474,7 +7471,7 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30" ht="15.75" thickBot="1">
+    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="108"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
@@ -7525,7 +7522,7 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30" ht="15.75" thickBot="1">
+    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="109"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
@@ -7576,7 +7573,7 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30" ht="15.75" thickBot="1">
+    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="109"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
@@ -7627,7 +7624,7 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30" ht="15.75" thickBot="1">
+    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="109"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
@@ -7678,7 +7675,7 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30" ht="15.75" thickBot="1">
+    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="110"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
@@ -7729,7 +7726,7 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30" ht="15.75" thickBot="1">
+    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="111">
         <v>46200</v>
       </c>
@@ -7782,7 +7779,7 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30" ht="15.75" thickBot="1">
+    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
@@ -7833,7 +7830,7 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30" ht="15.75" thickBot="1">
+    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
@@ -7884,7 +7881,7 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30" ht="15.75" thickBot="1">
+    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
@@ -7935,7 +7932,7 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30" ht="15.75" thickBot="1">
+    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
@@ -7986,7 +7983,7 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30" ht="15.75" thickBot="1">
+    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
@@ -8037,7 +8034,7 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F74" s="19" t="s">
         <v>129</v>
       </c>
@@ -8124,11 +8121,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -8142,9 +8134,14 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
-  <conditionalFormatting sqref="G54:Z73 G53:W53 Y53:Z53 G2:Z37 G40:Z52 G38:U39 W38:Z39 V39">
+  <conditionalFormatting sqref="G2:Z37 G38:U39 W38:Z39 V39 G40:Z52 G53:W53 Y53:Z53 G54:Z73">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND($AC2&lt;&gt;"",G2=$AC2)</formula>
     </cfRule>

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060AF2B1-C37B-473D-A352-2F7B957FF956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF39674-143D-4550-AC38-08BC1F5BC1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="136">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -1559,6 +1559,27 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1583,6 +1604,18 @@
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1594,39 +1627,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2696,7 +2696,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="115"/>
+      <c r="F1" s="103"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2768,7 +2768,7 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="122">
+      <c r="A2" s="118">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2785,7 +2785,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="116"/>
+      <c r="F2" s="104"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2860,7 +2860,7 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="123"/>
+      <c r="A3" s="119"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2875,7 +2875,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="117"/>
+      <c r="F3" s="105"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2950,7 +2950,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="124">
+      <c r="A4" s="120">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2967,7 +2967,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="116"/>
+      <c r="F4" s="104"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3043,7 +3043,7 @@
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="125"/>
+      <c r="A5" s="121"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -3058,7 +3058,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="117"/>
+      <c r="F5" s="105"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3134,7 +3134,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="103">
+      <c r="A6" s="110">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3151,7 +3151,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="116"/>
+      <c r="F6" s="104"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3227,7 +3227,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="104"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3242,7 +3242,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="118"/>
+      <c r="F7" s="106"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3318,7 +3318,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="105"/>
+      <c r="A8" s="112"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3333,7 +3333,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="119"/>
+      <c r="F8" s="107"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3409,7 +3409,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="106"/>
+      <c r="A9" s="113"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3424,7 +3424,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="120"/>
+      <c r="F9" s="108"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3500,7 +3500,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="107">
+      <c r="A10" s="114">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3517,7 +3517,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="116"/>
+      <c r="F10" s="104"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3591,7 +3591,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="108"/>
+      <c r="A11" s="115"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3606,7 +3606,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="106"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3682,7 +3682,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="109"/>
+      <c r="A12" s="116"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3697,7 +3697,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="119"/>
+      <c r="F12" s="107"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3773,7 +3773,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="110"/>
+      <c r="A13" s="117"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3788,7 +3788,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="120"/>
+      <c r="F13" s="108"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3864,7 +3864,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="103">
+      <c r="A14" s="110">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3881,7 +3881,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="116"/>
+      <c r="F14" s="104"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3957,7 +3957,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="104"/>
+      <c r="A15" s="111"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3972,7 +3972,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="118"/>
+      <c r="F15" s="106"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4048,7 +4048,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="105"/>
+      <c r="A16" s="112"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4063,7 +4063,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="119"/>
+      <c r="F16" s="107"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4139,7 +4139,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="106"/>
+      <c r="A17" s="113"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4154,7 +4154,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="120"/>
+      <c r="F17" s="108"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4230,7 +4230,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="107">
+      <c r="A18" s="114">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4247,7 +4247,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="116"/>
+      <c r="F18" s="104"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4323,7 +4323,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="108"/>
+      <c r="A19" s="115"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4338,7 +4338,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="118"/>
+      <c r="F19" s="106"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4414,7 +4414,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="109"/>
+      <c r="A20" s="116"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4429,7 +4429,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="119"/>
+      <c r="F20" s="107"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4505,7 +4505,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="110"/>
+      <c r="A21" s="117"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4520,7 +4520,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="120"/>
+      <c r="F21" s="108"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4596,7 +4596,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="103">
+      <c r="A22" s="110">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4613,7 +4613,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="116"/>
+      <c r="F22" s="104"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4689,7 +4689,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="104"/>
+      <c r="A23" s="111"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4704,7 +4704,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="118"/>
+      <c r="F23" s="106"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4780,7 +4780,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="105"/>
+      <c r="A24" s="112"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4795,7 +4795,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="119"/>
+      <c r="F24" s="107"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4871,7 +4871,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="106"/>
+      <c r="A25" s="113"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4886,7 +4886,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="120"/>
+      <c r="F25" s="108"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4962,7 +4962,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="107">
+      <c r="A26" s="114">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4979,7 +4979,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="116"/>
+      <c r="F26" s="104"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5055,7 +5055,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="108"/>
+      <c r="A27" s="115"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5070,7 +5070,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="118"/>
+      <c r="F27" s="106"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5144,7 +5144,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="109"/>
+      <c r="A28" s="116"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5159,7 +5159,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="119"/>
+      <c r="F28" s="107"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5233,7 +5233,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="110"/>
+      <c r="A29" s="117"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5248,7 +5248,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="120"/>
+      <c r="F29" s="108"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5322,7 +5322,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="103">
+      <c r="A30" s="110">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5339,7 +5339,7 @@
       <c r="E30" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="116"/>
+      <c r="F30" s="104"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5413,7 +5413,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="104"/>
+      <c r="A31" s="111"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5428,7 +5428,7 @@
       <c r="E31" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="118"/>
+      <c r="F31" s="106"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5504,7 +5504,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="105"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5519,7 +5519,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="119"/>
+      <c r="F32" s="107"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5593,7 +5593,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="106"/>
+      <c r="A33" s="113"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5608,7 +5608,7 @@
       <c r="E33" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="120"/>
+      <c r="F33" s="108"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5684,7 +5684,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="107">
+      <c r="A34" s="114">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5701,7 +5701,7 @@
       <c r="E34" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="116"/>
+      <c r="F34" s="104"/>
       <c r="G34" s="60" t="s">
         <v>44</v>
       </c>
@@ -5777,7 +5777,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="108"/>
+      <c r="A35" s="115"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5792,7 +5792,7 @@
       <c r="E35" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="118"/>
+      <c r="F35" s="106"/>
       <c r="G35" s="63" t="s">
         <v>44</v>
       </c>
@@ -5868,7 +5868,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="109"/>
+      <c r="A36" s="116"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5883,7 +5883,7 @@
       <c r="E36" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="107"/>
       <c r="G36" s="65" t="s">
         <v>44</v>
       </c>
@@ -5959,7 +5959,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="110"/>
+      <c r="A37" s="117"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5974,7 +5974,7 @@
       <c r="E37" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="120"/>
+      <c r="F37" s="108"/>
       <c r="G37" s="68" t="s">
         <v>45</v>
       </c>
@@ -6050,7 +6050,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="103">
+      <c r="A38" s="110">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -6067,7 +6067,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="116"/>
+      <c r="F38" s="104"/>
       <c r="G38" s="60" t="s">
         <v>44</v>
       </c>
@@ -6083,7 +6083,9 @@
       <c r="K38" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="L38" s="61"/>
+      <c r="L38" s="61" t="s">
+        <v>44</v>
+      </c>
       <c r="M38" s="61" t="s">
         <v>44</v>
       </c>
@@ -6137,7 +6139,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="104"/>
+      <c r="A39" s="111"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -6152,7 +6154,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="118"/>
+      <c r="F39" s="106"/>
       <c r="G39" s="63" t="s">
         <v>46</v>
       </c>
@@ -6168,7 +6170,9 @@
       <c r="K39" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="L39" s="71"/>
+      <c r="L39" s="71" t="s">
+        <v>46</v>
+      </c>
       <c r="M39" s="71" t="s">
         <v>45</v>
       </c>
@@ -6222,7 +6226,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="105"/>
+      <c r="A40" s="112"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -6237,7 +6241,7 @@
       <c r="E40" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F40" s="119"/>
+      <c r="F40" s="107"/>
       <c r="G40" s="65" t="s">
         <v>44</v>
       </c>
@@ -6253,7 +6257,9 @@
       <c r="K40" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="L40" s="66"/>
+      <c r="L40" s="66" t="s">
+        <v>44</v>
+      </c>
       <c r="M40" s="66" t="s">
         <v>44</v>
       </c>
@@ -6307,7 +6313,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="106"/>
+      <c r="A41" s="113"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6322,7 +6328,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="120"/>
+      <c r="F41" s="108"/>
       <c r="G41" s="68" t="s">
         <v>44</v>
       </c>
@@ -6338,7 +6344,9 @@
       <c r="K41" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="L41" s="69"/>
+      <c r="L41" s="69" t="s">
+        <v>44</v>
+      </c>
       <c r="M41" s="69" t="s">
         <v>44</v>
       </c>
@@ -6392,7 +6400,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="107">
+      <c r="A42" s="114">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6409,7 +6417,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="116"/>
+      <c r="F42" s="104"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -6445,7 +6453,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="108"/>
+      <c r="A43" s="115"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6460,7 +6468,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="118"/>
+      <c r="F43" s="106"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6496,7 +6504,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="109"/>
+      <c r="A44" s="116"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6511,7 +6519,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="119"/>
+      <c r="F44" s="107"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6547,7 +6555,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="110"/>
+      <c r="A45" s="117"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6562,7 +6570,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="120"/>
+      <c r="F45" s="108"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6598,7 +6606,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="103">
+      <c r="A46" s="110">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6615,7 +6623,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="116"/>
+      <c r="F46" s="104"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6651,7 +6659,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="104"/>
+      <c r="A47" s="111"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6666,7 +6674,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="118"/>
+      <c r="F47" s="106"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6702,7 +6710,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="105"/>
+      <c r="A48" s="112"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6717,7 +6725,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="119"/>
+      <c r="F48" s="107"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6753,7 +6761,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="106"/>
+      <c r="A49" s="113"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6768,7 +6776,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="120"/>
+      <c r="F49" s="108"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6804,7 +6812,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="107">
+      <c r="A50" s="114">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6821,7 +6829,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="116"/>
+      <c r="F50" s="104"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6857,7 +6865,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="108"/>
+      <c r="A51" s="115"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6872,7 +6880,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="118"/>
+      <c r="F51" s="106"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6908,7 +6916,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="109"/>
+      <c r="A52" s="116"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6923,7 +6931,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="119"/>
+      <c r="F52" s="107"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6959,7 +6967,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="109"/>
+      <c r="A53" s="116"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6974,7 +6982,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="119"/>
+      <c r="F53" s="107"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -7009,7 +7017,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="109"/>
+      <c r="A54" s="116"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -7024,7 +7032,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="119"/>
+      <c r="F54" s="107"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -7060,7 +7068,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="110"/>
+      <c r="A55" s="117"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -7075,7 +7083,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="120"/>
+      <c r="F55" s="108"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -7111,7 +7119,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="103">
+      <c r="A56" s="110">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -7128,7 +7136,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="116"/>
+      <c r="F56" s="104"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -7164,7 +7172,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="104"/>
+      <c r="A57" s="111"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -7179,7 +7187,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="118"/>
+      <c r="F57" s="106"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -7215,7 +7223,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="105"/>
+      <c r="A58" s="112"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -7230,7 +7238,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="119"/>
+      <c r="F58" s="107"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -7266,7 +7274,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="105"/>
+      <c r="A59" s="112"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -7281,7 +7289,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="119"/>
+      <c r="F59" s="107"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -7317,7 +7325,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="105"/>
+      <c r="A60" s="112"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7332,7 +7340,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="119"/>
+      <c r="F60" s="107"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7368,7 +7376,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="106"/>
+      <c r="A61" s="113"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7383,7 +7391,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="120"/>
+      <c r="F61" s="108"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7419,7 +7427,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="107">
+      <c r="A62" s="114">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7436,7 +7444,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="116"/>
+      <c r="F62" s="104"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7472,7 +7480,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="108"/>
+      <c r="A63" s="115"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7487,7 +7495,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="118"/>
+      <c r="F63" s="106"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7523,7 +7531,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="109"/>
+      <c r="A64" s="116"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7538,7 +7546,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="119"/>
+      <c r="F64" s="107"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7574,7 +7582,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="109"/>
+      <c r="A65" s="116"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7589,7 +7597,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="119"/>
+      <c r="F65" s="107"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7625,7 +7633,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="109"/>
+      <c r="A66" s="116"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7640,7 +7648,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="119"/>
+      <c r="F66" s="107"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7676,7 +7684,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="110"/>
+      <c r="A67" s="117"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7691,7 +7699,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="120"/>
+      <c r="F67" s="108"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7727,7 +7735,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="111">
+      <c r="A68" s="122">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7744,7 +7752,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="116"/>
+      <c r="F68" s="104"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7780,7 +7788,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="112"/>
+      <c r="A69" s="123"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7795,7 +7803,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="118"/>
+      <c r="F69" s="106"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7831,7 +7839,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="113"/>
+      <c r="A70" s="124"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7846,7 +7854,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="119"/>
+      <c r="F70" s="107"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7882,7 +7890,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="113"/>
+      <c r="A71" s="124"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7897,7 +7905,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="119"/>
+      <c r="F71" s="107"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7933,7 +7941,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="113"/>
+      <c r="A72" s="124"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7948,7 +7956,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="119"/>
+      <c r="F72" s="107"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7984,7 +7992,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="114"/>
+      <c r="A73" s="125"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -7999,7 +8007,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="121"/>
+      <c r="F73" s="109"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -8121,6 +8129,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A55"/>
@@ -8137,8 +8147,6 @@
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z37 G38:U39 W38:Z39 V39 G40:Z52 G53:W53 Y53:Z53 G54:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10612"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="137">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -471,6 +471,9 @@
   </si>
   <si>
     <t>0x4</t>
+  </si>
+  <si>
+    <t>4x0</t>
   </si>
 </sst>
 </file>
@@ -1559,6 +1562,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -1592,18 +1619,6 @@
     <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1615,18 +1630,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2108,13 +2111,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="3" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.75" customWidth="1"/>
+    <col min="2" max="3" width="14.2578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
@@ -2126,7 +2129,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="126"/>
       <c r="B2" s="126"/>
       <c r="C2" s="13"/>
@@ -2136,7 +2139,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="126"/>
       <c r="B3" s="126"/>
       <c r="C3" s="13"/>
@@ -2154,7 +2157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2162,7 +2165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2170,7 +2173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2178,7 +2181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2186,7 +2189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2194,7 +2197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2202,7 +2205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2210,7 +2213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2218,7 +2221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2226,7 +2229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2234,7 +2237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2242,7 +2245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2250,7 +2253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2258,7 +2261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2266,7 +2269,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2274,7 +2277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2306,16 +2309,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="7" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="22.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.6484375" customWidth="1"/>
+    <col min="2" max="2" width="20.984375" customWidth="1"/>
+    <col min="3" max="7" width="12.10546875" customWidth="1"/>
+    <col min="9" max="9" width="22.8671875" customWidth="1"/>
+    <col min="10" max="10" width="9.55078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="127" t="s">
         <v>20</v>
       </c>
@@ -2326,7 +2329,7 @@
       <c r="F1" s="128"/>
       <c r="G1" s="128"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2347,7 +2350,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2374,7 +2377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2396,7 +2399,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2417,7 +2420,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2441,7 +2444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2465,7 +2468,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2486,7 +2489,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2507,7 +2510,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2528,7 +2531,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2549,7 +2552,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2570,7 +2573,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2591,7 +2594,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2612,7 +2615,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2633,7 +2636,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2670,17 +2673,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="29" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.8359375" customWidth="1"/>
+    <col min="2" max="2" width="32.41796875" customWidth="1"/>
+    <col min="3" max="4" width="20.58203125" customWidth="1"/>
+    <col min="5" max="5" width="12.5078125" customWidth="1"/>
+    <col min="6" max="6" width="6.05078125" customWidth="1"/>
+    <col min="7" max="29" width="16.41015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2696,7 +2699,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="103"/>
+      <c r="F1" s="111"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2767,8 +2770,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="118">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A2" s="122">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2785,7 +2788,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="104"/>
+      <c r="F2" s="112"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2859,8 +2862,8 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2875,7 +2878,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="105"/>
+      <c r="F3" s="113"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2949,8 +2952,8 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="120">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A4" s="124">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2967,7 +2970,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="104"/>
+      <c r="F4" s="112"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3042,8 +3045,8 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="121"/>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -3058,7 +3061,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="105"/>
+      <c r="F5" s="113"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3133,8 +3136,8 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="110">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A6" s="118">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3151,7 +3154,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="104"/>
+      <c r="F6" s="112"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3226,8 +3229,8 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="111"/>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A7" s="119"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3242,7 +3245,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="106"/>
+      <c r="F7" s="114"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3317,8 +3320,8 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="112"/>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A8" s="120"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3333,7 +3336,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="107"/>
+      <c r="F8" s="115"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3408,8 +3411,8 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="113"/>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A9" s="121"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3424,7 +3427,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="116"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3499,8 +3502,8 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="114">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A10" s="103">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3517,7 +3520,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="104"/>
+      <c r="F10" s="112"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3590,8 +3593,8 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="115"/>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A11" s="104"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3606,7 +3609,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="106"/>
+      <c r="F11" s="114"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3681,8 +3684,8 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="116"/>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A12" s="105"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3697,7 +3700,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="107"/>
+      <c r="F12" s="115"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3772,8 +3775,8 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="117"/>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A13" s="106"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3788,7 +3791,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="108"/>
+      <c r="F13" s="116"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3863,8 +3866,8 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="110">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A14" s="118">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3881,7 +3884,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="104"/>
+      <c r="F14" s="112"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3956,8 +3959,8 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="111"/>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A15" s="119"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3972,7 +3975,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="106"/>
+      <c r="F15" s="114"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4047,8 +4050,8 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="112"/>
+    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="120"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4063,7 +4066,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="107"/>
+      <c r="F16" s="115"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4138,8 +4141,8 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="113"/>
+    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="121"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4154,7 +4157,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="108"/>
+      <c r="F17" s="116"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4229,8 +4232,8 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="114">
+    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="103">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4247,7 +4250,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="104"/>
+      <c r="F18" s="112"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +4325,8 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="115"/>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A19" s="104"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4338,7 +4341,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="106"/>
+      <c r="F19" s="114"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4413,8 +4416,8 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="116"/>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A20" s="105"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4429,7 +4432,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="107"/>
+      <c r="F20" s="115"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4504,8 +4507,8 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="117"/>
+    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="106"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4520,7 +4523,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="108"/>
+      <c r="F21" s="116"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4595,8 +4598,8 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="110">
+    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="118">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4613,7 +4616,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="104"/>
+      <c r="F22" s="112"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4688,8 +4691,8 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="111"/>
+    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="119"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4704,7 +4707,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="106"/>
+      <c r="F23" s="114"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4779,8 +4782,8 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="112"/>
+    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="120"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4795,7 +4798,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="107"/>
+      <c r="F24" s="115"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4870,8 +4873,8 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="113"/>
+    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="121"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4886,7 +4889,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="108"/>
+      <c r="F25" s="116"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4961,8 +4964,8 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="114">
+    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="103">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4979,7 +4982,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="104"/>
+      <c r="F26" s="112"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5054,8 +5057,8 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="115"/>
+    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="104"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5070,7 +5073,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="106"/>
+      <c r="F27" s="114"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5143,8 +5146,8 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="116"/>
+    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="105"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5159,7 +5162,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="107"/>
+      <c r="F28" s="115"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5232,8 +5235,8 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="106"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5248,7 +5251,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="108"/>
+      <c r="F29" s="116"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5321,8 +5324,8 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="110">
+    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="118">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5339,7 +5342,7 @@
       <c r="E30" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="104"/>
+      <c r="F30" s="112"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5412,8 +5415,8 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="111"/>
+    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="119"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5428,7 +5431,7 @@
       <c r="E31" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="106"/>
+      <c r="F31" s="114"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5503,8 +5506,8 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="112"/>
+    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="120"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5519,7 +5522,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="107"/>
+      <c r="F32" s="115"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5592,8 +5595,8 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="113"/>
+    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="121"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5608,7 +5611,7 @@
       <c r="E33" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="108"/>
+      <c r="F33" s="116"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5683,8 +5686,8 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="114">
+    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="103">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5701,7 +5704,7 @@
       <c r="E34" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="104"/>
+      <c r="F34" s="112"/>
       <c r="G34" s="60" t="s">
         <v>44</v>
       </c>
@@ -5776,8 +5779,8 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="115"/>
+    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="104"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5792,7 +5795,7 @@
       <c r="E35" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="106"/>
+      <c r="F35" s="114"/>
       <c r="G35" s="63" t="s">
         <v>44</v>
       </c>
@@ -5867,8 +5870,8 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="116"/>
+    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="105"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5883,7 +5886,7 @@
       <c r="E36" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="107"/>
+      <c r="F36" s="115"/>
       <c r="G36" s="65" t="s">
         <v>44</v>
       </c>
@@ -5958,8 +5961,8 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="117"/>
+    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="106"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5974,7 +5977,7 @@
       <c r="E37" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="108"/>
+      <c r="F37" s="116"/>
       <c r="G37" s="68" t="s">
         <v>45</v>
       </c>
@@ -6049,8 +6052,8 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="110">
+    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="118">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -6067,7 +6070,7 @@
       <c r="E38" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="104"/>
+      <c r="F38" s="112"/>
       <c r="G38" s="60" t="s">
         <v>44</v>
       </c>
@@ -6098,7 +6101,9 @@
       <c r="P38" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="61"/>
+      <c r="Q38" s="61" t="s">
+        <v>44</v>
+      </c>
       <c r="R38" s="61"/>
       <c r="S38" s="61" t="s">
         <v>46</v>
@@ -6138,8 +6143,8 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="111"/>
+    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="119"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -6154,7 +6159,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="106"/>
+      <c r="F39" s="114"/>
       <c r="G39" s="63" t="s">
         <v>46</v>
       </c>
@@ -6185,7 +6190,9 @@
       <c r="P39" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="Q39" s="71"/>
+      <c r="Q39" s="71" t="s">
+        <v>44</v>
+      </c>
       <c r="R39" s="71"/>
       <c r="S39" s="71" t="s">
         <v>46</v>
@@ -6225,8 +6232,8 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="112"/>
+    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="120"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -6239,9 +6246,9 @@
         <v>Arábia Saudita</v>
       </c>
       <c r="E40" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="F40" s="107"/>
+        <v>136</v>
+      </c>
+      <c r="F40" s="115"/>
       <c r="G40" s="65" t="s">
         <v>44</v>
       </c>
@@ -6272,7 +6279,9 @@
       <c r="P40" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66" t="s">
+        <v>44</v>
+      </c>
       <c r="R40" s="66"/>
       <c r="S40" s="66" t="s">
         <v>44</v>
@@ -6298,22 +6307,22 @@
       <c r="Z40" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="AA40" s="81" t="str">
+      <c r="AA40" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB40" s="90" t="str">
+        <v>4</v>
+      </c>
+      <c r="AB40" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC40" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="113"/>
+    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="121"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6328,7 +6337,7 @@
       <c r="E41" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="108"/>
+      <c r="F41" s="116"/>
       <c r="G41" s="68" t="s">
         <v>44</v>
       </c>
@@ -6359,7 +6368,9 @@
       <c r="P41" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="Q41" s="69"/>
+      <c r="Q41" s="69" t="s">
+        <v>46</v>
+      </c>
       <c r="R41" s="69"/>
       <c r="S41" s="69" t="s">
         <v>44</v>
@@ -6399,8 +6410,8 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="114">
+    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="103">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6417,7 +6428,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="104"/>
+      <c r="F42" s="112"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -6452,8 +6463,8 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="115"/>
+    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="104"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6468,7 +6479,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="106"/>
+      <c r="F43" s="114"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6503,8 +6514,8 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="116"/>
+    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="105"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6519,7 +6530,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="107"/>
+      <c r="F44" s="115"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6554,8 +6565,8 @@
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="117"/>
+    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="106"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6570,7 +6581,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="108"/>
+      <c r="F45" s="116"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6605,8 +6616,8 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="110">
+    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="118">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6623,7 +6634,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="104"/>
+      <c r="F46" s="112"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6658,8 +6669,8 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="111"/>
+    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="119"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6674,7 +6685,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="106"/>
+      <c r="F47" s="114"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6709,8 +6720,8 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="112"/>
+    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="120"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6725,7 +6736,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="107"/>
+      <c r="F48" s="115"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6760,8 +6771,8 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="113"/>
+    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="121"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6776,7 +6787,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="108"/>
+      <c r="F49" s="116"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6811,8 +6822,8 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="114">
+    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="103">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6829,7 +6840,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="104"/>
+      <c r="F50" s="112"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6864,8 +6875,8 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="115"/>
+    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="104"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6880,7 +6891,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="106"/>
+      <c r="F51" s="114"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6915,8 +6926,8 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="116"/>
+    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="105"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6931,7 +6942,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="107"/>
+      <c r="F52" s="115"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6966,8 +6977,8 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="116"/>
+    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="105"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6982,7 +6993,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="107"/>
+      <c r="F53" s="115"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -7016,8 +7027,8 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="116"/>
+    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="105"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -7032,7 +7043,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="107"/>
+      <c r="F54" s="115"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -7067,8 +7078,8 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="117"/>
+    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="106"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -7083,7 +7094,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="108"/>
+      <c r="F55" s="116"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -7118,8 +7129,8 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="110">
+    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="118">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -7136,7 +7147,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="104"/>
+      <c r="F56" s="112"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -7171,8 +7182,8 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="111"/>
+    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="119"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -7187,7 +7198,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="106"/>
+      <c r="F57" s="114"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -7222,8 +7233,8 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="112"/>
+    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="120"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -7238,7 +7249,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="107"/>
+      <c r="F58" s="115"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -7273,8 +7284,8 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="112"/>
+    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="120"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -7289,7 +7300,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="107"/>
+      <c r="F59" s="115"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -7324,8 +7335,8 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="112"/>
+    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="120"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7340,7 +7351,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="107"/>
+      <c r="F60" s="115"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7375,8 +7386,8 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="113"/>
+    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="121"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7391,7 +7402,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="108"/>
+      <c r="F61" s="116"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7426,8 +7437,8 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="114">
+    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="103">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7444,7 +7455,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="104"/>
+      <c r="F62" s="112"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7479,8 +7490,8 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="115"/>
+    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="104"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7495,7 +7506,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="106"/>
+      <c r="F63" s="114"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7530,8 +7541,8 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="116"/>
+    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="105"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7546,7 +7557,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="107"/>
+      <c r="F64" s="115"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7581,8 +7592,8 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="116"/>
+    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="105"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7597,7 +7608,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="107"/>
+      <c r="F65" s="115"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7632,8 +7643,8 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="116"/>
+    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="105"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7648,7 +7659,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="107"/>
+      <c r="F66" s="115"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7683,8 +7694,8 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="117"/>
+    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="106"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7699,7 +7710,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="108"/>
+      <c r="F67" s="116"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7734,8 +7745,8 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="122">
+    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="107">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7752,7 +7763,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="104"/>
+      <c r="F68" s="112"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7787,8 +7798,8 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="123"/>
+    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="108"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7803,7 +7814,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="106"/>
+      <c r="F69" s="114"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7838,8 +7849,8 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="124"/>
+    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="109"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7854,7 +7865,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="107"/>
+      <c r="F70" s="115"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7889,8 +7900,8 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="124"/>
+    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="109"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7905,7 +7916,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="107"/>
+      <c r="F71" s="115"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7940,8 +7951,8 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="124"/>
+    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="109"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7956,7 +7967,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="107"/>
+      <c r="F72" s="115"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7991,8 +8002,8 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="125"/>
+    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="110"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -8007,7 +8018,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="109"/>
+      <c r="F73" s="117"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -8042,53 +8053,53 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F74" s="19" t="s">
         <v>129</v>
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -8096,39 +8107,41 @@
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
@@ -8145,8 +8158,6 @@
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z37 G38:U39 W38:Z39 V39 G40:Z52 G53:W53 Y53:Z53 G54:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF39674-143D-4550-AC38-08BC1F5BC1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BE11BA-C260-45E5-B84B-DD63E9AF74FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="137">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -471,6 +471,9 @@
   </si>
   <si>
     <t>0x4</t>
+  </si>
+  <si>
+    <t>4x0</t>
   </si>
 </sst>
 </file>
@@ -1559,6 +1562,42 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -1581,30 +1620,6 @@
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1615,18 +1630,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2696,7 +2699,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="103"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2768,7 +2771,7 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="118">
+      <c r="A2" s="122">
         <v>46184</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -2785,7 +2788,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="104"/>
+      <c r="F2" s="116"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2860,7 +2863,7 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119"/>
+      <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
       </c>
@@ -2875,7 +2878,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="105"/>
+      <c r="F3" s="117"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2950,7 +2953,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="120">
+      <c r="A4" s="124">
         <v>46185</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -2967,7 +2970,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="104"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3043,7 +3046,7 @@
       <c r="AD4" s="54"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="121"/>
+      <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
       </c>
@@ -3058,7 +3061,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="105"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3134,7 +3137,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="110">
+      <c r="A6" s="107">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3151,7 +3154,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="104"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3227,7 +3230,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="111"/>
+      <c r="A7" s="108"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3242,7 +3245,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="106"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3318,7 +3321,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="112"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3333,7 +3336,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="107"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3409,7 +3412,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="113"/>
+      <c r="A9" s="110"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3424,7 +3427,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="120"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3500,7 +3503,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="114">
+      <c r="A10" s="103">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3517,7 +3520,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="104"/>
+      <c r="F10" s="116"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3591,7 +3594,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="115"/>
+      <c r="A11" s="104"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3606,7 +3609,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="106"/>
+      <c r="F11" s="118"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3682,7 +3685,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="116"/>
+      <c r="A12" s="105"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3697,7 +3700,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="107"/>
+      <c r="F12" s="119"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3773,7 +3776,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="117"/>
+      <c r="A13" s="106"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3788,7 +3791,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="108"/>
+      <c r="F13" s="120"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3864,7 +3867,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="110">
+      <c r="A14" s="107">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3881,7 +3884,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="104"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3957,7 +3960,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="111"/>
+      <c r="A15" s="108"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3972,7 +3975,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="106"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4048,7 +4051,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="112"/>
+      <c r="A16" s="109"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4063,7 +4066,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="107"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4139,7 +4142,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="113"/>
+      <c r="A17" s="110"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4154,7 +4157,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="108"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4230,7 +4233,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="114">
+      <c r="A18" s="103">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4247,7 +4250,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="104"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4323,7 +4326,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="115"/>
+      <c r="A19" s="104"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4338,7 +4341,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="106"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4414,7 +4417,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="116"/>
+      <c r="A20" s="105"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4429,7 +4432,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="107"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4505,7 +4508,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="117"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4520,7 +4523,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="108"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4596,7 +4599,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="110">
+      <c r="A22" s="107">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4613,7 +4616,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="104"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4689,7 +4692,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="111"/>
+      <c r="A23" s="108"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4704,7 +4707,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="106"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4780,7 +4783,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="112"/>
+      <c r="A24" s="109"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4795,7 +4798,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="107"/>
+      <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4871,7 +4874,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="113"/>
+      <c r="A25" s="110"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4886,7 +4889,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="108"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4962,7 +4965,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="114">
+      <c r="A26" s="103">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4979,7 +4982,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="104"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5055,7 +5058,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="115"/>
+      <c r="A27" s="104"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5070,7 +5073,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="106"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5144,7 +5147,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="116"/>
+      <c r="A28" s="105"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5159,7 +5162,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="107"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5233,7 +5236,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5248,7 +5251,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="108"/>
+      <c r="F29" s="120"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5322,7 +5325,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="110">
+      <c r="A30" s="107">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5339,7 +5342,7 @@
       <c r="E30" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="104"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5413,7 +5416,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="111"/>
+      <c r="A31" s="108"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5428,7 +5431,7 @@
       <c r="E31" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="106"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5504,7 +5507,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="112"/>
+      <c r="A32" s="109"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5519,7 +5522,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="107"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5593,7 +5596,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="113"/>
+      <c r="A33" s="110"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5608,7 +5611,7 @@
       <c r="E33" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="108"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5684,7 +5687,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="114">
+      <c r="A34" s="103">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5701,7 +5704,7 @@
       <c r="E34" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="104"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="60" t="s">
         <v>44</v>
       </c>
@@ -5777,7 +5780,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="115"/>
+      <c r="A35" s="104"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5792,7 +5795,7 @@
       <c r="E35" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="106"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="63" t="s">
         <v>44</v>
       </c>
@@ -5868,7 +5871,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="116"/>
+      <c r="A36" s="105"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5883,7 +5886,7 @@
       <c r="E36" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="107"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="65" t="s">
         <v>44</v>
       </c>
@@ -5959,7 +5962,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="117"/>
+      <c r="A37" s="106"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5974,7 +5977,7 @@
       <c r="E37" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="108"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="68" t="s">
         <v>45</v>
       </c>
@@ -6050,7 +6053,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="110">
+      <c r="A38" s="107">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -6065,9 +6068,9 @@
         <v>Irã</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="F38" s="104"/>
+        <v>69</v>
+      </c>
+      <c r="F38" s="116"/>
       <c r="G38" s="60" t="s">
         <v>44</v>
       </c>
@@ -6098,7 +6101,9 @@
       <c r="P38" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="61"/>
+      <c r="Q38" s="61" t="s">
+        <v>44</v>
+      </c>
       <c r="R38" s="61"/>
       <c r="S38" s="61" t="s">
         <v>46</v>
@@ -6124,22 +6129,22 @@
       <c r="Z38" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="AA38" s="81" t="str">
+      <c r="AA38" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB38" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC38" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="111"/>
+      <c r="A39" s="108"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -6154,7 +6159,7 @@
       <c r="E39" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="106"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="63" t="s">
         <v>46</v>
       </c>
@@ -6185,8 +6190,12 @@
       <c r="P39" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="Q39" s="71"/>
-      <c r="R39" s="71"/>
+      <c r="Q39" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="R39" s="71" t="s">
+        <v>44</v>
+      </c>
       <c r="S39" s="71" t="s">
         <v>46</v>
       </c>
@@ -6226,7 +6235,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="112"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -6239,9 +6248,9 @@
         <v>Arábia Saudita</v>
       </c>
       <c r="E40" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="F40" s="107"/>
+        <v>136</v>
+      </c>
+      <c r="F40" s="119"/>
       <c r="G40" s="65" t="s">
         <v>44</v>
       </c>
@@ -6272,7 +6281,9 @@
       <c r="P40" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="Q40" s="66"/>
+      <c r="Q40" s="66" t="s">
+        <v>44</v>
+      </c>
       <c r="R40" s="66"/>
       <c r="S40" s="66" t="s">
         <v>44</v>
@@ -6298,22 +6309,22 @@
       <c r="Z40" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="AA40" s="81" t="str">
+      <c r="AA40" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB40" s="90" t="str">
+        <v>4</v>
+      </c>
+      <c r="AB40" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC40" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="113"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6326,9 +6337,9 @@
         <v>Cabo Verde</v>
       </c>
       <c r="E41" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="F41" s="108"/>
+        <v>63</v>
+      </c>
+      <c r="F41" s="120"/>
       <c r="G41" s="68" t="s">
         <v>44</v>
       </c>
@@ -6359,7 +6370,9 @@
       <c r="P41" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="Q41" s="69"/>
+      <c r="Q41" s="69" t="s">
+        <v>46</v>
+      </c>
       <c r="R41" s="69"/>
       <c r="S41" s="69" t="s">
         <v>44</v>
@@ -6385,22 +6398,22 @@
       <c r="Z41" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="AA41" s="81" t="str">
+      <c r="AA41" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB41" s="90" t="str">
+        <v>2</v>
+      </c>
+      <c r="AB41" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC41" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>E</v>
       </c>
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="114">
+      <c r="A42" s="103">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6417,7 +6430,7 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="104"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="60"/>
       <c r="H42" s="61"/>
       <c r="I42" s="61"/>
@@ -6453,7 +6466,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="115"/>
+      <c r="A43" s="104"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6468,7 +6481,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="106"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="63"/>
       <c r="H43" s="71"/>
       <c r="I43" s="71"/>
@@ -6504,7 +6517,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="116"/>
+      <c r="A44" s="105"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6519,7 +6532,7 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="107"/>
+      <c r="F44" s="119"/>
       <c r="G44" s="65"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
@@ -6555,7 +6568,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="117"/>
+      <c r="A45" s="106"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6570,7 +6583,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="108"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
       <c r="I45" s="69"/>
@@ -6606,7 +6619,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="110">
+      <c r="A46" s="107">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6623,7 +6636,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="104"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6659,7 +6672,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="111"/>
+      <c r="A47" s="108"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6674,7 +6687,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="106"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6710,7 +6723,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="112"/>
+      <c r="A48" s="109"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6725,7 +6738,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="107"/>
+      <c r="F48" s="119"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6761,7 +6774,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="113"/>
+      <c r="A49" s="110"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6776,7 +6789,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="108"/>
+      <c r="F49" s="120"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6812,7 +6825,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="114">
+      <c r="A50" s="103">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6829,7 +6842,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="104"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6865,7 +6878,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="115"/>
+      <c r="A51" s="104"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6880,7 +6893,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="106"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6916,7 +6929,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="116"/>
+      <c r="A52" s="105"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6931,7 +6944,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="107"/>
+      <c r="F52" s="119"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6967,7 +6980,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="116"/>
+      <c r="A53" s="105"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6982,7 +6995,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="107"/>
+      <c r="F53" s="119"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -7017,7 +7030,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="116"/>
+      <c r="A54" s="105"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -7032,7 +7045,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="107"/>
+      <c r="F54" s="119"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -7068,7 +7081,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="117"/>
+      <c r="A55" s="106"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -7083,7 +7096,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="108"/>
+      <c r="F55" s="120"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -7119,7 +7132,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="110">
+      <c r="A56" s="107">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -7136,7 +7149,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="104"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -7172,7 +7185,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="111"/>
+      <c r="A57" s="108"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -7187,7 +7200,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="106"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -7223,7 +7236,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="112"/>
+      <c r="A58" s="109"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -7238,7 +7251,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="107"/>
+      <c r="F58" s="119"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -7274,7 +7287,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="112"/>
+      <c r="A59" s="109"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -7289,7 +7302,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="107"/>
+      <c r="F59" s="119"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -7325,7 +7338,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="112"/>
+      <c r="A60" s="109"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7340,7 +7353,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="107"/>
+      <c r="F60" s="119"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7376,7 +7389,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="113"/>
+      <c r="A61" s="110"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7391,7 +7404,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="108"/>
+      <c r="F61" s="120"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7427,7 +7440,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="114">
+      <c r="A62" s="103">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7444,7 +7457,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="104"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7480,7 +7493,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="115"/>
+      <c r="A63" s="104"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7495,7 +7508,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="106"/>
+      <c r="F63" s="118"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7531,7 +7544,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="116"/>
+      <c r="A64" s="105"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7546,7 +7559,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="107"/>
+      <c r="F64" s="119"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7582,7 +7595,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="116"/>
+      <c r="A65" s="105"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7597,7 +7610,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="107"/>
+      <c r="F65" s="119"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7633,7 +7646,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="116"/>
+      <c r="A66" s="105"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7648,7 +7661,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="107"/>
+      <c r="F66" s="119"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7684,7 +7697,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="117"/>
+      <c r="A67" s="106"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7699,7 +7712,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="108"/>
+      <c r="F67" s="120"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7735,7 +7748,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="122">
+      <c r="A68" s="111">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7752,7 +7765,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="104"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7788,7 +7801,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="123"/>
+      <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7803,7 +7816,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="106"/>
+      <c r="F69" s="118"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7839,7 +7852,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="124"/>
+      <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7854,7 +7867,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="107"/>
+      <c r="F70" s="119"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7890,7 +7903,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="124"/>
+      <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7905,7 +7918,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="107"/>
+      <c r="F71" s="119"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7941,7 +7954,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="124"/>
+      <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7956,7 +7969,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="107"/>
+      <c r="F72" s="119"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -7992,7 +8005,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="125"/>
+      <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -8007,7 +8020,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="109"/>
+      <c r="F73" s="121"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -8048,47 +8061,47 @@
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -8096,39 +8109,43 @@
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
@@ -8143,10 +8160,6 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z37 G38:U39 W38:Z39 V39 G40:Z52 G53:W53 Y53:Z53 G54:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10612"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BE11BA-C260-45E5-B84B-DD63E9AF74FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{007218A1-B94B-7A4F-9895-F63331845DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -2111,13 +2111,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="3" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.75" customWidth="1"/>
+    <col min="2" max="3" width="14.2578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
@@ -2129,7 +2129,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="126"/>
       <c r="B2" s="126"/>
       <c r="C2" s="13"/>
@@ -2139,7 +2139,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="126"/>
       <c r="B3" s="126"/>
       <c r="C3" s="13"/>
@@ -2157,7 +2157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2309,16 +2309,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="7" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="22.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.6484375" customWidth="1"/>
+    <col min="2" max="2" width="20.984375" customWidth="1"/>
+    <col min="3" max="7" width="12.10546875" customWidth="1"/>
+    <col min="9" max="9" width="22.8671875" customWidth="1"/>
+    <col min="10" max="10" width="9.55078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="127" t="s">
         <v>20</v>
       </c>
@@ -2329,7 +2329,7 @@
       <c r="F1" s="128"/>
       <c r="G1" s="128"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2377,7 +2377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2420,7 +2420,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2444,7 +2444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2468,7 +2468,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2489,7 +2489,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2510,7 +2510,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2531,7 +2531,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2552,7 +2552,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2573,7 +2573,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2594,7 +2594,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2615,7 +2615,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2636,7 +2636,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2673,17 +2673,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="29" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.8359375" customWidth="1"/>
+    <col min="2" max="2" width="32.41796875" customWidth="1"/>
+    <col min="3" max="4" width="20.58203125" customWidth="1"/>
+    <col min="5" max="5" width="12.5078125" customWidth="1"/>
+    <col min="6" max="6" width="6.05078125" customWidth="1"/>
+    <col min="7" max="29" width="16.41015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="122">
         <v>46184</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2952,7 +2952,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="124">
         <v>46185</v>
       </c>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="107">
         <v>46186</v>
       </c>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="108"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="109"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="110"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="103">
         <v>46187</v>
       </c>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="104"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="105"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="106"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="107">
         <v>46188</v>
       </c>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="108"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="109"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="110"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="103">
         <v>46189</v>
       </c>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" s="104"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" s="105"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="106"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="107">
         <v>46190</v>
       </c>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="108"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="109"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="110"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="103">
         <v>46191</v>
       </c>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="104"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="105"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="106"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="107">
         <v>46192</v>
       </c>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="108"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="109"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="110"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="103">
         <v>46193</v>
       </c>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="104"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="105"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="106"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="107">
         <v>46194</v>
       </c>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="108"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
@@ -6157,7 +6157,7 @@
         <v>Egito</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="F39" s="118"/>
       <c r="G39" s="63" t="s">
@@ -6220,21 +6220,21 @@
       <c r="Z39" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AA39" s="81" t="str">
+      <c r="AA39" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB39" s="90" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AC39" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="109"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="110"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="103">
         <v>46195</v>
       </c>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="104"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="105"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="106"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="107">
         <v>46196</v>
       </c>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="108"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="109"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="110"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="103">
         <v>46197</v>
       </c>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="104"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="105"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="105"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="105"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="106"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="107">
         <v>46198</v>
       </c>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="108"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="109"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="109"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="109"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="110"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="103">
         <v>46199</v>
       </c>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="104"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="105"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="105"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="105"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="106"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="111">
         <v>46200</v>
       </c>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F74" s="19" t="s">
         <v>129</v>
       </c>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -8085,19 +8085,19 @@
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -8113,15 +8113,15 @@
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -8137,16 +8137,11 @@
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -8160,6 +8155,11 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z37 G38:U39 W38:Z39 V39 G40:Z52 G53:W53 Y53:Z53 G54:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="137">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -1562,6 +1562,51 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1573,51 +1618,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2699,7 +2699,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="115"/>
+      <c r="F1" s="107"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2788,7 +2788,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="116"/>
+      <c r="F2" s="108"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2878,7 +2878,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="117"/>
+      <c r="F3" s="109"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2970,7 +2970,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="116"/>
+      <c r="F4" s="108"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3061,7 +3061,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="117"/>
+      <c r="F5" s="109"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3137,7 +3137,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="107">
+      <c r="A6" s="114">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3154,7 +3154,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="116"/>
+      <c r="F6" s="108"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3230,7 +3230,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="108"/>
+      <c r="A7" s="115"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3245,7 +3245,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="118"/>
+      <c r="F7" s="110"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3321,7 +3321,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="109"/>
+      <c r="A8" s="116"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3336,7 +3336,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="119"/>
+      <c r="F8" s="111"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3412,7 +3412,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="110"/>
+      <c r="A9" s="117"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3427,7 +3427,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="120"/>
+      <c r="F9" s="112"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3503,7 +3503,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="103">
+      <c r="A10" s="118">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3520,7 +3520,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="116"/>
+      <c r="F10" s="108"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3594,7 +3594,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="104"/>
+      <c r="A11" s="119"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3609,7 +3609,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="118"/>
+      <c r="F11" s="110"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3685,7 +3685,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A12" s="105"/>
+      <c r="A12" s="120"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3700,7 +3700,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="119"/>
+      <c r="F12" s="111"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3776,7 +3776,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="106"/>
+      <c r="A13" s="121"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3791,7 +3791,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="120"/>
+      <c r="F13" s="112"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3867,7 +3867,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="107">
+      <c r="A14" s="114">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3884,7 +3884,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="116"/>
+      <c r="F14" s="108"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3960,7 +3960,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="108"/>
+      <c r="A15" s="115"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3975,7 +3975,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="118"/>
+      <c r="F15" s="110"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4051,7 +4051,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="109"/>
+      <c r="A16" s="116"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4066,7 +4066,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="119"/>
+      <c r="F16" s="111"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4142,7 +4142,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="110"/>
+      <c r="A17" s="117"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4157,7 +4157,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="120"/>
+      <c r="F17" s="112"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4233,7 +4233,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="103">
+      <c r="A18" s="118">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4250,7 +4250,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="116"/>
+      <c r="F18" s="108"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4326,7 +4326,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A19" s="104"/>
+      <c r="A19" s="119"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4341,7 +4341,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="118"/>
+      <c r="F19" s="110"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4417,7 +4417,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A20" s="105"/>
+      <c r="A20" s="120"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4432,7 +4432,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="119"/>
+      <c r="F20" s="111"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4508,7 +4508,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="106"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4523,7 +4523,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="120"/>
+      <c r="F21" s="112"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4599,7 +4599,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="107">
+      <c r="A22" s="114">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4616,7 +4616,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="116"/>
+      <c r="F22" s="108"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4692,7 +4692,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="108"/>
+      <c r="A23" s="115"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4707,7 +4707,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="118"/>
+      <c r="F23" s="110"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4783,7 +4783,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="109"/>
+      <c r="A24" s="116"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4798,7 +4798,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="119"/>
+      <c r="F24" s="111"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4874,7 +4874,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="110"/>
+      <c r="A25" s="117"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4889,7 +4889,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="120"/>
+      <c r="F25" s="112"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4965,7 +4965,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="103">
+      <c r="A26" s="118">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4982,7 +4982,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="116"/>
+      <c r="F26" s="108"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5058,7 +5058,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="104"/>
+      <c r="A27" s="119"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5073,7 +5073,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="118"/>
+      <c r="F27" s="110"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5147,7 +5147,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="105"/>
+      <c r="A28" s="120"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5162,7 +5162,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="119"/>
+      <c r="F28" s="111"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5236,7 +5236,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="106"/>
+      <c r="A29" s="121"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5251,7 +5251,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="120"/>
+      <c r="F29" s="112"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5325,7 +5325,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="107">
+      <c r="A30" s="114">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5342,7 +5342,7 @@
       <c r="E30" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="116"/>
+      <c r="F30" s="108"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5416,7 +5416,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="108"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5431,7 +5431,7 @@
       <c r="E31" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="118"/>
+      <c r="F31" s="110"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5507,7 +5507,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="109"/>
+      <c r="A32" s="116"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5522,7 +5522,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="119"/>
+      <c r="F32" s="111"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5596,7 +5596,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="110"/>
+      <c r="A33" s="117"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5611,7 +5611,7 @@
       <c r="E33" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="120"/>
+      <c r="F33" s="112"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5687,7 +5687,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="103">
+      <c r="A34" s="118">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5704,7 +5704,7 @@
       <c r="E34" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="116"/>
+      <c r="F34" s="108"/>
       <c r="G34" s="60" t="s">
         <v>44</v>
       </c>
@@ -5780,7 +5780,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="104"/>
+      <c r="A35" s="119"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5795,7 +5795,7 @@
       <c r="E35" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="118"/>
+      <c r="F35" s="110"/>
       <c r="G35" s="63" t="s">
         <v>44</v>
       </c>
@@ -5871,7 +5871,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="105"/>
+      <c r="A36" s="120"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5886,7 +5886,7 @@
       <c r="E36" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="119"/>
+      <c r="F36" s="111"/>
       <c r="G36" s="65" t="s">
         <v>44</v>
       </c>
@@ -5962,7 +5962,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="106"/>
+      <c r="A37" s="121"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5977,7 +5977,7 @@
       <c r="E37" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="120"/>
+      <c r="F37" s="112"/>
       <c r="G37" s="68" t="s">
         <v>45</v>
       </c>
@@ -6053,7 +6053,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="107">
+      <c r="A38" s="114">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -6070,7 +6070,7 @@
       <c r="E38" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="116"/>
+      <c r="F38" s="108"/>
       <c r="G38" s="60" t="s">
         <v>44</v>
       </c>
@@ -6144,7 +6144,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="108"/>
+      <c r="A39" s="115"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -6159,7 +6159,7 @@
       <c r="E39" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="F39" s="118"/>
+      <c r="F39" s="110"/>
       <c r="G39" s="63" t="s">
         <v>46</v>
       </c>
@@ -6235,7 +6235,7 @@
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="109"/>
+      <c r="A40" s="116"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -6250,7 +6250,7 @@
       <c r="E40" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="F40" s="119"/>
+      <c r="F40" s="111"/>
       <c r="G40" s="65" t="s">
         <v>44</v>
       </c>
@@ -6324,7 +6324,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="110"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6339,7 +6339,7 @@
       <c r="E41" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="F41" s="120"/>
+      <c r="F41" s="112"/>
       <c r="G41" s="68" t="s">
         <v>44</v>
       </c>
@@ -6413,7 +6413,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="103">
+      <c r="A42" s="118">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6430,27 +6430,67 @@
       <c r="E42" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F42" s="116"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
-      <c r="J42" s="61"/>
-      <c r="K42" s="61"/>
-      <c r="L42" s="61"/>
-      <c r="M42" s="61"/>
-      <c r="N42" s="61"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="61"/>
-      <c r="Q42" s="61"/>
-      <c r="R42" s="61"/>
-      <c r="S42" s="61"/>
-      <c r="T42" s="61"/>
-      <c r="U42" s="62"/>
-      <c r="V42" s="62"/>
-      <c r="W42" s="62"/>
-      <c r="X42" s="62"/>
-      <c r="Y42" s="62"/>
-      <c r="Z42" s="76"/>
+      <c r="F42" s="108"/>
+      <c r="G42" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="H42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="I42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="J42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="K42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="L42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="M42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="N42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="O42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="P42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="R42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="S42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="T42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="U42" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="V42" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="W42" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="X42" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y42" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" s="76" t="s">
+        <v>44</v>
+      </c>
       <c r="AA42" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6466,7 +6506,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="104"/>
+      <c r="A43" s="119"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6481,27 +6521,63 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="118"/>
-      <c r="G43" s="63"/>
-      <c r="H43" s="71"/>
-      <c r="I43" s="71"/>
-      <c r="J43" s="71"/>
-      <c r="K43" s="71"/>
-      <c r="L43" s="71"/>
-      <c r="M43" s="71"/>
-      <c r="N43" s="71"/>
-      <c r="O43" s="71"/>
-      <c r="P43" s="71"/>
-      <c r="Q43" s="71"/>
-      <c r="R43" s="71"/>
+      <c r="F43" s="110"/>
+      <c r="G43" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="I43" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="J43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="L43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="M43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="N43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O43" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="P43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="R43" s="71" t="s">
+        <v>44</v>
+      </c>
       <c r="S43" s="71"/>
-      <c r="T43" s="71"/>
-      <c r="U43" s="56"/>
+      <c r="T43" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="U43" s="56" t="s">
+        <v>46</v>
+      </c>
       <c r="V43" s="56"/>
-      <c r="W43" s="56"/>
-      <c r="X43" s="56"/>
-      <c r="Y43" s="56"/>
-      <c r="Z43" s="80"/>
+      <c r="W43" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="X43" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y43" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" s="80" t="s">
+        <v>45</v>
+      </c>
       <c r="AA43" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6517,7 +6593,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="105"/>
+      <c r="A44" s="120"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6532,27 +6608,67 @@
       <c r="E44" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F44" s="119"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="66"/>
-      <c r="I44" s="66"/>
-      <c r="J44" s="66"/>
-      <c r="K44" s="66"/>
-      <c r="L44" s="66"/>
-      <c r="M44" s="66"/>
-      <c r="N44" s="66"/>
-      <c r="O44" s="66"/>
-      <c r="P44" s="66"/>
-      <c r="Q44" s="66"/>
-      <c r="R44" s="66"/>
-      <c r="S44" s="66"/>
-      <c r="T44" s="66"/>
-      <c r="U44" s="67"/>
-      <c r="V44" s="67"/>
-      <c r="W44" s="67"/>
-      <c r="X44" s="67"/>
-      <c r="Y44" s="67"/>
-      <c r="Z44" s="78"/>
+      <c r="F44" s="111"/>
+      <c r="G44" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="J44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="K44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="L44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="M44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="N44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="P44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q44" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="R44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="S44" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="T44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="U44" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="V44" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W44" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="X44" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y44" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" s="78" t="s">
+        <v>45</v>
+      </c>
       <c r="AA44" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6568,7 +6684,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="106"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6583,27 +6699,61 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="120"/>
-      <c r="G45" s="68"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="69"/>
-      <c r="J45" s="69"/>
-      <c r="K45" s="69"/>
-      <c r="L45" s="69"/>
-      <c r="M45" s="69"/>
-      <c r="N45" s="69"/>
-      <c r="O45" s="69"/>
-      <c r="P45" s="69"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="H45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="I45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="J45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="K45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="L45" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="M45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="N45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="O45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="P45" s="69" t="s">
+        <v>45</v>
+      </c>
       <c r="Q45" s="69"/>
-      <c r="R45" s="69"/>
+      <c r="R45" s="69" t="s">
+        <v>45</v>
+      </c>
       <c r="S45" s="69"/>
-      <c r="T45" s="69"/>
-      <c r="U45" s="70"/>
+      <c r="T45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="U45" s="70" t="s">
+        <v>46</v>
+      </c>
       <c r="V45" s="70"/>
-      <c r="W45" s="70"/>
-      <c r="X45" s="70"/>
-      <c r="Y45" s="70"/>
-      <c r="Z45" s="79"/>
+      <c r="W45" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="X45" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y45" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z45" s="79" t="s">
+        <v>46</v>
+      </c>
       <c r="AA45" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6619,7 +6769,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="107">
+      <c r="A46" s="114">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6636,7 +6786,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="116"/>
+      <c r="F46" s="108"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6672,7 +6822,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="108"/>
+      <c r="A47" s="115"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6687,7 +6837,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="118"/>
+      <c r="F47" s="110"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6723,7 +6873,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="109"/>
+      <c r="A48" s="116"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6738,7 +6888,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="119"/>
+      <c r="F48" s="111"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6774,7 +6924,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="110"/>
+      <c r="A49" s="117"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6789,7 +6939,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="120"/>
+      <c r="F49" s="112"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6825,7 +6975,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="103">
+      <c r="A50" s="118">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6842,7 +6992,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="116"/>
+      <c r="F50" s="108"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -6878,7 +7028,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="104"/>
+      <c r="A51" s="119"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6893,7 +7043,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="118"/>
+      <c r="F51" s="110"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -6929,7 +7079,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="105"/>
+      <c r="A52" s="120"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6944,7 +7094,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="119"/>
+      <c r="F52" s="111"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -6980,7 +7130,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="105"/>
+      <c r="A53" s="120"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -6995,7 +7145,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="119"/>
+      <c r="F53" s="111"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -7030,7 +7180,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="105"/>
+      <c r="A54" s="120"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -7045,7 +7195,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="119"/>
+      <c r="F54" s="111"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -7081,7 +7231,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="106"/>
+      <c r="A55" s="121"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -7096,7 +7246,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="120"/>
+      <c r="F55" s="112"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -7132,7 +7282,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="107">
+      <c r="A56" s="114">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -7149,7 +7299,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="116"/>
+      <c r="F56" s="108"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -7185,7 +7335,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="108"/>
+      <c r="A57" s="115"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -7200,7 +7350,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="118"/>
+      <c r="F57" s="110"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -7236,7 +7386,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="109"/>
+      <c r="A58" s="116"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -7251,7 +7401,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="119"/>
+      <c r="F58" s="111"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -7287,7 +7437,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="109"/>
+      <c r="A59" s="116"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -7302,7 +7452,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="119"/>
+      <c r="F59" s="111"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -7338,7 +7488,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="109"/>
+      <c r="A60" s="116"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7353,7 +7503,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="119"/>
+      <c r="F60" s="111"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7389,7 +7539,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="110"/>
+      <c r="A61" s="117"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7404,7 +7554,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="120"/>
+      <c r="F61" s="112"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7440,7 +7590,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="103">
+      <c r="A62" s="118">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7457,7 +7607,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="116"/>
+      <c r="F62" s="108"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7493,7 +7643,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="104"/>
+      <c r="A63" s="119"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7508,7 +7658,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="118"/>
+      <c r="F63" s="110"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7544,7 +7694,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="105"/>
+      <c r="A64" s="120"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7559,7 +7709,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="119"/>
+      <c r="F64" s="111"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7595,7 +7745,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="105"/>
+      <c r="A65" s="120"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7610,7 +7760,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="119"/>
+      <c r="F65" s="111"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7646,7 +7796,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="105"/>
+      <c r="A66" s="120"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7661,7 +7811,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="119"/>
+      <c r="F66" s="111"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7697,7 +7847,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="106"/>
+      <c r="A67" s="121"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7712,7 +7862,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="120"/>
+      <c r="F67" s="112"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7748,7 +7898,7 @@
       <c r="AD67" s="54"/>
     </row>
     <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="111">
+      <c r="A68" s="103">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7765,7 +7915,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="116"/>
+      <c r="F68" s="108"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7801,7 +7951,7 @@
       <c r="AD68" s="54"/>
     </row>
     <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="112"/>
+      <c r="A69" s="104"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7816,7 +7966,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="118"/>
+      <c r="F69" s="110"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -7852,7 +8002,7 @@
       <c r="AD69" s="54"/>
     </row>
     <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="113"/>
+      <c r="A70" s="105"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -7867,7 +8017,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="119"/>
+      <c r="F70" s="111"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -7903,7 +8053,7 @@
       <c r="AD70" s="54"/>
     </row>
     <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="113"/>
+      <c r="A71" s="105"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -7918,7 +8068,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="119"/>
+      <c r="F71" s="111"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -7954,7 +8104,7 @@
       <c r="AD71" s="54"/>
     </row>
     <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="113"/>
+      <c r="A72" s="105"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -7969,7 +8119,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="119"/>
+      <c r="F72" s="111"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -8005,7 +8155,7 @@
       <c r="AD72" s="54"/>
     </row>
     <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="114"/>
+      <c r="A73" s="106"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -8020,7 +8170,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="121"/>
+      <c r="F73" s="113"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -8142,6 +8292,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="F1:F73"/>
     <mergeCell ref="A46:A49"/>
@@ -8158,8 +8310,6 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z37 G38:U39 W38:Z39 V39 G40:Z52 G53:W53 Y53:Z53 G54:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BE11BA-C260-45E5-B84B-DD63E9AF74FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D8C27B-D76A-427A-9106-5DAEA14347CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="137">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -1562,6 +1562,18 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1572,18 +1584,6 @@
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3137,7 +3137,7 @@
       <c r="AD5" s="54"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="107">
+      <c r="A6" s="103">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3230,7 +3230,7 @@
       <c r="AD6" s="54"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="108"/>
+      <c r="A7" s="104"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3321,7 +3321,7 @@
       <c r="AD7" s="54"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="109"/>
+      <c r="A8" s="105"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3412,7 +3412,7 @@
       <c r="AD8" s="54"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="110"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3503,7 +3503,7 @@
       <c r="AD9" s="54"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="103">
+      <c r="A10" s="107">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3594,7 +3594,7 @@
       <c r="AD10" s="54"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="104"/>
+      <c r="A11" s="108"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3685,7 +3685,7 @@
       <c r="AD11" s="54"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="105"/>
+      <c r="A12" s="109"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3776,7 +3776,7 @@
       <c r="AD12" s="54"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="106"/>
+      <c r="A13" s="110"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3867,7 +3867,7 @@
       <c r="AD13" s="54"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="107">
+      <c r="A14" s="103">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3960,7 +3960,7 @@
       <c r="AD14" s="54"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="108"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -4051,7 +4051,7 @@
       <c r="AD15" s="54"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="109"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4142,7 +4142,7 @@
       <c r="AD16" s="54"/>
     </row>
     <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="110"/>
+      <c r="A17" s="106"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4233,7 +4233,7 @@
       <c r="AD17" s="54"/>
     </row>
     <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="103">
+      <c r="A18" s="107">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4326,7 +4326,7 @@
       <c r="AD18" s="54"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="104"/>
+      <c r="A19" s="108"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4417,7 +4417,7 @@
       <c r="AD19" s="54"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="105"/>
+      <c r="A20" s="109"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4508,7 +4508,7 @@
       <c r="AD20" s="54"/>
     </row>
     <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="106"/>
+      <c r="A21" s="110"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4599,7 +4599,7 @@
       <c r="AD21" s="54"/>
     </row>
     <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="107">
+      <c r="A22" s="103">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4692,7 +4692,7 @@
       <c r="AD22" s="54"/>
     </row>
     <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="108"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4783,7 +4783,7 @@
       <c r="AD23" s="54"/>
     </row>
     <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="109"/>
+      <c r="A24" s="105"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4874,7 +4874,7 @@
       <c r="AD24" s="54"/>
     </row>
     <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="110"/>
+      <c r="A25" s="106"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4965,7 +4965,7 @@
       <c r="AD25" s="54"/>
     </row>
     <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="103">
+      <c r="A26" s="107">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -5058,7 +5058,7 @@
       <c r="AD26" s="54"/>
     </row>
     <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="104"/>
+      <c r="A27" s="108"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5147,7 +5147,7 @@
       <c r="AD27" s="54"/>
     </row>
     <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="105"/>
+      <c r="A28" s="109"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5236,7 +5236,7 @@
       <c r="AD28" s="54"/>
     </row>
     <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="106"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5325,7 +5325,7 @@
       <c r="AD29" s="54"/>
     </row>
     <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="107">
+      <c r="A30" s="103">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5416,7 +5416,7 @@
       <c r="AD30" s="54"/>
     </row>
     <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="108"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5507,7 +5507,7 @@
       <c r="AD31" s="54"/>
     </row>
     <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="109"/>
+      <c r="A32" s="105"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5596,7 +5596,7 @@
       <c r="AD32" s="54"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="110"/>
+      <c r="A33" s="106"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5687,7 +5687,7 @@
       <c r="AD33" s="54"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="103">
+      <c r="A34" s="107">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5780,7 +5780,7 @@
       <c r="AD34" s="54"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="104"/>
+      <c r="A35" s="108"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5871,7 +5871,7 @@
       <c r="AD35" s="54"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="105"/>
+      <c r="A36" s="109"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5962,7 +5962,7 @@
       <c r="AD36" s="54"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="106"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -6053,7 +6053,7 @@
       <c r="AD37" s="54"/>
     </row>
     <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="107">
+      <c r="A38" s="103">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -6144,7 +6144,7 @@
       <c r="AD38" s="54"/>
     </row>
     <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="108"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -6157,7 +6157,7 @@
         <v>Egito</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="F39" s="118"/>
       <c r="G39" s="63" t="s">
@@ -6220,22 +6220,22 @@
       <c r="Z39" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AA39" s="81" t="str">
+      <c r="AA39" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB39" s="90" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AC39" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>B</v>
       </c>
       <c r="AD39" s="54"/>
     </row>
     <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="109"/>
+      <c r="A40" s="105"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -6324,7 +6324,7 @@
       <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="110"/>
+      <c r="A41" s="106"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6413,7 +6413,7 @@
       <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="103">
+      <c r="A42" s="107">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6431,26 +6431,66 @@
         <v>74</v>
       </c>
       <c r="F42" s="116"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
-      <c r="J42" s="61"/>
-      <c r="K42" s="61"/>
-      <c r="L42" s="61"/>
-      <c r="M42" s="61"/>
-      <c r="N42" s="61"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="61"/>
-      <c r="Q42" s="61"/>
-      <c r="R42" s="61"/>
-      <c r="S42" s="61"/>
-      <c r="T42" s="61"/>
-      <c r="U42" s="62"/>
-      <c r="V42" s="62"/>
-      <c r="W42" s="62"/>
-      <c r="X42" s="62"/>
-      <c r="Y42" s="62"/>
-      <c r="Z42" s="76"/>
+      <c r="G42" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="H42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="I42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="J42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="K42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="L42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="M42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="N42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="O42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="P42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="R42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="S42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="T42" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="U42" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="V42" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="W42" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="X42" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y42" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z42" s="76" t="s">
+        <v>44</v>
+      </c>
       <c r="AA42" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6466,7 +6506,7 @@
       <c r="AD42" s="54"/>
     </row>
     <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="104"/>
+      <c r="A43" s="108"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6482,26 +6522,66 @@
         <v>74</v>
       </c>
       <c r="F43" s="118"/>
-      <c r="G43" s="63"/>
-      <c r="H43" s="71"/>
-      <c r="I43" s="71"/>
-      <c r="J43" s="71"/>
-      <c r="K43" s="71"/>
-      <c r="L43" s="71"/>
-      <c r="M43" s="71"/>
-      <c r="N43" s="71"/>
-      <c r="O43" s="71"/>
-      <c r="P43" s="71"/>
-      <c r="Q43" s="71"/>
-      <c r="R43" s="71"/>
-      <c r="S43" s="71"/>
-      <c r="T43" s="71"/>
-      <c r="U43" s="56"/>
-      <c r="V43" s="56"/>
-      <c r="W43" s="56"/>
-      <c r="X43" s="56"/>
-      <c r="Y43" s="56"/>
-      <c r="Z43" s="80"/>
+      <c r="G43" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="I43" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="J43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="L43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="M43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="N43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O43" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="P43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="R43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="S43" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="T43" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="U43" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="V43" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="W43" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="X43" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y43" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z43" s="80" t="s">
+        <v>45</v>
+      </c>
       <c r="AA43" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6517,7 +6597,7 @@
       <c r="AD43" s="54"/>
     </row>
     <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="105"/>
+      <c r="A44" s="109"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6533,26 +6613,66 @@
         <v>74</v>
       </c>
       <c r="F44" s="119"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="66"/>
-      <c r="I44" s="66"/>
-      <c r="J44" s="66"/>
-      <c r="K44" s="66"/>
-      <c r="L44" s="66"/>
-      <c r="M44" s="66"/>
-      <c r="N44" s="66"/>
-      <c r="O44" s="66"/>
-      <c r="P44" s="66"/>
-      <c r="Q44" s="66"/>
-      <c r="R44" s="66"/>
-      <c r="S44" s="66"/>
-      <c r="T44" s="66"/>
-      <c r="U44" s="67"/>
-      <c r="V44" s="67"/>
-      <c r="W44" s="67"/>
-      <c r="X44" s="67"/>
-      <c r="Y44" s="67"/>
-      <c r="Z44" s="78"/>
+      <c r="G44" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="J44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="K44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="L44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="M44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="N44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="O44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="P44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q44" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="R44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="S44" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="T44" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="U44" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="V44" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W44" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="X44" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y44" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z44" s="78" t="s">
+        <v>45</v>
+      </c>
       <c r="AA44" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6568,7 +6688,7 @@
       <c r="AD44" s="54"/>
     </row>
     <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="106"/>
+      <c r="A45" s="110"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6584,26 +6704,66 @@
         <v>74</v>
       </c>
       <c r="F45" s="120"/>
-      <c r="G45" s="68"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="69"/>
-      <c r="J45" s="69"/>
-      <c r="K45" s="69"/>
-      <c r="L45" s="69"/>
-      <c r="M45" s="69"/>
-      <c r="N45" s="69"/>
-      <c r="O45" s="69"/>
-      <c r="P45" s="69"/>
-      <c r="Q45" s="69"/>
-      <c r="R45" s="69"/>
-      <c r="S45" s="69"/>
-      <c r="T45" s="69"/>
-      <c r="U45" s="70"/>
-      <c r="V45" s="70"/>
-      <c r="W45" s="70"/>
-      <c r="X45" s="70"/>
-      <c r="Y45" s="70"/>
-      <c r="Z45" s="79"/>
+      <c r="G45" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="H45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="I45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="J45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="K45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="L45" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="M45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="N45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="O45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="P45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="R45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="S45" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="T45" s="69" t="s">
+        <v>45</v>
+      </c>
+      <c r="U45" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="V45" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="W45" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="X45" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y45" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z45" s="79" t="s">
+        <v>46</v>
+      </c>
       <c r="AA45" s="81" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -6619,7 +6779,7 @@
       <c r="AD45" s="54"/>
     </row>
     <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="107">
+      <c r="A46" s="103">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6672,7 +6832,7 @@
       <c r="AD46" s="54"/>
     </row>
     <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="108"/>
+      <c r="A47" s="104"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6723,7 +6883,7 @@
       <c r="AD47" s="54"/>
     </row>
     <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="109"/>
+      <c r="A48" s="105"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6774,7 +6934,7 @@
       <c r="AD48" s="54"/>
     </row>
     <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="110"/>
+      <c r="A49" s="106"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6825,7 +6985,7 @@
       <c r="AD49" s="54"/>
     </row>
     <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="103">
+      <c r="A50" s="107">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6878,7 +7038,7 @@
       <c r="AD50" s="54"/>
     </row>
     <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="104"/>
+      <c r="A51" s="108"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -6929,7 +7089,7 @@
       <c r="AD51" s="54"/>
     </row>
     <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="105"/>
+      <c r="A52" s="109"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -6980,7 +7140,7 @@
       <c r="AD52" s="54"/>
     </row>
     <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="105"/>
+      <c r="A53" s="109"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -7030,7 +7190,7 @@
       <c r="AD53" s="54"/>
     </row>
     <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="105"/>
+      <c r="A54" s="109"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -7081,7 +7241,7 @@
       <c r="AD54" s="54"/>
     </row>
     <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="106"/>
+      <c r="A55" s="110"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -7132,7 +7292,7 @@
       <c r="AD55" s="54"/>
     </row>
     <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="107">
+      <c r="A56" s="103">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -7185,7 +7345,7 @@
       <c r="AD56" s="54"/>
     </row>
     <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="108"/>
+      <c r="A57" s="104"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -7236,7 +7396,7 @@
       <c r="AD57" s="54"/>
     </row>
     <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="109"/>
+      <c r="A58" s="105"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -7287,7 +7447,7 @@
       <c r="AD58" s="54"/>
     </row>
     <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="109"/>
+      <c r="A59" s="105"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -7338,7 +7498,7 @@
       <c r="AD59" s="54"/>
     </row>
     <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="109"/>
+      <c r="A60" s="105"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7389,7 +7549,7 @@
       <c r="AD60" s="54"/>
     </row>
     <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="110"/>
+      <c r="A61" s="106"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7440,7 +7600,7 @@
       <c r="AD61" s="54"/>
     </row>
     <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="103">
+      <c r="A62" s="107">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7493,7 +7653,7 @@
       <c r="AD62" s="54"/>
     </row>
     <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="104"/>
+      <c r="A63" s="108"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7544,7 +7704,7 @@
       <c r="AD63" s="54"/>
     </row>
     <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="105"/>
+      <c r="A64" s="109"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7595,7 +7755,7 @@
       <c r="AD64" s="54"/>
     </row>
     <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="105"/>
+      <c r="A65" s="109"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7646,7 +7806,7 @@
       <c r="AD65" s="54"/>
     </row>
     <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="105"/>
+      <c r="A66" s="109"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7697,7 +7857,7 @@
       <c r="AD66" s="54"/>
     </row>
     <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="106"/>
+      <c r="A67" s="110"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -8069,7 +8229,7 @@
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -8085,19 +8245,19 @@
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -8113,15 +8273,15 @@
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -8129,7 +8289,7 @@
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
@@ -8137,12 +8297,11 @@
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
@@ -8160,6 +8319,7 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z37 G38:U39 W38:Z39 V39 G40:Z52 G53:W53 Y53:Z53 G54:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10612"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{007218A1-B94B-7A4F-9895-F63331845DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9D1C9C-E8E2-4326-83BF-75DF1E69A9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -1562,6 +1562,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
@@ -1594,30 +1618,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2111,13 +2111,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.75" customWidth="1"/>
-    <col min="2" max="3" width="14.2578125" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="3" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
@@ -2129,7 +2129,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="126"/>
       <c r="B2" s="126"/>
       <c r="C2" s="13"/>
@@ -2139,7 +2139,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="126"/>
       <c r="B3" s="126"/>
       <c r="C3" s="13"/>
@@ -2157,7 +2157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2309,16 +2309,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.6484375" customWidth="1"/>
-    <col min="2" max="2" width="20.984375" customWidth="1"/>
-    <col min="3" max="7" width="12.10546875" customWidth="1"/>
-    <col min="9" max="9" width="22.8671875" customWidth="1"/>
-    <col min="10" max="10" width="9.55078125" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="7" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="127" t="s">
         <v>20</v>
       </c>
@@ -2329,7 +2329,7 @@
       <c r="F1" s="128"/>
       <c r="G1" s="128"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2377,7 +2377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2420,7 +2420,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2444,7 +2444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2468,7 +2468,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2489,7 +2489,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2510,7 +2510,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2531,7 +2531,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2552,7 +2552,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2573,7 +2573,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2594,7 +2594,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2615,7 +2615,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2636,7 +2636,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2673,17 +2673,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.8359375" customWidth="1"/>
-    <col min="2" max="2" width="32.41796875" customWidth="1"/>
-    <col min="3" max="4" width="20.58203125" customWidth="1"/>
-    <col min="5" max="5" width="12.5078125" customWidth="1"/>
-    <col min="6" max="6" width="6.05078125" customWidth="1"/>
-    <col min="7" max="29" width="16.41015625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="29" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2699,7 +2699,7 @@
       <c r="E1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="107"/>
+      <c r="F1" s="115"/>
       <c r="G1" s="83" t="s">
         <v>3</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="122">
         <v>46184</v>
       </c>
@@ -2788,7 +2788,7 @@
       <c r="E2" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="108"/>
+      <c r="F2" s="116"/>
       <c r="G2" s="63" t="s">
         <v>44</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2878,7 +2878,7 @@
       <c r="E3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="109"/>
+      <c r="F3" s="117"/>
       <c r="G3" s="57" t="s">
         <v>46</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="124">
         <v>46185</v>
       </c>
@@ -2970,7 +2970,7 @@
       <c r="E4" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="116"/>
       <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -3061,7 +3061,7 @@
       <c r="E5" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="109"/>
+      <c r="F5" s="117"/>
       <c r="G5" s="57" t="s">
         <v>45</v>
       </c>
@@ -3136,8 +3136,8 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="114">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" s="103">
         <v>46186</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3154,7 +3154,7 @@
       <c r="E6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="116"/>
       <c r="G6" s="60" t="s">
         <v>45</v>
       </c>
@@ -3229,8 +3229,8 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="115"/>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" s="104"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
       </c>
@@ -3245,7 +3245,7 @@
       <c r="E7" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="110"/>
+      <c r="F7" s="118"/>
       <c r="G7" s="63" t="s">
         <v>44</v>
       </c>
@@ -3320,8 +3320,8 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="116"/>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" s="105"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
       </c>
@@ -3336,7 +3336,7 @@
       <c r="E8" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="111"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="65" t="s">
         <v>44</v>
       </c>
@@ -3411,8 +3411,8 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="117"/>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" s="106"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
@@ -3427,7 +3427,7 @@
       <c r="E9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="112"/>
+      <c r="F9" s="120"/>
       <c r="G9" s="68" t="s">
         <v>44</v>
       </c>
@@ -3502,8 +3502,8 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="118">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A10" s="107">
         <v>46187</v>
       </c>
       <c r="B10" s="22" t="s">
@@ -3520,7 +3520,7 @@
       <c r="E10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="116"/>
       <c r="G10" s="60" t="s">
         <v>44</v>
       </c>
@@ -3593,8 +3593,8 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="119"/>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A11" s="108"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
       </c>
@@ -3609,7 +3609,7 @@
       <c r="E11" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="110"/>
+      <c r="F11" s="118"/>
       <c r="G11" s="63" t="s">
         <v>44</v>
       </c>
@@ -3684,8 +3684,8 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A12" s="120"/>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A12" s="109"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
       </c>
@@ -3700,7 +3700,7 @@
       <c r="E12" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="111"/>
+      <c r="F12" s="119"/>
       <c r="G12" s="65" t="s">
         <v>44</v>
       </c>
@@ -3775,8 +3775,8 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="121"/>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A13" s="110"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
       </c>
@@ -3791,7 +3791,7 @@
       <c r="E13" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="112"/>
+      <c r="F13" s="120"/>
       <c r="G13" s="68" t="s">
         <v>46</v>
       </c>
@@ -3866,8 +3866,8 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A14" s="114">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A14" s="103">
         <v>46188</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3884,7 +3884,7 @@
       <c r="E14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="108"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="60" t="s">
         <v>44</v>
       </c>
@@ -3959,8 +3959,8 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A15" s="115"/>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A15" s="104"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
       </c>
@@ -3975,7 +3975,7 @@
       <c r="E15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="110"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="63" t="s">
         <v>46</v>
       </c>
@@ -4050,8 +4050,8 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="116"/>
+    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="105"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
       </c>
@@ -4066,7 +4066,7 @@
       <c r="E16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="111"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="65" t="s">
         <v>44</v>
       </c>
@@ -4141,8 +4141,8 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="117"/>
+    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="106"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
       </c>
@@ -4157,7 +4157,7 @@
       <c r="E17" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="112"/>
+      <c r="F17" s="120"/>
       <c r="G17" s="68" t="s">
         <v>45</v>
       </c>
@@ -4232,8 +4232,8 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="118">
+    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="107">
         <v>46189</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -4250,7 +4250,7 @@
       <c r="E18" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="108"/>
+      <c r="F18" s="116"/>
       <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
@@ -4325,8 +4325,8 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A19" s="119"/>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A19" s="108"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
       </c>
@@ -4341,7 +4341,7 @@
       <c r="E19" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="110"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="63" t="s">
         <v>46</v>
       </c>
@@ -4416,8 +4416,8 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A20" s="120"/>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A20" s="109"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
       </c>
@@ -4432,7 +4432,7 @@
       <c r="E20" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="111"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="65" t="s">
         <v>44</v>
       </c>
@@ -4507,8 +4507,8 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="121"/>
+    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="110"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
       </c>
@@ -4523,7 +4523,7 @@
       <c r="E21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="112"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
@@ -4598,8 +4598,8 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="114">
+    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="103">
         <v>46190</v>
       </c>
       <c r="B22" s="24" t="s">
@@ -4616,7 +4616,7 @@
       <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="108"/>
+      <c r="F22" s="116"/>
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
@@ -4691,8 +4691,8 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="115"/>
+    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="104"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
       </c>
@@ -4707,7 +4707,7 @@
       <c r="E23" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="F23" s="110"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="63" t="s">
         <v>45</v>
       </c>
@@ -4782,8 +4782,8 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="116"/>
+    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="105"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
       </c>
@@ -4798,7 +4798,7 @@
       <c r="E24" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="111"/>
+      <c r="F24" s="119"/>
       <c r="G24" s="97" t="s">
         <v>44</v>
       </c>
@@ -4873,8 +4873,8 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="117"/>
+    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="106"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
       </c>
@@ -4889,7 +4889,7 @@
       <c r="E25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="112"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="101" t="s">
         <v>44</v>
       </c>
@@ -4964,8 +4964,8 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="118">
+    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="107">
         <v>46191</v>
       </c>
       <c r="B26" s="22" t="s">
@@ -4982,7 +4982,7 @@
       <c r="E26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="108"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="60" t="s">
         <v>44</v>
       </c>
@@ -5057,8 +5057,8 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="119"/>
+    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="108"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
       </c>
@@ -5073,7 +5073,7 @@
       <c r="E27" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="110"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="63" t="s">
         <v>44</v>
       </c>
@@ -5146,8 +5146,8 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="120"/>
+    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="109"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
       </c>
@@ -5162,7 +5162,7 @@
       <c r="E28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="111"/>
+      <c r="F28" s="119"/>
       <c r="G28" s="65" t="s">
         <v>44</v>
       </c>
@@ -5235,8 +5235,8 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="121"/>
+    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="110"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
       </c>
@@ -5251,7 +5251,7 @@
       <c r="E29" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="112"/>
+      <c r="F29" s="120"/>
       <c r="G29" s="68" t="s">
         <v>44</v>
       </c>
@@ -5324,8 +5324,8 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="114">
+    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="103">
         <v>46192</v>
       </c>
       <c r="B30" s="24" t="s">
@@ -5342,7 +5342,7 @@
       <c r="E30" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="108"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="60" t="s">
         <v>45</v>
       </c>
@@ -5415,8 +5415,8 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="115"/>
+    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="104"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
       </c>
@@ -5431,7 +5431,7 @@
       <c r="E31" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="110"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="63" t="s">
         <v>44</v>
       </c>
@@ -5506,8 +5506,8 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="116"/>
+    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="105"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
@@ -5522,7 +5522,7 @@
       <c r="E32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="111"/>
+      <c r="F32" s="119"/>
       <c r="G32" s="65" t="s">
         <v>44</v>
       </c>
@@ -5595,8 +5595,8 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="117"/>
+    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="106"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
       </c>
@@ -5611,7 +5611,7 @@
       <c r="E33" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="112"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="68" t="s">
         <v>44</v>
       </c>
@@ -5686,8 +5686,8 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="118">
+    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="107">
         <v>46193</v>
       </c>
       <c r="B34" s="22" t="s">
@@ -5704,7 +5704,7 @@
       <c r="E34" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="108"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="60" t="s">
         <v>44</v>
       </c>
@@ -5779,8 +5779,8 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="119"/>
+    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="108"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
       </c>
@@ -5795,7 +5795,7 @@
       <c r="E35" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="110"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="63" t="s">
         <v>44</v>
       </c>
@@ -5870,8 +5870,8 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="120"/>
+    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="109"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
       </c>
@@ -5886,7 +5886,7 @@
       <c r="E36" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="111"/>
+      <c r="F36" s="119"/>
       <c r="G36" s="65" t="s">
         <v>44</v>
       </c>
@@ -5961,8 +5961,8 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="121"/>
+    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="110"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
       </c>
@@ -5977,7 +5977,7 @@
       <c r="E37" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="112"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="68" t="s">
         <v>45</v>
       </c>
@@ -6052,8 +6052,8 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="114">
+    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="103">
         <v>46194</v>
       </c>
       <c r="B38" s="24" t="s">
@@ -6070,7 +6070,7 @@
       <c r="E38" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="108"/>
+      <c r="F38" s="116"/>
       <c r="G38" s="60" t="s">
         <v>44</v>
       </c>
@@ -6143,8 +6143,8 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="115"/>
+    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="104"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
       </c>
@@ -6159,7 +6159,7 @@
       <c r="E39" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="F39" s="110"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="63" t="s">
         <v>46</v>
       </c>
@@ -6234,8 +6234,8 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="116"/>
+    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="105"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
       </c>
@@ -6250,7 +6250,7 @@
       <c r="E40" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="F40" s="111"/>
+      <c r="F40" s="119"/>
       <c r="G40" s="65" t="s">
         <v>44</v>
       </c>
@@ -6323,8 +6323,8 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="117"/>
+    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="106"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
       </c>
@@ -6339,7 +6339,7 @@
       <c r="E41" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="F41" s="112"/>
+      <c r="F41" s="120"/>
       <c r="G41" s="68" t="s">
         <v>44</v>
       </c>
@@ -6412,8 +6412,8 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="118">
+    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="107">
         <v>46195</v>
       </c>
       <c r="B42" s="22" t="s">
@@ -6428,9 +6428,9 @@
         <v>Iraque</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" s="108"/>
+        <v>61</v>
+      </c>
+      <c r="F42" s="116"/>
       <c r="G42" s="60" t="s">
         <v>44</v>
       </c>
@@ -6491,22 +6491,22 @@
       <c r="Z42" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="AA42" s="81" t="str">
+      <c r="AA42" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB42" s="90" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC42" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="119"/>
+    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="108"/>
       <c r="B43" s="28" t="s">
         <v>98</v>
       </c>
@@ -6521,7 +6521,7 @@
       <c r="E43" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="110"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="63" t="s">
         <v>44</v>
       </c>
@@ -6592,8 +6592,8 @@
       </c>
       <c r="AD43" s="54"/>
     </row>
-    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="120"/>
+    <row r="44" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="109"/>
       <c r="B44" s="29" t="s">
         <v>99</v>
       </c>
@@ -6606,9 +6606,9 @@
         <v>Áustria</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="F44" s="111"/>
+        <v>43</v>
+      </c>
+      <c r="F44" s="119"/>
       <c r="G44" s="65" t="s">
         <v>44</v>
       </c>
@@ -6669,22 +6669,22 @@
       <c r="Z44" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="AA44" s="81" t="str">
+      <c r="AA44" s="81">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AB44" s="90" t="str">
+        <v>2</v>
+      </c>
+      <c r="AB44" s="90">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC44" s="85" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>A</v>
       </c>
       <c r="AD44" s="54"/>
     </row>
-    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="121"/>
+    <row r="45" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="110"/>
       <c r="B45" s="30" t="s">
         <v>100</v>
       </c>
@@ -6699,7 +6699,7 @@
       <c r="E45" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="112"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="68" t="s">
         <v>45</v>
       </c>
@@ -6768,8 +6768,8 @@
       </c>
       <c r="AD45" s="54"/>
     </row>
-    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="114">
+    <row r="46" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="103">
         <v>46196</v>
       </c>
       <c r="B46" s="24" t="s">
@@ -6786,7 +6786,7 @@
       <c r="E46" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="108"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="60"/>
       <c r="H46" s="61"/>
       <c r="I46" s="61"/>
@@ -6821,8 +6821,8 @@
       </c>
       <c r="AD46" s="54"/>
     </row>
-    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="115"/>
+    <row r="47" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="104"/>
       <c r="B47" s="25" t="s">
         <v>102</v>
       </c>
@@ -6837,7 +6837,7 @@
       <c r="E47" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="110"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="63"/>
       <c r="H47" s="71"/>
       <c r="I47" s="71"/>
@@ -6872,8 +6872,8 @@
       </c>
       <c r="AD47" s="54"/>
     </row>
-    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="116"/>
+    <row r="48" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="105"/>
       <c r="B48" s="26" t="s">
         <v>103</v>
       </c>
@@ -6888,7 +6888,7 @@
       <c r="E48" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="111"/>
+      <c r="F48" s="119"/>
       <c r="G48" s="65"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -6923,8 +6923,8 @@
       </c>
       <c r="AD48" s="54"/>
     </row>
-    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="117"/>
+    <row r="49" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="106"/>
       <c r="B49" s="27" t="s">
         <v>104</v>
       </c>
@@ -6939,7 +6939,7 @@
       <c r="E49" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="112"/>
+      <c r="F49" s="120"/>
       <c r="G49" s="68"/>
       <c r="H49" s="69"/>
       <c r="I49" s="69"/>
@@ -6974,8 +6974,8 @@
       </c>
       <c r="AD49" s="54"/>
     </row>
-    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="118">
+    <row r="50" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="107">
         <v>46197</v>
       </c>
       <c r="B50" s="22" t="s">
@@ -6992,7 +6992,7 @@
       <c r="E50" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F50" s="108"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="60"/>
       <c r="H50" s="61"/>
       <c r="I50" s="61"/>
@@ -7027,8 +7027,8 @@
       </c>
       <c r="AD50" s="54"/>
     </row>
-    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="119"/>
+    <row r="51" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="108"/>
       <c r="B51" s="28" t="s">
         <v>106</v>
       </c>
@@ -7043,7 +7043,7 @@
       <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F51" s="110"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="63"/>
       <c r="H51" s="71"/>
       <c r="I51" s="71"/>
@@ -7078,8 +7078,8 @@
       </c>
       <c r="AD51" s="54"/>
     </row>
-    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="120"/>
+    <row r="52" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="109"/>
       <c r="B52" s="29" t="s">
         <v>107</v>
       </c>
@@ -7094,7 +7094,7 @@
       <c r="E52" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="111"/>
+      <c r="F52" s="119"/>
       <c r="G52" s="65"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
@@ -7129,8 +7129,8 @@
       </c>
       <c r="AD52" s="54"/>
     </row>
-    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="120"/>
+    <row r="53" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="109"/>
       <c r="B53" s="29" t="s">
         <v>108</v>
       </c>
@@ -7145,7 +7145,7 @@
       <c r="E53" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="111"/>
+      <c r="F53" s="119"/>
       <c r="G53" s="65"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
@@ -7179,8 +7179,8 @@
       </c>
       <c r="AD53" s="54"/>
     </row>
-    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="120"/>
+    <row r="54" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="109"/>
       <c r="B54" s="29" t="s">
         <v>109</v>
       </c>
@@ -7195,7 +7195,7 @@
       <c r="E54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="111"/>
+      <c r="F54" s="119"/>
       <c r="G54" s="65"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
@@ -7230,8 +7230,8 @@
       </c>
       <c r="AD54" s="54"/>
     </row>
-    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="121"/>
+    <row r="55" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="110"/>
       <c r="B55" s="30" t="s">
         <v>110</v>
       </c>
@@ -7246,7 +7246,7 @@
       <c r="E55" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="112"/>
+      <c r="F55" s="120"/>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
       <c r="I55" s="69"/>
@@ -7281,8 +7281,8 @@
       </c>
       <c r="AD55" s="54"/>
     </row>
-    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="114">
+    <row r="56" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="103">
         <v>46198</v>
       </c>
       <c r="B56" s="24" t="s">
@@ -7299,7 +7299,7 @@
       <c r="E56" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F56" s="108"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="60"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
@@ -7334,8 +7334,8 @@
       </c>
       <c r="AD56" s="54"/>
     </row>
-    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="115"/>
+    <row r="57" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="104"/>
       <c r="B57" s="25" t="s">
         <v>112</v>
       </c>
@@ -7350,7 +7350,7 @@
       <c r="E57" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F57" s="110"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="63"/>
       <c r="H57" s="71"/>
       <c r="I57" s="71"/>
@@ -7385,8 +7385,8 @@
       </c>
       <c r="AD57" s="54"/>
     </row>
-    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="116"/>
+    <row r="58" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="105"/>
       <c r="B58" s="26" t="s">
         <v>113</v>
       </c>
@@ -7401,7 +7401,7 @@
       <c r="E58" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="111"/>
+      <c r="F58" s="119"/>
       <c r="G58" s="65"/>
       <c r="H58" s="66"/>
       <c r="I58" s="66"/>
@@ -7436,8 +7436,8 @@
       </c>
       <c r="AD58" s="54"/>
     </row>
-    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="116"/>
+    <row r="59" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="105"/>
       <c r="B59" s="26" t="s">
         <v>114</v>
       </c>
@@ -7452,7 +7452,7 @@
       <c r="E59" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="111"/>
+      <c r="F59" s="119"/>
       <c r="G59" s="65"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
@@ -7487,8 +7487,8 @@
       </c>
       <c r="AD59" s="54"/>
     </row>
-    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="116"/>
+    <row r="60" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="105"/>
       <c r="B60" s="26" t="s">
         <v>115</v>
       </c>
@@ -7503,7 +7503,7 @@
       <c r="E60" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F60" s="111"/>
+      <c r="F60" s="119"/>
       <c r="G60" s="65"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -7538,8 +7538,8 @@
       </c>
       <c r="AD60" s="54"/>
     </row>
-    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="117"/>
+    <row r="61" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="106"/>
       <c r="B61" s="27" t="s">
         <v>116</v>
       </c>
@@ -7554,7 +7554,7 @@
       <c r="E61" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F61" s="112"/>
+      <c r="F61" s="120"/>
       <c r="G61" s="68"/>
       <c r="H61" s="69"/>
       <c r="I61" s="69"/>
@@ -7589,8 +7589,8 @@
       </c>
       <c r="AD61" s="54"/>
     </row>
-    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="118">
+    <row r="62" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="107">
         <v>46199</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -7607,7 +7607,7 @@
       <c r="E62" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="F62" s="108"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="60"/>
       <c r="H62" s="61"/>
       <c r="I62" s="61"/>
@@ -7642,8 +7642,8 @@
       </c>
       <c r="AD62" s="54"/>
     </row>
-    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="119"/>
+    <row r="63" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="108"/>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
@@ -7658,7 +7658,7 @@
       <c r="E63" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="F63" s="110"/>
+      <c r="F63" s="118"/>
       <c r="G63" s="63"/>
       <c r="H63" s="71"/>
       <c r="I63" s="71"/>
@@ -7693,8 +7693,8 @@
       </c>
       <c r="AD63" s="54"/>
     </row>
-    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="120"/>
+    <row r="64" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="109"/>
       <c r="B64" s="29" t="s">
         <v>119</v>
       </c>
@@ -7709,7 +7709,7 @@
       <c r="E64" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="111"/>
+      <c r="F64" s="119"/>
       <c r="G64" s="65"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
@@ -7744,8 +7744,8 @@
       </c>
       <c r="AD64" s="54"/>
     </row>
-    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="120"/>
+    <row r="65" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="109"/>
       <c r="B65" s="29" t="s">
         <v>120</v>
       </c>
@@ -7760,7 +7760,7 @@
       <c r="E65" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F65" s="111"/>
+      <c r="F65" s="119"/>
       <c r="G65" s="65"/>
       <c r="H65" s="66"/>
       <c r="I65" s="66"/>
@@ -7795,8 +7795,8 @@
       </c>
       <c r="AD65" s="54"/>
     </row>
-    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="120"/>
+    <row r="66" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="109"/>
       <c r="B66" s="29" t="s">
         <v>121</v>
       </c>
@@ -7811,7 +7811,7 @@
       <c r="E66" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="111"/>
+      <c r="F66" s="119"/>
       <c r="G66" s="65"/>
       <c r="H66" s="66"/>
       <c r="I66" s="66"/>
@@ -7846,8 +7846,8 @@
       </c>
       <c r="AD66" s="54"/>
     </row>
-    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="121"/>
+    <row r="67" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="110"/>
       <c r="B67" s="30" t="s">
         <v>122</v>
       </c>
@@ -7862,7 +7862,7 @@
       <c r="E67" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="F67" s="112"/>
+      <c r="F67" s="120"/>
       <c r="G67" s="68"/>
       <c r="H67" s="69"/>
       <c r="I67" s="69"/>
@@ -7897,8 +7897,8 @@
       </c>
       <c r="AD67" s="54"/>
     </row>
-    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="103">
+    <row r="68" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="111">
         <v>46200</v>
       </c>
       <c r="B68" s="24" t="s">
@@ -7915,7 +7915,7 @@
       <c r="E68" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="F68" s="108"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="60"/>
       <c r="H68" s="61"/>
       <c r="I68" s="61"/>
@@ -7950,8 +7950,8 @@
       </c>
       <c r="AD68" s="54"/>
     </row>
-    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="104"/>
+    <row r="69" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="112"/>
       <c r="B69" s="25" t="s">
         <v>124</v>
       </c>
@@ -7966,7 +7966,7 @@
       <c r="E69" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="110"/>
+      <c r="F69" s="118"/>
       <c r="G69" s="63"/>
       <c r="H69" s="71"/>
       <c r="I69" s="71"/>
@@ -8001,8 +8001,8 @@
       </c>
       <c r="AD69" s="54"/>
     </row>
-    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="105"/>
+    <row r="70" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="113"/>
       <c r="B70" s="26" t="s">
         <v>125</v>
       </c>
@@ -8017,7 +8017,7 @@
       <c r="E70" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="111"/>
+      <c r="F70" s="119"/>
       <c r="G70" s="65"/>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -8052,8 +8052,8 @@
       </c>
       <c r="AD70" s="54"/>
     </row>
-    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="105"/>
+    <row r="71" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="113"/>
       <c r="B71" s="26" t="s">
         <v>126</v>
       </c>
@@ -8068,7 +8068,7 @@
       <c r="E71" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="111"/>
+      <c r="F71" s="119"/>
       <c r="G71" s="65"/>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -8103,8 +8103,8 @@
       </c>
       <c r="AD71" s="54"/>
     </row>
-    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="105"/>
+    <row r="72" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="113"/>
       <c r="B72" s="26" t="s">
         <v>127</v>
       </c>
@@ -8119,7 +8119,7 @@
       <c r="E72" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="111"/>
+      <c r="F72" s="119"/>
       <c r="G72" s="65"/>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -8154,8 +8154,8 @@
       </c>
       <c r="AD72" s="54"/>
     </row>
-    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="106"/>
+    <row r="73" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="114"/>
       <c r="B73" s="31" t="s">
         <v>128</v>
       </c>
@@ -8170,7 +8170,7 @@
       <c r="E73" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="113"/>
+      <c r="F73" s="121"/>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
       <c r="I73" s="69"/>
@@ -8205,93 +8205,95 @@
       </c>
       <c r="AD73" s="54"/>
     </row>
-    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F74" s="19" t="s">
         <v>129</v>
       </c>
       <c r="G74" s="74" cm="1">
         <f t="array" ref="G74">SUMPRODUCT(--(UPPER(G2:G73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H74" s="74" cm="1">
         <f t="array" ref="H74">SUMPRODUCT(--(UPPER(H2:H73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I74" s="74" cm="1">
         <f t="array" ref="I74">SUMPRODUCT(--(UPPER(I2:I73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J74" s="74" cm="1">
         <f t="array" ref="J74">SUMPRODUCT(--(UPPER(J2:J73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K74" s="74" cm="1">
         <f t="array" ref="K74">SUMPRODUCT(--(UPPER(K2:K73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L74" s="74" cm="1">
         <f t="array" ref="L74">SUMPRODUCT(--(UPPER(L2:L73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M74" s="74" cm="1">
         <f t="array" ref="M74">SUMPRODUCT(--(UPPER(M2:M73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N74" s="74" cm="1">
         <f t="array" ref="N74">SUMPRODUCT(--(UPPER(N2:N73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O74" s="74" cm="1">
         <f t="array" ref="O74">SUMPRODUCT(--(UPPER(O2:O73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P74" s="74" cm="1">
         <f t="array" ref="P74">SUMPRODUCT(--(UPPER(P2:P73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q74" s="74" cm="1">
         <f t="array" ref="Q74">SUMPRODUCT(--(UPPER(Q2:Q73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R74" s="74" cm="1">
         <f t="array" ref="R74">SUMPRODUCT(--(UPPER(R2:R73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S74" s="74" cm="1">
         <f t="array" ref="S74">SUMPRODUCT(--(UPPER(S2:S73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T74" s="74" cm="1">
         <f t="array" ref="T74">SUMPRODUCT(--(UPPER(T2:T73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="U74" s="74" cm="1">
         <f t="array" ref="U74">SUMPRODUCT(--(UPPER(U2:U73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V74" s="74" cm="1">
         <f t="array" ref="V74">SUMPRODUCT(--(UPPER(V2:V73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W74" s="74" cm="1">
         <f t="array" ref="W74">SUMPRODUCT(--(UPPER(W2:W73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="X74" s="74" cm="1">
         <f t="array" ref="X74">SUMPRODUCT(--(UPPER(X2:X73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y74" s="74" cm="1">
         <f t="array" ref="Y74">SUMPRODUCT(--(UPPER(Y2:Y73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z74" s="74" cm="1">
         <f t="array" ref="Z74">SUMPRODUCT(--(UPPER(Z2:Z73)=$AC$2:$AC$73),--($AC$2:$AC$73&lt;&gt;""))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="A56:A61"/>
     <mergeCell ref="A62:A67"/>
     <mergeCell ref="A68:A73"/>
@@ -8308,8 +8310,6 @@
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="G2:Z37 G38:U39 W38:Z39 V39 G40:Z52 G53:W53 Y53:Z53 G54:Z73">

--- a/BOLAO.xlsx
+++ b/BOLAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10612"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\BolaoCopa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9D1C9C-E8E2-4326-83BF-75DF1E69A9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15C36222-7B4E-D04F-8FE3-EE600E0D0481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{126756CB-841B-4483-9AA9-4CA1801C3655}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="139">
   <si>
     <t>BOLÃO DA COPA 2026</t>
   </si>
@@ -474,6 +474,12 @@
   </si>
   <si>
     <t>4x0</t>
+  </si>
+  <si>
+    <t>3x2</t>
+  </si>
+  <si>
+    <t>1x2</t>
   </si>
 </sst>
 </file>
@@ -2111,13 +2117,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9EB9C6-68D0-4D2F-A5BE-E5AEA76F05E0}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="3" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.75" customWidth="1"/>
+    <col min="2" max="3" width="14.2578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
@@ -2129,7 +2135,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="126"/>
       <c r="B2" s="126"/>
       <c r="C2" s="13"/>
@@ -2139,7 +2145,7 @@
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="126"/>
       <c r="B3" s="126"/>
       <c r="C3" s="13"/>
@@ -2157,7 +2163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2165,7 +2171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2173,7 +2179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2181,7 +2187,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2189,7 +2195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2197,7 +2203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2205,7 +2211,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2213,7 +2219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2221,7 +2227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2229,7 +2235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2237,7 +2243,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2245,7 +2251,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2253,7 +2259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2261,7 +2267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2269,7 +2275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2277,7 +2283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2309,16 +2315,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A13565-F431-42B0-AFCE-662FFB8D74CF}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="7" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="22.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.6484375" customWidth="1"/>
+    <col min="2" max="2" width="20.984375" customWidth="1"/>
+    <col min="3" max="7" width="12.10546875" customWidth="1"/>
+    <col min="9" max="9" width="22.8671875" customWidth="1"/>
+    <col min="10" max="10" width="9.55078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="127" t="s">
         <v>20</v>
       </c>
@@ -2329,7 +2335,7 @@
       <c r="F1" s="128"/>
       <c r="G1" s="128"/>
     </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -2350,7 +2356,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2377,7 +2383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <f t="shared" ref="A5:A17" si="0">ROW()-3</f>
         <v>2</v>
@@ -2399,7 +2405,7 @@
       </c>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2420,7 +2426,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2444,7 +2450,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2468,7 +2474,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2489,7 +2495,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2510,7 +2516,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2531,7 +2537,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2552,7 +2558,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2573,7 +2579,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2594,7 +2600,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2615,7 +2621,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2636,7 +2642,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2673,17 +2679,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A20EA7-5EA0-4748-B530-C51A9976ED39}">
   <dimension ref="A1:AD74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
-    <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="29" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.8359375" customWidth="1"/>
+    <col min="2" max="2" width="32.41796875" customWidth="1"/>
+    <col min="3" max="4" width="20.58203125" customWidth="1"/>
+    <col min="5" max="5" width="12.5078125" customWidth="1"/>
+    <col min="6" max="6" width="6.05078125" customWidth="1"/>
+    <col min="7" max="29" width="16.41015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2770,7 +2776,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="122">
         <v>46184</v>
       </c>
@@ -2862,7 +2868,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="123"/>
       <c r="B3" s="21" t="s">
         <v>47</v>
@@ -2952,7 +2958,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="124">
         <v>46185</v>
       </c>
@@ -3045,7 +3051,7 @@
       </c>
       <c r="AD4" s="54"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="125"/>
       <c r="B5" s="23" t="s">
         <v>51</v>
@@ -3136,7 +3142,7 @@
       </c>
       <c r="AD5" s="54"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="103">
         <v>46186</v>
       </c>
@@ -3229,7 +3235,7 @@
       </c>
       <c r="AD6" s="54"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="104"/>
       <c r="B7" s="25" t="s">
         <v>54</v>
@@ -3320,7 +3326,7 @@
       </c>
       <c r="AD7" s="54"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="105"/>
       <c r="B8" s="26" t="s">
         <v>55</v>
@@ -3411,7 +3417,7 @@
       </c>
       <c r="AD8" s="54"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="106"/>
       <c r="B9" s="27" t="s">
         <v>57</v>
@@ -3502,7 +3508,7 @@
       </c>
       <c r="AD9" s="54"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="107">
         <v>46187</v>
       </c>
@@ -3593,7 +3599,7 @@
       </c>
       <c r="AD10" s="54"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="108"/>
       <c r="B11" s="28" t="s">
         <v>60</v>
@@ -3684,7 +3690,7 @@
       </c>
       <c r="AD11" s="54"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="109"/>
       <c r="B12" s="29" t="s">
         <v>62</v>
@@ -3775,7 +3781,7 @@
       </c>
       <c r="AD12" s="54"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="110"/>
       <c r="B13" s="30" t="s">
         <v>64</v>
@@ -3866,7 +3872,7 @@
       </c>
       <c r="AD13" s="54"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="103">
         <v>46188</v>
       </c>
@@ -3959,7 +3965,7 @@
       </c>
       <c r="AD14" s="54"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="104"/>
       <c r="B15" s="25" t="s">
         <v>67</v>
@@ -4050,7 +4056,7 @@
       </c>
       <c r="AD15" s="54"/>
     </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="105"/>
       <c r="B16" s="26" t="s">
         <v>68</v>
@@ -4141,7 +4147,7 @@
       </c>
       <c r="AD16" s="54"/>
     </row>
-    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="106"/>
       <c r="B17" s="27" t="s">
         <v>70</v>
@@ -4232,7 +4238,7 @@
       </c>
       <c r="AD17" s="54"/>
     </row>
-    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="107">
         <v>46189</v>
       </c>
@@ -4325,7 +4331,7 @@
       </c>
       <c r="AD18" s="54"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" s="108"/>
       <c r="B19" s="28" t="s">
         <v>73</v>
@@ -4416,7 +4422,7 @@
       </c>
       <c r="AD19" s="54"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" s="109"/>
       <c r="B20" s="29" t="s">
         <v>75</v>
@@ -4507,7 +4513,7 @@
       </c>
       <c r="AD20" s="54"/>
     </row>
-    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="110"/>
       <c r="B21" s="30" t="s">
         <v>76</v>
@@ -4598,7 +4604,7 @@
       </c>
       <c r="AD21" s="54"/>
     </row>
-    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="103">
         <v>46190</v>
       </c>
@@ -4691,7 +4697,7 @@
       </c>
       <c r="AD22" s="54"/>
     </row>
-    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="104"/>
       <c r="B23" s="25" t="s">
         <v>78</v>
@@ -4782,7 +4788,7 @@
       </c>
       <c r="AD23" s="54"/>
     </row>
-    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="105"/>
       <c r="B24" s="26" t="s">
         <v>79</v>
@@ -4873,7 +4879,7 @@
       </c>
       <c r="AD24" s="54"/>
     </row>
-    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="106"/>
       <c r="B25" s="27" t="s">
         <v>80</v>
@@ -4964,7 +4970,7 @@
       </c>
       <c r="AD25" s="54"/>
     </row>
-    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="107">
         <v>46191</v>
       </c>
@@ -5057,7 +5063,7 @@
       </c>
       <c r="AD26" s="54"/>
     </row>
-    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="108"/>
       <c r="B27" s="28" t="s">
         <v>82</v>
@@ -5146,7 +5152,7 @@
       </c>
       <c r="AD27" s="54"/>
     </row>
-    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="109"/>
       <c r="B28" s="29" t="s">
         <v>83</v>
@@ -5235,7 +5241,7 @@
       </c>
       <c r="AD28" s="54"/>
     </row>
-    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="110"/>
       <c r="B29" s="30" t="s">
         <v>84</v>
@@ -5324,7 +5330,7 @@
       </c>
       <c r="AD29" s="54"/>
     </row>
-    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="103">
         <v>46192</v>
       </c>
@@ -5415,7 +5421,7 @@
       </c>
       <c r="AD30" s="54"/>
     </row>
-    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="104"/>
       <c r="B31" s="25" t="s">
         <v>86</v>
@@ -5506,7 +5512,7 @@
       </c>
       <c r="AD31" s="54"/>
     </row>
-    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="105"/>
       <c r="B32" s="26" t="s">
         <v>87</v>
@@ -5595,7 +5601,7 @@
       </c>
       <c r="AD32" s="54"/>
     </row>
-    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="106"/>
       <c r="B33" s="27" t="s">
         <v>88</v>
@@ -5686,7 +5692,7 @@
       </c>
       <c r="AD33" s="54"/>
     </row>
-    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="107">
         <v>46193</v>
       </c>
@@ -5779,7 +5785,7 @@
       </c>
       <c r="AD34" s="54"/>
     </row>
-    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="108"/>
       <c r="B35" s="28" t="s">
         <v>90</v>
@@ -5870,7 +5876,7 @@
       </c>
       <c r="AD35" s="54"/>
     </row>
-    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="109"/>
       <c r="B36" s="29" t="s">
         <v>91</v>
@@ -5961,7 +5967,7 @@
       </c>
       <c r="AD36" s="54"/>
     </row>
-    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="110"/>
       <c r="B37" s="30" t="s">
         <v>92</v>
@@ -6052,7 +6058,7 @@
       </c>
       <c r="AD37" s="54"/>
     </row>
-    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="103">
         <v>46194</v>
       </c>
@@ -6143,7 +6149,7 @@
       </c>
       <c r="AD38" s="54"/>
     </row>
-    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="104"/>
       <c r="B39" s="25" t="s">
         <v>94</v>
@@ -6234,7 +6240,7 @@
       </c>
       <c r="AD39" s="54"/>
     </row>
-    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="105"/>
       <c r="B40" s="26" t="s">
         <v>95</v>
@@ -6323,7 +6329,7 @@
       </c>
       <c r="AD40" s="54"/>
     </row>
-    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="106"/>
       <c r="B41" s="27" t="s">
         <v>96</v>
@@ -6412,7 +6418,7 @@
       </c>
       <c r="AD41" s="54"/>
     </row>
-    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="107">
         <v>46195</v>
       </c>
@@ -6505,7 +6511,7 @@
       </c>
       <c r="AD42" s="54"/>
     </row>
-    <row r="43" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" ht="15.75" thickBot="1" x